--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AJ$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AJ$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="146">
   <si>
     <t>id</t>
   </si>
@@ -158,7 +158,7 @@
     <t>创建需要的魔力</t>
   </si>
   <si>
-    <t>生物类型0创建 1抽卡 2敌人</t>
+    <t>生物类型0创建 1抽卡 2敌人 9测试</t>
   </si>
   <si>
     <t>生物位置优先级</t>
@@ -456,6 +456,12 @@
   </si>
   <si>
     <t>人类-魔法师（冰）</t>
+  </si>
+  <si>
+    <t>测试骷髅战士</t>
+  </si>
+  <si>
+    <t>测试骷髅投手</t>
   </si>
   <si>
     <t>Card_Scene_4</t>
@@ -1435,11 +1441,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ171"/>
+  <dimension ref="A1:AJ173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="26.875" customWidth="1"/>
+    <col min="3" max="3" width="33.25" customWidth="1"/>
     <col min="4" max="4" width="19.375" customWidth="1"/>
     <col min="5" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -4646,20 +4652,34 @@
     </row>
     <row r="45" customFormat="1" spans="1:36">
       <c r="A45" s="1">
-        <v>989996</v>
-      </c>
-      <c r="B45" s="2"/>
+        <v>900001</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
       <c r="C45">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G45">
+        <v>2000001</v>
+      </c>
+      <c r="H45">
+        <v>21010001</v>
+      </c>
+      <c r="I45" t="s">
+        <v>86</v>
+      </c>
+      <c r="M45" t="s">
+        <v>93</v>
       </c>
       <c r="O45">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="R45">
         <v>2</v>
       </c>
       <c r="S45">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="T45">
         <v>1</v>
@@ -4672,12 +4692,15 @@
       </c>
       <c r="W45">
         <v>0.5</v>
+      </c>
+      <c r="X45">
+        <v>10</v>
       </c>
       <c r="Y45">
         <v>100</v>
       </c>
       <c r="AA45">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="AB45">
         <v>1</v>
@@ -4685,37 +4708,61 @@
       <c r="AC45">
         <v>1</v>
       </c>
-      <c r="AD45" s="1">
-        <v>989996</v>
-      </c>
-      <c r="AE45" s="2"/>
-      <c r="AF45" s="2"/>
+      <c r="AD45">
+        <v>2</v>
+      </c>
+      <c r="AE45">
+        <v>2000001</v>
+      </c>
+      <c r="AF45" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="AG45" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH45">
+        <v>300200001</v>
+      </c>
+      <c r="AI45" s="1">
+        <v>900001</v>
+      </c>
+      <c r="AJ45" t="s">
         <v>142</v>
-      </c>
-      <c r="AI45">
-        <v>1</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:36">
       <c r="A46" s="1">
-        <v>989997</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>900002</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
       <c r="C46">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G46">
+        <v>2000001</v>
+      </c>
+      <c r="H46">
+        <v>21000001</v>
+      </c>
+      <c r="I46" t="s">
+        <v>86</v>
+      </c>
+      <c r="M46" t="s">
+        <v>95</v>
       </c>
       <c r="O46">
         <v>200001</v>
       </c>
+      <c r="P46" t="s">
+        <v>96</v>
+      </c>
       <c r="R46">
         <v>2</v>
       </c>
       <c r="S46">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -4728,12 +4775,15 @@
       </c>
       <c r="W46">
         <v>0.5</v>
+      </c>
+      <c r="X46">
+        <v>10</v>
       </c>
       <c r="Y46">
         <v>100</v>
       </c>
       <c r="AA46">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="AB46">
         <v>1</v>
@@ -4741,16 +4791,23 @@
       <c r="AC46">
         <v>1</v>
       </c>
-      <c r="AD46" s="1">
-        <v>989997</v>
-      </c>
-      <c r="AE46" s="2"/>
-      <c r="AF46" s="2"/>
+      <c r="AD46">
+        <v>2</v>
+      </c>
+      <c r="AE46">
+        <v>2000001</v>
+      </c>
+      <c r="AF46" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="AG46" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI46">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="AH46">
+        <v>300200002</v>
+      </c>
+      <c r="AI46" s="1">
+        <v>900002</v>
       </c>
       <c r="AJ46" t="s">
         <v>143</v>
@@ -4758,7 +4815,7 @@
     </row>
     <row r="47" customFormat="1" spans="1:36">
       <c r="A47" s="1">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47">
@@ -4798,23 +4855,23 @@
         <v>1</v>
       </c>
       <c r="AD47" s="1">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="AE47" s="2"/>
       <c r="AF47" s="2"/>
       <c r="AG47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI47">
         <v>1</v>
       </c>
       <c r="AJ47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:36">
       <c r="A48" s="1">
-        <v>989999</v>
+        <v>989997</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48">
@@ -4853,22 +4910,24 @@
       <c r="AC48">
         <v>1</v>
       </c>
-      <c r="AD48">
-        <v>989999</v>
-      </c>
+      <c r="AD48" s="1">
+        <v>989997</v>
+      </c>
+      <c r="AE48" s="2"/>
+      <c r="AF48" s="2"/>
       <c r="AG48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI48">
         <v>1</v>
       </c>
       <c r="AJ48" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:36">
       <c r="A49" s="1">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49">
@@ -4908,23 +4967,23 @@
         <v>1</v>
       </c>
       <c r="AD49" s="1">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
       <c r="AG49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI49">
         <v>1</v>
       </c>
       <c r="AJ49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:36">
       <c r="A50" s="1">
-        <v>999948</v>
+        <v>989999</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50">
@@ -4963,24 +5022,22 @@
       <c r="AC50">
         <v>1</v>
       </c>
-      <c r="AD50" s="1">
-        <v>999948</v>
-      </c>
-      <c r="AE50" s="2"/>
-      <c r="AF50" s="2"/>
+      <c r="AD50">
+        <v>989999</v>
+      </c>
       <c r="AG50" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI50">
         <v>1</v>
       </c>
       <c r="AJ50" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:36">
       <c r="A51" s="1">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51">
@@ -5020,23 +5077,23 @@
         <v>1</v>
       </c>
       <c r="AD51" s="1">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="AE51" s="2"/>
       <c r="AF51" s="2"/>
       <c r="AG51" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI51">
         <v>1</v>
       </c>
       <c r="AJ51" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:36">
       <c r="A52" s="1">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52">
@@ -5076,23 +5133,23 @@
         <v>1</v>
       </c>
       <c r="AD52" s="1">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="AE52" s="2"/>
       <c r="AF52" s="2"/>
       <c r="AG52" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI52">
         <v>1</v>
       </c>
       <c r="AJ52" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:36">
       <c r="A53" s="1">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53">
@@ -5132,23 +5189,23 @@
         <v>1</v>
       </c>
       <c r="AD53" s="1">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="AE53" s="2"/>
       <c r="AF53" s="2"/>
       <c r="AG53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI53">
         <v>1</v>
       </c>
       <c r="AJ53" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:36">
       <c r="A54" s="1">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54">
@@ -5188,23 +5245,23 @@
         <v>1</v>
       </c>
       <c r="AD54" s="1">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="AE54" s="2"/>
       <c r="AF54" s="2"/>
       <c r="AG54" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI54">
         <v>1</v>
       </c>
       <c r="AJ54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:36">
       <c r="A55" s="1">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55">
@@ -5244,23 +5301,23 @@
         <v>1</v>
       </c>
       <c r="AD55" s="1">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="AE55" s="2"/>
       <c r="AF55" s="2"/>
       <c r="AG55" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI55">
         <v>1</v>
       </c>
       <c r="AJ55" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:36">
       <c r="A56" s="1">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56">
@@ -5300,23 +5357,23 @@
         <v>1</v>
       </c>
       <c r="AD56" s="1">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="AE56" s="2"/>
       <c r="AF56" s="2"/>
       <c r="AG56" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI56">
         <v>1</v>
       </c>
       <c r="AJ56" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:36">
       <c r="A57" s="1">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57">
@@ -5356,23 +5413,23 @@
         <v>1</v>
       </c>
       <c r="AD57" s="1">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="AE57" s="2"/>
       <c r="AF57" s="2"/>
       <c r="AG57" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI57">
         <v>1</v>
       </c>
       <c r="AJ57" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:36">
       <c r="A58" s="1">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58">
@@ -5412,23 +5469,23 @@
         <v>1</v>
       </c>
       <c r="AD58" s="1">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="AE58" s="2"/>
       <c r="AF58" s="2"/>
       <c r="AG58" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI58">
         <v>1</v>
       </c>
       <c r="AJ58" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:36">
       <c r="A59" s="1">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59">
@@ -5468,23 +5525,23 @@
         <v>1</v>
       </c>
       <c r="AD59" s="1">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
       <c r="AG59" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI59">
         <v>1</v>
       </c>
       <c r="AJ59" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:36">
       <c r="A60" s="1">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60">
@@ -5524,23 +5581,23 @@
         <v>1</v>
       </c>
       <c r="AD60" s="1">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
       <c r="AG60" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI60">
         <v>1</v>
       </c>
       <c r="AJ60" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:36">
       <c r="A61" s="1">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61">
@@ -5580,23 +5637,23 @@
         <v>1</v>
       </c>
       <c r="AD61" s="1">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
       <c r="AG61" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI61">
         <v>1</v>
       </c>
       <c r="AJ61" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:36">
       <c r="A62" s="1">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62">
@@ -5636,23 +5693,23 @@
         <v>1</v>
       </c>
       <c r="AD62" s="1">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="AE62" s="2"/>
       <c r="AF62" s="2"/>
       <c r="AG62" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI62">
         <v>1</v>
       </c>
       <c r="AJ62" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:36">
       <c r="A63" s="1">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63">
@@ -5692,23 +5749,23 @@
         <v>1</v>
       </c>
       <c r="AD63" s="1">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
       <c r="AG63" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI63">
         <v>1</v>
       </c>
       <c r="AJ63" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:36">
       <c r="A64" s="1">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64">
@@ -5748,23 +5805,23 @@
         <v>1</v>
       </c>
       <c r="AD64" s="1">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="AE64" s="2"/>
       <c r="AF64" s="2"/>
       <c r="AG64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI64">
         <v>1</v>
       </c>
       <c r="AJ64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:36">
       <c r="A65" s="1">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65">
@@ -5804,23 +5861,23 @@
         <v>1</v>
       </c>
       <c r="AD65" s="1">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="AE65" s="2"/>
       <c r="AF65" s="2"/>
       <c r="AG65" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI65">
         <v>1</v>
       </c>
       <c r="AJ65" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:36">
       <c r="A66" s="1">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66">
@@ -5860,23 +5917,23 @@
         <v>1</v>
       </c>
       <c r="AD66" s="1">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
       <c r="AG66" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI66">
         <v>1</v>
       </c>
       <c r="AJ66" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:36">
       <c r="A67" s="1">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67">
@@ -5916,23 +5973,23 @@
         <v>1</v>
       </c>
       <c r="AD67" s="1">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="AE67" s="2"/>
       <c r="AF67" s="2"/>
       <c r="AG67" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI67">
         <v>1</v>
       </c>
       <c r="AJ67" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:36">
       <c r="A68" s="1">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68">
@@ -5972,23 +6029,23 @@
         <v>1</v>
       </c>
       <c r="AD68" s="1">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="AE68" s="2"/>
       <c r="AF68" s="2"/>
       <c r="AG68" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI68">
         <v>1</v>
       </c>
       <c r="AJ68" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:36">
       <c r="A69" s="1">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69">
@@ -6028,23 +6085,23 @@
         <v>1</v>
       </c>
       <c r="AD69" s="1">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="AE69" s="2"/>
       <c r="AF69" s="2"/>
       <c r="AG69" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI69">
         <v>1</v>
       </c>
       <c r="AJ69" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:36">
       <c r="A70" s="1">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70">
@@ -6084,23 +6141,23 @@
         <v>1</v>
       </c>
       <c r="AD70" s="1">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
       <c r="AG70" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI70">
         <v>1</v>
       </c>
       <c r="AJ70" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:36">
       <c r="A71" s="1">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71">
@@ -6140,23 +6197,23 @@
         <v>1</v>
       </c>
       <c r="AD71" s="1">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="AE71" s="2"/>
       <c r="AF71" s="2"/>
       <c r="AG71" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI71">
         <v>1</v>
       </c>
       <c r="AJ71" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:36">
       <c r="A72" s="1">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72">
@@ -6196,23 +6253,23 @@
         <v>1</v>
       </c>
       <c r="AD72" s="1">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="AE72" s="2"/>
       <c r="AF72" s="2"/>
       <c r="AG72" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI72">
         <v>1</v>
       </c>
       <c r="AJ72" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:36">
       <c r="A73" s="1">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73">
@@ -6252,23 +6309,23 @@
         <v>1</v>
       </c>
       <c r="AD73" s="1">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="AE73" s="2"/>
       <c r="AF73" s="2"/>
       <c r="AG73" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI73">
         <v>1</v>
       </c>
       <c r="AJ73" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:36">
       <c r="A74" s="1">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74">
@@ -6308,23 +6365,23 @@
         <v>1</v>
       </c>
       <c r="AD74" s="1">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="AE74" s="2"/>
       <c r="AF74" s="2"/>
       <c r="AG74" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI74">
         <v>1</v>
       </c>
       <c r="AJ74" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:36">
       <c r="A75" s="1">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75">
@@ -6364,23 +6421,23 @@
         <v>1</v>
       </c>
       <c r="AD75" s="1">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="AE75" s="2"/>
       <c r="AF75" s="2"/>
       <c r="AG75" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI75">
         <v>1</v>
       </c>
       <c r="AJ75" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:36">
       <c r="A76" s="1">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76">
@@ -6420,23 +6477,23 @@
         <v>1</v>
       </c>
       <c r="AD76" s="1">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="AE76" s="2"/>
       <c r="AF76" s="2"/>
       <c r="AG76" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI76">
         <v>1</v>
       </c>
       <c r="AJ76" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:36">
       <c r="A77" s="1">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77">
@@ -6476,23 +6533,23 @@
         <v>1</v>
       </c>
       <c r="AD77" s="1">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="AE77" s="2"/>
       <c r="AF77" s="2"/>
       <c r="AG77" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI77">
         <v>1</v>
       </c>
       <c r="AJ77" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:36">
       <c r="A78" s="1">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78">
@@ -6532,23 +6589,23 @@
         <v>1</v>
       </c>
       <c r="AD78" s="1">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="AE78" s="2"/>
       <c r="AF78" s="2"/>
       <c r="AG78" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI78">
         <v>1</v>
       </c>
       <c r="AJ78" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:36">
       <c r="A79" s="1">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79">
@@ -6588,23 +6645,23 @@
         <v>1</v>
       </c>
       <c r="AD79" s="1">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="AE79" s="2"/>
       <c r="AF79" s="2"/>
       <c r="AG79" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI79">
         <v>1</v>
       </c>
       <c r="AJ79" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:36">
       <c r="A80" s="1">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80">
@@ -6644,23 +6701,23 @@
         <v>1</v>
       </c>
       <c r="AD80" s="1">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="AE80" s="2"/>
       <c r="AF80" s="2"/>
       <c r="AG80" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI80">
         <v>1</v>
       </c>
       <c r="AJ80" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:36">
       <c r="A81" s="1">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81">
@@ -6700,23 +6757,23 @@
         <v>1</v>
       </c>
       <c r="AD81" s="1">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="AE81" s="2"/>
       <c r="AF81" s="2"/>
       <c r="AG81" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI81">
         <v>1</v>
       </c>
       <c r="AJ81" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:36">
       <c r="A82" s="1">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82">
@@ -6756,23 +6813,23 @@
         <v>1</v>
       </c>
       <c r="AD82" s="1">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="AE82" s="2"/>
       <c r="AF82" s="2"/>
       <c r="AG82" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI82">
         <v>1</v>
       </c>
       <c r="AJ82" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:36">
       <c r="A83" s="1">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83">
@@ -6812,24 +6869,25 @@
         <v>1</v>
       </c>
       <c r="AD83" s="1">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="AE83" s="2"/>
       <c r="AF83" s="2"/>
       <c r="AG83" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI83">
         <v>1</v>
       </c>
       <c r="AJ83" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:36">
-      <c r="A84">
-        <v>999982</v>
-      </c>
+      <c r="A84" s="1">
+        <v>999980</v>
+      </c>
+      <c r="B84" s="2"/>
       <c r="C84">
         <v>1</v>
       </c>
@@ -6866,23 +6924,26 @@
       <c r="AC84">
         <v>1</v>
       </c>
-      <c r="AD84">
-        <v>999982</v>
-      </c>
+      <c r="AD84" s="1">
+        <v>999980</v>
+      </c>
+      <c r="AE84" s="2"/>
+      <c r="AF84" s="2"/>
       <c r="AG84" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI84">
         <v>1</v>
       </c>
       <c r="AJ84" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:36">
-      <c r="A85">
-        <v>999983</v>
-      </c>
+      <c r="A85" s="1">
+        <v>999981</v>
+      </c>
+      <c r="B85" s="2"/>
       <c r="C85">
         <v>1</v>
       </c>
@@ -6919,22 +6980,24 @@
       <c r="AC85">
         <v>1</v>
       </c>
-      <c r="AD85">
-        <v>999983</v>
-      </c>
+      <c r="AD85" s="1">
+        <v>999981</v>
+      </c>
+      <c r="AE85" s="2"/>
+      <c r="AF85" s="2"/>
       <c r="AG85" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI85">
         <v>1</v>
       </c>
       <c r="AJ85" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:36">
       <c r="A86">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6973,21 +7036,21 @@
         <v>1</v>
       </c>
       <c r="AD86">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="AG86" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI86">
         <v>1</v>
       </c>
       <c r="AJ86" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:36">
       <c r="A87">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7026,21 +7089,21 @@
         <v>1</v>
       </c>
       <c r="AD87">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="AG87" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI87">
         <v>1</v>
       </c>
       <c r="AJ87" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:36">
       <c r="A88">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7079,21 +7142,21 @@
         <v>1</v>
       </c>
       <c r="AD88">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="AG88" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI88">
         <v>1</v>
       </c>
       <c r="AJ88" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:36">
       <c r="A89">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7132,21 +7195,21 @@
         <v>1</v>
       </c>
       <c r="AD89">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="AG89" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI89">
         <v>1</v>
       </c>
       <c r="AJ89" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:36">
       <c r="A90">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7185,21 +7248,21 @@
         <v>1</v>
       </c>
       <c r="AD90">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="AG90" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI90">
         <v>1</v>
       </c>
       <c r="AJ90" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:36">
       <c r="A91">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7238,21 +7301,21 @@
         <v>1</v>
       </c>
       <c r="AD91">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="AG91" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI91">
         <v>1</v>
       </c>
       <c r="AJ91" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:36">
       <c r="A92">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7291,21 +7354,21 @@
         <v>1</v>
       </c>
       <c r="AD92">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="AG92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI92">
         <v>1</v>
       </c>
       <c r="AJ92" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:36">
       <c r="A93">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7344,21 +7407,21 @@
         <v>1</v>
       </c>
       <c r="AD93">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="AG93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI93">
         <v>1</v>
       </c>
       <c r="AJ93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:36">
       <c r="A94">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7397,21 +7460,21 @@
         <v>1</v>
       </c>
       <c r="AD94">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="AG94" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI94">
         <v>1</v>
       </c>
       <c r="AJ94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:36">
       <c r="A95">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7450,21 +7513,21 @@
         <v>1</v>
       </c>
       <c r="AD95">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="AG95" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI95">
         <v>1</v>
       </c>
       <c r="AJ95" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:36">
       <c r="A96">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7503,21 +7566,21 @@
         <v>1</v>
       </c>
       <c r="AD96">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="AG96" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI96">
         <v>1</v>
       </c>
       <c r="AJ96" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:36">
       <c r="A97">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7556,21 +7619,21 @@
         <v>1</v>
       </c>
       <c r="AD97">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="AG97" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI97">
         <v>1</v>
       </c>
       <c r="AJ97" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:36">
       <c r="A98">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7609,21 +7672,21 @@
         <v>1</v>
       </c>
       <c r="AD98">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="AG98" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI98">
         <v>1</v>
       </c>
       <c r="AJ98" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:36">
       <c r="A99">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7662,21 +7725,21 @@
         <v>1</v>
       </c>
       <c r="AD99">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="AG99" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI99">
         <v>1</v>
       </c>
       <c r="AJ99" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:36">
       <c r="A100">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7715,21 +7778,21 @@
         <v>1</v>
       </c>
       <c r="AD100">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="AG100" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AI100">
         <v>1</v>
       </c>
       <c r="AJ100" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:36">
       <c r="A101">
-        <v>999999</v>
+        <v>999997</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -7768,20 +7831,124 @@
         <v>1</v>
       </c>
       <c r="AD101">
+        <v>999997</v>
+      </c>
+      <c r="AG101" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI101">
+        <v>1</v>
+      </c>
+      <c r="AJ101" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:36">
+      <c r="A102">
+        <v>999998</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="O102">
+        <v>200001</v>
+      </c>
+      <c r="R102">
+        <v>2</v>
+      </c>
+      <c r="S102">
+        <v>6</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
+      </c>
+      <c r="U102">
+        <v>1</v>
+      </c>
+      <c r="V102">
+        <v>0.5</v>
+      </c>
+      <c r="W102">
+        <v>0.5</v>
+      </c>
+      <c r="Y102">
+        <v>100</v>
+      </c>
+      <c r="AA102">
+        <v>35</v>
+      </c>
+      <c r="AB102">
+        <v>1</v>
+      </c>
+      <c r="AC102">
+        <v>1</v>
+      </c>
+      <c r="AD102">
+        <v>999998</v>
+      </c>
+      <c r="AG102" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI102">
+        <v>1</v>
+      </c>
+      <c r="AJ102" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:36">
+      <c r="A103">
         <v>999999</v>
       </c>
-      <c r="AG101" t="s">
-        <v>142</v>
-      </c>
-      <c r="AI101">
-        <v>1</v>
-      </c>
-      <c r="AJ101" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1"/>
-    <row r="122" ht="15" customHeight="1"/>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>200001</v>
+      </c>
+      <c r="R103">
+        <v>2</v>
+      </c>
+      <c r="S103">
+        <v>6</v>
+      </c>
+      <c r="T103">
+        <v>1</v>
+      </c>
+      <c r="U103">
+        <v>1</v>
+      </c>
+      <c r="V103">
+        <v>0.5</v>
+      </c>
+      <c r="W103">
+        <v>0.5</v>
+      </c>
+      <c r="Y103">
+        <v>100</v>
+      </c>
+      <c r="AA103">
+        <v>35</v>
+      </c>
+      <c r="AB103">
+        <v>1</v>
+      </c>
+      <c r="AC103">
+        <v>1</v>
+      </c>
+      <c r="AD103">
+        <v>999999</v>
+      </c>
+      <c r="AG103" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI103">
+        <v>1</v>
+      </c>
+      <c r="AJ103" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="123" ht="15" customHeight="1"/>
     <row r="124" ht="15" customHeight="1"/>
     <row r="125" ht="15" customHeight="1"/>
@@ -7791,8 +7958,8 @@
     <row r="129" ht="15" customHeight="1"/>
     <row r="130" ht="15" customHeight="1"/>
     <row r="131" ht="15" customHeight="1"/>
-    <row r="163" ht="12" customHeight="1"/>
-    <row r="164" ht="12" customHeight="1"/>
+    <row r="132" ht="15" customHeight="1"/>
+    <row r="133" ht="15" customHeight="1"/>
     <row r="165" ht="12" customHeight="1"/>
     <row r="166" ht="12" customHeight="1"/>
     <row r="167" ht="12" customHeight="1"/>
@@ -7800,8 +7967,10 @@
     <row r="169" ht="12" customHeight="1"/>
     <row r="170" ht="12" customHeight="1"/>
     <row r="171" ht="12" customHeight="1"/>
+    <row r="172" ht="12" customHeight="1"/>
+    <row r="173" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AJ101" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AJ103" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AJ$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AK$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="149">
   <si>
     <t>id</t>
   </si>
@@ -59,6 +59,9 @@
     <t>equip_items_type</t>
   </si>
   <si>
+    <t>equip_items_weapon_type</t>
+  </si>
+  <si>
     <t>anim_idle</t>
   </si>
   <si>
@@ -179,6 +182,9 @@
     <t>可装备类型</t>
   </si>
   <si>
+    <t>可装备武器类型</t>
+  </si>
+  <si>
     <t>等待动画名字</t>
   </si>
   <si>
@@ -335,6 +341,9 @@
     <t>骷髅魔法师（冰）</t>
   </si>
   <si>
+    <t>1,6</t>
+  </si>
+  <si>
     <t>ui_research_51</t>
   </si>
   <si>
@@ -362,7 +371,7 @@
     <t>战之魅魔</t>
   </si>
   <si>
-    <t>1,2,3,</t>
+    <t>1,2,3,6</t>
   </si>
   <si>
     <t>ui_research_45</t>
@@ -437,7 +446,7 @@
     <t>兽人战士</t>
   </si>
   <si>
-    <t>兽人弓箭手</t>
+    <t>兽人投手</t>
   </si>
   <si>
     <t>兽人魔法师（火）</t>
@@ -1441,7 +1450,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ173"/>
+  <dimension ref="A1:AK173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1451,29 +1460,30 @@
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="24.875" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="11.875" customWidth="1"/>
-    <col min="13" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
-    <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="20.375" customWidth="1"/>
-    <col min="18" max="18" width="35.875" customWidth="1"/>
-    <col min="19" max="19" width="21.5" customWidth="1"/>
-    <col min="20" max="21" width="29.625" customWidth="1"/>
-    <col min="22" max="24" width="20.25" customWidth="1"/>
-    <col min="25" max="26" width="11.75" customWidth="1"/>
-    <col min="27" max="27" width="20.25" customWidth="1"/>
-    <col min="28" max="28" width="8.875" customWidth="1"/>
-    <col min="29" max="30" width="14.75" customWidth="1"/>
-    <col min="31" max="32" width="34" customWidth="1"/>
-    <col min="33" max="34" width="13.75" customWidth="1"/>
-    <col min="35" max="35" width="16" customWidth="1"/>
-    <col min="36" max="36" width="42.875" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
+    <col min="15" max="15" width="18.25" customWidth="1"/>
+    <col min="16" max="16" width="16.5" customWidth="1"/>
+    <col min="17" max="17" width="27" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
+    <col min="19" max="19" width="35.875" customWidth="1"/>
+    <col min="20" max="20" width="21.5" customWidth="1"/>
+    <col min="21" max="22" width="29.625" customWidth="1"/>
+    <col min="23" max="25" width="20.25" customWidth="1"/>
+    <col min="26" max="27" width="11.75" customWidth="1"/>
+    <col min="28" max="28" width="20.25" customWidth="1"/>
+    <col min="29" max="29" width="8.875" customWidth="1"/>
+    <col min="30" max="31" width="14.75" customWidth="1"/>
+    <col min="32" max="33" width="34" customWidth="1"/>
+    <col min="34" max="35" width="13.75" customWidth="1"/>
+    <col min="36" max="36" width="16" customWidth="1"/>
+    <col min="37" max="37" width="42.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1564,13 +1574,13 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AH1" t="s">
@@ -1582,228 +1592,237 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:36">
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
         <v>38</v>
       </c>
       <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" t="s">
         <v>38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
       </c>
       <c r="P2" t="s">
         <v>38</v>
       </c>
       <c r="Q2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AF2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AH2" t="s">
         <v>39</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AI2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK2" t="s">
         <v>39</v>
       </c>
-      <c r="V2" t="s">
-        <v>39</v>
-      </c>
-      <c r="W2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36">
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AB3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AC3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AE3" t="s">
         <v>71</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AF3" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="AG3" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="AH3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:36">
+        <v>76</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:37">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1813,32 +1832,32 @@
       <c r="G4">
         <v>1000001</v>
       </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
       <c r="U4">
         <v>1</v>
       </c>
-      <c r="Y4">
-        <v>1</v>
-      </c>
-      <c r="AD4">
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
         <v>1</v>
       </c>
       <c r="AE4">
         <v>1</v>
       </c>
-      <c r="AG4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI4">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:36">
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:37">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1848,64 +1867,64 @@
       <c r="G5">
         <v>2000001</v>
       </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
       <c r="U5">
         <v>1</v>
       </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>2</v>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
       </c>
       <c r="AE5">
         <v>2</v>
       </c>
-      <c r="AG5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI5">
-        <v>2</v>
-      </c>
-      <c r="AJ5" t="s">
+      <c r="AF5">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:36">
+      <c r="AJ5">
+        <v>2</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:37">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
       <c r="U6">
         <v>1</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>3</v>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
-      <c r="AG6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI6">
+      <c r="AF6">
         <v>3</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:36">
+      <c r="AH6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ6">
+        <v>3</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:37">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1915,32 +1934,32 @@
       <c r="G7">
         <v>4000001</v>
       </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
       <c r="U7">
         <v>1</v>
       </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>4</v>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
       </c>
       <c r="AE7">
         <v>4</v>
       </c>
-      <c r="AG7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI7">
+      <c r="AF7">
         <v>4</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:36">
+      <c r="AH7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ7">
+        <v>4</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:37">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1950,32 +1969,32 @@
       <c r="G8">
         <v>5000001</v>
       </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
       <c r="U8">
         <v>1</v>
       </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>5</v>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
       </c>
       <c r="AE8">
         <v>5</v>
       </c>
-      <c r="AG8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI8">
+      <c r="AF8">
         <v>5</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:36">
+      <c r="AH8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ8">
+        <v>5</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:37">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1985,32 +2004,32 @@
       <c r="G9">
         <v>6000001</v>
       </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
       <c r="U9">
         <v>1</v>
       </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>6</v>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
       </c>
       <c r="AE9">
         <v>6</v>
       </c>
-      <c r="AG9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI9">
-        <v>6</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:36">
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ9">
+        <v>6</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:37">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2020,32 +2039,32 @@
       <c r="G10">
         <v>7000001</v>
       </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
       <c r="U10">
         <v>1</v>
       </c>
-      <c r="Y10">
-        <v>1</v>
-      </c>
-      <c r="AD10">
-        <v>7</v>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
       </c>
       <c r="AE10">
         <v>7</v>
       </c>
-      <c r="AG10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI10">
+      <c r="AF10">
         <v>7</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:36">
+      <c r="AH10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ10">
+        <v>7</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:37">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -2056,62 +2075,62 @@
       <c r="G11">
         <v>1000001</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>100001</v>
       </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
       <c r="S11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U11">
         <v>1</v>
       </c>
       <c r="V11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W11">
         <v>0.5</v>
       </c>
-      <c r="Y11">
-        <v>100</v>
-      </c>
-      <c r="AA11">
+      <c r="X11">
+        <v>0.5</v>
+      </c>
+      <c r="Z11">
+        <v>100</v>
+      </c>
+      <c r="AB11">
         <v>10</v>
       </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
       <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
         <v>0.2</v>
       </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
       <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
         <v>1000001</v>
       </c>
-      <c r="AF11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH11" s="1">
+      <c r="AG11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI11" s="1">
         <v>300100001</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <v>1001</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:36">
+      <c r="AK11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:37">
       <c r="A12">
         <v>1002</v>
       </c>
@@ -2122,64 +2141,67 @@
         <v>1000001</v>
       </c>
       <c r="I12" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12">
+        <v>88</v>
+      </c>
+      <c r="J12">
+        <v>7</v>
+      </c>
+      <c r="P12">
         <v>200001</v>
       </c>
-      <c r="R12">
-        <v>1</v>
-      </c>
       <c r="S12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U12">
         <v>1</v>
       </c>
       <c r="V12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W12">
         <v>0.5</v>
       </c>
-      <c r="Y12">
-        <v>100</v>
-      </c>
-      <c r="AA12">
+      <c r="X12">
+        <v>0.5</v>
+      </c>
+      <c r="Z12">
+        <v>100</v>
+      </c>
+      <c r="AB12">
         <v>10</v>
       </c>
-      <c r="AB12">
-        <v>1</v>
-      </c>
       <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
         <v>0.2</v>
       </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
       <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
         <v>1000001</v>
       </c>
-      <c r="AF12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH12" s="1">
+      <c r="AG12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI12" s="1">
         <v>300100002</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <v>1002</v>
       </c>
-      <c r="AJ12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:36">
+      <c r="AK12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:37">
       <c r="A13">
         <v>1003</v>
       </c>
@@ -2190,64 +2212,67 @@
         <v>1000001</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
-      </c>
-      <c r="O13">
+        <v>88</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="P13">
         <v>201001</v>
       </c>
-      <c r="R13">
-        <v>1</v>
-      </c>
       <c r="S13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U13">
         <v>1</v>
       </c>
       <c r="V13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W13">
         <v>0.5</v>
       </c>
-      <c r="Y13">
-        <v>100</v>
-      </c>
-      <c r="AA13">
+      <c r="X13">
+        <v>0.5</v>
+      </c>
+      <c r="Z13">
+        <v>100</v>
+      </c>
+      <c r="AB13">
         <v>10</v>
       </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
       <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
         <v>0.2</v>
       </c>
-      <c r="AD13">
-        <v>1</v>
-      </c>
       <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
         <v>1000001</v>
       </c>
-      <c r="AF13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH13" s="1">
+      <c r="AG13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI13" s="1">
         <v>300100003</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <v>1003</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:36">
+      <c r="AK13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:37">
       <c r="A14">
         <v>1004</v>
       </c>
@@ -2258,64 +2283,67 @@
         <v>1000001</v>
       </c>
       <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="O14">
+        <v>88</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="P14">
         <v>201002</v>
       </c>
-      <c r="R14">
-        <v>1</v>
-      </c>
       <c r="S14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U14">
         <v>1</v>
       </c>
       <c r="V14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W14">
         <v>0.5</v>
       </c>
-      <c r="Y14">
-        <v>100</v>
-      </c>
-      <c r="AA14">
+      <c r="X14">
+        <v>0.5</v>
+      </c>
+      <c r="Z14">
+        <v>100</v>
+      </c>
+      <c r="AB14">
         <v>10</v>
       </c>
-      <c r="AB14">
-        <v>1</v>
-      </c>
       <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
         <v>0.2</v>
       </c>
-      <c r="AD14">
-        <v>1</v>
-      </c>
       <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
         <v>1000001</v>
       </c>
-      <c r="AF14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH14" s="1">
+      <c r="AG14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI14" s="1">
         <v>300100004</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>1004</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="1:36">
+      <c r="AK14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1" spans="1:37">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -2332,70 +2360,73 @@
         <v>21010001</v>
       </c>
       <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="N15" t="s">
+        <v>95</v>
+      </c>
+      <c r="P15">
+        <v>100001</v>
+      </c>
+      <c r="S15">
+        <v>2</v>
+      </c>
+      <c r="T15">
+        <v>0.5</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>0.5</v>
+      </c>
+      <c r="X15">
+        <v>0.5</v>
+      </c>
+      <c r="Y15">
+        <v>10</v>
+      </c>
+      <c r="Z15">
+        <v>100</v>
+      </c>
+      <c r="AB15">
+        <v>10</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>2000001</v>
+      </c>
+      <c r="AG15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M15" t="s">
-        <v>93</v>
-      </c>
-      <c r="O15">
-        <v>100001</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>0.5</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>0.5</v>
-      </c>
-      <c r="W15">
-        <v>0.5</v>
-      </c>
-      <c r="X15">
-        <v>10</v>
-      </c>
-      <c r="Y15">
-        <v>100</v>
-      </c>
-      <c r="AA15">
-        <v>10</v>
-      </c>
-      <c r="AB15">
-        <v>1</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>2</v>
-      </c>
-      <c r="AE15">
-        <v>2000001</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH15">
+      <c r="AH15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI15">
         <v>300200001</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <v>2001</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36">
+      <c r="AK15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
       <c r="A16">
         <v>2002</v>
       </c>
@@ -2412,73 +2443,76 @@
         <v>21000001</v>
       </c>
       <c r="I16" t="s">
-        <v>86</v>
-      </c>
-      <c r="M16" t="s">
-        <v>95</v>
-      </c>
-      <c r="O16">
+        <v>88</v>
+      </c>
+      <c r="J16">
+        <v>8</v>
+      </c>
+      <c r="N16" t="s">
+        <v>97</v>
+      </c>
+      <c r="P16">
         <v>200001</v>
       </c>
-      <c r="P16" t="s">
-        <v>96</v>
-      </c>
-      <c r="R16">
-        <v>2</v>
+      <c r="Q16" t="s">
+        <v>98</v>
       </c>
       <c r="S16">
+        <v>2</v>
+      </c>
+      <c r="T16">
         <v>10</v>
       </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
       <c r="U16">
         <v>1</v>
       </c>
       <c r="V16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W16">
         <v>0.5</v>
       </c>
       <c r="X16">
+        <v>0.5</v>
+      </c>
+      <c r="Y16">
         <v>10</v>
       </c>
-      <c r="Y16">
-        <v>100</v>
-      </c>
-      <c r="AA16">
+      <c r="Z16">
+        <v>100</v>
+      </c>
+      <c r="AB16">
         <v>10</v>
       </c>
-      <c r="AB16">
-        <v>1</v>
-      </c>
       <c r="AC16">
         <v>1</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE16">
+        <v>2</v>
+      </c>
+      <c r="AF16">
         <v>2000001</v>
       </c>
-      <c r="AF16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH16">
+      <c r="AG16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI16">
         <v>300200002</v>
       </c>
-      <c r="AI16">
+      <c r="AJ16">
         <v>2002</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36">
+      <c r="AK16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -2495,73 +2529,76 @@
         <v>21010002</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="N17" t="s">
+        <v>100</v>
+      </c>
+      <c r="P17">
+        <v>201001</v>
+      </c>
+      <c r="Q17" t="s">
         <v>98</v>
       </c>
-      <c r="O17">
-        <v>201001</v>
-      </c>
-      <c r="P17" t="s">
-        <v>96</v>
-      </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
       <c r="S17">
+        <v>2</v>
+      </c>
+      <c r="T17">
         <v>10</v>
       </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
       <c r="U17">
         <v>1</v>
       </c>
       <c r="V17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W17">
         <v>0.5</v>
       </c>
       <c r="X17">
+        <v>0.5</v>
+      </c>
+      <c r="Y17">
         <v>20</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>50</v>
       </c>
-      <c r="AA17">
-        <v>6</v>
-      </c>
       <c r="AB17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>1</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17">
+        <v>2</v>
+      </c>
+      <c r="AF17">
         <v>2000001</v>
       </c>
-      <c r="AF17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH17">
+      <c r="AG17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI17">
         <v>300200003</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <v>2003</v>
       </c>
-      <c r="AJ17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36">
+      <c r="AK17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
       <c r="A18">
         <v>2004</v>
       </c>
@@ -2578,73 +2615,76 @@
         <v>21010003</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
-      </c>
-      <c r="M18" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>201002</v>
+      </c>
+      <c r="Q18" t="s">
         <v>98</v>
       </c>
-      <c r="O18">
-        <v>201002</v>
-      </c>
-      <c r="P18" t="s">
-        <v>96</v>
-      </c>
-      <c r="R18">
-        <v>2</v>
-      </c>
       <c r="S18">
+        <v>2</v>
+      </c>
+      <c r="T18">
         <v>10</v>
       </c>
-      <c r="T18">
-        <v>1</v>
-      </c>
       <c r="U18">
         <v>1</v>
       </c>
       <c r="V18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W18">
         <v>0.5</v>
       </c>
       <c r="X18">
+        <v>0.5</v>
+      </c>
+      <c r="Y18">
         <v>20</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>50</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>3</v>
       </c>
-      <c r="AB18">
-        <v>1</v>
-      </c>
       <c r="AC18">
         <v>1</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18">
+        <v>2</v>
+      </c>
+      <c r="AF18">
         <v>2000001</v>
       </c>
-      <c r="AF18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH18">
+      <c r="AG18" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI18">
         <v>300200004</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <v>2004</v>
       </c>
-      <c r="AJ18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:36">
+      <c r="AK18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
       <c r="A19">
         <v>3001</v>
       </c>
@@ -2654,68 +2694,68 @@
       <c r="C19">
         <v>1</v>
       </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>2</v>
+      <c r="I19" t="s">
+        <v>103</v>
       </c>
       <c r="S19">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
       <c r="V19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W19">
         <v>0.5</v>
       </c>
       <c r="X19">
+        <v>0.5</v>
+      </c>
+      <c r="Y19">
         <v>120</v>
       </c>
-      <c r="Y19">
-        <v>100</v>
-      </c>
       <c r="Z19">
+        <v>100</v>
+      </c>
+      <c r="AA19">
         <v>500</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AB19">
-        <v>1</v>
-      </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
         <v>3</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>3000001</v>
       </c>
-      <c r="AF19" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH19">
+      <c r="AG19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI19">
         <v>300300001</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <v>3001</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:36">
+      <c r="AK19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:37">
       <c r="A20">
         <v>3002</v>
       </c>
@@ -2725,74 +2765,74 @@
       <c r="C20">
         <v>1</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="M20" t="s">
-        <v>93</v>
-      </c>
-      <c r="O20">
+      <c r="I20" t="s">
+        <v>103</v>
+      </c>
+      <c r="N20" t="s">
+        <v>95</v>
+      </c>
+      <c r="P20">
         <v>300001</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>11</v>
       </c>
-      <c r="R20">
-        <v>2</v>
-      </c>
       <c r="S20">
+        <v>2</v>
+      </c>
+      <c r="T20">
         <v>1.5</v>
       </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
       <c r="U20">
         <v>1</v>
       </c>
       <c r="V20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W20">
+        <v>0.5</v>
+      </c>
+      <c r="X20">
         <v>0.15</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>120</v>
       </c>
-      <c r="Y20">
-        <v>100</v>
-      </c>
-      <c r="AA20">
+      <c r="Z20">
+        <v>100</v>
+      </c>
+      <c r="AB20">
         <v>500</v>
       </c>
-      <c r="AB20">
-        <v>1</v>
-      </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
         <v>3</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>3000001</v>
       </c>
-      <c r="AF20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH20">
+      <c r="AG20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI20">
         <v>300300002</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <v>3002</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:36">
+      <c r="AK20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:37">
       <c r="A21">
         <v>3003</v>
       </c>
@@ -2803,79 +2843,79 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
-        <v>98</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
+        <v>108</v>
+      </c>
+      <c r="I21" t="s">
+        <v>103</v>
+      </c>
+      <c r="N21" t="s">
+        <v>100</v>
       </c>
       <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
         <v>400001</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>11</v>
       </c>
-      <c r="R21">
-        <v>2</v>
-      </c>
       <c r="S21">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U21">
         <v>1</v>
       </c>
       <c r="V21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W21">
         <v>0.5</v>
       </c>
       <c r="X21">
+        <v>0.5</v>
+      </c>
+      <c r="Y21">
         <v>120</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>50</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>0</v>
       </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
       <c r="AC21">
         <v>1</v>
       </c>
       <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21">
         <v>3</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>3000001</v>
       </c>
-      <c r="AF21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH21">
+      <c r="AG21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI21">
         <v>300300003</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>3003</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:36">
+      <c r="AK21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:37">
       <c r="A22">
         <v>3004</v>
       </c>
@@ -2886,79 +2926,79 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
-        <v>98</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
+        <v>108</v>
+      </c>
+      <c r="I22" t="s">
+        <v>103</v>
+      </c>
+      <c r="N22" t="s">
+        <v>100</v>
       </c>
       <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
         <v>400002</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>11</v>
       </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
       <c r="S22">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U22">
         <v>1</v>
       </c>
       <c r="V22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W22">
         <v>0.5</v>
       </c>
       <c r="X22">
+        <v>0.5</v>
+      </c>
+      <c r="Y22">
         <v>120</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
         <v>50</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>0</v>
       </c>
-      <c r="AB22">
-        <v>1</v>
-      </c>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
         <v>3</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>3000001</v>
       </c>
-      <c r="AF22" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH22">
+      <c r="AG22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI22">
         <v>300300004</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>3004</v>
       </c>
-      <c r="AJ22" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:36">
+      <c r="AK22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:37">
       <c r="A23">
         <v>4001</v>
       </c>
@@ -2975,70 +3015,73 @@
         <v>41000002</v>
       </c>
       <c r="I23" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>95</v>
+      </c>
+      <c r="P23">
+        <v>101001</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>0.5</v>
+      </c>
+      <c r="X23">
+        <v>0.5</v>
+      </c>
+      <c r="Y23">
+        <v>50</v>
+      </c>
+      <c r="Z23">
+        <v>100</v>
+      </c>
+      <c r="AB23">
+        <v>6</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>4</v>
+      </c>
+      <c r="AF23">
+        <v>4000001</v>
+      </c>
+      <c r="AG23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M23" t="s">
-        <v>93</v>
-      </c>
-      <c r="O23">
-        <v>101001</v>
-      </c>
-      <c r="R23">
-        <v>2</v>
-      </c>
-      <c r="S23">
-        <v>3</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23">
-        <v>0.5</v>
-      </c>
-      <c r="W23">
-        <v>0.5</v>
-      </c>
-      <c r="X23">
-        <v>50</v>
-      </c>
-      <c r="Y23">
-        <v>100</v>
-      </c>
-      <c r="AA23">
-        <v>6</v>
-      </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-      <c r="AC23">
-        <v>1</v>
-      </c>
-      <c r="AD23">
-        <v>4</v>
-      </c>
-      <c r="AE23">
-        <v>4000001</v>
-      </c>
-      <c r="AF23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH23">
+      <c r="AH23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI23">
         <v>300400001</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>4001</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:36">
+      <c r="AK23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:37">
       <c r="A24">
         <v>4002</v>
       </c>
@@ -3052,17 +3095,14 @@
         <v>4000001</v>
       </c>
       <c r="I24" t="s">
-        <v>110</v>
-      </c>
-      <c r="O24">
+        <v>113</v>
+      </c>
+      <c r="P24">
         <v>500001</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>12</v>
       </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
       <c r="S24">
         <v>1</v>
       </c>
@@ -3073,19 +3113,19 @@
         <v>1</v>
       </c>
       <c r="V24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W24">
         <v>0.5</v>
       </c>
       <c r="X24">
+        <v>0.5</v>
+      </c>
+      <c r="Y24">
         <v>50</v>
       </c>
-      <c r="Y24">
-        <v>100</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
+      <c r="Z24">
+        <v>100</v>
       </c>
       <c r="AB24">
         <v>1</v>
@@ -3094,28 +3134,31 @@
         <v>1</v>
       </c>
       <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
         <v>4</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>4000001</v>
       </c>
-      <c r="AF24" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH24">
+      <c r="AG24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI24">
         <v>300400002</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>4002</v>
       </c>
-      <c r="AJ24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:36">
+      <c r="AK24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:37">
       <c r="A25">
         <v>4003</v>
       </c>
@@ -3129,70 +3172,70 @@
         <v>4000001</v>
       </c>
       <c r="I25" t="s">
-        <v>110</v>
-      </c>
-      <c r="O25">
+        <v>113</v>
+      </c>
+      <c r="P25">
         <v>600001</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>32</v>
       </c>
-      <c r="R25">
-        <v>2</v>
-      </c>
       <c r="S25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>1</v>
       </c>
       <c r="V25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W25">
         <v>0.5</v>
       </c>
       <c r="X25">
+        <v>0.5</v>
+      </c>
+      <c r="Y25">
         <v>50</v>
       </c>
-      <c r="Y25">
-        <v>100</v>
-      </c>
-      <c r="AA25">
+      <c r="Z25">
+        <v>100</v>
+      </c>
+      <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AB25">
-        <v>1</v>
-      </c>
       <c r="AC25">
         <v>1</v>
       </c>
       <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
         <v>4</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>4000001</v>
       </c>
-      <c r="AF25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH25">
+      <c r="AG25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI25">
         <v>300400003</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <v>4003</v>
       </c>
-      <c r="AJ25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:36">
+      <c r="AK25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:37">
       <c r="A26">
         <v>4004</v>
       </c>
@@ -3206,73 +3249,73 @@
         <v>4000001</v>
       </c>
       <c r="I26" t="s">
-        <v>110</v>
-      </c>
-      <c r="O26">
+        <v>113</v>
+      </c>
+      <c r="P26">
         <v>202001</v>
       </c>
-      <c r="P26" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q26">
+      <c r="Q26" t="s">
+        <v>98</v>
+      </c>
+      <c r="R26">
         <v>30</v>
       </c>
-      <c r="R26">
-        <v>2</v>
-      </c>
       <c r="S26">
+        <v>2</v>
+      </c>
+      <c r="T26">
         <v>10</v>
       </c>
-      <c r="T26">
-        <v>1</v>
-      </c>
       <c r="U26">
         <v>1</v>
       </c>
       <c r="V26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W26">
         <v>0.5</v>
       </c>
       <c r="X26">
+        <v>0.5</v>
+      </c>
+      <c r="Y26">
         <v>50</v>
       </c>
-      <c r="Y26">
-        <v>100</v>
-      </c>
-      <c r="AA26">
+      <c r="Z26">
+        <v>100</v>
+      </c>
+      <c r="AB26">
         <v>3</v>
       </c>
-      <c r="AB26">
-        <v>1</v>
-      </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AD26">
+        <v>1</v>
+      </c>
+      <c r="AE26">
         <v>4</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>4000001</v>
       </c>
-      <c r="AF26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH26">
+      <c r="AG26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI26">
         <v>300400004</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <v>4004</v>
       </c>
-      <c r="AJ26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:36">
+      <c r="AK26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:37">
       <c r="A27">
         <v>4005</v>
       </c>
@@ -3286,17 +3329,14 @@
         <v>4000001</v>
       </c>
       <c r="I27" t="s">
-        <v>110</v>
-      </c>
-      <c r="O27">
+        <v>113</v>
+      </c>
+      <c r="P27">
         <v>500002</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>13</v>
       </c>
-      <c r="R27">
-        <v>1</v>
-      </c>
       <c r="S27">
         <v>1</v>
       </c>
@@ -3307,21 +3347,21 @@
         <v>1</v>
       </c>
       <c r="V27">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W27">
         <v>0.5</v>
       </c>
       <c r="X27">
+        <v>0.5</v>
+      </c>
+      <c r="Y27">
         <v>50</v>
       </c>
-      <c r="Y27">
-        <v>100</v>
-      </c>
-      <c r="Z27"/>
-      <c r="AA27">
-        <v>1</v>
-      </c>
+      <c r="Z27">
+        <v>100</v>
+      </c>
+      <c r="AA27"/>
       <c r="AB27">
         <v>1</v>
       </c>
@@ -3329,28 +3369,31 @@
         <v>1</v>
       </c>
       <c r="AD27">
+        <v>1</v>
+      </c>
+      <c r="AE27">
         <v>4</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>4000001</v>
       </c>
-      <c r="AF27" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH27">
+      <c r="AG27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI27">
         <v>300400005</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <v>4005</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:36">
+      <c r="AK27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:37">
       <c r="A28">
         <v>5001</v>
       </c>
@@ -3364,70 +3407,70 @@
         <v>5000001</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
-      </c>
-      <c r="O28">
+        <v>121</v>
+      </c>
+      <c r="P28">
         <v>101002</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>11</v>
       </c>
-      <c r="R28">
-        <v>2</v>
-      </c>
       <c r="S28">
+        <v>2</v>
+      </c>
+      <c r="T28">
         <v>1.5</v>
       </c>
-      <c r="T28">
-        <v>1</v>
-      </c>
       <c r="U28">
         <v>1</v>
       </c>
       <c r="V28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W28">
         <v>0.5</v>
       </c>
       <c r="X28">
+        <v>0.5</v>
+      </c>
+      <c r="Y28">
         <v>60</v>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <v>300</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>3</v>
       </c>
-      <c r="AB28">
-        <v>1</v>
-      </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AD28">
+        <v>1</v>
+      </c>
+      <c r="AE28">
         <v>5</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>5000001</v>
       </c>
-      <c r="AF28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH28" s="1">
+      <c r="AG28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI28" s="1">
         <v>300500001</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <v>5001</v>
       </c>
-      <c r="AJ28" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:36">
+      <c r="AK28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:37">
       <c r="A29">
         <v>5002</v>
       </c>
@@ -3444,73 +3487,76 @@
         <v>51010001</v>
       </c>
       <c r="I29" t="s">
-        <v>120</v>
-      </c>
-      <c r="O29">
+        <v>123</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="P29">
         <v>203001</v>
       </c>
-      <c r="P29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
+      <c r="Q29" t="s">
+        <v>124</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S29">
+        <v>2</v>
+      </c>
+      <c r="T29">
         <v>10</v>
       </c>
-      <c r="T29">
-        <v>1</v>
-      </c>
       <c r="U29">
         <v>1</v>
       </c>
       <c r="V29">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W29">
         <v>0.5</v>
       </c>
       <c r="X29">
+        <v>0.5</v>
+      </c>
+      <c r="Y29">
         <v>60</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <v>300</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>10</v>
       </c>
-      <c r="AB29">
-        <v>1</v>
-      </c>
       <c r="AC29">
         <v>1</v>
       </c>
       <c r="AD29">
+        <v>1</v>
+      </c>
+      <c r="AE29">
         <v>5</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>5000001</v>
       </c>
-      <c r="AF29" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH29" s="1">
+      <c r="AG29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI29" s="1">
         <v>300500002</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <v>5002</v>
       </c>
-      <c r="AJ29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:36">
+      <c r="AK29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:37">
       <c r="A30">
         <v>5003</v>
       </c>
@@ -3524,70 +3570,70 @@
         <v>5000001</v>
       </c>
       <c r="I30" t="s">
-        <v>118</v>
-      </c>
-      <c r="O30">
+        <v>121</v>
+      </c>
+      <c r="P30">
         <v>700001</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>41</v>
       </c>
-      <c r="R30">
-        <v>2</v>
-      </c>
       <c r="S30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>1</v>
       </c>
       <c r="V30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W30">
         <v>0.5</v>
       </c>
       <c r="X30">
+        <v>0.5</v>
+      </c>
+      <c r="Y30">
         <v>45</v>
       </c>
-      <c r="Y30">
+      <c r="Z30">
         <v>150</v>
       </c>
-      <c r="AA30">
-        <v>6</v>
-      </c>
       <c r="AB30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC30">
         <v>1</v>
       </c>
       <c r="AD30">
+        <v>1</v>
+      </c>
+      <c r="AE30">
         <v>5</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>5000001</v>
       </c>
-      <c r="AF30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH30" s="1">
+      <c r="AG30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI30" s="1">
         <v>300500003</v>
       </c>
-      <c r="AI30">
+      <c r="AJ30">
         <v>5003</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:36">
+      <c r="AK30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:37">
       <c r="A31">
         <v>5004</v>
       </c>
@@ -3601,70 +3647,70 @@
         <v>5000001</v>
       </c>
       <c r="I31" t="s">
-        <v>118</v>
-      </c>
-      <c r="O31">
+        <v>121</v>
+      </c>
+      <c r="P31">
         <v>700002</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>41</v>
       </c>
-      <c r="R31">
-        <v>2</v>
-      </c>
       <c r="S31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>1</v>
       </c>
       <c r="V31">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W31">
         <v>0.5</v>
       </c>
       <c r="X31">
+        <v>0.5</v>
+      </c>
+      <c r="Y31">
         <v>45</v>
       </c>
-      <c r="Y31">
+      <c r="Z31">
         <v>150</v>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <v>3</v>
       </c>
-      <c r="AB31">
-        <v>1</v>
-      </c>
       <c r="AC31">
         <v>1</v>
       </c>
       <c r="AD31">
+        <v>1</v>
+      </c>
+      <c r="AE31">
         <v>5</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>5000001</v>
       </c>
-      <c r="AF31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH31" s="1">
+      <c r="AG31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI31" s="1">
         <v>300500004</v>
       </c>
-      <c r="AI31">
+      <c r="AJ31">
         <v>5004</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:36">
+      <c r="AK31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:37">
       <c r="A32">
         <v>6001</v>
       </c>
@@ -3675,73 +3721,76 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G32">
         <v>6000001</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
-      </c>
-      <c r="O32">
+        <v>88</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="P32">
         <v>200001</v>
       </c>
-      <c r="R32">
-        <v>2</v>
-      </c>
       <c r="S32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>1</v>
       </c>
       <c r="V32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W32">
         <v>0.5</v>
       </c>
       <c r="X32">
+        <v>0.5</v>
+      </c>
+      <c r="Y32">
         <v>30</v>
       </c>
-      <c r="Y32">
+      <c r="Z32">
         <v>80</v>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <v>5</v>
       </c>
-      <c r="AB32">
-        <v>1</v>
-      </c>
       <c r="AC32">
         <v>1</v>
       </c>
       <c r="AD32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE32">
+        <v>6</v>
+      </c>
+      <c r="AF32">
         <v>6000001</v>
       </c>
-      <c r="AF32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH32" s="1">
+      <c r="AG32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI32" s="1">
         <v>300600001</v>
       </c>
-      <c r="AI32">
+      <c r="AJ32">
         <v>6001</v>
       </c>
-      <c r="AJ32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:36">
+      <c r="AK32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:37">
       <c r="A33">
         <v>6002</v>
       </c>
@@ -3758,73 +3807,76 @@
         <v>61010002</v>
       </c>
       <c r="I33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33">
+        <v>7</v>
+      </c>
+      <c r="N33" t="s">
+        <v>95</v>
+      </c>
+      <c r="P33">
+        <v>204001</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>131</v>
+      </c>
+      <c r="S33">
+        <v>2</v>
+      </c>
+      <c r="T33">
+        <v>10</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33">
+        <v>1</v>
+      </c>
+      <c r="W33">
+        <v>0.5</v>
+      </c>
+      <c r="X33">
+        <v>0.5</v>
+      </c>
+      <c r="Y33">
+        <v>30</v>
+      </c>
+      <c r="Z33">
+        <v>80</v>
+      </c>
+      <c r="AB33">
+        <v>10</v>
+      </c>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
+      </c>
+      <c r="AE33">
+        <v>6</v>
+      </c>
+      <c r="AF33">
+        <v>6000001</v>
+      </c>
+      <c r="AG33" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M33" t="s">
-        <v>93</v>
-      </c>
-      <c r="O33">
-        <v>204001</v>
-      </c>
-      <c r="P33" t="s">
-        <v>128</v>
-      </c>
-      <c r="R33">
-        <v>2</v>
-      </c>
-      <c r="S33">
-        <v>10</v>
-      </c>
-      <c r="T33">
-        <v>1</v>
-      </c>
-      <c r="U33">
-        <v>1</v>
-      </c>
-      <c r="V33">
-        <v>0.5</v>
-      </c>
-      <c r="W33">
-        <v>0.5</v>
-      </c>
-      <c r="X33">
-        <v>30</v>
-      </c>
-      <c r="Y33">
-        <v>80</v>
-      </c>
-      <c r="AA33">
-        <v>10</v>
-      </c>
-      <c r="AB33">
-        <v>1</v>
-      </c>
-      <c r="AC33">
-        <v>1</v>
-      </c>
-      <c r="AD33">
-        <v>6</v>
-      </c>
-      <c r="AE33">
-        <v>6000001</v>
-      </c>
-      <c r="AF33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH33" s="1">
+      <c r="AH33" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI33" s="1">
         <v>300600002</v>
       </c>
-      <c r="AI33">
+      <c r="AJ33">
         <v>6002</v>
       </c>
-      <c r="AJ33" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:36">
+      <c r="AK33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:37">
       <c r="A34">
         <v>6003</v>
       </c>
@@ -3838,67 +3890,70 @@
         <v>6000001</v>
       </c>
       <c r="I34" t="s">
-        <v>110</v>
-      </c>
-      <c r="O34">
+        <v>88</v>
+      </c>
+      <c r="J34">
+        <v>8</v>
+      </c>
+      <c r="P34">
         <v>200001</v>
       </c>
-      <c r="R34">
-        <v>2</v>
-      </c>
       <c r="S34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>1</v>
       </c>
       <c r="V34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W34">
         <v>0.5</v>
       </c>
       <c r="X34">
+        <v>0.5</v>
+      </c>
+      <c r="Y34">
         <v>300</v>
       </c>
-      <c r="Y34">
-        <v>100</v>
-      </c>
-      <c r="AA34">
+      <c r="Z34">
+        <v>100</v>
+      </c>
+      <c r="AB34">
         <v>500</v>
       </c>
-      <c r="AB34">
-        <v>1</v>
-      </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE34">
+        <v>6</v>
+      </c>
+      <c r="AF34">
         <v>6000001</v>
       </c>
-      <c r="AF34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH34" s="1">
+      <c r="AG34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI34" s="1">
         <v>300600003</v>
       </c>
-      <c r="AI34">
+      <c r="AJ34">
         <v>6003</v>
       </c>
-      <c r="AJ34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:36">
+      <c r="AK34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:37">
       <c r="A35">
         <v>6004</v>
       </c>
@@ -3915,73 +3970,76 @@
         <v>61010003</v>
       </c>
       <c r="I35" t="s">
-        <v>86</v>
-      </c>
-      <c r="M35" t="s">
-        <v>98</v>
-      </c>
-      <c r="O35">
+        <v>88</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="N35" t="s">
+        <v>100</v>
+      </c>
+      <c r="P35">
         <v>204002</v>
       </c>
-      <c r="P35" t="s">
-        <v>128</v>
-      </c>
-      <c r="R35">
-        <v>2</v>
+      <c r="Q35" t="s">
+        <v>131</v>
       </c>
       <c r="S35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>1</v>
       </c>
       <c r="V35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W35">
         <v>0.5</v>
       </c>
       <c r="X35">
+        <v>0.5</v>
+      </c>
+      <c r="Y35">
         <v>20</v>
       </c>
-      <c r="Y35">
+      <c r="Z35">
         <v>40</v>
       </c>
-      <c r="AA35">
-        <v>6</v>
-      </c>
       <c r="AB35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC35">
         <v>1</v>
       </c>
       <c r="AD35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE35">
+        <v>6</v>
+      </c>
+      <c r="AF35">
         <v>6000001</v>
       </c>
-      <c r="AF35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH35" s="1">
+      <c r="AG35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI35" s="1">
         <v>300600004</v>
       </c>
-      <c r="AI35">
+      <c r="AJ35">
         <v>6004</v>
       </c>
-      <c r="AJ35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:36">
+      <c r="AK35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:37">
       <c r="A36">
         <v>6005</v>
       </c>
@@ -3998,73 +4056,76 @@
         <v>61010003</v>
       </c>
       <c r="I36" t="s">
-        <v>86</v>
-      </c>
-      <c r="M36" t="s">
-        <v>98</v>
-      </c>
-      <c r="O36">
+        <v>88</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
+        <v>100</v>
+      </c>
+      <c r="P36">
         <v>204003</v>
       </c>
-      <c r="P36" t="s">
-        <v>128</v>
-      </c>
-      <c r="R36">
-        <v>2</v>
+      <c r="Q36" t="s">
+        <v>131</v>
       </c>
       <c r="S36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T36">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>1</v>
       </c>
       <c r="V36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W36">
         <v>0.5</v>
       </c>
       <c r="X36">
+        <v>0.5</v>
+      </c>
+      <c r="Y36">
         <v>20</v>
       </c>
-      <c r="Y36">
+      <c r="Z36">
         <v>40</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>3</v>
       </c>
-      <c r="AB36">
-        <v>1</v>
-      </c>
       <c r="AC36">
         <v>1</v>
       </c>
       <c r="AD36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE36">
+        <v>6</v>
+      </c>
+      <c r="AF36">
         <v>6000001</v>
       </c>
-      <c r="AF36" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG36" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH36" s="1">
+      <c r="AG36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI36" s="1">
         <v>300600005</v>
       </c>
-      <c r="AI36">
+      <c r="AJ36">
         <v>6005</v>
       </c>
-      <c r="AJ36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:36">
+      <c r="AK36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:37">
       <c r="A37">
         <v>7001</v>
       </c>
@@ -4075,73 +4136,73 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G37">
         <v>7000001</v>
       </c>
       <c r="I37" t="s">
-        <v>110</v>
-      </c>
-      <c r="O37">
+        <v>113</v>
+      </c>
+      <c r="P37">
         <v>200001</v>
       </c>
-      <c r="R37">
-        <v>2</v>
-      </c>
       <c r="S37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>1</v>
       </c>
       <c r="V37">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W37">
         <v>0.5</v>
       </c>
       <c r="X37">
+        <v>0.5</v>
+      </c>
+      <c r="Y37">
         <v>45</v>
       </c>
-      <c r="Y37">
+      <c r="Z37">
         <v>120</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>12</v>
       </c>
-      <c r="AB37">
-        <v>1</v>
-      </c>
       <c r="AC37">
         <v>1</v>
       </c>
       <c r="AD37">
+        <v>1</v>
+      </c>
+      <c r="AE37">
         <v>7</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>7000001</v>
       </c>
-      <c r="AF37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG37" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH37" s="1">
+      <c r="AG37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI37" s="1">
         <v>300700001</v>
       </c>
-      <c r="AI37">
+      <c r="AJ37">
         <v>7001</v>
       </c>
-      <c r="AJ37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:36">
+      <c r="AK37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:37">
       <c r="A38">
         <v>7002</v>
       </c>
@@ -4158,73 +4219,76 @@
         <v>71000001</v>
       </c>
       <c r="I38" t="s">
-        <v>86</v>
-      </c>
-      <c r="M38" t="s">
+        <v>123</v>
+      </c>
+      <c r="J38">
+        <v>8</v>
+      </c>
+      <c r="N38" t="s">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>205001</v>
+      </c>
+      <c r="Q38" t="s">
         <v>98</v>
       </c>
-      <c r="O38">
-        <v>205001</v>
-      </c>
-      <c r="P38" t="s">
-        <v>96</v>
-      </c>
-      <c r="R38">
-        <v>2</v>
-      </c>
       <c r="S38">
+        <v>2</v>
+      </c>
+      <c r="T38">
         <v>10</v>
       </c>
-      <c r="T38">
-        <v>1</v>
-      </c>
       <c r="U38">
         <v>1</v>
       </c>
       <c r="V38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W38">
         <v>0.5</v>
       </c>
       <c r="X38">
+        <v>0.5</v>
+      </c>
+      <c r="Y38">
         <v>45</v>
       </c>
-      <c r="Y38">
+      <c r="Z38">
         <v>120</v>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <v>3</v>
       </c>
-      <c r="AB38">
-        <v>1</v>
-      </c>
       <c r="AC38">
         <v>1</v>
       </c>
       <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AE38">
         <v>7</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>7000001</v>
       </c>
-      <c r="AF38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG38" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH38" s="1">
+      <c r="AG38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI38" s="1">
         <v>300700002</v>
       </c>
-      <c r="AI38">
+      <c r="AJ38">
         <v>7002</v>
       </c>
-      <c r="AJ38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:36">
+      <c r="AK38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:37">
       <c r="A39">
         <v>7003</v>
       </c>
@@ -4241,73 +4305,76 @@
         <v>71010004</v>
       </c>
       <c r="I39" t="s">
-        <v>86</v>
-      </c>
-      <c r="M39" t="s">
-        <v>93</v>
-      </c>
-      <c r="O39">
+        <v>88</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>95</v>
+      </c>
+      <c r="P39">
         <v>205002</v>
       </c>
-      <c r="P39" t="s">
-        <v>96</v>
-      </c>
-      <c r="R39">
-        <v>2</v>
+      <c r="Q39" t="s">
+        <v>98</v>
       </c>
       <c r="S39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>1</v>
       </c>
       <c r="V39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W39">
         <v>0.5</v>
       </c>
       <c r="X39">
+        <v>0.5</v>
+      </c>
+      <c r="Y39">
         <v>45</v>
       </c>
-      <c r="Y39">
+      <c r="Z39">
         <v>60</v>
       </c>
-      <c r="AA39">
-        <v>6</v>
-      </c>
       <c r="AB39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AC39">
         <v>1</v>
       </c>
       <c r="AD39">
+        <v>1</v>
+      </c>
+      <c r="AE39">
         <v>7</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>7000001</v>
       </c>
-      <c r="AF39" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH39" s="1">
+      <c r="AG39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI39" s="1">
         <v>300700003</v>
       </c>
-      <c r="AI39">
+      <c r="AJ39">
         <v>7003</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:36">
+      <c r="AK39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:37">
       <c r="A40">
         <v>7004</v>
       </c>
@@ -4324,73 +4391,76 @@
         <v>71010004</v>
       </c>
       <c r="I40" t="s">
-        <v>86</v>
-      </c>
-      <c r="M40" t="s">
+        <v>88</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>95</v>
+      </c>
+      <c r="P40">
+        <v>205003</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>98</v>
+      </c>
+      <c r="S40">
+        <v>2</v>
+      </c>
+      <c r="T40">
+        <v>6</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40">
+        <v>0.5</v>
+      </c>
+      <c r="X40">
+        <v>0.5</v>
+      </c>
+      <c r="Y40">
+        <v>45</v>
+      </c>
+      <c r="Z40">
+        <v>60</v>
+      </c>
+      <c r="AB40">
+        <v>3</v>
+      </c>
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AD40">
+        <v>1</v>
+      </c>
+      <c r="AE40">
+        <v>7</v>
+      </c>
+      <c r="AF40">
+        <v>7000001</v>
+      </c>
+      <c r="AG40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="O40">
-        <v>205003</v>
-      </c>
-      <c r="P40" t="s">
-        <v>96</v>
-      </c>
-      <c r="R40">
-        <v>2</v>
-      </c>
-      <c r="S40">
-        <v>6</v>
-      </c>
-      <c r="T40">
-        <v>1</v>
-      </c>
-      <c r="U40">
-        <v>1</v>
-      </c>
-      <c r="V40">
-        <v>0.5</v>
-      </c>
-      <c r="W40">
-        <v>0.5</v>
-      </c>
-      <c r="X40">
-        <v>45</v>
-      </c>
-      <c r="Y40">
-        <v>60</v>
-      </c>
-      <c r="AA40">
-        <v>3</v>
-      </c>
-      <c r="AB40">
-        <v>1</v>
-      </c>
-      <c r="AC40">
-        <v>1</v>
-      </c>
-      <c r="AD40">
-        <v>7</v>
-      </c>
-      <c r="AE40">
-        <v>7000001</v>
-      </c>
-      <c r="AF40" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH40" s="1">
+      <c r="AH40" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI40" s="1">
         <v>300700004</v>
       </c>
-      <c r="AI40">
+      <c r="AJ40">
         <v>7004</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:36">
+      <c r="AK40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:37">
       <c r="A41">
         <v>101001</v>
       </c>
@@ -4401,61 +4471,64 @@
         <v>1000001</v>
       </c>
       <c r="I41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="P41">
+        <v>100001</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>0.5</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41">
+        <v>0.5</v>
+      </c>
+      <c r="X41">
+        <v>0.5</v>
+      </c>
+      <c r="Z41">
+        <v>100</v>
+      </c>
+      <c r="AB41">
+        <v>10</v>
+      </c>
+      <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AD41">
+        <v>0.2</v>
+      </c>
+      <c r="AE41">
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>1000001</v>
+      </c>
+      <c r="AG41" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O41">
-        <v>100001</v>
-      </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41">
-        <v>0.5</v>
-      </c>
-      <c r="T41">
-        <v>1</v>
-      </c>
-      <c r="U41">
-        <v>1</v>
-      </c>
-      <c r="V41">
-        <v>0.5</v>
-      </c>
-      <c r="W41">
-        <v>0.5</v>
-      </c>
-      <c r="Y41">
-        <v>100</v>
-      </c>
-      <c r="AA41">
-        <v>10</v>
-      </c>
-      <c r="AB41">
-        <v>1</v>
-      </c>
-      <c r="AC41">
-        <v>0.2</v>
-      </c>
-      <c r="AD41">
-        <v>1</v>
-      </c>
-      <c r="AE41">
-        <v>1000001</v>
-      </c>
-      <c r="AF41" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI41">
+      <c r="AH41" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ41">
         <v>101001</v>
       </c>
-      <c r="AJ41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:36">
+      <c r="AK41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:37">
       <c r="A42">
         <v>102001</v>
       </c>
@@ -4466,61 +4539,64 @@
         <v>1000001</v>
       </c>
       <c r="I42" t="s">
-        <v>86</v>
-      </c>
-      <c r="O42">
+        <v>88</v>
+      </c>
+      <c r="J42">
+        <v>7</v>
+      </c>
+      <c r="P42">
         <v>200001</v>
       </c>
-      <c r="R42">
-        <v>1</v>
-      </c>
       <c r="S42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T42">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U42">
         <v>1</v>
       </c>
       <c r="V42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W42">
         <v>0.5</v>
       </c>
-      <c r="Y42">
-        <v>100</v>
-      </c>
-      <c r="AA42">
+      <c r="X42">
+        <v>0.5</v>
+      </c>
+      <c r="Z42">
+        <v>100</v>
+      </c>
+      <c r="AB42">
         <v>10</v>
       </c>
-      <c r="AB42">
-        <v>1</v>
-      </c>
       <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AD42">
         <v>0.2</v>
       </c>
-      <c r="AD42">
-        <v>1</v>
-      </c>
       <c r="AE42">
+        <v>1</v>
+      </c>
+      <c r="AF42">
         <v>1000001</v>
       </c>
-      <c r="AF42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI42">
+      <c r="AG42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ42">
         <v>102001</v>
       </c>
-      <c r="AJ42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:36">
+      <c r="AK42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:37">
       <c r="A43">
         <v>103001</v>
       </c>
@@ -4531,61 +4607,64 @@
         <v>1000001</v>
       </c>
       <c r="I43" t="s">
-        <v>86</v>
-      </c>
-      <c r="O43">
+        <v>88</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="P43">
         <v>201001</v>
       </c>
-      <c r="R43">
-        <v>1</v>
-      </c>
       <c r="S43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T43">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U43">
         <v>1</v>
       </c>
       <c r="V43">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W43">
         <v>0.5</v>
       </c>
-      <c r="Y43">
-        <v>100</v>
-      </c>
-      <c r="AA43">
+      <c r="X43">
+        <v>0.5</v>
+      </c>
+      <c r="Z43">
+        <v>100</v>
+      </c>
+      <c r="AB43">
         <v>10</v>
       </c>
-      <c r="AB43">
-        <v>1</v>
-      </c>
       <c r="AC43">
+        <v>1</v>
+      </c>
+      <c r="AD43">
         <v>0.2</v>
       </c>
-      <c r="AD43">
-        <v>1</v>
-      </c>
       <c r="AE43">
+        <v>1</v>
+      </c>
+      <c r="AF43">
         <v>1000001</v>
       </c>
-      <c r="AF43" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI43">
+      <c r="AG43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ43">
         <v>103001</v>
       </c>
-      <c r="AJ43" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:36">
+      <c r="AK43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:37">
       <c r="A44">
         <v>103002</v>
       </c>
@@ -4596,61 +4675,64 @@
         <v>1000001</v>
       </c>
       <c r="I44" t="s">
-        <v>86</v>
-      </c>
-      <c r="O44">
+        <v>88</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="P44">
         <v>201002</v>
       </c>
-      <c r="R44">
-        <v>1</v>
-      </c>
       <c r="S44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T44">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U44">
         <v>1</v>
       </c>
       <c r="V44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W44">
         <v>0.5</v>
       </c>
-      <c r="Y44">
-        <v>100</v>
-      </c>
-      <c r="AA44">
+      <c r="X44">
+        <v>0.5</v>
+      </c>
+      <c r="Z44">
+        <v>100</v>
+      </c>
+      <c r="AB44">
         <v>10</v>
       </c>
-      <c r="AB44">
-        <v>1</v>
-      </c>
       <c r="AC44">
+        <v>1</v>
+      </c>
+      <c r="AD44">
         <v>0.2</v>
       </c>
-      <c r="AD44">
-        <v>1</v>
-      </c>
       <c r="AE44">
+        <v>1</v>
+      </c>
+      <c r="AF44">
         <v>1000001</v>
       </c>
-      <c r="AF44" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI44">
+      <c r="AG44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ44">
         <v>103002</v>
       </c>
-      <c r="AJ44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:36">
+      <c r="AK44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:37">
       <c r="A45" s="1">
         <v>900001</v>
       </c>
@@ -4667,70 +4749,73 @@
         <v>21010001</v>
       </c>
       <c r="I45" t="s">
+        <v>88</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="N45" t="s">
+        <v>95</v>
+      </c>
+      <c r="P45">
+        <v>100001</v>
+      </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
+      <c r="T45">
+        <v>0.5</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45">
+        <v>1</v>
+      </c>
+      <c r="W45">
+        <v>0.5</v>
+      </c>
+      <c r="X45">
+        <v>0.5</v>
+      </c>
+      <c r="Y45">
+        <v>10</v>
+      </c>
+      <c r="Z45">
+        <v>100</v>
+      </c>
+      <c r="AB45">
+        <v>100</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AD45">
+        <v>1</v>
+      </c>
+      <c r="AE45">
+        <v>2</v>
+      </c>
+      <c r="AF45">
+        <v>2000001</v>
+      </c>
+      <c r="AG45" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M45" t="s">
-        <v>93</v>
-      </c>
-      <c r="O45">
-        <v>100001</v>
-      </c>
-      <c r="R45">
-        <v>2</v>
-      </c>
-      <c r="S45">
-        <v>0.5</v>
-      </c>
-      <c r="T45">
-        <v>1</v>
-      </c>
-      <c r="U45">
-        <v>1</v>
-      </c>
-      <c r="V45">
-        <v>0.5</v>
-      </c>
-      <c r="W45">
-        <v>0.5</v>
-      </c>
-      <c r="X45">
-        <v>10</v>
-      </c>
-      <c r="Y45">
-        <v>100</v>
-      </c>
-      <c r="AA45">
-        <v>100</v>
-      </c>
-      <c r="AB45">
-        <v>1</v>
-      </c>
-      <c r="AC45">
-        <v>1</v>
-      </c>
-      <c r="AD45">
-        <v>2</v>
-      </c>
-      <c r="AE45">
-        <v>2000001</v>
-      </c>
-      <c r="AF45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH45">
+      <c r="AH45" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI45">
         <v>300200001</v>
       </c>
-      <c r="AI45" s="1">
+      <c r="AJ45" s="1">
         <v>900001</v>
       </c>
-      <c r="AJ45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:36">
+      <c r="AK45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:37">
       <c r="A46" s="1">
         <v>900002</v>
       </c>
@@ -4747,73 +4832,76 @@
         <v>21000001</v>
       </c>
       <c r="I46" t="s">
-        <v>86</v>
-      </c>
-      <c r="M46" t="s">
-        <v>95</v>
-      </c>
-      <c r="O46">
+        <v>88</v>
+      </c>
+      <c r="J46">
+        <v>8</v>
+      </c>
+      <c r="N46" t="s">
+        <v>97</v>
+      </c>
+      <c r="P46">
         <v>200001</v>
       </c>
-      <c r="P46" t="s">
-        <v>96</v>
-      </c>
-      <c r="R46">
-        <v>2</v>
+      <c r="Q46" t="s">
+        <v>98</v>
       </c>
       <c r="S46">
+        <v>2</v>
+      </c>
+      <c r="T46">
         <v>10</v>
       </c>
-      <c r="T46">
-        <v>1</v>
-      </c>
       <c r="U46">
         <v>1</v>
       </c>
       <c r="V46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W46">
         <v>0.5</v>
       </c>
       <c r="X46">
+        <v>0.5</v>
+      </c>
+      <c r="Y46">
         <v>10</v>
       </c>
-      <c r="Y46">
-        <v>100</v>
-      </c>
-      <c r="AA46">
+      <c r="Z46">
         <v>100</v>
       </c>
       <c r="AB46">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AC46">
         <v>1</v>
       </c>
       <c r="AD46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE46">
+        <v>2</v>
+      </c>
+      <c r="AF46">
         <v>2000001</v>
       </c>
-      <c r="AF46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH46">
+      <c r="AG46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI46">
         <v>300200002</v>
       </c>
-      <c r="AI46" s="1">
+      <c r="AJ46" s="1">
         <v>900002</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:36">
+      <c r="AK46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:37">
       <c r="A47" s="1">
         <v>989996</v>
       </c>
@@ -4821,55 +4909,55 @@
       <c r="C47">
         <v>1</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>200001</v>
       </c>
-      <c r="R47">
-        <v>2</v>
-      </c>
       <c r="S47">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T47">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U47">
         <v>1</v>
       </c>
       <c r="V47">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W47">
         <v>0.5</v>
       </c>
-      <c r="Y47">
-        <v>100</v>
-      </c>
-      <c r="AA47">
+      <c r="X47">
+        <v>0.5</v>
+      </c>
+      <c r="Z47">
+        <v>100</v>
+      </c>
+      <c r="AB47">
         <v>35</v>
       </c>
-      <c r="AB47">
-        <v>1</v>
-      </c>
       <c r="AC47">
         <v>1</v>
       </c>
-      <c r="AD47" s="1">
+      <c r="AD47">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="1">
         <v>989996</v>
       </c>
-      <c r="AE47" s="2"/>
       <c r="AF47" s="2"/>
-      <c r="AG47" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI47">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:36">
+      <c r="AG47" s="2"/>
+      <c r="AH47" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ47">
+        <v>1</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:37">
       <c r="A48" s="1">
         <v>989997</v>
       </c>
@@ -4877,55 +4965,55 @@
       <c r="C48">
         <v>1</v>
       </c>
-      <c r="O48">
+      <c r="P48">
         <v>200001</v>
       </c>
-      <c r="R48">
-        <v>2</v>
-      </c>
       <c r="S48">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T48">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U48">
         <v>1</v>
       </c>
       <c r="V48">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W48">
         <v>0.5</v>
       </c>
-      <c r="Y48">
-        <v>100</v>
-      </c>
-      <c r="AA48">
+      <c r="X48">
+        <v>0.5</v>
+      </c>
+      <c r="Z48">
+        <v>100</v>
+      </c>
+      <c r="AB48">
         <v>35</v>
       </c>
-      <c r="AB48">
-        <v>1</v>
-      </c>
       <c r="AC48">
         <v>1</v>
       </c>
-      <c r="AD48" s="1">
+      <c r="AD48">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="1">
         <v>989997</v>
       </c>
-      <c r="AE48" s="2"/>
       <c r="AF48" s="2"/>
-      <c r="AG48" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI48">
-        <v>1</v>
-      </c>
-      <c r="AJ48" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:36">
+      <c r="AG48" s="2"/>
+      <c r="AH48" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ48">
+        <v>1</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:37">
       <c r="A49" s="1">
         <v>989998</v>
       </c>
@@ -4933,55 +5021,55 @@
       <c r="C49">
         <v>1</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>200001</v>
       </c>
-      <c r="R49">
-        <v>2</v>
-      </c>
       <c r="S49">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U49">
         <v>1</v>
       </c>
       <c r="V49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W49">
         <v>0.5</v>
       </c>
-      <c r="Y49">
-        <v>100</v>
-      </c>
-      <c r="AA49">
+      <c r="X49">
+        <v>0.5</v>
+      </c>
+      <c r="Z49">
+        <v>100</v>
+      </c>
+      <c r="AB49">
         <v>35</v>
       </c>
-      <c r="AB49">
-        <v>1</v>
-      </c>
       <c r="AC49">
         <v>1</v>
       </c>
-      <c r="AD49" s="1">
+      <c r="AD49">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="1">
         <v>989998</v>
       </c>
-      <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
-      <c r="AG49" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI49">
-        <v>1</v>
-      </c>
-      <c r="AJ49" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:36">
+      <c r="AG49" s="2"/>
+      <c r="AH49" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ49">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:37">
       <c r="A50" s="1">
         <v>989999</v>
       </c>
@@ -4989,53 +5077,53 @@
       <c r="C50">
         <v>1</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <v>200001</v>
       </c>
-      <c r="R50">
-        <v>2</v>
-      </c>
       <c r="S50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U50">
         <v>1</v>
       </c>
       <c r="V50">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W50">
         <v>0.5</v>
       </c>
-      <c r="Y50">
-        <v>100</v>
-      </c>
-      <c r="AA50">
+      <c r="X50">
+        <v>0.5</v>
+      </c>
+      <c r="Z50">
+        <v>100</v>
+      </c>
+      <c r="AB50">
         <v>35</v>
       </c>
-      <c r="AB50">
-        <v>1</v>
-      </c>
       <c r="AC50">
         <v>1</v>
       </c>
       <c r="AD50">
+        <v>1</v>
+      </c>
+      <c r="AE50">
         <v>989999</v>
       </c>
-      <c r="AG50" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI50">
-        <v>1</v>
-      </c>
-      <c r="AJ50" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:36">
+      <c r="AH50" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ50">
+        <v>1</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:37">
       <c r="A51" s="1">
         <v>999947</v>
       </c>
@@ -5043,55 +5131,55 @@
       <c r="C51">
         <v>1</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <v>200001</v>
       </c>
-      <c r="R51">
-        <v>2</v>
-      </c>
       <c r="S51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U51">
         <v>1</v>
       </c>
       <c r="V51">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W51">
         <v>0.5</v>
       </c>
-      <c r="Y51">
-        <v>100</v>
-      </c>
-      <c r="AA51">
+      <c r="X51">
+        <v>0.5</v>
+      </c>
+      <c r="Z51">
+        <v>100</v>
+      </c>
+      <c r="AB51">
         <v>35</v>
       </c>
-      <c r="AB51">
-        <v>1</v>
-      </c>
       <c r="AC51">
         <v>1</v>
       </c>
-      <c r="AD51" s="1">
+      <c r="AD51">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="1">
         <v>999947</v>
       </c>
-      <c r="AE51" s="2"/>
       <c r="AF51" s="2"/>
-      <c r="AG51" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI51">
-        <v>1</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:36">
+      <c r="AG51" s="2"/>
+      <c r="AH51" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ51">
+        <v>1</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:37">
       <c r="A52" s="1">
         <v>999948</v>
       </c>
@@ -5099,55 +5187,55 @@
       <c r="C52">
         <v>1</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <v>200001</v>
       </c>
-      <c r="R52">
-        <v>2</v>
-      </c>
       <c r="S52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U52">
         <v>1</v>
       </c>
       <c r="V52">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W52">
         <v>0.5</v>
       </c>
-      <c r="Y52">
-        <v>100</v>
-      </c>
-      <c r="AA52">
+      <c r="X52">
+        <v>0.5</v>
+      </c>
+      <c r="Z52">
+        <v>100</v>
+      </c>
+      <c r="AB52">
         <v>35</v>
       </c>
-      <c r="AB52">
-        <v>1</v>
-      </c>
       <c r="AC52">
         <v>1</v>
       </c>
-      <c r="AD52" s="1">
+      <c r="AD52">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="1">
         <v>999948</v>
       </c>
-      <c r="AE52" s="2"/>
       <c r="AF52" s="2"/>
-      <c r="AG52" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI52">
-        <v>1</v>
-      </c>
-      <c r="AJ52" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:36">
+      <c r="AG52" s="2"/>
+      <c r="AH52" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ52">
+        <v>1</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:37">
       <c r="A53" s="1">
         <v>999949</v>
       </c>
@@ -5155,55 +5243,55 @@
       <c r="C53">
         <v>1</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>200001</v>
       </c>
-      <c r="R53">
-        <v>2</v>
-      </c>
       <c r="S53">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U53">
         <v>1</v>
       </c>
       <c r="V53">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W53">
         <v>0.5</v>
       </c>
-      <c r="Y53">
-        <v>100</v>
-      </c>
-      <c r="AA53">
+      <c r="X53">
+        <v>0.5</v>
+      </c>
+      <c r="Z53">
+        <v>100</v>
+      </c>
+      <c r="AB53">
         <v>35</v>
       </c>
-      <c r="AB53">
-        <v>1</v>
-      </c>
       <c r="AC53">
         <v>1</v>
       </c>
-      <c r="AD53" s="1">
+      <c r="AD53">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="1">
         <v>999949</v>
       </c>
-      <c r="AE53" s="2"/>
       <c r="AF53" s="2"/>
-      <c r="AG53" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI53">
-        <v>1</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:36">
+      <c r="AG53" s="2"/>
+      <c r="AH53" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ53">
+        <v>1</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:37">
       <c r="A54" s="1">
         <v>999950</v>
       </c>
@@ -5211,55 +5299,55 @@
       <c r="C54">
         <v>1</v>
       </c>
-      <c r="O54">
+      <c r="P54">
         <v>200001</v>
       </c>
-      <c r="R54">
-        <v>2</v>
-      </c>
       <c r="S54">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U54">
         <v>1</v>
       </c>
       <c r="V54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W54">
         <v>0.5</v>
       </c>
-      <c r="Y54">
-        <v>100</v>
-      </c>
-      <c r="AA54">
+      <c r="X54">
+        <v>0.5</v>
+      </c>
+      <c r="Z54">
+        <v>100</v>
+      </c>
+      <c r="AB54">
         <v>35</v>
       </c>
-      <c r="AB54">
-        <v>1</v>
-      </c>
       <c r="AC54">
         <v>1</v>
       </c>
-      <c r="AD54" s="1">
+      <c r="AD54">
+        <v>1</v>
+      </c>
+      <c r="AE54" s="1">
         <v>999950</v>
       </c>
-      <c r="AE54" s="2"/>
       <c r="AF54" s="2"/>
-      <c r="AG54" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI54">
-        <v>1</v>
-      </c>
-      <c r="AJ54" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:36">
+      <c r="AG54" s="2"/>
+      <c r="AH54" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ54">
+        <v>1</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:37">
       <c r="A55" s="1">
         <v>999951</v>
       </c>
@@ -5267,55 +5355,55 @@
       <c r="C55">
         <v>1</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>200001</v>
       </c>
-      <c r="R55">
-        <v>2</v>
-      </c>
       <c r="S55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U55">
         <v>1</v>
       </c>
       <c r="V55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W55">
         <v>0.5</v>
       </c>
-      <c r="Y55">
-        <v>100</v>
-      </c>
-      <c r="AA55">
+      <c r="X55">
+        <v>0.5</v>
+      </c>
+      <c r="Z55">
+        <v>100</v>
+      </c>
+      <c r="AB55">
         <v>35</v>
       </c>
-      <c r="AB55">
-        <v>1</v>
-      </c>
       <c r="AC55">
         <v>1</v>
       </c>
-      <c r="AD55" s="1">
+      <c r="AD55">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="1">
         <v>999951</v>
       </c>
-      <c r="AE55" s="2"/>
       <c r="AF55" s="2"/>
-      <c r="AG55" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI55">
-        <v>1</v>
-      </c>
-      <c r="AJ55" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:36">
+      <c r="AG55" s="2"/>
+      <c r="AH55" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ55">
+        <v>1</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:37">
       <c r="A56" s="1">
         <v>999952</v>
       </c>
@@ -5323,55 +5411,55 @@
       <c r="C56">
         <v>1</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>200001</v>
       </c>
-      <c r="R56">
-        <v>2</v>
-      </c>
       <c r="S56">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U56">
         <v>1</v>
       </c>
       <c r="V56">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W56">
         <v>0.5</v>
       </c>
-      <c r="Y56">
-        <v>100</v>
-      </c>
-      <c r="AA56">
+      <c r="X56">
+        <v>0.5</v>
+      </c>
+      <c r="Z56">
+        <v>100</v>
+      </c>
+      <c r="AB56">
         <v>35</v>
       </c>
-      <c r="AB56">
-        <v>1</v>
-      </c>
       <c r="AC56">
         <v>1</v>
       </c>
-      <c r="AD56" s="1">
+      <c r="AD56">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="1">
         <v>999952</v>
       </c>
-      <c r="AE56" s="2"/>
       <c r="AF56" s="2"/>
-      <c r="AG56" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI56">
-        <v>1</v>
-      </c>
-      <c r="AJ56" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:36">
+      <c r="AG56" s="2"/>
+      <c r="AH56" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ56">
+        <v>1</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:37">
       <c r="A57" s="1">
         <v>999953</v>
       </c>
@@ -5379,55 +5467,55 @@
       <c r="C57">
         <v>1</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>200001</v>
       </c>
-      <c r="R57">
-        <v>2</v>
-      </c>
       <c r="S57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T57">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U57">
         <v>1</v>
       </c>
       <c r="V57">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W57">
         <v>0.5</v>
       </c>
-      <c r="Y57">
-        <v>100</v>
-      </c>
-      <c r="AA57">
+      <c r="X57">
+        <v>0.5</v>
+      </c>
+      <c r="Z57">
+        <v>100</v>
+      </c>
+      <c r="AB57">
         <v>35</v>
       </c>
-      <c r="AB57">
-        <v>1</v>
-      </c>
       <c r="AC57">
         <v>1</v>
       </c>
-      <c r="AD57" s="1">
+      <c r="AD57">
+        <v>1</v>
+      </c>
+      <c r="AE57" s="1">
         <v>999953</v>
       </c>
-      <c r="AE57" s="2"/>
       <c r="AF57" s="2"/>
-      <c r="AG57" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI57">
-        <v>1</v>
-      </c>
-      <c r="AJ57" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:36">
+      <c r="AG57" s="2"/>
+      <c r="AH57" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ57">
+        <v>1</v>
+      </c>
+      <c r="AK57" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:37">
       <c r="A58" s="1">
         <v>999954</v>
       </c>
@@ -5435,55 +5523,55 @@
       <c r="C58">
         <v>1</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>200001</v>
       </c>
-      <c r="R58">
-        <v>2</v>
-      </c>
       <c r="S58">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U58">
         <v>1</v>
       </c>
       <c r="V58">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W58">
         <v>0.5</v>
       </c>
-      <c r="Y58">
-        <v>100</v>
-      </c>
-      <c r="AA58">
+      <c r="X58">
+        <v>0.5</v>
+      </c>
+      <c r="Z58">
+        <v>100</v>
+      </c>
+      <c r="AB58">
         <v>35</v>
       </c>
-      <c r="AB58">
-        <v>1</v>
-      </c>
       <c r="AC58">
         <v>1</v>
       </c>
-      <c r="AD58" s="1">
+      <c r="AD58">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="1">
         <v>999954</v>
       </c>
-      <c r="AE58" s="2"/>
       <c r="AF58" s="2"/>
-      <c r="AG58" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI58">
-        <v>1</v>
-      </c>
-      <c r="AJ58" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:36">
+      <c r="AG58" s="2"/>
+      <c r="AH58" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ58">
+        <v>1</v>
+      </c>
+      <c r="AK58" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:37">
       <c r="A59" s="1">
         <v>999955</v>
       </c>
@@ -5491,55 +5579,55 @@
       <c r="C59">
         <v>1</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>200001</v>
       </c>
-      <c r="R59">
-        <v>2</v>
-      </c>
       <c r="S59">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T59">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U59">
         <v>1</v>
       </c>
       <c r="V59">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W59">
         <v>0.5</v>
       </c>
-      <c r="Y59">
-        <v>100</v>
-      </c>
-      <c r="AA59">
+      <c r="X59">
+        <v>0.5</v>
+      </c>
+      <c r="Z59">
+        <v>100</v>
+      </c>
+      <c r="AB59">
         <v>35</v>
       </c>
-      <c r="AB59">
-        <v>1</v>
-      </c>
       <c r="AC59">
         <v>1</v>
       </c>
-      <c r="AD59" s="1">
+      <c r="AD59">
+        <v>1</v>
+      </c>
+      <c r="AE59" s="1">
         <v>999955</v>
       </c>
-      <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
-      <c r="AG59" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI59">
-        <v>1</v>
-      </c>
-      <c r="AJ59" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:36">
+      <c r="AG59" s="2"/>
+      <c r="AH59" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ59">
+        <v>1</v>
+      </c>
+      <c r="AK59" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:37">
       <c r="A60" s="1">
         <v>999956</v>
       </c>
@@ -5547,55 +5635,55 @@
       <c r="C60">
         <v>1</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <v>200001</v>
       </c>
-      <c r="R60">
-        <v>2</v>
-      </c>
       <c r="S60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U60">
         <v>1</v>
       </c>
       <c r="V60">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W60">
         <v>0.5</v>
       </c>
-      <c r="Y60">
-        <v>100</v>
-      </c>
-      <c r="AA60">
+      <c r="X60">
+        <v>0.5</v>
+      </c>
+      <c r="Z60">
+        <v>100</v>
+      </c>
+      <c r="AB60">
         <v>35</v>
       </c>
-      <c r="AB60">
-        <v>1</v>
-      </c>
       <c r="AC60">
         <v>1</v>
       </c>
-      <c r="AD60" s="1">
+      <c r="AD60">
+        <v>1</v>
+      </c>
+      <c r="AE60" s="1">
         <v>999956</v>
       </c>
-      <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
-      <c r="AG60" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI60">
-        <v>1</v>
-      </c>
-      <c r="AJ60" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:36">
+      <c r="AG60" s="2"/>
+      <c r="AH60" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ60">
+        <v>1</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:37">
       <c r="A61" s="1">
         <v>999957</v>
       </c>
@@ -5603,55 +5691,55 @@
       <c r="C61">
         <v>1</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>200001</v>
       </c>
-      <c r="R61">
-        <v>2</v>
-      </c>
       <c r="S61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T61">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U61">
         <v>1</v>
       </c>
       <c r="V61">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W61">
         <v>0.5</v>
       </c>
-      <c r="Y61">
-        <v>100</v>
-      </c>
-      <c r="AA61">
+      <c r="X61">
+        <v>0.5</v>
+      </c>
+      <c r="Z61">
+        <v>100</v>
+      </c>
+      <c r="AB61">
         <v>35</v>
       </c>
-      <c r="AB61">
-        <v>1</v>
-      </c>
       <c r="AC61">
         <v>1</v>
       </c>
-      <c r="AD61" s="1">
+      <c r="AD61">
+        <v>1</v>
+      </c>
+      <c r="AE61" s="1">
         <v>999957</v>
       </c>
-      <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
-      <c r="AG61" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI61">
-        <v>1</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:36">
+      <c r="AG61" s="2"/>
+      <c r="AH61" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ61">
+        <v>1</v>
+      </c>
+      <c r="AK61" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:37">
       <c r="A62" s="1">
         <v>999958</v>
       </c>
@@ -5659,55 +5747,55 @@
       <c r="C62">
         <v>1</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <v>200001</v>
       </c>
-      <c r="R62">
-        <v>2</v>
-      </c>
       <c r="S62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U62">
         <v>1</v>
       </c>
       <c r="V62">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W62">
         <v>0.5</v>
       </c>
-      <c r="Y62">
-        <v>100</v>
-      </c>
-      <c r="AA62">
+      <c r="X62">
+        <v>0.5</v>
+      </c>
+      <c r="Z62">
+        <v>100</v>
+      </c>
+      <c r="AB62">
         <v>35</v>
       </c>
-      <c r="AB62">
-        <v>1</v>
-      </c>
       <c r="AC62">
         <v>1</v>
       </c>
-      <c r="AD62" s="1">
+      <c r="AD62">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="1">
         <v>999958</v>
       </c>
-      <c r="AE62" s="2"/>
       <c r="AF62" s="2"/>
-      <c r="AG62" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI62">
-        <v>1</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:36">
+      <c r="AG62" s="2"/>
+      <c r="AH62" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ62">
+        <v>1</v>
+      </c>
+      <c r="AK62" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:37">
       <c r="A63" s="1">
         <v>999959</v>
       </c>
@@ -5715,55 +5803,55 @@
       <c r="C63">
         <v>1</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <v>200001</v>
       </c>
-      <c r="R63">
-        <v>2</v>
-      </c>
       <c r="S63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T63">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U63">
         <v>1</v>
       </c>
       <c r="V63">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W63">
         <v>0.5</v>
       </c>
-      <c r="Y63">
-        <v>100</v>
-      </c>
-      <c r="AA63">
+      <c r="X63">
+        <v>0.5</v>
+      </c>
+      <c r="Z63">
+        <v>100</v>
+      </c>
+      <c r="AB63">
         <v>35</v>
       </c>
-      <c r="AB63">
-        <v>1</v>
-      </c>
       <c r="AC63">
         <v>1</v>
       </c>
-      <c r="AD63" s="1">
+      <c r="AD63">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="1">
         <v>999959</v>
       </c>
-      <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
-      <c r="AG63" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI63">
-        <v>1</v>
-      </c>
-      <c r="AJ63" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:36">
+      <c r="AG63" s="2"/>
+      <c r="AH63" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ63">
+        <v>1</v>
+      </c>
+      <c r="AK63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:37">
       <c r="A64" s="1">
         <v>999960</v>
       </c>
@@ -5771,55 +5859,55 @@
       <c r="C64">
         <v>1</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>200001</v>
       </c>
-      <c r="R64">
-        <v>2</v>
-      </c>
       <c r="S64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U64">
         <v>1</v>
       </c>
       <c r="V64">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W64">
         <v>0.5</v>
       </c>
-      <c r="Y64">
-        <v>100</v>
-      </c>
-      <c r="AA64">
+      <c r="X64">
+        <v>0.5</v>
+      </c>
+      <c r="Z64">
+        <v>100</v>
+      </c>
+      <c r="AB64">
         <v>35</v>
       </c>
-      <c r="AB64">
-        <v>1</v>
-      </c>
       <c r="AC64">
         <v>1</v>
       </c>
-      <c r="AD64" s="1">
+      <c r="AD64">
+        <v>1</v>
+      </c>
+      <c r="AE64" s="1">
         <v>999960</v>
       </c>
-      <c r="AE64" s="2"/>
       <c r="AF64" s="2"/>
-      <c r="AG64" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI64">
-        <v>1</v>
-      </c>
-      <c r="AJ64" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" spans="1:36">
+      <c r="AG64" s="2"/>
+      <c r="AH64" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ64">
+        <v>1</v>
+      </c>
+      <c r="AK64" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:37">
       <c r="A65" s="1">
         <v>999961</v>
       </c>
@@ -5827,55 +5915,55 @@
       <c r="C65">
         <v>1</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>200001</v>
       </c>
-      <c r="R65">
-        <v>2</v>
-      </c>
       <c r="S65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U65">
         <v>1</v>
       </c>
       <c r="V65">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W65">
         <v>0.5</v>
       </c>
-      <c r="Y65">
-        <v>100</v>
-      </c>
-      <c r="AA65">
+      <c r="X65">
+        <v>0.5</v>
+      </c>
+      <c r="Z65">
+        <v>100</v>
+      </c>
+      <c r="AB65">
         <v>35</v>
       </c>
-      <c r="AB65">
-        <v>1</v>
-      </c>
       <c r="AC65">
         <v>1</v>
       </c>
-      <c r="AD65" s="1">
+      <c r="AD65">
+        <v>1</v>
+      </c>
+      <c r="AE65" s="1">
         <v>999961</v>
       </c>
-      <c r="AE65" s="2"/>
       <c r="AF65" s="2"/>
-      <c r="AG65" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI65">
-        <v>1</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" spans="1:36">
+      <c r="AG65" s="2"/>
+      <c r="AH65" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ65">
+        <v>1</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:37">
       <c r="A66" s="1">
         <v>999962</v>
       </c>
@@ -5883,55 +5971,55 @@
       <c r="C66">
         <v>1</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>200001</v>
       </c>
-      <c r="R66">
-        <v>2</v>
-      </c>
       <c r="S66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U66">
         <v>1</v>
       </c>
       <c r="V66">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W66">
         <v>0.5</v>
       </c>
-      <c r="Y66">
-        <v>100</v>
-      </c>
-      <c r="AA66">
+      <c r="X66">
+        <v>0.5</v>
+      </c>
+      <c r="Z66">
+        <v>100</v>
+      </c>
+      <c r="AB66">
         <v>35</v>
       </c>
-      <c r="AB66">
-        <v>1</v>
-      </c>
       <c r="AC66">
         <v>1</v>
       </c>
-      <c r="AD66" s="1">
+      <c r="AD66">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="1">
         <v>999962</v>
       </c>
-      <c r="AE66" s="2"/>
       <c r="AF66" s="2"/>
-      <c r="AG66" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI66">
-        <v>1</v>
-      </c>
-      <c r="AJ66" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" spans="1:36">
+      <c r="AG66" s="2"/>
+      <c r="AH66" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ66">
+        <v>1</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:37">
       <c r="A67" s="1">
         <v>999963</v>
       </c>
@@ -5939,55 +6027,55 @@
       <c r="C67">
         <v>1</v>
       </c>
-      <c r="O67">
+      <c r="P67">
         <v>200001</v>
       </c>
-      <c r="R67">
-        <v>2</v>
-      </c>
       <c r="S67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T67">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U67">
         <v>1</v>
       </c>
       <c r="V67">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W67">
         <v>0.5</v>
       </c>
-      <c r="Y67">
-        <v>100</v>
-      </c>
-      <c r="AA67">
+      <c r="X67">
+        <v>0.5</v>
+      </c>
+      <c r="Z67">
+        <v>100</v>
+      </c>
+      <c r="AB67">
         <v>35</v>
       </c>
-      <c r="AB67">
-        <v>1</v>
-      </c>
       <c r="AC67">
         <v>1</v>
       </c>
-      <c r="AD67" s="1">
+      <c r="AD67">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="1">
         <v>999963</v>
       </c>
-      <c r="AE67" s="2"/>
       <c r="AF67" s="2"/>
-      <c r="AG67" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI67">
-        <v>1</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" spans="1:36">
+      <c r="AG67" s="2"/>
+      <c r="AH67" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ67">
+        <v>1</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:37">
       <c r="A68" s="1">
         <v>999964</v>
       </c>
@@ -5995,55 +6083,55 @@
       <c r="C68">
         <v>1</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>200001</v>
       </c>
-      <c r="R68">
-        <v>2</v>
-      </c>
       <c r="S68">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U68">
         <v>1</v>
       </c>
       <c r="V68">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W68">
         <v>0.5</v>
       </c>
-      <c r="Y68">
-        <v>100</v>
-      </c>
-      <c r="AA68">
+      <c r="X68">
+        <v>0.5</v>
+      </c>
+      <c r="Z68">
+        <v>100</v>
+      </c>
+      <c r="AB68">
         <v>35</v>
       </c>
-      <c r="AB68">
-        <v>1</v>
-      </c>
       <c r="AC68">
         <v>1</v>
       </c>
-      <c r="AD68" s="1">
+      <c r="AD68">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="1">
         <v>999964</v>
       </c>
-      <c r="AE68" s="2"/>
       <c r="AF68" s="2"/>
-      <c r="AG68" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI68">
-        <v>1</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" spans="1:36">
+      <c r="AG68" s="2"/>
+      <c r="AH68" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ68">
+        <v>1</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:37">
       <c r="A69" s="1">
         <v>999965</v>
       </c>
@@ -6051,55 +6139,55 @@
       <c r="C69">
         <v>1</v>
       </c>
-      <c r="O69">
+      <c r="P69">
         <v>200001</v>
       </c>
-      <c r="R69">
-        <v>2</v>
-      </c>
       <c r="S69">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T69">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U69">
         <v>1</v>
       </c>
       <c r="V69">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W69">
         <v>0.5</v>
       </c>
-      <c r="Y69">
-        <v>100</v>
-      </c>
-      <c r="AA69">
+      <c r="X69">
+        <v>0.5</v>
+      </c>
+      <c r="Z69">
+        <v>100</v>
+      </c>
+      <c r="AB69">
         <v>35</v>
       </c>
-      <c r="AB69">
-        <v>1</v>
-      </c>
       <c r="AC69">
         <v>1</v>
       </c>
-      <c r="AD69" s="1">
+      <c r="AD69">
+        <v>1</v>
+      </c>
+      <c r="AE69" s="1">
         <v>999965</v>
       </c>
-      <c r="AE69" s="2"/>
       <c r="AF69" s="2"/>
-      <c r="AG69" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI69">
-        <v>1</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" spans="1:36">
+      <c r="AG69" s="2"/>
+      <c r="AH69" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ69">
+        <v>1</v>
+      </c>
+      <c r="AK69" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:37">
       <c r="A70" s="1">
         <v>999966</v>
       </c>
@@ -6107,55 +6195,55 @@
       <c r="C70">
         <v>1</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>200001</v>
       </c>
-      <c r="R70">
-        <v>2</v>
-      </c>
       <c r="S70">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T70">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U70">
         <v>1</v>
       </c>
       <c r="V70">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W70">
         <v>0.5</v>
       </c>
-      <c r="Y70">
-        <v>100</v>
-      </c>
-      <c r="AA70">
+      <c r="X70">
+        <v>0.5</v>
+      </c>
+      <c r="Z70">
+        <v>100</v>
+      </c>
+      <c r="AB70">
         <v>35</v>
       </c>
-      <c r="AB70">
-        <v>1</v>
-      </c>
       <c r="AC70">
         <v>1</v>
       </c>
-      <c r="AD70" s="1">
+      <c r="AD70">
+        <v>1</v>
+      </c>
+      <c r="AE70" s="1">
         <v>999966</v>
       </c>
-      <c r="AE70" s="2"/>
       <c r="AF70" s="2"/>
-      <c r="AG70" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI70">
-        <v>1</v>
-      </c>
-      <c r="AJ70" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="71" customFormat="1" spans="1:36">
+      <c r="AG70" s="2"/>
+      <c r="AH70" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ70">
+        <v>1</v>
+      </c>
+      <c r="AK70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:37">
       <c r="A71" s="1">
         <v>999967</v>
       </c>
@@ -6163,55 +6251,55 @@
       <c r="C71">
         <v>1</v>
       </c>
-      <c r="O71">
+      <c r="P71">
         <v>200001</v>
       </c>
-      <c r="R71">
-        <v>2</v>
-      </c>
       <c r="S71">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U71">
         <v>1</v>
       </c>
       <c r="V71">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W71">
         <v>0.5</v>
       </c>
-      <c r="Y71">
-        <v>100</v>
-      </c>
-      <c r="AA71">
+      <c r="X71">
+        <v>0.5</v>
+      </c>
+      <c r="Z71">
+        <v>100</v>
+      </c>
+      <c r="AB71">
         <v>35</v>
       </c>
-      <c r="AB71">
-        <v>1</v>
-      </c>
       <c r="AC71">
         <v>1</v>
       </c>
-      <c r="AD71" s="1">
+      <c r="AD71">
+        <v>1</v>
+      </c>
+      <c r="AE71" s="1">
         <v>999967</v>
       </c>
-      <c r="AE71" s="2"/>
       <c r="AF71" s="2"/>
-      <c r="AG71" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI71">
-        <v>1</v>
-      </c>
-      <c r="AJ71" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" customFormat="1" spans="1:36">
+      <c r="AG71" s="2"/>
+      <c r="AH71" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ71">
+        <v>1</v>
+      </c>
+      <c r="AK71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:37">
       <c r="A72" s="1">
         <v>999968</v>
       </c>
@@ -6219,55 +6307,55 @@
       <c r="C72">
         <v>1</v>
       </c>
-      <c r="O72">
+      <c r="P72">
         <v>200001</v>
       </c>
-      <c r="R72">
-        <v>2</v>
-      </c>
       <c r="S72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T72">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U72">
         <v>1</v>
       </c>
       <c r="V72">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W72">
         <v>0.5</v>
       </c>
-      <c r="Y72">
-        <v>100</v>
-      </c>
-      <c r="AA72">
+      <c r="X72">
+        <v>0.5</v>
+      </c>
+      <c r="Z72">
+        <v>100</v>
+      </c>
+      <c r="AB72">
         <v>35</v>
       </c>
-      <c r="AB72">
-        <v>1</v>
-      </c>
       <c r="AC72">
         <v>1</v>
       </c>
-      <c r="AD72" s="1">
+      <c r="AD72">
+        <v>1</v>
+      </c>
+      <c r="AE72" s="1">
         <v>999968</v>
       </c>
-      <c r="AE72" s="2"/>
       <c r="AF72" s="2"/>
-      <c r="AG72" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI72">
-        <v>1</v>
-      </c>
-      <c r="AJ72" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" spans="1:36">
+      <c r="AG72" s="2"/>
+      <c r="AH72" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ72">
+        <v>1</v>
+      </c>
+      <c r="AK72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:37">
       <c r="A73" s="1">
         <v>999969</v>
       </c>
@@ -6275,55 +6363,55 @@
       <c r="C73">
         <v>1</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>200001</v>
       </c>
-      <c r="R73">
-        <v>2</v>
-      </c>
       <c r="S73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U73">
         <v>1</v>
       </c>
       <c r="V73">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W73">
         <v>0.5</v>
       </c>
-      <c r="Y73">
-        <v>100</v>
-      </c>
-      <c r="AA73">
+      <c r="X73">
+        <v>0.5</v>
+      </c>
+      <c r="Z73">
+        <v>100</v>
+      </c>
+      <c r="AB73">
         <v>35</v>
       </c>
-      <c r="AB73">
-        <v>1</v>
-      </c>
       <c r="AC73">
         <v>1</v>
       </c>
-      <c r="AD73" s="1">
+      <c r="AD73">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="1">
         <v>999969</v>
       </c>
-      <c r="AE73" s="2"/>
       <c r="AF73" s="2"/>
-      <c r="AG73" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI73">
-        <v>1</v>
-      </c>
-      <c r="AJ73" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" spans="1:36">
+      <c r="AG73" s="2"/>
+      <c r="AH73" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ73">
+        <v>1</v>
+      </c>
+      <c r="AK73" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:37">
       <c r="A74" s="1">
         <v>999970</v>
       </c>
@@ -6331,55 +6419,55 @@
       <c r="C74">
         <v>1</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>200001</v>
       </c>
-      <c r="R74">
-        <v>2</v>
-      </c>
       <c r="S74">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U74">
         <v>1</v>
       </c>
       <c r="V74">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W74">
         <v>0.5</v>
       </c>
-      <c r="Y74">
-        <v>100</v>
-      </c>
-      <c r="AA74">
+      <c r="X74">
+        <v>0.5</v>
+      </c>
+      <c r="Z74">
+        <v>100</v>
+      </c>
+      <c r="AB74">
         <v>35</v>
       </c>
-      <c r="AB74">
-        <v>1</v>
-      </c>
       <c r="AC74">
         <v>1</v>
       </c>
-      <c r="AD74" s="1">
+      <c r="AD74">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="1">
         <v>999970</v>
       </c>
-      <c r="AE74" s="2"/>
       <c r="AF74" s="2"/>
-      <c r="AG74" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI74">
-        <v>1</v>
-      </c>
-      <c r="AJ74" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:36">
+      <c r="AG74" s="2"/>
+      <c r="AH74" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ74">
+        <v>1</v>
+      </c>
+      <c r="AK74" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:37">
       <c r="A75" s="1">
         <v>999971</v>
       </c>
@@ -6387,55 +6475,55 @@
       <c r="C75">
         <v>1</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>200001</v>
       </c>
-      <c r="R75">
-        <v>2</v>
-      </c>
       <c r="S75">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U75">
         <v>1</v>
       </c>
       <c r="V75">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W75">
         <v>0.5</v>
       </c>
-      <c r="Y75">
-        <v>100</v>
-      </c>
-      <c r="AA75">
+      <c r="X75">
+        <v>0.5</v>
+      </c>
+      <c r="Z75">
+        <v>100</v>
+      </c>
+      <c r="AB75">
         <v>35</v>
       </c>
-      <c r="AB75">
-        <v>1</v>
-      </c>
       <c r="AC75">
         <v>1</v>
       </c>
-      <c r="AD75" s="1">
+      <c r="AD75">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="1">
         <v>999971</v>
       </c>
-      <c r="AE75" s="2"/>
       <c r="AF75" s="2"/>
-      <c r="AG75" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI75">
-        <v>1</v>
-      </c>
-      <c r="AJ75" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" spans="1:36">
+      <c r="AG75" s="2"/>
+      <c r="AH75" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ75">
+        <v>1</v>
+      </c>
+      <c r="AK75" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:37">
       <c r="A76" s="1">
         <v>999972</v>
       </c>
@@ -6443,55 +6531,55 @@
       <c r="C76">
         <v>1</v>
       </c>
-      <c r="O76">
+      <c r="P76">
         <v>200001</v>
       </c>
-      <c r="R76">
-        <v>2</v>
-      </c>
       <c r="S76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T76">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U76">
         <v>1</v>
       </c>
       <c r="V76">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W76">
         <v>0.5</v>
       </c>
-      <c r="Y76">
-        <v>100</v>
-      </c>
-      <c r="AA76">
+      <c r="X76">
+        <v>0.5</v>
+      </c>
+      <c r="Z76">
+        <v>100</v>
+      </c>
+      <c r="AB76">
         <v>35</v>
       </c>
-      <c r="AB76">
-        <v>1</v>
-      </c>
       <c r="AC76">
         <v>1</v>
       </c>
-      <c r="AD76" s="1">
+      <c r="AD76">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="1">
         <v>999972</v>
       </c>
-      <c r="AE76" s="2"/>
       <c r="AF76" s="2"/>
-      <c r="AG76" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI76">
-        <v>1</v>
-      </c>
-      <c r="AJ76" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" spans="1:36">
+      <c r="AG76" s="2"/>
+      <c r="AH76" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ76">
+        <v>1</v>
+      </c>
+      <c r="AK76" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="1:37">
       <c r="A77" s="1">
         <v>999973</v>
       </c>
@@ -6499,55 +6587,55 @@
       <c r="C77">
         <v>1</v>
       </c>
-      <c r="O77">
+      <c r="P77">
         <v>200001</v>
       </c>
-      <c r="R77">
-        <v>2</v>
-      </c>
       <c r="S77">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U77">
         <v>1</v>
       </c>
       <c r="V77">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W77">
         <v>0.5</v>
       </c>
-      <c r="Y77">
-        <v>100</v>
-      </c>
-      <c r="AA77">
+      <c r="X77">
+        <v>0.5</v>
+      </c>
+      <c r="Z77">
+        <v>100</v>
+      </c>
+      <c r="AB77">
         <v>35</v>
       </c>
-      <c r="AB77">
-        <v>1</v>
-      </c>
       <c r="AC77">
         <v>1</v>
       </c>
-      <c r="AD77" s="1">
+      <c r="AD77">
+        <v>1</v>
+      </c>
+      <c r="AE77" s="1">
         <v>999973</v>
       </c>
-      <c r="AE77" s="2"/>
       <c r="AF77" s="2"/>
-      <c r="AG77" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI77">
-        <v>1</v>
-      </c>
-      <c r="AJ77" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="78" customFormat="1" spans="1:36">
+      <c r="AG77" s="2"/>
+      <c r="AH77" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ77">
+        <v>1</v>
+      </c>
+      <c r="AK77" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="1:37">
       <c r="A78" s="1">
         <v>999974</v>
       </c>
@@ -6555,55 +6643,55 @@
       <c r="C78">
         <v>1</v>
       </c>
-      <c r="O78">
+      <c r="P78">
         <v>200001</v>
       </c>
-      <c r="R78">
-        <v>2</v>
-      </c>
       <c r="S78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T78">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U78">
         <v>1</v>
       </c>
       <c r="V78">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W78">
         <v>0.5</v>
       </c>
-      <c r="Y78">
-        <v>100</v>
-      </c>
-      <c r="AA78">
+      <c r="X78">
+        <v>0.5</v>
+      </c>
+      <c r="Z78">
+        <v>100</v>
+      </c>
+      <c r="AB78">
         <v>35</v>
       </c>
-      <c r="AB78">
-        <v>1</v>
-      </c>
       <c r="AC78">
         <v>1</v>
       </c>
-      <c r="AD78" s="1">
+      <c r="AD78">
+        <v>1</v>
+      </c>
+      <c r="AE78" s="1">
         <v>999974</v>
       </c>
-      <c r="AE78" s="2"/>
       <c r="AF78" s="2"/>
-      <c r="AG78" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI78">
-        <v>1</v>
-      </c>
-      <c r="AJ78" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="79" customFormat="1" spans="1:36">
+      <c r="AG78" s="2"/>
+      <c r="AH78" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ78">
+        <v>1</v>
+      </c>
+      <c r="AK78" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:37">
       <c r="A79" s="1">
         <v>999975</v>
       </c>
@@ -6611,55 +6699,55 @@
       <c r="C79">
         <v>1</v>
       </c>
-      <c r="O79">
+      <c r="P79">
         <v>200001</v>
       </c>
-      <c r="R79">
-        <v>2</v>
-      </c>
       <c r="S79">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T79">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U79">
         <v>1</v>
       </c>
       <c r="V79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W79">
         <v>0.5</v>
       </c>
-      <c r="Y79">
-        <v>100</v>
-      </c>
-      <c r="AA79">
+      <c r="X79">
+        <v>0.5</v>
+      </c>
+      <c r="Z79">
+        <v>100</v>
+      </c>
+      <c r="AB79">
         <v>35</v>
       </c>
-      <c r="AB79">
-        <v>1</v>
-      </c>
       <c r="AC79">
         <v>1</v>
       </c>
-      <c r="AD79" s="1">
+      <c r="AD79">
+        <v>1</v>
+      </c>
+      <c r="AE79" s="1">
         <v>999975</v>
       </c>
-      <c r="AE79" s="2"/>
       <c r="AF79" s="2"/>
-      <c r="AG79" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI79">
-        <v>1</v>
-      </c>
-      <c r="AJ79" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="80" customFormat="1" spans="1:36">
+      <c r="AG79" s="2"/>
+      <c r="AH79" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ79">
+        <v>1</v>
+      </c>
+      <c r="AK79" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" spans="1:37">
       <c r="A80" s="1">
         <v>999976</v>
       </c>
@@ -6667,55 +6755,55 @@
       <c r="C80">
         <v>1</v>
       </c>
-      <c r="O80">
+      <c r="P80">
         <v>200001</v>
       </c>
-      <c r="R80">
-        <v>2</v>
-      </c>
       <c r="S80">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T80">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U80">
         <v>1</v>
       </c>
       <c r="V80">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W80">
         <v>0.5</v>
       </c>
-      <c r="Y80">
-        <v>100</v>
-      </c>
-      <c r="AA80">
+      <c r="X80">
+        <v>0.5</v>
+      </c>
+      <c r="Z80">
+        <v>100</v>
+      </c>
+      <c r="AB80">
         <v>35</v>
       </c>
-      <c r="AB80">
-        <v>1</v>
-      </c>
       <c r="AC80">
         <v>1</v>
       </c>
-      <c r="AD80" s="1">
+      <c r="AD80">
+        <v>1</v>
+      </c>
+      <c r="AE80" s="1">
         <v>999976</v>
       </c>
-      <c r="AE80" s="2"/>
       <c r="AF80" s="2"/>
-      <c r="AG80" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI80">
-        <v>1</v>
-      </c>
-      <c r="AJ80" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" spans="1:36">
+      <c r="AG80" s="2"/>
+      <c r="AH80" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ80">
+        <v>1</v>
+      </c>
+      <c r="AK80" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:37">
       <c r="A81" s="1">
         <v>999977</v>
       </c>
@@ -6723,55 +6811,55 @@
       <c r="C81">
         <v>1</v>
       </c>
-      <c r="O81">
+      <c r="P81">
         <v>200001</v>
       </c>
-      <c r="R81">
-        <v>2</v>
-      </c>
       <c r="S81">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T81">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U81">
         <v>1</v>
       </c>
       <c r="V81">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W81">
         <v>0.5</v>
       </c>
-      <c r="Y81">
-        <v>100</v>
-      </c>
-      <c r="AA81">
+      <c r="X81">
+        <v>0.5</v>
+      </c>
+      <c r="Z81">
+        <v>100</v>
+      </c>
+      <c r="AB81">
         <v>35</v>
       </c>
-      <c r="AB81">
-        <v>1</v>
-      </c>
       <c r="AC81">
         <v>1</v>
       </c>
-      <c r="AD81" s="1">
+      <c r="AD81">
+        <v>1</v>
+      </c>
+      <c r="AE81" s="1">
         <v>999977</v>
       </c>
-      <c r="AE81" s="2"/>
       <c r="AF81" s="2"/>
-      <c r="AG81" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI81">
-        <v>1</v>
-      </c>
-      <c r="AJ81" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:36">
+      <c r="AG81" s="2"/>
+      <c r="AH81" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ81">
+        <v>1</v>
+      </c>
+      <c r="AK81" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:37">
       <c r="A82" s="1">
         <v>999978</v>
       </c>
@@ -6779,55 +6867,55 @@
       <c r="C82">
         <v>1</v>
       </c>
-      <c r="O82">
+      <c r="P82">
         <v>200001</v>
       </c>
-      <c r="R82">
-        <v>2</v>
-      </c>
       <c r="S82">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T82">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U82">
         <v>1</v>
       </c>
       <c r="V82">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W82">
         <v>0.5</v>
       </c>
-      <c r="Y82">
-        <v>100</v>
-      </c>
-      <c r="AA82">
+      <c r="X82">
+        <v>0.5</v>
+      </c>
+      <c r="Z82">
+        <v>100</v>
+      </c>
+      <c r="AB82">
         <v>35</v>
       </c>
-      <c r="AB82">
-        <v>1</v>
-      </c>
       <c r="AC82">
         <v>1</v>
       </c>
-      <c r="AD82" s="1">
+      <c r="AD82">
+        <v>1</v>
+      </c>
+      <c r="AE82" s="1">
         <v>999978</v>
       </c>
-      <c r="AE82" s="2"/>
       <c r="AF82" s="2"/>
-      <c r="AG82" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI82">
-        <v>1</v>
-      </c>
-      <c r="AJ82" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" spans="1:36">
+      <c r="AG82" s="2"/>
+      <c r="AH82" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ82">
+        <v>1</v>
+      </c>
+      <c r="AK82" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:37">
       <c r="A83" s="1">
         <v>999979</v>
       </c>
@@ -6835,55 +6923,55 @@
       <c r="C83">
         <v>1</v>
       </c>
-      <c r="O83">
+      <c r="P83">
         <v>200001</v>
       </c>
-      <c r="R83">
-        <v>2</v>
-      </c>
       <c r="S83">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T83">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U83">
         <v>1</v>
       </c>
       <c r="V83">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W83">
         <v>0.5</v>
       </c>
-      <c r="Y83">
-        <v>100</v>
-      </c>
-      <c r="AA83">
+      <c r="X83">
+        <v>0.5</v>
+      </c>
+      <c r="Z83">
+        <v>100</v>
+      </c>
+      <c r="AB83">
         <v>35</v>
       </c>
-      <c r="AB83">
-        <v>1</v>
-      </c>
       <c r="AC83">
         <v>1</v>
       </c>
-      <c r="AD83" s="1">
+      <c r="AD83">
+        <v>1</v>
+      </c>
+      <c r="AE83" s="1">
         <v>999979</v>
       </c>
-      <c r="AE83" s="2"/>
       <c r="AF83" s="2"/>
-      <c r="AG83" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI83">
-        <v>1</v>
-      </c>
-      <c r="AJ83" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:36">
+      <c r="AG83" s="2"/>
+      <c r="AH83" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ83">
+        <v>1</v>
+      </c>
+      <c r="AK83" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:37">
       <c r="A84" s="1">
         <v>999980</v>
       </c>
@@ -6891,55 +6979,55 @@
       <c r="C84">
         <v>1</v>
       </c>
-      <c r="O84">
+      <c r="P84">
         <v>200001</v>
       </c>
-      <c r="R84">
-        <v>2</v>
-      </c>
       <c r="S84">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T84">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U84">
         <v>1</v>
       </c>
       <c r="V84">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W84">
         <v>0.5</v>
       </c>
-      <c r="Y84">
-        <v>100</v>
-      </c>
-      <c r="AA84">
+      <c r="X84">
+        <v>0.5</v>
+      </c>
+      <c r="Z84">
+        <v>100</v>
+      </c>
+      <c r="AB84">
         <v>35</v>
       </c>
-      <c r="AB84">
-        <v>1</v>
-      </c>
       <c r="AC84">
         <v>1</v>
       </c>
-      <c r="AD84" s="1">
+      <c r="AD84">
+        <v>1</v>
+      </c>
+      <c r="AE84" s="1">
         <v>999980</v>
       </c>
-      <c r="AE84" s="2"/>
       <c r="AF84" s="2"/>
-      <c r="AG84" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI84">
-        <v>1</v>
-      </c>
-      <c r="AJ84" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="1:36">
+      <c r="AG84" s="2"/>
+      <c r="AH84" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ84">
+        <v>1</v>
+      </c>
+      <c r="AK84" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:37">
       <c r="A85" s="1">
         <v>999981</v>
       </c>
@@ -6947,1006 +7035,1006 @@
       <c r="C85">
         <v>1</v>
       </c>
-      <c r="O85">
+      <c r="P85">
         <v>200001</v>
       </c>
-      <c r="R85">
-        <v>2</v>
-      </c>
       <c r="S85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T85">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U85">
         <v>1</v>
       </c>
       <c r="V85">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W85">
         <v>0.5</v>
       </c>
-      <c r="Y85">
-        <v>100</v>
-      </c>
-      <c r="AA85">
+      <c r="X85">
+        <v>0.5</v>
+      </c>
+      <c r="Z85">
+        <v>100</v>
+      </c>
+      <c r="AB85">
         <v>35</v>
       </c>
-      <c r="AB85">
-        <v>1</v>
-      </c>
       <c r="AC85">
         <v>1</v>
       </c>
-      <c r="AD85" s="1">
+      <c r="AD85">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="1">
         <v>999981</v>
       </c>
-      <c r="AE85" s="2"/>
       <c r="AF85" s="2"/>
-      <c r="AG85" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI85">
-        <v>1</v>
-      </c>
-      <c r="AJ85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="86" customFormat="1" spans="1:36">
+      <c r="AG85" s="2"/>
+      <c r="AH85" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ85">
+        <v>1</v>
+      </c>
+      <c r="AK85" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:37">
       <c r="A86">
         <v>999982</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
-      <c r="O86">
+      <c r="P86">
         <v>200001</v>
       </c>
-      <c r="R86">
-        <v>2</v>
-      </c>
       <c r="S86">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T86">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U86">
         <v>1</v>
       </c>
       <c r="V86">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W86">
         <v>0.5</v>
       </c>
-      <c r="Y86">
-        <v>100</v>
-      </c>
-      <c r="AA86">
+      <c r="X86">
+        <v>0.5</v>
+      </c>
+      <c r="Z86">
+        <v>100</v>
+      </c>
+      <c r="AB86">
         <v>35</v>
       </c>
-      <c r="AB86">
-        <v>1</v>
-      </c>
       <c r="AC86">
         <v>1</v>
       </c>
       <c r="AD86">
+        <v>1</v>
+      </c>
+      <c r="AE86">
         <v>999982</v>
       </c>
-      <c r="AG86" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI86">
-        <v>1</v>
-      </c>
-      <c r="AJ86" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="87" customFormat="1" spans="1:36">
+      <c r="AH86" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ86">
+        <v>1</v>
+      </c>
+      <c r="AK86" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:37">
       <c r="A87">
         <v>999983</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
-      <c r="O87">
+      <c r="P87">
         <v>200001</v>
       </c>
-      <c r="R87">
-        <v>2</v>
-      </c>
       <c r="S87">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T87">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U87">
         <v>1</v>
       </c>
       <c r="V87">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W87">
         <v>0.5</v>
       </c>
-      <c r="Y87">
-        <v>100</v>
-      </c>
-      <c r="AA87">
+      <c r="X87">
+        <v>0.5</v>
+      </c>
+      <c r="Z87">
+        <v>100</v>
+      </c>
+      <c r="AB87">
         <v>35</v>
       </c>
-      <c r="AB87">
-        <v>1</v>
-      </c>
       <c r="AC87">
         <v>1</v>
       </c>
       <c r="AD87">
+        <v>1</v>
+      </c>
+      <c r="AE87">
         <v>999983</v>
       </c>
-      <c r="AG87" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI87">
-        <v>1</v>
-      </c>
-      <c r="AJ87" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" spans="1:36">
+      <c r="AH87" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ87">
+        <v>1</v>
+      </c>
+      <c r="AK87" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:37">
       <c r="A88">
         <v>999984</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
-      <c r="O88">
+      <c r="P88">
         <v>200001</v>
       </c>
-      <c r="R88">
-        <v>2</v>
-      </c>
       <c r="S88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T88">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U88">
         <v>1</v>
       </c>
       <c r="V88">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W88">
         <v>0.5</v>
       </c>
-      <c r="Y88">
-        <v>100</v>
-      </c>
-      <c r="AA88">
+      <c r="X88">
+        <v>0.5</v>
+      </c>
+      <c r="Z88">
+        <v>100</v>
+      </c>
+      <c r="AB88">
         <v>35</v>
       </c>
-      <c r="AB88">
-        <v>1</v>
-      </c>
       <c r="AC88">
         <v>1</v>
       </c>
       <c r="AD88">
+        <v>1</v>
+      </c>
+      <c r="AE88">
         <v>999984</v>
       </c>
-      <c r="AG88" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI88">
-        <v>1</v>
-      </c>
-      <c r="AJ88" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="89" customFormat="1" spans="1:36">
+      <c r="AH88" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ88">
+        <v>1</v>
+      </c>
+      <c r="AK88" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:37">
       <c r="A89">
         <v>999985</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
-      <c r="O89">
+      <c r="P89">
         <v>200001</v>
       </c>
-      <c r="R89">
-        <v>2</v>
-      </c>
       <c r="S89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T89">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U89">
         <v>1</v>
       </c>
       <c r="V89">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W89">
         <v>0.5</v>
       </c>
-      <c r="Y89">
-        <v>100</v>
-      </c>
-      <c r="AA89">
+      <c r="X89">
+        <v>0.5</v>
+      </c>
+      <c r="Z89">
+        <v>100</v>
+      </c>
+      <c r="AB89">
         <v>35</v>
       </c>
-      <c r="AB89">
-        <v>1</v>
-      </c>
       <c r="AC89">
         <v>1</v>
       </c>
       <c r="AD89">
+        <v>1</v>
+      </c>
+      <c r="AE89">
         <v>999985</v>
       </c>
-      <c r="AG89" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI89">
-        <v>1</v>
-      </c>
-      <c r="AJ89" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:36">
+      <c r="AH89" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ89">
+        <v>1</v>
+      </c>
+      <c r="AK89" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:37">
       <c r="A90">
         <v>999986</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
-      <c r="O90">
+      <c r="P90">
         <v>200001</v>
       </c>
-      <c r="R90">
-        <v>2</v>
-      </c>
       <c r="S90">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U90">
         <v>1</v>
       </c>
       <c r="V90">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W90">
         <v>0.5</v>
       </c>
-      <c r="Y90">
-        <v>100</v>
-      </c>
-      <c r="AA90">
+      <c r="X90">
+        <v>0.5</v>
+      </c>
+      <c r="Z90">
+        <v>100</v>
+      </c>
+      <c r="AB90">
         <v>35</v>
       </c>
-      <c r="AB90">
-        <v>1</v>
-      </c>
       <c r="AC90">
         <v>1</v>
       </c>
       <c r="AD90">
+        <v>1</v>
+      </c>
+      <c r="AE90">
         <v>999986</v>
       </c>
-      <c r="AG90" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI90">
-        <v>1</v>
-      </c>
-      <c r="AJ90" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:36">
+      <c r="AH90" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ90">
+        <v>1</v>
+      </c>
+      <c r="AK90" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:37">
       <c r="A91">
         <v>999987</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
-      <c r="O91">
+      <c r="P91">
         <v>200001</v>
       </c>
-      <c r="R91">
-        <v>2</v>
-      </c>
       <c r="S91">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T91">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U91">
         <v>1</v>
       </c>
       <c r="V91">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W91">
         <v>0.5</v>
       </c>
-      <c r="Y91">
-        <v>100</v>
-      </c>
-      <c r="AA91">
+      <c r="X91">
+        <v>0.5</v>
+      </c>
+      <c r="Z91">
+        <v>100</v>
+      </c>
+      <c r="AB91">
         <v>35</v>
       </c>
-      <c r="AB91">
-        <v>1</v>
-      </c>
       <c r="AC91">
         <v>1</v>
       </c>
       <c r="AD91">
+        <v>1</v>
+      </c>
+      <c r="AE91">
         <v>999987</v>
       </c>
-      <c r="AG91" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI91">
-        <v>1</v>
-      </c>
-      <c r="AJ91" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="92" customFormat="1" spans="1:36">
+      <c r="AH91" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ91">
+        <v>1</v>
+      </c>
+      <c r="AK91" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:37">
       <c r="A92">
         <v>999988</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
-      <c r="O92">
+      <c r="P92">
         <v>200001</v>
       </c>
-      <c r="R92">
-        <v>2</v>
-      </c>
       <c r="S92">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T92">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U92">
         <v>1</v>
       </c>
       <c r="V92">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W92">
         <v>0.5</v>
       </c>
-      <c r="Y92">
-        <v>100</v>
-      </c>
-      <c r="AA92">
+      <c r="X92">
+        <v>0.5</v>
+      </c>
+      <c r="Z92">
+        <v>100</v>
+      </c>
+      <c r="AB92">
         <v>35</v>
       </c>
-      <c r="AB92">
-        <v>1</v>
-      </c>
       <c r="AC92">
         <v>1</v>
       </c>
       <c r="AD92">
+        <v>1</v>
+      </c>
+      <c r="AE92">
         <v>999988</v>
       </c>
-      <c r="AG92" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI92">
-        <v>1</v>
-      </c>
-      <c r="AJ92" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:36">
+      <c r="AH92" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ92">
+        <v>1</v>
+      </c>
+      <c r="AK92" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:37">
       <c r="A93">
         <v>999989</v>
       </c>
       <c r="C93">
         <v>1</v>
       </c>
-      <c r="O93">
+      <c r="P93">
         <v>200001</v>
       </c>
-      <c r="R93">
-        <v>2</v>
-      </c>
       <c r="S93">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T93">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U93">
         <v>1</v>
       </c>
       <c r="V93">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W93">
         <v>0.5</v>
       </c>
-      <c r="Y93">
-        <v>100</v>
-      </c>
-      <c r="AA93">
+      <c r="X93">
+        <v>0.5</v>
+      </c>
+      <c r="Z93">
+        <v>100</v>
+      </c>
+      <c r="AB93">
         <v>35</v>
       </c>
-      <c r="AB93">
-        <v>1</v>
-      </c>
       <c r="AC93">
         <v>1</v>
       </c>
       <c r="AD93">
+        <v>1</v>
+      </c>
+      <c r="AE93">
         <v>999989</v>
       </c>
-      <c r="AG93" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI93">
-        <v>1</v>
-      </c>
-      <c r="AJ93" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="94" customFormat="1" spans="1:36">
+      <c r="AH93" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ93">
+        <v>1</v>
+      </c>
+      <c r="AK93" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:37">
       <c r="A94">
         <v>999990</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
-      <c r="O94">
+      <c r="P94">
         <v>200001</v>
       </c>
-      <c r="R94">
-        <v>2</v>
-      </c>
       <c r="S94">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T94">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U94">
         <v>1</v>
       </c>
       <c r="V94">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W94">
         <v>0.5</v>
       </c>
-      <c r="Y94">
-        <v>100</v>
-      </c>
-      <c r="AA94">
+      <c r="X94">
+        <v>0.5</v>
+      </c>
+      <c r="Z94">
+        <v>100</v>
+      </c>
+      <c r="AB94">
         <v>35</v>
       </c>
-      <c r="AB94">
-        <v>1</v>
-      </c>
       <c r="AC94">
         <v>1</v>
       </c>
       <c r="AD94">
+        <v>1</v>
+      </c>
+      <c r="AE94">
         <v>999990</v>
       </c>
-      <c r="AG94" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI94">
-        <v>1</v>
-      </c>
-      <c r="AJ94" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="95" customFormat="1" spans="1:36">
+      <c r="AH94" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ94">
+        <v>1</v>
+      </c>
+      <c r="AK94" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:37">
       <c r="A95">
         <v>999991</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
-      <c r="O95">
+      <c r="P95">
         <v>200001</v>
       </c>
-      <c r="R95">
-        <v>2</v>
-      </c>
       <c r="S95">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T95">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U95">
         <v>1</v>
       </c>
       <c r="V95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W95">
         <v>0.5</v>
       </c>
-      <c r="Y95">
-        <v>100</v>
-      </c>
-      <c r="AA95">
+      <c r="X95">
+        <v>0.5</v>
+      </c>
+      <c r="Z95">
+        <v>100</v>
+      </c>
+      <c r="AB95">
         <v>35</v>
       </c>
-      <c r="AB95">
-        <v>1</v>
-      </c>
       <c r="AC95">
         <v>1</v>
       </c>
       <c r="AD95">
+        <v>1</v>
+      </c>
+      <c r="AE95">
         <v>999991</v>
       </c>
-      <c r="AG95" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI95">
-        <v>1</v>
-      </c>
-      <c r="AJ95" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="96" customFormat="1" spans="1:36">
+      <c r="AH95" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ95">
+        <v>1</v>
+      </c>
+      <c r="AK95" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:37">
       <c r="A96">
         <v>999992</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
-      <c r="O96">
+      <c r="P96">
         <v>200001</v>
       </c>
-      <c r="R96">
-        <v>2</v>
-      </c>
       <c r="S96">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T96">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U96">
         <v>1</v>
       </c>
       <c r="V96">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W96">
         <v>0.5</v>
       </c>
-      <c r="Y96">
-        <v>100</v>
-      </c>
-      <c r="AA96">
+      <c r="X96">
+        <v>0.5</v>
+      </c>
+      <c r="Z96">
+        <v>100</v>
+      </c>
+      <c r="AB96">
         <v>35</v>
       </c>
-      <c r="AB96">
-        <v>1</v>
-      </c>
       <c r="AC96">
         <v>1</v>
       </c>
       <c r="AD96">
+        <v>1</v>
+      </c>
+      <c r="AE96">
         <v>999992</v>
       </c>
-      <c r="AG96" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI96">
-        <v>1</v>
-      </c>
-      <c r="AJ96" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="97" customFormat="1" spans="1:36">
+      <c r="AH96" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ96">
+        <v>1</v>
+      </c>
+      <c r="AK96" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:37">
       <c r="A97">
         <v>999993</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
-      <c r="O97">
+      <c r="P97">
         <v>200001</v>
       </c>
-      <c r="R97">
-        <v>2</v>
-      </c>
       <c r="S97">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T97">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U97">
         <v>1</v>
       </c>
       <c r="V97">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W97">
         <v>0.5</v>
       </c>
-      <c r="Y97">
-        <v>100</v>
-      </c>
-      <c r="AA97">
+      <c r="X97">
+        <v>0.5</v>
+      </c>
+      <c r="Z97">
+        <v>100</v>
+      </c>
+      <c r="AB97">
         <v>35</v>
       </c>
-      <c r="AB97">
-        <v>1</v>
-      </c>
       <c r="AC97">
         <v>1</v>
       </c>
       <c r="AD97">
+        <v>1</v>
+      </c>
+      <c r="AE97">
         <v>999993</v>
       </c>
-      <c r="AG97" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI97">
-        <v>1</v>
-      </c>
-      <c r="AJ97" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" customFormat="1" spans="1:36">
+      <c r="AH97" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ97">
+        <v>1</v>
+      </c>
+      <c r="AK97" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" spans="1:37">
       <c r="A98">
         <v>999994</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
-      <c r="O98">
+      <c r="P98">
         <v>200001</v>
       </c>
-      <c r="R98">
-        <v>2</v>
-      </c>
       <c r="S98">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T98">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U98">
         <v>1</v>
       </c>
       <c r="V98">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W98">
         <v>0.5</v>
       </c>
-      <c r="Y98">
-        <v>100</v>
-      </c>
-      <c r="AA98">
+      <c r="X98">
+        <v>0.5</v>
+      </c>
+      <c r="Z98">
+        <v>100</v>
+      </c>
+      <c r="AB98">
         <v>35</v>
       </c>
-      <c r="AB98">
-        <v>1</v>
-      </c>
       <c r="AC98">
         <v>1</v>
       </c>
       <c r="AD98">
+        <v>1</v>
+      </c>
+      <c r="AE98">
         <v>999994</v>
       </c>
-      <c r="AG98" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI98">
-        <v>1</v>
-      </c>
-      <c r="AJ98" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="99" customFormat="1" spans="1:36">
+      <c r="AH98" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ98">
+        <v>1</v>
+      </c>
+      <c r="AK98" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" spans="1:37">
       <c r="A99">
         <v>999995</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
-      <c r="O99">
+      <c r="P99">
         <v>200001</v>
       </c>
-      <c r="R99">
-        <v>2</v>
-      </c>
       <c r="S99">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T99">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U99">
         <v>1</v>
       </c>
       <c r="V99">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W99">
         <v>0.5</v>
       </c>
-      <c r="Y99">
-        <v>100</v>
-      </c>
-      <c r="AA99">
+      <c r="X99">
+        <v>0.5</v>
+      </c>
+      <c r="Z99">
+        <v>100</v>
+      </c>
+      <c r="AB99">
         <v>35</v>
       </c>
-      <c r="AB99">
-        <v>1</v>
-      </c>
       <c r="AC99">
         <v>1</v>
       </c>
       <c r="AD99">
+        <v>1</v>
+      </c>
+      <c r="AE99">
         <v>999995</v>
       </c>
-      <c r="AG99" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI99">
-        <v>1</v>
-      </c>
-      <c r="AJ99" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="100" customFormat="1" spans="1:36">
+      <c r="AH99" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ99">
+        <v>1</v>
+      </c>
+      <c r="AK99" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:37">
       <c r="A100">
         <v>999996</v>
       </c>
       <c r="C100">
         <v>1</v>
       </c>
-      <c r="O100">
+      <c r="P100">
         <v>200001</v>
       </c>
-      <c r="R100">
-        <v>2</v>
-      </c>
       <c r="S100">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T100">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U100">
         <v>1</v>
       </c>
       <c r="V100">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W100">
         <v>0.5</v>
       </c>
-      <c r="Y100">
-        <v>100</v>
-      </c>
-      <c r="AA100">
+      <c r="X100">
+        <v>0.5</v>
+      </c>
+      <c r="Z100">
+        <v>100</v>
+      </c>
+      <c r="AB100">
         <v>35</v>
       </c>
-      <c r="AB100">
-        <v>1</v>
-      </c>
       <c r="AC100">
         <v>1</v>
       </c>
       <c r="AD100">
+        <v>1</v>
+      </c>
+      <c r="AE100">
         <v>999996</v>
       </c>
-      <c r="AG100" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI100">
-        <v>1</v>
-      </c>
-      <c r="AJ100" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="101" customFormat="1" spans="1:36">
+      <c r="AH100" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ100">
+        <v>1</v>
+      </c>
+      <c r="AK100" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:37">
       <c r="A101">
         <v>999997</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
-      <c r="O101">
+      <c r="P101">
         <v>200001</v>
       </c>
-      <c r="R101">
-        <v>2</v>
-      </c>
       <c r="S101">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U101">
         <v>1</v>
       </c>
       <c r="V101">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W101">
         <v>0.5</v>
       </c>
-      <c r="Y101">
-        <v>100</v>
-      </c>
-      <c r="AA101">
+      <c r="X101">
+        <v>0.5</v>
+      </c>
+      <c r="Z101">
+        <v>100</v>
+      </c>
+      <c r="AB101">
         <v>35</v>
       </c>
-      <c r="AB101">
-        <v>1</v>
-      </c>
       <c r="AC101">
         <v>1</v>
       </c>
       <c r="AD101">
+        <v>1</v>
+      </c>
+      <c r="AE101">
         <v>999997</v>
       </c>
-      <c r="AG101" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI101">
-        <v>1</v>
-      </c>
-      <c r="AJ101" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:36">
+      <c r="AH101" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ101">
+        <v>1</v>
+      </c>
+      <c r="AK101" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:37">
       <c r="A102">
         <v>999998</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
-      <c r="O102">
+      <c r="P102">
         <v>200001</v>
       </c>
-      <c r="R102">
-        <v>2</v>
-      </c>
       <c r="S102">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T102">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U102">
         <v>1</v>
       </c>
       <c r="V102">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W102">
         <v>0.5</v>
       </c>
-      <c r="Y102">
-        <v>100</v>
-      </c>
-      <c r="AA102">
+      <c r="X102">
+        <v>0.5</v>
+      </c>
+      <c r="Z102">
+        <v>100</v>
+      </c>
+      <c r="AB102">
         <v>35</v>
       </c>
-      <c r="AB102">
-        <v>1</v>
-      </c>
       <c r="AC102">
         <v>1</v>
       </c>
       <c r="AD102">
+        <v>1</v>
+      </c>
+      <c r="AE102">
         <v>999998</v>
       </c>
-      <c r="AG102" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI102">
-        <v>1</v>
-      </c>
-      <c r="AJ102" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="103" customFormat="1" spans="1:36">
+      <c r="AH102" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ102">
+        <v>1</v>
+      </c>
+      <c r="AK102" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:37">
       <c r="A103">
         <v>999999</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
-      <c r="O103">
+      <c r="P103">
         <v>200001</v>
       </c>
-      <c r="R103">
-        <v>2</v>
-      </c>
       <c r="S103">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T103">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U103">
         <v>1</v>
       </c>
       <c r="V103">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W103">
         <v>0.5</v>
       </c>
-      <c r="Y103">
-        <v>100</v>
-      </c>
-      <c r="AA103">
+      <c r="X103">
+        <v>0.5</v>
+      </c>
+      <c r="Z103">
+        <v>100</v>
+      </c>
+      <c r="AB103">
         <v>35</v>
       </c>
-      <c r="AB103">
-        <v>1</v>
-      </c>
       <c r="AC103">
         <v>1</v>
       </c>
       <c r="AD103">
+        <v>1</v>
+      </c>
+      <c r="AE103">
         <v>999999</v>
       </c>
-      <c r="AG103" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI103">
-        <v>1</v>
-      </c>
-      <c r="AJ103" t="s">
-        <v>145</v>
+      <c r="AH103" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ103">
+        <v>1</v>
+      </c>
+      <c r="AK103" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1"/>
@@ -7970,7 +8058,7 @@
     <row r="172" ht="12" customHeight="1"/>
     <row r="173" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AJ103" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK103" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -10,7 +10,7 @@
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AK$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="157">
   <si>
     <t>id</t>
   </si>
@@ -110,6 +110,9 @@
     <t>HP</t>
   </si>
   <si>
+    <t>MP</t>
+  </si>
+  <si>
     <t>DR</t>
   </si>
   <si>
@@ -122,6 +125,12 @@
     <t>MSPD</t>
   </si>
   <si>
+    <t>MPR</t>
+  </si>
+  <si>
+    <t>MPF</t>
+  </si>
+  <si>
     <t>model_id</t>
   </si>
   <si>
@@ -233,6 +242,9 @@
     <t>生命值</t>
   </si>
   <si>
+    <t>魔力</t>
+  </si>
+  <si>
     <t>护甲</t>
   </si>
   <si>
@@ -245,6 +257,12 @@
     <t>移动速度</t>
   </si>
   <si>
+    <t>魔力回复（百分比）</t>
+  </si>
+  <si>
+    <t>魔力回复(固定值)</t>
+  </si>
+  <si>
     <t>模组ID</t>
   </si>
   <si>
@@ -266,12 +284,15 @@
     <t>备注</t>
   </si>
   <si>
+    <t>Card_Scene_2</t>
+  </si>
+  <si>
+    <t>创建角色-人类</t>
+  </si>
+  <si>
     <t>Card_Scene_1</t>
   </si>
   <si>
-    <t>创建角色-人类</t>
-  </si>
-  <si>
     <t>创建角色-骷髅</t>
   </si>
   <si>
@@ -420,6 +441,9 @@
   </si>
   <si>
     <t>ui_research_44</t>
+  </si>
+  <si>
+    <t>Card_Scene_7</t>
   </si>
   <si>
     <t>哥布林刺客</t>
@@ -1450,7 +1474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK173"/>
+  <dimension ref="A1:AN173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1472,18 +1496,22 @@
     <col min="19" max="19" width="35.875" customWidth="1"/>
     <col min="20" max="20" width="21.5" customWidth="1"/>
     <col min="21" max="22" width="29.625" customWidth="1"/>
-    <col min="23" max="25" width="20.25" customWidth="1"/>
+    <col min="23" max="24" width="20.25" customWidth="1"/>
+    <col min="25" max="25" width="11.125" customWidth="1"/>
     <col min="26" max="27" width="11.75" customWidth="1"/>
-    <col min="28" max="28" width="20.25" customWidth="1"/>
-    <col min="29" max="29" width="8.875" customWidth="1"/>
-    <col min="30" max="31" width="14.75" customWidth="1"/>
-    <col min="32" max="33" width="34" customWidth="1"/>
-    <col min="34" max="35" width="13.75" customWidth="1"/>
-    <col min="36" max="36" width="16" customWidth="1"/>
-    <col min="37" max="37" width="42.875" customWidth="1"/>
+    <col min="28" max="28" width="6.375" customWidth="1"/>
+    <col min="29" max="29" width="7" customWidth="1"/>
+    <col min="30" max="31" width="8.875" customWidth="1"/>
+    <col min="32" max="32" width="19.125" customWidth="1"/>
+    <col min="33" max="33" width="17.25" customWidth="1"/>
+    <col min="34" max="34" width="14.75" customWidth="1"/>
+    <col min="35" max="36" width="34" customWidth="1"/>
+    <col min="37" max="38" width="13.75" customWidth="1"/>
+    <col min="39" max="39" width="16" customWidth="1"/>
+    <col min="40" max="40" width="42.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1577,252 +1605,279 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
       <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
       <c r="AK1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:37">
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH2" t="s">
         <v>40</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AI2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AJ2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="s">
         <v>40</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AM2" t="s">
         <v>40</v>
       </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="AN2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="T3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="V3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="X3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Y3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Z3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AA3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AC3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AE3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>76</v>
       </c>
       <c r="AH3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="AK3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:37">
+        <v>80</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:40">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1841,23 +1896,29 @@
       <c r="Z4">
         <v>1</v>
       </c>
-      <c r="AE4">
-        <v>1</v>
-      </c>
-      <c r="AF4">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ4">
+      <c r="AA4">
+        <v>100</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:37">
+        <v>84</v>
+      </c>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:40">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1876,23 +1937,29 @@
       <c r="Z5">
         <v>1</v>
       </c>
-      <c r="AE5">
-        <v>2</v>
-      </c>
-      <c r="AF5">
-        <v>2</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ5">
+      <c r="AA5">
+        <v>100</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>2</v>
+      </c>
+      <c r="AI5">
         <v>2</v>
       </c>
       <c r="AK5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:37">
+        <v>86</v>
+      </c>
+      <c r="AM5">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:40">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1908,23 +1975,29 @@
       <c r="Z6">
         <v>1</v>
       </c>
-      <c r="AE6">
+      <c r="AA6">
+        <v>100</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
         <v>3</v>
       </c>
-      <c r="AF6">
+      <c r="AI6">
         <v>3</v>
       </c>
-      <c r="AH6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ6">
+      <c r="AK6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM6">
         <v>3</v>
       </c>
-      <c r="AK6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:37">
+      <c r="AN6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:40">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1943,23 +2016,29 @@
       <c r="Z7">
         <v>1</v>
       </c>
-      <c r="AE7">
+      <c r="AA7">
+        <v>100</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
         <v>4</v>
       </c>
-      <c r="AF7">
+      <c r="AI7">
         <v>4</v>
       </c>
-      <c r="AH7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ7">
+      <c r="AK7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM7">
         <v>4</v>
       </c>
-      <c r="AK7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:37">
+      <c r="AN7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:40">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1978,23 +2057,29 @@
       <c r="Z8">
         <v>1</v>
       </c>
-      <c r="AE8">
+      <c r="AA8">
+        <v>100</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
         <v>5</v>
       </c>
-      <c r="AF8">
+      <c r="AI8">
         <v>5</v>
       </c>
-      <c r="AH8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ8">
+      <c r="AK8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM8">
         <v>5</v>
       </c>
-      <c r="AK8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:37">
+      <c r="AN8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:40">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2013,23 +2098,29 @@
       <c r="Z9">
         <v>1</v>
       </c>
-      <c r="AE9">
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
         <v>6</v>
       </c>
-      <c r="AF9">
+      <c r="AI9">
         <v>6</v>
       </c>
-      <c r="AH9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ9">
+      <c r="AK9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM9">
         <v>6</v>
       </c>
-      <c r="AK9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:37">
+      <c r="AN9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:40">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2048,23 +2139,29 @@
       <c r="Z10">
         <v>1</v>
       </c>
-      <c r="AE10">
+      <c r="AA10">
+        <v>100</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
         <v>7</v>
       </c>
-      <c r="AF10">
+      <c r="AI10">
         <v>7</v>
       </c>
-      <c r="AH10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ10">
+      <c r="AK10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AM10">
         <v>7</v>
       </c>
-      <c r="AK10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:37">
+      <c r="AN10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:40">
       <c r="A11">
         <v>1001</v>
       </c>
@@ -2099,38 +2196,38 @@
       <c r="Z11">
         <v>100</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>10</v>
       </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
       <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
         <v>0.2</v>
       </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-      <c r="AF11">
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
         <v>1000001</v>
       </c>
-      <c r="AG11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI11" s="1">
+      <c r="AJ11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL11" s="1">
         <v>300100001</v>
       </c>
-      <c r="AJ11">
+      <c r="AM11">
         <v>1001</v>
       </c>
-      <c r="AK11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:37">
+      <c r="AN11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:40">
       <c r="A12">
         <v>1002</v>
       </c>
@@ -2141,7 +2238,7 @@
         <v>1000001</v>
       </c>
       <c r="I12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -2170,38 +2267,38 @@
       <c r="Z12">
         <v>100</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>10</v>
       </c>
-      <c r="AC12">
-        <v>1</v>
-      </c>
       <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
         <v>0.2</v>
       </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
         <v>1000001</v>
       </c>
-      <c r="AG12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI12" s="1">
+      <c r="AJ12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL12" s="1">
         <v>300100002</v>
       </c>
-      <c r="AJ12">
+      <c r="AM12">
         <v>1002</v>
       </c>
-      <c r="AK12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:37">
+      <c r="AN12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:40">
       <c r="A13">
         <v>1003</v>
       </c>
@@ -2212,7 +2309,7 @@
         <v>1000001</v>
       </c>
       <c r="I13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2241,38 +2338,38 @@
       <c r="Z13">
         <v>100</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>10</v>
       </c>
-      <c r="AC13">
-        <v>1</v>
-      </c>
       <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
         <v>0.2</v>
       </c>
-      <c r="AE13">
-        <v>1</v>
-      </c>
-      <c r="AF13">
+      <c r="AH13">
+        <v>1</v>
+      </c>
+      <c r="AI13">
         <v>1000001</v>
       </c>
-      <c r="AG13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI13" s="1">
+      <c r="AJ13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL13" s="1">
         <v>300100003</v>
       </c>
-      <c r="AJ13">
+      <c r="AM13">
         <v>1003</v>
       </c>
-      <c r="AK13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:37">
+      <c r="AN13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:40">
       <c r="A14">
         <v>1004</v>
       </c>
@@ -2283,7 +2380,7 @@
         <v>1000001</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2312,38 +2409,38 @@
       <c r="Z14">
         <v>100</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>10</v>
       </c>
-      <c r="AC14">
-        <v>1</v>
-      </c>
       <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
         <v>0.2</v>
       </c>
-      <c r="AE14">
-        <v>1</v>
-      </c>
-      <c r="AF14">
+      <c r="AH14">
+        <v>1</v>
+      </c>
+      <c r="AI14">
         <v>1000001</v>
       </c>
-      <c r="AG14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI14" s="1">
+      <c r="AJ14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL14" s="1">
         <v>300100004</v>
       </c>
-      <c r="AJ14">
+      <c r="AM14">
         <v>1004</v>
       </c>
-      <c r="AK14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="1:37">
+      <c r="AN14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1" spans="1:40">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -2360,13 +2457,13 @@
         <v>21010001</v>
       </c>
       <c r="I15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J15">
         <v>2</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P15">
         <v>100001</v>
@@ -2395,38 +2492,38 @@
       <c r="Z15">
         <v>100</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>10</v>
       </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
       <c r="AD15">
         <v>1</v>
       </c>
       <c r="AE15">
-        <v>2</v>
-      </c>
-      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>2</v>
+      </c>
+      <c r="AI15">
         <v>2000001</v>
       </c>
-      <c r="AG15" s="1" t="s">
+      <c r="AJ15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK15" t="s">
         <v>86</v>
       </c>
-      <c r="AH15" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI15">
+      <c r="AL15">
         <v>300200001</v>
       </c>
-      <c r="AJ15">
+      <c r="AM15">
         <v>2001</v>
       </c>
-      <c r="AK15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
+      <c r="AN15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
       <c r="A16">
         <v>2002</v>
       </c>
@@ -2443,19 +2540,19 @@
         <v>21000001</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J16">
         <v>8</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="P16">
         <v>200001</v>
       </c>
       <c r="Q16" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S16">
         <v>2</v>
@@ -2481,38 +2578,38 @@
       <c r="Z16">
         <v>100</v>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <v>10</v>
       </c>
-      <c r="AC16">
-        <v>1</v>
-      </c>
       <c r="AD16">
         <v>1</v>
       </c>
       <c r="AE16">
-        <v>2</v>
-      </c>
-      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>2</v>
+      </c>
+      <c r="AI16">
         <v>2000001</v>
       </c>
-      <c r="AG16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI16">
+      <c r="AJ16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL16">
         <v>300200002</v>
       </c>
-      <c r="AJ16">
+      <c r="AM16">
         <v>2002</v>
       </c>
-      <c r="AK16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
+      <c r="AN16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -2529,19 +2626,19 @@
         <v>21010002</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P17">
         <v>201001</v>
       </c>
       <c r="Q17" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S17">
         <v>2</v>
@@ -2567,38 +2664,38 @@
       <c r="Z17">
         <v>50</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>6</v>
       </c>
-      <c r="AC17">
-        <v>1</v>
-      </c>
       <c r="AD17">
         <v>1</v>
       </c>
       <c r="AE17">
-        <v>2</v>
-      </c>
-      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>2</v>
+      </c>
+      <c r="AI17">
         <v>2000001</v>
       </c>
-      <c r="AG17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI17">
+      <c r="AJ17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL17">
         <v>300200003</v>
       </c>
-      <c r="AJ17">
+      <c r="AM17">
         <v>2003</v>
       </c>
-      <c r="AK17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
+      <c r="AN17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40">
       <c r="A18">
         <v>2004</v>
       </c>
@@ -2615,19 +2712,19 @@
         <v>21010003</v>
       </c>
       <c r="I18" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P18">
         <v>201002</v>
       </c>
       <c r="Q18" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S18">
         <v>2</v>
@@ -2653,38 +2750,38 @@
       <c r="Z18">
         <v>50</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>3</v>
       </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
       <c r="AD18">
         <v>1</v>
       </c>
       <c r="AE18">
-        <v>2</v>
-      </c>
-      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>2</v>
+      </c>
+      <c r="AI18">
         <v>2000001</v>
       </c>
-      <c r="AG18" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI18">
+      <c r="AJ18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL18">
         <v>300200004</v>
       </c>
-      <c r="AJ18">
+      <c r="AM18">
         <v>2004</v>
       </c>
-      <c r="AK18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
+      <c r="AN18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40">
       <c r="A19">
         <v>3001</v>
       </c>
@@ -2695,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="S19">
         <v>2</v>
@@ -2721,41 +2818,41 @@
       <c r="Z19">
         <v>100</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>500</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>0</v>
       </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
       <c r="AD19">
         <v>1</v>
       </c>
       <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
         <v>3</v>
       </c>
-      <c r="AF19">
+      <c r="AI19">
         <v>3000001</v>
       </c>
-      <c r="AG19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI19">
+      <c r="AJ19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL19">
         <v>300300001</v>
       </c>
-      <c r="AJ19">
+      <c r="AM19">
         <v>3001</v>
       </c>
-      <c r="AK19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:37">
+      <c r="AN19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:40">
       <c r="A20">
         <v>3002</v>
       </c>
@@ -2766,10 +2863,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N20" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P20">
         <v>300001</v>
@@ -2801,38 +2898,38 @@
       <c r="Z20">
         <v>100</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>500</v>
       </c>
-      <c r="AC20">
-        <v>1</v>
-      </c>
       <c r="AD20">
         <v>1</v>
       </c>
       <c r="AE20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
         <v>3</v>
       </c>
-      <c r="AF20">
+      <c r="AI20">
         <v>3000001</v>
       </c>
-      <c r="AG20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI20">
+      <c r="AJ20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL20">
         <v>300300002</v>
       </c>
-      <c r="AJ20">
+      <c r="AM20">
         <v>3002</v>
       </c>
-      <c r="AK20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:37">
+      <c r="AN20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:40">
       <c r="A21">
         <v>3003</v>
       </c>
@@ -2843,13 +2940,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N21" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O21">
         <v>1</v>
@@ -2884,38 +2981,38 @@
       <c r="Z21">
         <v>50</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>0</v>
       </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
       <c r="AD21">
         <v>1</v>
       </c>
       <c r="AE21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
         <v>3</v>
       </c>
-      <c r="AF21">
+      <c r="AI21">
         <v>3000001</v>
       </c>
-      <c r="AG21" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI21">
+      <c r="AJ21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL21">
         <v>300300003</v>
       </c>
-      <c r="AJ21">
+      <c r="AM21">
         <v>3003</v>
       </c>
-      <c r="AK21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:37">
+      <c r="AN21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:40">
       <c r="A22">
         <v>3004</v>
       </c>
@@ -2926,13 +3023,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N22" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -2967,38 +3064,38 @@
       <c r="Z22">
         <v>50</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>0</v>
       </c>
-      <c r="AC22">
-        <v>1</v>
-      </c>
       <c r="AD22">
         <v>1</v>
       </c>
       <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
         <v>3</v>
       </c>
-      <c r="AF22">
+      <c r="AI22">
         <v>3000001</v>
       </c>
-      <c r="AG22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI22">
+      <c r="AJ22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL22">
         <v>300300004</v>
       </c>
-      <c r="AJ22">
+      <c r="AM22">
         <v>3004</v>
       </c>
-      <c r="AK22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:37">
+      <c r="AN22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:40">
       <c r="A23">
         <v>4001</v>
       </c>
@@ -3015,13 +3112,13 @@
         <v>41000002</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J23">
         <v>2</v>
       </c>
       <c r="N23" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P23">
         <v>101001</v>
@@ -3050,38 +3147,38 @@
       <c r="Z23">
         <v>100</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>6</v>
       </c>
-      <c r="AC23">
-        <v>1</v>
-      </c>
       <c r="AD23">
         <v>1</v>
       </c>
       <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
         <v>4</v>
       </c>
-      <c r="AF23">
+      <c r="AI23">
         <v>4000001</v>
       </c>
-      <c r="AG23" s="1" t="s">
+      <c r="AJ23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK23" t="s">
         <v>86</v>
       </c>
-      <c r="AH23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI23">
+      <c r="AL23">
         <v>300400001</v>
       </c>
-      <c r="AJ23">
+      <c r="AM23">
         <v>4001</v>
       </c>
-      <c r="AK23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:37">
+      <c r="AN23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:40">
       <c r="A24">
         <v>4002</v>
       </c>
@@ -3095,7 +3192,7 @@
         <v>4000001</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P24">
         <v>500001</v>
@@ -3127,9 +3224,6 @@
       <c r="Z24">
         <v>100</v>
       </c>
-      <c r="AB24">
-        <v>1</v>
-      </c>
       <c r="AC24">
         <v>1</v>
       </c>
@@ -3137,28 +3231,31 @@
         <v>1</v>
       </c>
       <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
         <v>4</v>
       </c>
-      <c r="AF24">
+      <c r="AI24">
         <v>4000001</v>
       </c>
-      <c r="AG24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI24">
+      <c r="AJ24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL24">
         <v>300400002</v>
       </c>
-      <c r="AJ24">
+      <c r="AM24">
         <v>4002</v>
       </c>
-      <c r="AK24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:37">
+      <c r="AN24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:40">
       <c r="A25">
         <v>4003</v>
       </c>
@@ -3172,7 +3269,7 @@
         <v>4000001</v>
       </c>
       <c r="I25" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P25">
         <v>600001</v>
@@ -3204,38 +3301,38 @@
       <c r="Z25">
         <v>100</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>0</v>
       </c>
-      <c r="AC25">
-        <v>1</v>
-      </c>
       <c r="AD25">
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
         <v>4</v>
       </c>
-      <c r="AF25">
+      <c r="AI25">
         <v>4000001</v>
       </c>
-      <c r="AG25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI25">
+      <c r="AJ25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL25">
         <v>300400003</v>
       </c>
-      <c r="AJ25">
+      <c r="AM25">
         <v>4003</v>
       </c>
-      <c r="AK25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:37">
+      <c r="AN25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:40">
       <c r="A26">
         <v>4004</v>
       </c>
@@ -3249,13 +3346,13 @@
         <v>4000001</v>
       </c>
       <c r="I26" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P26">
         <v>202001</v>
       </c>
       <c r="Q26" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="R26">
         <v>30</v>
@@ -3284,38 +3381,38 @@
       <c r="Z26">
         <v>100</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>3</v>
       </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
       <c r="AD26">
         <v>1</v>
       </c>
       <c r="AE26">
+        <v>1</v>
+      </c>
+      <c r="AH26">
         <v>4</v>
       </c>
-      <c r="AF26">
+      <c r="AI26">
         <v>4000001</v>
       </c>
-      <c r="AG26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI26">
+      <c r="AJ26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL26">
         <v>300400004</v>
       </c>
-      <c r="AJ26">
+      <c r="AM26">
         <v>4004</v>
       </c>
-      <c r="AK26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:37">
+      <c r="AN26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:40">
       <c r="A27">
         <v>4005</v>
       </c>
@@ -3329,7 +3426,7 @@
         <v>4000001</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P27">
         <v>500002</v>
@@ -3361,10 +3458,6 @@
       <c r="Z27">
         <v>100</v>
       </c>
-      <c r="AA27"/>
-      <c r="AB27">
-        <v>1</v>
-      </c>
       <c r="AC27">
         <v>1</v>
       </c>
@@ -3372,28 +3465,31 @@
         <v>1</v>
       </c>
       <c r="AE27">
+        <v>1</v>
+      </c>
+      <c r="AH27">
         <v>4</v>
       </c>
-      <c r="AF27">
+      <c r="AI27">
         <v>4000001</v>
       </c>
-      <c r="AG27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI27">
+      <c r="AJ27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL27">
         <v>300400005</v>
       </c>
-      <c r="AJ27">
+      <c r="AM27">
         <v>4005</v>
       </c>
-      <c r="AK27" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:37">
+      <c r="AN27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:40">
       <c r="A28">
         <v>5001</v>
       </c>
@@ -3407,7 +3503,7 @@
         <v>5000001</v>
       </c>
       <c r="I28" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P28">
         <v>101002</v>
@@ -3439,38 +3535,38 @@
       <c r="Z28">
         <v>300</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>3</v>
       </c>
-      <c r="AC28">
-        <v>1</v>
-      </c>
       <c r="AD28">
         <v>1</v>
       </c>
       <c r="AE28">
+        <v>1</v>
+      </c>
+      <c r="AH28">
         <v>5</v>
       </c>
-      <c r="AF28">
+      <c r="AI28">
         <v>5000001</v>
       </c>
-      <c r="AG28" s="1" t="s">
+      <c r="AJ28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK28" t="s">
         <v>86</v>
       </c>
-      <c r="AH28" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI28" s="1">
+      <c r="AL28" s="1">
         <v>300500001</v>
       </c>
-      <c r="AJ28">
+      <c r="AM28">
         <v>5001</v>
       </c>
-      <c r="AK28" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:37">
+      <c r="AN28" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:40">
       <c r="A29">
         <v>5002</v>
       </c>
@@ -3487,7 +3583,7 @@
         <v>51010001</v>
       </c>
       <c r="I29" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J29">
         <v>8</v>
@@ -3496,7 +3592,7 @@
         <v>203001</v>
       </c>
       <c r="Q29" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -3525,38 +3621,38 @@
       <c r="Z29">
         <v>300</v>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <v>10</v>
       </c>
-      <c r="AC29">
-        <v>1</v>
-      </c>
       <c r="AD29">
         <v>1</v>
       </c>
       <c r="AE29">
+        <v>1</v>
+      </c>
+      <c r="AH29">
         <v>5</v>
       </c>
-      <c r="AF29">
+      <c r="AI29">
         <v>5000001</v>
       </c>
-      <c r="AG29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI29" s="1">
+      <c r="AJ29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL29" s="1">
         <v>300500002</v>
       </c>
-      <c r="AJ29">
+      <c r="AM29">
         <v>5002</v>
       </c>
-      <c r="AK29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:37">
+      <c r="AN29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:40">
       <c r="A30">
         <v>5003</v>
       </c>
@@ -3570,7 +3666,7 @@
         <v>5000001</v>
       </c>
       <c r="I30" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P30">
         <v>700001</v>
@@ -3602,38 +3698,38 @@
       <c r="Z30">
         <v>150</v>
       </c>
-      <c r="AB30">
+      <c r="AC30">
         <v>6</v>
       </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
       <c r="AD30">
         <v>1</v>
       </c>
       <c r="AE30">
+        <v>1</v>
+      </c>
+      <c r="AH30">
         <v>5</v>
       </c>
-      <c r="AF30">
+      <c r="AI30">
         <v>5000001</v>
       </c>
-      <c r="AG30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI30" s="1">
+      <c r="AJ30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL30" s="1">
         <v>300500003</v>
       </c>
-      <c r="AJ30">
+      <c r="AM30">
         <v>5003</v>
       </c>
-      <c r="AK30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:37">
+      <c r="AN30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:40">
       <c r="A31">
         <v>5004</v>
       </c>
@@ -3647,7 +3743,7 @@
         <v>5000001</v>
       </c>
       <c r="I31" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="P31">
         <v>700002</v>
@@ -3679,38 +3775,38 @@
       <c r="Z31">
         <v>150</v>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <v>3</v>
       </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
       <c r="AD31">
         <v>1</v>
       </c>
       <c r="AE31">
+        <v>1</v>
+      </c>
+      <c r="AH31">
         <v>5</v>
       </c>
-      <c r="AF31">
+      <c r="AI31">
         <v>5000001</v>
       </c>
-      <c r="AG31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI31" s="1">
+      <c r="AJ31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL31" s="1">
         <v>300500004</v>
       </c>
-      <c r="AJ31">
+      <c r="AM31">
         <v>5004</v>
       </c>
-      <c r="AK31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:37">
+      <c r="AN31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:40">
       <c r="A32">
         <v>6001</v>
       </c>
@@ -3721,13 +3817,13 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G32">
         <v>6000001</v>
       </c>
       <c r="I32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -3759,38 +3855,38 @@
       <c r="Z32">
         <v>80</v>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <v>5</v>
       </c>
-      <c r="AC32">
-        <v>1</v>
-      </c>
       <c r="AD32">
         <v>1</v>
       </c>
       <c r="AE32">
+        <v>1</v>
+      </c>
+      <c r="AH32">
         <v>6</v>
       </c>
-      <c r="AF32">
+      <c r="AI32">
         <v>6000001</v>
       </c>
-      <c r="AG32" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI32" s="1">
+      <c r="AJ32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL32" s="1">
         <v>300600001</v>
       </c>
-      <c r="AJ32">
+      <c r="AM32">
         <v>6001</v>
       </c>
-      <c r="AK32" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:37">
+      <c r="AN32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:40">
       <c r="A33">
         <v>6002</v>
       </c>
@@ -3807,19 +3903,19 @@
         <v>61010002</v>
       </c>
       <c r="I33" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="N33" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P33">
         <v>204001</v>
       </c>
       <c r="Q33" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="S33">
         <v>2</v>
@@ -3845,38 +3941,38 @@
       <c r="Z33">
         <v>80</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>10</v>
       </c>
-      <c r="AC33">
-        <v>1</v>
-      </c>
       <c r="AD33">
         <v>1</v>
       </c>
       <c r="AE33">
+        <v>1</v>
+      </c>
+      <c r="AH33">
         <v>6</v>
       </c>
-      <c r="AF33">
+      <c r="AI33">
         <v>6000001</v>
       </c>
-      <c r="AG33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI33" s="1">
+      <c r="AJ33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL33" s="1">
         <v>300600002</v>
       </c>
-      <c r="AJ33">
+      <c r="AM33">
         <v>6002</v>
       </c>
-      <c r="AK33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:37">
+      <c r="AN33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:40">
       <c r="A34">
         <v>6003</v>
       </c>
@@ -3890,7 +3986,7 @@
         <v>6000001</v>
       </c>
       <c r="I34" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J34">
         <v>8</v>
@@ -3922,38 +4018,38 @@
       <c r="Z34">
         <v>100</v>
       </c>
-      <c r="AB34">
+      <c r="AC34">
         <v>500</v>
       </c>
-      <c r="AC34">
-        <v>1</v>
-      </c>
       <c r="AD34">
         <v>1</v>
       </c>
       <c r="AE34">
+        <v>1</v>
+      </c>
+      <c r="AH34">
         <v>6</v>
       </c>
-      <c r="AF34">
+      <c r="AI34">
         <v>6000001</v>
       </c>
-      <c r="AG34" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI34" s="1">
+      <c r="AJ34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL34" s="1">
         <v>300600003</v>
       </c>
-      <c r="AJ34">
+      <c r="AM34">
         <v>6003</v>
       </c>
-      <c r="AK34" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:37">
+      <c r="AN34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:40">
       <c r="A35">
         <v>6004</v>
       </c>
@@ -3970,19 +4066,19 @@
         <v>61010003</v>
       </c>
       <c r="I35" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P35">
         <v>204002</v>
       </c>
       <c r="Q35" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="S35">
         <v>2</v>
@@ -4008,38 +4104,38 @@
       <c r="Z35">
         <v>40</v>
       </c>
-      <c r="AB35">
+      <c r="AC35">
         <v>6</v>
       </c>
-      <c r="AC35">
-        <v>1</v>
-      </c>
       <c r="AD35">
         <v>1</v>
       </c>
       <c r="AE35">
+        <v>1</v>
+      </c>
+      <c r="AH35">
         <v>6</v>
       </c>
-      <c r="AF35">
+      <c r="AI35">
         <v>6000001</v>
       </c>
-      <c r="AG35" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI35" s="1">
+      <c r="AJ35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL35" s="1">
         <v>300600004</v>
       </c>
-      <c r="AJ35">
+      <c r="AM35">
         <v>6004</v>
       </c>
-      <c r="AK35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:37">
+      <c r="AN35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:40">
       <c r="A36">
         <v>6005</v>
       </c>
@@ -4056,19 +4152,19 @@
         <v>61010003</v>
       </c>
       <c r="I36" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P36">
         <v>204003</v>
       </c>
       <c r="Q36" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="S36">
         <v>2</v>
@@ -4094,38 +4190,38 @@
       <c r="Z36">
         <v>40</v>
       </c>
-      <c r="AB36">
+      <c r="AC36">
         <v>3</v>
       </c>
-      <c r="AC36">
-        <v>1</v>
-      </c>
       <c r="AD36">
         <v>1</v>
       </c>
       <c r="AE36">
+        <v>1</v>
+      </c>
+      <c r="AH36">
         <v>6</v>
       </c>
-      <c r="AF36">
+      <c r="AI36">
         <v>6000001</v>
       </c>
-      <c r="AG36" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI36" s="1">
+      <c r="AJ36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL36" s="1">
         <v>300600005</v>
       </c>
-      <c r="AJ36">
+      <c r="AM36">
         <v>6005</v>
       </c>
-      <c r="AK36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:37">
+      <c r="AN36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:40">
       <c r="A37">
         <v>7001</v>
       </c>
@@ -4136,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G37">
         <v>7000001</v>
       </c>
       <c r="I37" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P37">
         <v>200001</v>
@@ -4171,38 +4267,38 @@
       <c r="Z37">
         <v>120</v>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <v>12</v>
       </c>
-      <c r="AC37">
-        <v>1</v>
-      </c>
       <c r="AD37">
         <v>1</v>
       </c>
       <c r="AE37">
+        <v>1</v>
+      </c>
+      <c r="AH37">
         <v>7</v>
       </c>
-      <c r="AF37">
+      <c r="AI37">
         <v>7000001</v>
       </c>
-      <c r="AG37" s="1" t="s">
+      <c r="AJ37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK37" t="s">
         <v>86</v>
       </c>
-      <c r="AH37" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI37" s="1">
+      <c r="AL37" s="1">
         <v>300700001</v>
       </c>
-      <c r="AJ37">
+      <c r="AM37">
         <v>7001</v>
       </c>
-      <c r="AK37" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:37">
+      <c r="AN37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:40">
       <c r="A38">
         <v>7002</v>
       </c>
@@ -4219,19 +4315,19 @@
         <v>71000001</v>
       </c>
       <c r="I38" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J38">
         <v>8</v>
       </c>
       <c r="N38" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P38">
         <v>205001</v>
       </c>
       <c r="Q38" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S38">
         <v>2</v>
@@ -4257,38 +4353,38 @@
       <c r="Z38">
         <v>120</v>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <v>3</v>
       </c>
-      <c r="AC38">
-        <v>1</v>
-      </c>
       <c r="AD38">
         <v>1</v>
       </c>
       <c r="AE38">
+        <v>1</v>
+      </c>
+      <c r="AH38">
         <v>7</v>
       </c>
-      <c r="AF38">
+      <c r="AI38">
         <v>7000001</v>
       </c>
-      <c r="AG38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI38" s="1">
+      <c r="AJ38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL38" s="1">
         <v>300700002</v>
       </c>
-      <c r="AJ38">
+      <c r="AM38">
         <v>7002</v>
       </c>
-      <c r="AK38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:37">
+      <c r="AN38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:40">
       <c r="A39">
         <v>7003</v>
       </c>
@@ -4305,19 +4401,19 @@
         <v>71010004</v>
       </c>
       <c r="I39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P39">
         <v>205002</v>
       </c>
       <c r="Q39" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S39">
         <v>2</v>
@@ -4343,38 +4439,38 @@
       <c r="Z39">
         <v>60</v>
       </c>
-      <c r="AB39">
+      <c r="AC39">
         <v>6</v>
       </c>
-      <c r="AC39">
-        <v>1</v>
-      </c>
       <c r="AD39">
         <v>1</v>
       </c>
       <c r="AE39">
+        <v>1</v>
+      </c>
+      <c r="AH39">
         <v>7</v>
       </c>
-      <c r="AF39">
+      <c r="AI39">
         <v>7000001</v>
       </c>
-      <c r="AG39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI39" s="1">
+      <c r="AJ39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL39" s="1">
         <v>300700003</v>
       </c>
-      <c r="AJ39">
+      <c r="AM39">
         <v>7003</v>
       </c>
-      <c r="AK39" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:37">
+      <c r="AN39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:40">
       <c r="A40">
         <v>7004</v>
       </c>
@@ -4391,19 +4487,19 @@
         <v>71010004</v>
       </c>
       <c r="I40" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P40">
         <v>205003</v>
       </c>
       <c r="Q40" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S40">
         <v>2</v>
@@ -4429,38 +4525,38 @@
       <c r="Z40">
         <v>60</v>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <v>3</v>
       </c>
-      <c r="AC40">
-        <v>1</v>
-      </c>
       <c r="AD40">
         <v>1</v>
       </c>
       <c r="AE40">
+        <v>1</v>
+      </c>
+      <c r="AH40">
         <v>7</v>
       </c>
-      <c r="AF40">
+      <c r="AI40">
         <v>7000001</v>
       </c>
-      <c r="AG40" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI40" s="1">
+      <c r="AJ40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL40" s="1">
         <v>300700004</v>
       </c>
-      <c r="AJ40">
+      <c r="AM40">
         <v>7004</v>
       </c>
-      <c r="AK40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:37">
+      <c r="AN40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:40">
       <c r="A41">
         <v>101001</v>
       </c>
@@ -4471,7 +4567,7 @@
         <v>1000001</v>
       </c>
       <c r="I41" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -4500,35 +4596,35 @@
       <c r="Z41">
         <v>100</v>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <v>10</v>
       </c>
-      <c r="AC41">
-        <v>1</v>
-      </c>
       <c r="AD41">
+        <v>1</v>
+      </c>
+      <c r="AE41">
         <v>0.2</v>
       </c>
-      <c r="AE41">
-        <v>1</v>
-      </c>
-      <c r="AF41">
+      <c r="AH41">
+        <v>1</v>
+      </c>
+      <c r="AI41">
         <v>1000001</v>
       </c>
-      <c r="AG41" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ41">
+      <c r="AJ41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM41">
         <v>101001</v>
       </c>
-      <c r="AK41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:37">
+      <c r="AN41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:40">
       <c r="A42">
         <v>102001</v>
       </c>
@@ -4539,7 +4635,7 @@
         <v>1000001</v>
       </c>
       <c r="I42" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J42">
         <v>7</v>
@@ -4568,35 +4664,35 @@
       <c r="Z42">
         <v>100</v>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <v>10</v>
       </c>
-      <c r="AC42">
-        <v>1</v>
-      </c>
       <c r="AD42">
+        <v>1</v>
+      </c>
+      <c r="AE42">
         <v>0.2</v>
       </c>
-      <c r="AE42">
-        <v>1</v>
-      </c>
-      <c r="AF42">
+      <c r="AH42">
+        <v>1</v>
+      </c>
+      <c r="AI42">
         <v>1000001</v>
       </c>
-      <c r="AG42" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ42">
+      <c r="AJ42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM42">
         <v>102001</v>
       </c>
-      <c r="AK42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:37">
+      <c r="AN42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:40">
       <c r="A43">
         <v>103001</v>
       </c>
@@ -4607,7 +4703,7 @@
         <v>1000001</v>
       </c>
       <c r="I43" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -4636,35 +4732,35 @@
       <c r="Z43">
         <v>100</v>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <v>10</v>
       </c>
-      <c r="AC43">
-        <v>1</v>
-      </c>
       <c r="AD43">
+        <v>1</v>
+      </c>
+      <c r="AE43">
         <v>0.2</v>
       </c>
-      <c r="AE43">
-        <v>1</v>
-      </c>
-      <c r="AF43">
+      <c r="AH43">
+        <v>1</v>
+      </c>
+      <c r="AI43">
         <v>1000001</v>
       </c>
-      <c r="AG43" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH43" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ43">
+      <c r="AJ43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM43">
         <v>103001</v>
       </c>
-      <c r="AK43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:37">
+      <c r="AN43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:40">
       <c r="A44">
         <v>103002</v>
       </c>
@@ -4675,7 +4771,7 @@
         <v>1000001</v>
       </c>
       <c r="I44" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -4704,35 +4800,35 @@
       <c r="Z44">
         <v>100</v>
       </c>
-      <c r="AB44">
+      <c r="AC44">
         <v>10</v>
       </c>
-      <c r="AC44">
-        <v>1</v>
-      </c>
       <c r="AD44">
+        <v>1</v>
+      </c>
+      <c r="AE44">
         <v>0.2</v>
       </c>
-      <c r="AE44">
-        <v>1</v>
-      </c>
-      <c r="AF44">
+      <c r="AH44">
+        <v>1</v>
+      </c>
+      <c r="AI44">
         <v>1000001</v>
       </c>
-      <c r="AG44" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ44">
+      <c r="AJ44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM44">
         <v>103002</v>
       </c>
-      <c r="AK44" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:37">
+      <c r="AN44" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:40">
       <c r="A45" s="1">
         <v>900001</v>
       </c>
@@ -4749,13 +4845,13 @@
         <v>21010001</v>
       </c>
       <c r="I45" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J45">
         <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="P45">
         <v>100001</v>
@@ -4784,38 +4880,38 @@
       <c r="Z45">
         <v>100</v>
       </c>
-      <c r="AB45">
-        <v>100</v>
-      </c>
       <c r="AC45">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AD45">
         <v>1</v>
       </c>
       <c r="AE45">
-        <v>2</v>
-      </c>
-      <c r="AF45">
+        <v>1</v>
+      </c>
+      <c r="AH45">
+        <v>2</v>
+      </c>
+      <c r="AI45">
         <v>2000001</v>
       </c>
-      <c r="AG45" s="1" t="s">
+      <c r="AJ45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK45" t="s">
         <v>86</v>
       </c>
-      <c r="AH45" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI45">
+      <c r="AL45">
         <v>300200001</v>
       </c>
-      <c r="AJ45" s="1">
+      <c r="AM45" s="1">
         <v>900001</v>
       </c>
-      <c r="AK45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:37">
+      <c r="AN45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:40">
       <c r="A46" s="1">
         <v>900002</v>
       </c>
@@ -4832,19 +4928,19 @@
         <v>21000001</v>
       </c>
       <c r="I46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J46">
         <v>8</v>
       </c>
       <c r="N46" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="P46">
         <v>200001</v>
       </c>
       <c r="Q46" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="S46">
         <v>2</v>
@@ -4870,38 +4966,38 @@
       <c r="Z46">
         <v>100</v>
       </c>
-      <c r="AB46">
-        <v>100</v>
-      </c>
       <c r="AC46">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AD46">
         <v>1</v>
       </c>
       <c r="AE46">
-        <v>2</v>
-      </c>
-      <c r="AF46">
+        <v>1</v>
+      </c>
+      <c r="AH46">
+        <v>2</v>
+      </c>
+      <c r="AI46">
         <v>2000001</v>
       </c>
-      <c r="AG46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI46">
+      <c r="AJ46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL46">
         <v>300200002</v>
       </c>
-      <c r="AJ46" s="1">
+      <c r="AM46" s="1">
         <v>900002</v>
       </c>
-      <c r="AK46" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:37">
+      <c r="AN46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:40">
       <c r="A47" s="1">
         <v>989996</v>
       </c>
@@ -4933,31 +5029,31 @@
       <c r="Z47">
         <v>100</v>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <v>35</v>
       </c>
-      <c r="AC47">
-        <v>1</v>
-      </c>
       <c r="AD47">
         <v>1</v>
       </c>
-      <c r="AE47" s="1">
+      <c r="AE47">
+        <v>1</v>
+      </c>
+      <c r="AH47" s="1">
         <v>989996</v>
       </c>
-      <c r="AF47" s="2"/>
-      <c r="AG47" s="2"/>
-      <c r="AH47" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ47">
-        <v>1</v>
-      </c>
+      <c r="AI47" s="2"/>
+      <c r="AJ47" s="2"/>
       <c r="AK47" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM47">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:40">
       <c r="A48" s="1">
         <v>989997</v>
       </c>
@@ -4989,31 +5085,31 @@
       <c r="Z48">
         <v>100</v>
       </c>
-      <c r="AB48">
+      <c r="AC48">
         <v>35</v>
       </c>
-      <c r="AC48">
-        <v>1</v>
-      </c>
       <c r="AD48">
         <v>1</v>
       </c>
-      <c r="AE48" s="1">
+      <c r="AE48">
+        <v>1</v>
+      </c>
+      <c r="AH48" s="1">
         <v>989997</v>
       </c>
-      <c r="AF48" s="2"/>
-      <c r="AG48" s="2"/>
-      <c r="AH48" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ48">
-        <v>1</v>
-      </c>
+      <c r="AI48" s="2"/>
+      <c r="AJ48" s="2"/>
       <c r="AK48" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM48">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:40">
       <c r="A49" s="1">
         <v>989998</v>
       </c>
@@ -5045,31 +5141,31 @@
       <c r="Z49">
         <v>100</v>
       </c>
-      <c r="AB49">
+      <c r="AC49">
         <v>35</v>
       </c>
-      <c r="AC49">
-        <v>1</v>
-      </c>
       <c r="AD49">
         <v>1</v>
       </c>
-      <c r="AE49" s="1">
+      <c r="AE49">
+        <v>1</v>
+      </c>
+      <c r="AH49" s="1">
         <v>989998</v>
       </c>
-      <c r="AF49" s="2"/>
-      <c r="AG49" s="2"/>
-      <c r="AH49" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ49">
-        <v>1</v>
-      </c>
+      <c r="AI49" s="2"/>
+      <c r="AJ49" s="2"/>
       <c r="AK49" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM49">
+        <v>1</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:40">
       <c r="A50" s="1">
         <v>989999</v>
       </c>
@@ -5101,29 +5197,29 @@
       <c r="Z50">
         <v>100</v>
       </c>
-      <c r="AB50">
+      <c r="AC50">
         <v>35</v>
       </c>
-      <c r="AC50">
-        <v>1</v>
-      </c>
       <c r="AD50">
         <v>1</v>
       </c>
       <c r="AE50">
+        <v>1</v>
+      </c>
+      <c r="AH50">
         <v>989999</v>
       </c>
-      <c r="AH50" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ50">
-        <v>1</v>
-      </c>
       <c r="AK50" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM50">
+        <v>1</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:40">
       <c r="A51" s="1">
         <v>999947</v>
       </c>
@@ -5155,31 +5251,31 @@
       <c r="Z51">
         <v>100</v>
       </c>
-      <c r="AB51">
+      <c r="AC51">
         <v>35</v>
       </c>
-      <c r="AC51">
-        <v>1</v>
-      </c>
       <c r="AD51">
         <v>1</v>
       </c>
-      <c r="AE51" s="1">
+      <c r="AE51">
+        <v>1</v>
+      </c>
+      <c r="AH51" s="1">
         <v>999947</v>
       </c>
-      <c r="AF51" s="2"/>
-      <c r="AG51" s="2"/>
-      <c r="AH51" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ51">
-        <v>1</v>
-      </c>
+      <c r="AI51" s="2"/>
+      <c r="AJ51" s="2"/>
       <c r="AK51" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM51">
+        <v>1</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:40">
       <c r="A52" s="1">
         <v>999948</v>
       </c>
@@ -5211,31 +5307,31 @@
       <c r="Z52">
         <v>100</v>
       </c>
-      <c r="AB52">
+      <c r="AC52">
         <v>35</v>
       </c>
-      <c r="AC52">
-        <v>1</v>
-      </c>
       <c r="AD52">
         <v>1</v>
       </c>
-      <c r="AE52" s="1">
+      <c r="AE52">
+        <v>1</v>
+      </c>
+      <c r="AH52" s="1">
         <v>999948</v>
       </c>
-      <c r="AF52" s="2"/>
-      <c r="AG52" s="2"/>
-      <c r="AH52" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ52">
-        <v>1</v>
-      </c>
+      <c r="AI52" s="2"/>
+      <c r="AJ52" s="2"/>
       <c r="AK52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM52">
+        <v>1</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:40">
       <c r="A53" s="1">
         <v>999949</v>
       </c>
@@ -5267,31 +5363,31 @@
       <c r="Z53">
         <v>100</v>
       </c>
-      <c r="AB53">
+      <c r="AC53">
         <v>35</v>
       </c>
-      <c r="AC53">
-        <v>1</v>
-      </c>
       <c r="AD53">
         <v>1</v>
       </c>
-      <c r="AE53" s="1">
+      <c r="AE53">
+        <v>1</v>
+      </c>
+      <c r="AH53" s="1">
         <v>999949</v>
       </c>
-      <c r="AF53" s="2"/>
-      <c r="AG53" s="2"/>
-      <c r="AH53" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ53">
-        <v>1</v>
-      </c>
+      <c r="AI53" s="2"/>
+      <c r="AJ53" s="2"/>
       <c r="AK53" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM53">
+        <v>1</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:40">
       <c r="A54" s="1">
         <v>999950</v>
       </c>
@@ -5323,31 +5419,31 @@
       <c r="Z54">
         <v>100</v>
       </c>
-      <c r="AB54">
+      <c r="AC54">
         <v>35</v>
       </c>
-      <c r="AC54">
-        <v>1</v>
-      </c>
       <c r="AD54">
         <v>1</v>
       </c>
-      <c r="AE54" s="1">
+      <c r="AE54">
+        <v>1</v>
+      </c>
+      <c r="AH54" s="1">
         <v>999950</v>
       </c>
-      <c r="AF54" s="2"/>
-      <c r="AG54" s="2"/>
-      <c r="AH54" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ54">
-        <v>1</v>
-      </c>
+      <c r="AI54" s="2"/>
+      <c r="AJ54" s="2"/>
       <c r="AK54" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM54">
+        <v>1</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:40">
       <c r="A55" s="1">
         <v>999951</v>
       </c>
@@ -5379,31 +5475,31 @@
       <c r="Z55">
         <v>100</v>
       </c>
-      <c r="AB55">
+      <c r="AC55">
         <v>35</v>
       </c>
-      <c r="AC55">
-        <v>1</v>
-      </c>
       <c r="AD55">
         <v>1</v>
       </c>
-      <c r="AE55" s="1">
+      <c r="AE55">
+        <v>1</v>
+      </c>
+      <c r="AH55" s="1">
         <v>999951</v>
       </c>
-      <c r="AF55" s="2"/>
-      <c r="AG55" s="2"/>
-      <c r="AH55" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ55">
-        <v>1</v>
-      </c>
+      <c r="AI55" s="2"/>
+      <c r="AJ55" s="2"/>
       <c r="AK55" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM55">
+        <v>1</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:40">
       <c r="A56" s="1">
         <v>999952</v>
       </c>
@@ -5435,31 +5531,31 @@
       <c r="Z56">
         <v>100</v>
       </c>
-      <c r="AB56">
+      <c r="AC56">
         <v>35</v>
       </c>
-      <c r="AC56">
-        <v>1</v>
-      </c>
       <c r="AD56">
         <v>1</v>
       </c>
-      <c r="AE56" s="1">
+      <c r="AE56">
+        <v>1</v>
+      </c>
+      <c r="AH56" s="1">
         <v>999952</v>
       </c>
-      <c r="AF56" s="2"/>
-      <c r="AG56" s="2"/>
-      <c r="AH56" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ56">
-        <v>1</v>
-      </c>
+      <c r="AI56" s="2"/>
+      <c r="AJ56" s="2"/>
       <c r="AK56" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM56">
+        <v>1</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:40">
       <c r="A57" s="1">
         <v>999953</v>
       </c>
@@ -5491,31 +5587,31 @@
       <c r="Z57">
         <v>100</v>
       </c>
-      <c r="AB57">
+      <c r="AC57">
         <v>35</v>
       </c>
-      <c r="AC57">
-        <v>1</v>
-      </c>
       <c r="AD57">
         <v>1</v>
       </c>
-      <c r="AE57" s="1">
+      <c r="AE57">
+        <v>1</v>
+      </c>
+      <c r="AH57" s="1">
         <v>999953</v>
       </c>
-      <c r="AF57" s="2"/>
-      <c r="AG57" s="2"/>
-      <c r="AH57" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ57">
-        <v>1</v>
-      </c>
+      <c r="AI57" s="2"/>
+      <c r="AJ57" s="2"/>
       <c r="AK57" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM57">
+        <v>1</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:40">
       <c r="A58" s="1">
         <v>999954</v>
       </c>
@@ -5547,31 +5643,31 @@
       <c r="Z58">
         <v>100</v>
       </c>
-      <c r="AB58">
+      <c r="AC58">
         <v>35</v>
       </c>
-      <c r="AC58">
-        <v>1</v>
-      </c>
       <c r="AD58">
         <v>1</v>
       </c>
-      <c r="AE58" s="1">
+      <c r="AE58">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="1">
         <v>999954</v>
       </c>
-      <c r="AF58" s="2"/>
-      <c r="AG58" s="2"/>
-      <c r="AH58" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ58">
-        <v>1</v>
-      </c>
+      <c r="AI58" s="2"/>
+      <c r="AJ58" s="2"/>
       <c r="AK58" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM58">
+        <v>1</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:40">
       <c r="A59" s="1">
         <v>999955</v>
       </c>
@@ -5603,31 +5699,31 @@
       <c r="Z59">
         <v>100</v>
       </c>
-      <c r="AB59">
+      <c r="AC59">
         <v>35</v>
       </c>
-      <c r="AC59">
-        <v>1</v>
-      </c>
       <c r="AD59">
         <v>1</v>
       </c>
-      <c r="AE59" s="1">
+      <c r="AE59">
+        <v>1</v>
+      </c>
+      <c r="AH59" s="1">
         <v>999955</v>
       </c>
-      <c r="AF59" s="2"/>
-      <c r="AG59" s="2"/>
-      <c r="AH59" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ59">
-        <v>1</v>
-      </c>
+      <c r="AI59" s="2"/>
+      <c r="AJ59" s="2"/>
       <c r="AK59" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM59">
+        <v>1</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:40">
       <c r="A60" s="1">
         <v>999956</v>
       </c>
@@ -5659,31 +5755,31 @@
       <c r="Z60">
         <v>100</v>
       </c>
-      <c r="AB60">
+      <c r="AC60">
         <v>35</v>
       </c>
-      <c r="AC60">
-        <v>1</v>
-      </c>
       <c r="AD60">
         <v>1</v>
       </c>
-      <c r="AE60" s="1">
+      <c r="AE60">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="1">
         <v>999956</v>
       </c>
-      <c r="AF60" s="2"/>
-      <c r="AG60" s="2"/>
-      <c r="AH60" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ60">
-        <v>1</v>
-      </c>
+      <c r="AI60" s="2"/>
+      <c r="AJ60" s="2"/>
       <c r="AK60" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM60">
+        <v>1</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:40">
       <c r="A61" s="1">
         <v>999957</v>
       </c>
@@ -5715,31 +5811,31 @@
       <c r="Z61">
         <v>100</v>
       </c>
-      <c r="AB61">
+      <c r="AC61">
         <v>35</v>
       </c>
-      <c r="AC61">
-        <v>1</v>
-      </c>
       <c r="AD61">
         <v>1</v>
       </c>
-      <c r="AE61" s="1">
+      <c r="AE61">
+        <v>1</v>
+      </c>
+      <c r="AH61" s="1">
         <v>999957</v>
       </c>
-      <c r="AF61" s="2"/>
-      <c r="AG61" s="2"/>
-      <c r="AH61" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ61">
-        <v>1</v>
-      </c>
+      <c r="AI61" s="2"/>
+      <c r="AJ61" s="2"/>
       <c r="AK61" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM61">
+        <v>1</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:40">
       <c r="A62" s="1">
         <v>999958</v>
       </c>
@@ -5771,31 +5867,31 @@
       <c r="Z62">
         <v>100</v>
       </c>
-      <c r="AB62">
+      <c r="AC62">
         <v>35</v>
       </c>
-      <c r="AC62">
-        <v>1</v>
-      </c>
       <c r="AD62">
         <v>1</v>
       </c>
-      <c r="AE62" s="1">
+      <c r="AE62">
+        <v>1</v>
+      </c>
+      <c r="AH62" s="1">
         <v>999958</v>
       </c>
-      <c r="AF62" s="2"/>
-      <c r="AG62" s="2"/>
-      <c r="AH62" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ62">
-        <v>1</v>
-      </c>
+      <c r="AI62" s="2"/>
+      <c r="AJ62" s="2"/>
       <c r="AK62" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM62">
+        <v>1</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:40">
       <c r="A63" s="1">
         <v>999959</v>
       </c>
@@ -5827,31 +5923,31 @@
       <c r="Z63">
         <v>100</v>
       </c>
-      <c r="AB63">
+      <c r="AC63">
         <v>35</v>
       </c>
-      <c r="AC63">
-        <v>1</v>
-      </c>
       <c r="AD63">
         <v>1</v>
       </c>
-      <c r="AE63" s="1">
+      <c r="AE63">
+        <v>1</v>
+      </c>
+      <c r="AH63" s="1">
         <v>999959</v>
       </c>
-      <c r="AF63" s="2"/>
-      <c r="AG63" s="2"/>
-      <c r="AH63" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ63">
-        <v>1</v>
-      </c>
+      <c r="AI63" s="2"/>
+      <c r="AJ63" s="2"/>
       <c r="AK63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM63">
+        <v>1</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:40">
       <c r="A64" s="1">
         <v>999960</v>
       </c>
@@ -5883,31 +5979,31 @@
       <c r="Z64">
         <v>100</v>
       </c>
-      <c r="AB64">
+      <c r="AC64">
         <v>35</v>
       </c>
-      <c r="AC64">
-        <v>1</v>
-      </c>
       <c r="AD64">
         <v>1</v>
       </c>
-      <c r="AE64" s="1">
+      <c r="AE64">
+        <v>1</v>
+      </c>
+      <c r="AH64" s="1">
         <v>999960</v>
       </c>
-      <c r="AF64" s="2"/>
-      <c r="AG64" s="2"/>
-      <c r="AH64" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ64">
-        <v>1</v>
-      </c>
+      <c r="AI64" s="2"/>
+      <c r="AJ64" s="2"/>
       <c r="AK64" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM64">
+        <v>1</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:40">
       <c r="A65" s="1">
         <v>999961</v>
       </c>
@@ -5939,31 +6035,31 @@
       <c r="Z65">
         <v>100</v>
       </c>
-      <c r="AB65">
+      <c r="AC65">
         <v>35</v>
       </c>
-      <c r="AC65">
-        <v>1</v>
-      </c>
       <c r="AD65">
         <v>1</v>
       </c>
-      <c r="AE65" s="1">
+      <c r="AE65">
+        <v>1</v>
+      </c>
+      <c r="AH65" s="1">
         <v>999961</v>
       </c>
-      <c r="AF65" s="2"/>
-      <c r="AG65" s="2"/>
-      <c r="AH65" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ65">
-        <v>1</v>
-      </c>
+      <c r="AI65" s="2"/>
+      <c r="AJ65" s="2"/>
       <c r="AK65" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM65">
+        <v>1</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:40">
       <c r="A66" s="1">
         <v>999962</v>
       </c>
@@ -5995,31 +6091,31 @@
       <c r="Z66">
         <v>100</v>
       </c>
-      <c r="AB66">
+      <c r="AC66">
         <v>35</v>
       </c>
-      <c r="AC66">
-        <v>1</v>
-      </c>
       <c r="AD66">
         <v>1</v>
       </c>
-      <c r="AE66" s="1">
+      <c r="AE66">
+        <v>1</v>
+      </c>
+      <c r="AH66" s="1">
         <v>999962</v>
       </c>
-      <c r="AF66" s="2"/>
-      <c r="AG66" s="2"/>
-      <c r="AH66" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ66">
-        <v>1</v>
-      </c>
+      <c r="AI66" s="2"/>
+      <c r="AJ66" s="2"/>
       <c r="AK66" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM66">
+        <v>1</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:40">
       <c r="A67" s="1">
         <v>999963</v>
       </c>
@@ -6051,31 +6147,31 @@
       <c r="Z67">
         <v>100</v>
       </c>
-      <c r="AB67">
+      <c r="AC67">
         <v>35</v>
       </c>
-      <c r="AC67">
-        <v>1</v>
-      </c>
       <c r="AD67">
         <v>1</v>
       </c>
-      <c r="AE67" s="1">
+      <c r="AE67">
+        <v>1</v>
+      </c>
+      <c r="AH67" s="1">
         <v>999963</v>
       </c>
-      <c r="AF67" s="2"/>
-      <c r="AG67" s="2"/>
-      <c r="AH67" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ67">
-        <v>1</v>
-      </c>
+      <c r="AI67" s="2"/>
+      <c r="AJ67" s="2"/>
       <c r="AK67" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM67">
+        <v>1</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:40">
       <c r="A68" s="1">
         <v>999964</v>
       </c>
@@ -6107,31 +6203,31 @@
       <c r="Z68">
         <v>100</v>
       </c>
-      <c r="AB68">
+      <c r="AC68">
         <v>35</v>
       </c>
-      <c r="AC68">
-        <v>1</v>
-      </c>
       <c r="AD68">
         <v>1</v>
       </c>
-      <c r="AE68" s="1">
+      <c r="AE68">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="1">
         <v>999964</v>
       </c>
-      <c r="AF68" s="2"/>
-      <c r="AG68" s="2"/>
-      <c r="AH68" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ68">
-        <v>1</v>
-      </c>
+      <c r="AI68" s="2"/>
+      <c r="AJ68" s="2"/>
       <c r="AK68" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM68">
+        <v>1</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:40">
       <c r="A69" s="1">
         <v>999965</v>
       </c>
@@ -6163,31 +6259,31 @@
       <c r="Z69">
         <v>100</v>
       </c>
-      <c r="AB69">
+      <c r="AC69">
         <v>35</v>
       </c>
-      <c r="AC69">
-        <v>1</v>
-      </c>
       <c r="AD69">
         <v>1</v>
       </c>
-      <c r="AE69" s="1">
+      <c r="AE69">
+        <v>1</v>
+      </c>
+      <c r="AH69" s="1">
         <v>999965</v>
       </c>
-      <c r="AF69" s="2"/>
-      <c r="AG69" s="2"/>
-      <c r="AH69" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ69">
-        <v>1</v>
-      </c>
+      <c r="AI69" s="2"/>
+      <c r="AJ69" s="2"/>
       <c r="AK69" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM69">
+        <v>1</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:40">
       <c r="A70" s="1">
         <v>999966</v>
       </c>
@@ -6219,31 +6315,31 @@
       <c r="Z70">
         <v>100</v>
       </c>
-      <c r="AB70">
+      <c r="AC70">
         <v>35</v>
       </c>
-      <c r="AC70">
-        <v>1</v>
-      </c>
       <c r="AD70">
         <v>1</v>
       </c>
-      <c r="AE70" s="1">
+      <c r="AE70">
+        <v>1</v>
+      </c>
+      <c r="AH70" s="1">
         <v>999966</v>
       </c>
-      <c r="AF70" s="2"/>
-      <c r="AG70" s="2"/>
-      <c r="AH70" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ70">
-        <v>1</v>
-      </c>
+      <c r="AI70" s="2"/>
+      <c r="AJ70" s="2"/>
       <c r="AK70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM70">
+        <v>1</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:40">
       <c r="A71" s="1">
         <v>999967</v>
       </c>
@@ -6275,31 +6371,31 @@
       <c r="Z71">
         <v>100</v>
       </c>
-      <c r="AB71">
+      <c r="AC71">
         <v>35</v>
       </c>
-      <c r="AC71">
-        <v>1</v>
-      </c>
       <c r="AD71">
         <v>1</v>
       </c>
-      <c r="AE71" s="1">
+      <c r="AE71">
+        <v>1</v>
+      </c>
+      <c r="AH71" s="1">
         <v>999967</v>
       </c>
-      <c r="AF71" s="2"/>
-      <c r="AG71" s="2"/>
-      <c r="AH71" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ71">
-        <v>1</v>
-      </c>
+      <c r="AI71" s="2"/>
+      <c r="AJ71" s="2"/>
       <c r="AK71" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM71">
+        <v>1</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:40">
       <c r="A72" s="1">
         <v>999968</v>
       </c>
@@ -6331,31 +6427,31 @@
       <c r="Z72">
         <v>100</v>
       </c>
-      <c r="AB72">
+      <c r="AC72">
         <v>35</v>
       </c>
-      <c r="AC72">
-        <v>1</v>
-      </c>
       <c r="AD72">
         <v>1</v>
       </c>
-      <c r="AE72" s="1">
+      <c r="AE72">
+        <v>1</v>
+      </c>
+      <c r="AH72" s="1">
         <v>999968</v>
       </c>
-      <c r="AF72" s="2"/>
-      <c r="AG72" s="2"/>
-      <c r="AH72" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ72">
-        <v>1</v>
-      </c>
+      <c r="AI72" s="2"/>
+      <c r="AJ72" s="2"/>
       <c r="AK72" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM72">
+        <v>1</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:40">
       <c r="A73" s="1">
         <v>999969</v>
       </c>
@@ -6387,31 +6483,31 @@
       <c r="Z73">
         <v>100</v>
       </c>
-      <c r="AB73">
+      <c r="AC73">
         <v>35</v>
       </c>
-      <c r="AC73">
-        <v>1</v>
-      </c>
       <c r="AD73">
         <v>1</v>
       </c>
-      <c r="AE73" s="1">
+      <c r="AE73">
+        <v>1</v>
+      </c>
+      <c r="AH73" s="1">
         <v>999969</v>
       </c>
-      <c r="AF73" s="2"/>
-      <c r="AG73" s="2"/>
-      <c r="AH73" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ73">
-        <v>1</v>
-      </c>
+      <c r="AI73" s="2"/>
+      <c r="AJ73" s="2"/>
       <c r="AK73" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM73">
+        <v>1</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:40">
       <c r="A74" s="1">
         <v>999970</v>
       </c>
@@ -6443,31 +6539,31 @@
       <c r="Z74">
         <v>100</v>
       </c>
-      <c r="AB74">
+      <c r="AC74">
         <v>35</v>
       </c>
-      <c r="AC74">
-        <v>1</v>
-      </c>
       <c r="AD74">
         <v>1</v>
       </c>
-      <c r="AE74" s="1">
+      <c r="AE74">
+        <v>1</v>
+      </c>
+      <c r="AH74" s="1">
         <v>999970</v>
       </c>
-      <c r="AF74" s="2"/>
-      <c r="AG74" s="2"/>
-      <c r="AH74" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ74">
-        <v>1</v>
-      </c>
+      <c r="AI74" s="2"/>
+      <c r="AJ74" s="2"/>
       <c r="AK74" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM74">
+        <v>1</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:40">
       <c r="A75" s="1">
         <v>999971</v>
       </c>
@@ -6499,31 +6595,31 @@
       <c r="Z75">
         <v>100</v>
       </c>
-      <c r="AB75">
+      <c r="AC75">
         <v>35</v>
       </c>
-      <c r="AC75">
-        <v>1</v>
-      </c>
       <c r="AD75">
         <v>1</v>
       </c>
-      <c r="AE75" s="1">
+      <c r="AE75">
+        <v>1</v>
+      </c>
+      <c r="AH75" s="1">
         <v>999971</v>
       </c>
-      <c r="AF75" s="2"/>
-      <c r="AG75" s="2"/>
-      <c r="AH75" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ75">
-        <v>1</v>
-      </c>
+      <c r="AI75" s="2"/>
+      <c r="AJ75" s="2"/>
       <c r="AK75" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM75">
+        <v>1</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:40">
       <c r="A76" s="1">
         <v>999972</v>
       </c>
@@ -6555,31 +6651,31 @@
       <c r="Z76">
         <v>100</v>
       </c>
-      <c r="AB76">
+      <c r="AC76">
         <v>35</v>
       </c>
-      <c r="AC76">
-        <v>1</v>
-      </c>
       <c r="AD76">
         <v>1</v>
       </c>
-      <c r="AE76" s="1">
+      <c r="AE76">
+        <v>1</v>
+      </c>
+      <c r="AH76" s="1">
         <v>999972</v>
       </c>
-      <c r="AF76" s="2"/>
-      <c r="AG76" s="2"/>
-      <c r="AH76" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ76">
-        <v>1</v>
-      </c>
+      <c r="AI76" s="2"/>
+      <c r="AJ76" s="2"/>
       <c r="AK76" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM76">
+        <v>1</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="1:40">
       <c r="A77" s="1">
         <v>999973</v>
       </c>
@@ -6611,31 +6707,31 @@
       <c r="Z77">
         <v>100</v>
       </c>
-      <c r="AB77">
+      <c r="AC77">
         <v>35</v>
       </c>
-      <c r="AC77">
-        <v>1</v>
-      </c>
       <c r="AD77">
         <v>1</v>
       </c>
-      <c r="AE77" s="1">
+      <c r="AE77">
+        <v>1</v>
+      </c>
+      <c r="AH77" s="1">
         <v>999973</v>
       </c>
-      <c r="AF77" s="2"/>
-      <c r="AG77" s="2"/>
-      <c r="AH77" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ77">
-        <v>1</v>
-      </c>
+      <c r="AI77" s="2"/>
+      <c r="AJ77" s="2"/>
       <c r="AK77" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="78" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM77">
+        <v>1</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="1:40">
       <c r="A78" s="1">
         <v>999974</v>
       </c>
@@ -6667,31 +6763,31 @@
       <c r="Z78">
         <v>100</v>
       </c>
-      <c r="AB78">
+      <c r="AC78">
         <v>35</v>
       </c>
-      <c r="AC78">
-        <v>1</v>
-      </c>
       <c r="AD78">
         <v>1</v>
       </c>
-      <c r="AE78" s="1">
+      <c r="AE78">
+        <v>1</v>
+      </c>
+      <c r="AH78" s="1">
         <v>999974</v>
       </c>
-      <c r="AF78" s="2"/>
-      <c r="AG78" s="2"/>
-      <c r="AH78" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ78">
-        <v>1</v>
-      </c>
+      <c r="AI78" s="2"/>
+      <c r="AJ78" s="2"/>
       <c r="AK78" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="79" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM78">
+        <v>1</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:40">
       <c r="A79" s="1">
         <v>999975</v>
       </c>
@@ -6723,31 +6819,31 @@
       <c r="Z79">
         <v>100</v>
       </c>
-      <c r="AB79">
+      <c r="AC79">
         <v>35</v>
       </c>
-      <c r="AC79">
-        <v>1</v>
-      </c>
       <c r="AD79">
         <v>1</v>
       </c>
-      <c r="AE79" s="1">
+      <c r="AE79">
+        <v>1</v>
+      </c>
+      <c r="AH79" s="1">
         <v>999975</v>
       </c>
-      <c r="AF79" s="2"/>
-      <c r="AG79" s="2"/>
-      <c r="AH79" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ79">
-        <v>1</v>
-      </c>
+      <c r="AI79" s="2"/>
+      <c r="AJ79" s="2"/>
       <c r="AK79" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="80" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM79">
+        <v>1</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" spans="1:40">
       <c r="A80" s="1">
         <v>999976</v>
       </c>
@@ -6779,31 +6875,31 @@
       <c r="Z80">
         <v>100</v>
       </c>
-      <c r="AB80">
+      <c r="AC80">
         <v>35</v>
       </c>
-      <c r="AC80">
-        <v>1</v>
-      </c>
       <c r="AD80">
         <v>1</v>
       </c>
-      <c r="AE80" s="1">
+      <c r="AE80">
+        <v>1</v>
+      </c>
+      <c r="AH80" s="1">
         <v>999976</v>
       </c>
-      <c r="AF80" s="2"/>
-      <c r="AG80" s="2"/>
-      <c r="AH80" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ80">
-        <v>1</v>
-      </c>
+      <c r="AI80" s="2"/>
+      <c r="AJ80" s="2"/>
       <c r="AK80" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM80">
+        <v>1</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:40">
       <c r="A81" s="1">
         <v>999977</v>
       </c>
@@ -6835,31 +6931,31 @@
       <c r="Z81">
         <v>100</v>
       </c>
-      <c r="AB81">
+      <c r="AC81">
         <v>35</v>
       </c>
-      <c r="AC81">
-        <v>1</v>
-      </c>
       <c r="AD81">
         <v>1</v>
       </c>
-      <c r="AE81" s="1">
+      <c r="AE81">
+        <v>1</v>
+      </c>
+      <c r="AH81" s="1">
         <v>999977</v>
       </c>
-      <c r="AF81" s="2"/>
-      <c r="AG81" s="2"/>
-      <c r="AH81" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ81">
-        <v>1</v>
-      </c>
+      <c r="AI81" s="2"/>
+      <c r="AJ81" s="2"/>
       <c r="AK81" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM81">
+        <v>1</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:40">
       <c r="A82" s="1">
         <v>999978</v>
       </c>
@@ -6891,31 +6987,31 @@
       <c r="Z82">
         <v>100</v>
       </c>
-      <c r="AB82">
+      <c r="AC82">
         <v>35</v>
       </c>
-      <c r="AC82">
-        <v>1</v>
-      </c>
       <c r="AD82">
         <v>1</v>
       </c>
-      <c r="AE82" s="1">
+      <c r="AE82">
+        <v>1</v>
+      </c>
+      <c r="AH82" s="1">
         <v>999978</v>
       </c>
-      <c r="AF82" s="2"/>
-      <c r="AG82" s="2"/>
-      <c r="AH82" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ82">
-        <v>1</v>
-      </c>
+      <c r="AI82" s="2"/>
+      <c r="AJ82" s="2"/>
       <c r="AK82" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM82">
+        <v>1</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:40">
       <c r="A83" s="1">
         <v>999979</v>
       </c>
@@ -6947,31 +7043,31 @@
       <c r="Z83">
         <v>100</v>
       </c>
-      <c r="AB83">
+      <c r="AC83">
         <v>35</v>
       </c>
-      <c r="AC83">
-        <v>1</v>
-      </c>
       <c r="AD83">
         <v>1</v>
       </c>
-      <c r="AE83" s="1">
+      <c r="AE83">
+        <v>1</v>
+      </c>
+      <c r="AH83" s="1">
         <v>999979</v>
       </c>
-      <c r="AF83" s="2"/>
-      <c r="AG83" s="2"/>
-      <c r="AH83" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ83">
-        <v>1</v>
-      </c>
+      <c r="AI83" s="2"/>
+      <c r="AJ83" s="2"/>
       <c r="AK83" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM83">
+        <v>1</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:40">
       <c r="A84" s="1">
         <v>999980</v>
       </c>
@@ -7003,31 +7099,31 @@
       <c r="Z84">
         <v>100</v>
       </c>
-      <c r="AB84">
+      <c r="AC84">
         <v>35</v>
       </c>
-      <c r="AC84">
-        <v>1</v>
-      </c>
       <c r="AD84">
         <v>1</v>
       </c>
-      <c r="AE84" s="1">
+      <c r="AE84">
+        <v>1</v>
+      </c>
+      <c r="AH84" s="1">
         <v>999980</v>
       </c>
-      <c r="AF84" s="2"/>
-      <c r="AG84" s="2"/>
-      <c r="AH84" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ84">
-        <v>1</v>
-      </c>
+      <c r="AI84" s="2"/>
+      <c r="AJ84" s="2"/>
       <c r="AK84" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM84">
+        <v>1</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:40">
       <c r="A85" s="1">
         <v>999981</v>
       </c>
@@ -7059,31 +7155,31 @@
       <c r="Z85">
         <v>100</v>
       </c>
-      <c r="AB85">
+      <c r="AC85">
         <v>35</v>
       </c>
-      <c r="AC85">
-        <v>1</v>
-      </c>
       <c r="AD85">
         <v>1</v>
       </c>
-      <c r="AE85" s="1">
+      <c r="AE85">
+        <v>1</v>
+      </c>
+      <c r="AH85" s="1">
         <v>999981</v>
       </c>
-      <c r="AF85" s="2"/>
-      <c r="AG85" s="2"/>
-      <c r="AH85" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ85">
-        <v>1</v>
-      </c>
+      <c r="AI85" s="2"/>
+      <c r="AJ85" s="2"/>
       <c r="AK85" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="86" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM85">
+        <v>1</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:40">
       <c r="A86">
         <v>999982</v>
       </c>
@@ -7114,29 +7210,29 @@
       <c r="Z86">
         <v>100</v>
       </c>
-      <c r="AB86">
+      <c r="AC86">
         <v>35</v>
       </c>
-      <c r="AC86">
-        <v>1</v>
-      </c>
       <c r="AD86">
         <v>1</v>
       </c>
       <c r="AE86">
+        <v>1</v>
+      </c>
+      <c r="AH86">
         <v>999982</v>
       </c>
-      <c r="AH86" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ86">
-        <v>1</v>
-      </c>
       <c r="AK86" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="87" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM86">
+        <v>1</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:40">
       <c r="A87">
         <v>999983</v>
       </c>
@@ -7167,29 +7263,29 @@
       <c r="Z87">
         <v>100</v>
       </c>
-      <c r="AB87">
+      <c r="AC87">
         <v>35</v>
       </c>
-      <c r="AC87">
-        <v>1</v>
-      </c>
       <c r="AD87">
         <v>1</v>
       </c>
       <c r="AE87">
+        <v>1</v>
+      </c>
+      <c r="AH87">
         <v>999983</v>
       </c>
-      <c r="AH87" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ87">
-        <v>1</v>
-      </c>
       <c r="AK87" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM87">
+        <v>1</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:40">
       <c r="A88">
         <v>999984</v>
       </c>
@@ -7220,29 +7316,29 @@
       <c r="Z88">
         <v>100</v>
       </c>
-      <c r="AB88">
+      <c r="AC88">
         <v>35</v>
       </c>
-      <c r="AC88">
-        <v>1</v>
-      </c>
       <c r="AD88">
         <v>1</v>
       </c>
       <c r="AE88">
+        <v>1</v>
+      </c>
+      <c r="AH88">
         <v>999984</v>
       </c>
-      <c r="AH88" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ88">
-        <v>1</v>
-      </c>
       <c r="AK88" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="89" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM88">
+        <v>1</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:40">
       <c r="A89">
         <v>999985</v>
       </c>
@@ -7273,29 +7369,29 @@
       <c r="Z89">
         <v>100</v>
       </c>
-      <c r="AB89">
+      <c r="AC89">
         <v>35</v>
       </c>
-      <c r="AC89">
-        <v>1</v>
-      </c>
       <c r="AD89">
         <v>1</v>
       </c>
       <c r="AE89">
+        <v>1</v>
+      </c>
+      <c r="AH89">
         <v>999985</v>
       </c>
-      <c r="AH89" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ89">
-        <v>1</v>
-      </c>
       <c r="AK89" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM89">
+        <v>1</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:40">
       <c r="A90">
         <v>999986</v>
       </c>
@@ -7326,29 +7422,29 @@
       <c r="Z90">
         <v>100</v>
       </c>
-      <c r="AB90">
+      <c r="AC90">
         <v>35</v>
       </c>
-      <c r="AC90">
-        <v>1</v>
-      </c>
       <c r="AD90">
         <v>1</v>
       </c>
       <c r="AE90">
+        <v>1</v>
+      </c>
+      <c r="AH90">
         <v>999986</v>
       </c>
-      <c r="AH90" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ90">
-        <v>1</v>
-      </c>
       <c r="AK90" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM90">
+        <v>1</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:40">
       <c r="A91">
         <v>999987</v>
       </c>
@@ -7379,29 +7475,29 @@
       <c r="Z91">
         <v>100</v>
       </c>
-      <c r="AB91">
+      <c r="AC91">
         <v>35</v>
       </c>
-      <c r="AC91">
-        <v>1</v>
-      </c>
       <c r="AD91">
         <v>1</v>
       </c>
       <c r="AE91">
+        <v>1</v>
+      </c>
+      <c r="AH91">
         <v>999987</v>
       </c>
-      <c r="AH91" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ91">
-        <v>1</v>
-      </c>
       <c r="AK91" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="92" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM91">
+        <v>1</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:40">
       <c r="A92">
         <v>999988</v>
       </c>
@@ -7432,29 +7528,29 @@
       <c r="Z92">
         <v>100</v>
       </c>
-      <c r="AB92">
+      <c r="AC92">
         <v>35</v>
       </c>
-      <c r="AC92">
-        <v>1</v>
-      </c>
       <c r="AD92">
         <v>1</v>
       </c>
       <c r="AE92">
+        <v>1</v>
+      </c>
+      <c r="AH92">
         <v>999988</v>
       </c>
-      <c r="AH92" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ92">
-        <v>1</v>
-      </c>
       <c r="AK92" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM92">
+        <v>1</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:40">
       <c r="A93">
         <v>999989</v>
       </c>
@@ -7485,29 +7581,29 @@
       <c r="Z93">
         <v>100</v>
       </c>
-      <c r="AB93">
+      <c r="AC93">
         <v>35</v>
       </c>
-      <c r="AC93">
-        <v>1</v>
-      </c>
       <c r="AD93">
         <v>1</v>
       </c>
       <c r="AE93">
+        <v>1</v>
+      </c>
+      <c r="AH93">
         <v>999989</v>
       </c>
-      <c r="AH93" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ93">
-        <v>1</v>
-      </c>
       <c r="AK93" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="94" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM93">
+        <v>1</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:40">
       <c r="A94">
         <v>999990</v>
       </c>
@@ -7538,29 +7634,29 @@
       <c r="Z94">
         <v>100</v>
       </c>
-      <c r="AB94">
+      <c r="AC94">
         <v>35</v>
       </c>
-      <c r="AC94">
-        <v>1</v>
-      </c>
       <c r="AD94">
         <v>1</v>
       </c>
       <c r="AE94">
+        <v>1</v>
+      </c>
+      <c r="AH94">
         <v>999990</v>
       </c>
-      <c r="AH94" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ94">
-        <v>1</v>
-      </c>
       <c r="AK94" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="95" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM94">
+        <v>1</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:40">
       <c r="A95">
         <v>999991</v>
       </c>
@@ -7591,29 +7687,29 @@
       <c r="Z95">
         <v>100</v>
       </c>
-      <c r="AB95">
+      <c r="AC95">
         <v>35</v>
       </c>
-      <c r="AC95">
-        <v>1</v>
-      </c>
       <c r="AD95">
         <v>1</v>
       </c>
       <c r="AE95">
+        <v>1</v>
+      </c>
+      <c r="AH95">
         <v>999991</v>
       </c>
-      <c r="AH95" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ95">
-        <v>1</v>
-      </c>
       <c r="AK95" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="96" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM95">
+        <v>1</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:40">
       <c r="A96">
         <v>999992</v>
       </c>
@@ -7644,29 +7740,29 @@
       <c r="Z96">
         <v>100</v>
       </c>
-      <c r="AB96">
+      <c r="AC96">
         <v>35</v>
       </c>
-      <c r="AC96">
-        <v>1</v>
-      </c>
       <c r="AD96">
         <v>1</v>
       </c>
       <c r="AE96">
+        <v>1</v>
+      </c>
+      <c r="AH96">
         <v>999992</v>
       </c>
-      <c r="AH96" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ96">
-        <v>1</v>
-      </c>
       <c r="AK96" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="97" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM96">
+        <v>1</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:40">
       <c r="A97">
         <v>999993</v>
       </c>
@@ -7697,29 +7793,29 @@
       <c r="Z97">
         <v>100</v>
       </c>
-      <c r="AB97">
+      <c r="AC97">
         <v>35</v>
       </c>
-      <c r="AC97">
-        <v>1</v>
-      </c>
       <c r="AD97">
         <v>1</v>
       </c>
       <c r="AE97">
+        <v>1</v>
+      </c>
+      <c r="AH97">
         <v>999993</v>
       </c>
-      <c r="AH97" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ97">
-        <v>1</v>
-      </c>
       <c r="AK97" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="98" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM97">
+        <v>1</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" spans="1:40">
       <c r="A98">
         <v>999994</v>
       </c>
@@ -7750,29 +7846,29 @@
       <c r="Z98">
         <v>100</v>
       </c>
-      <c r="AB98">
+      <c r="AC98">
         <v>35</v>
       </c>
-      <c r="AC98">
-        <v>1</v>
-      </c>
       <c r="AD98">
         <v>1</v>
       </c>
       <c r="AE98">
+        <v>1</v>
+      </c>
+      <c r="AH98">
         <v>999994</v>
       </c>
-      <c r="AH98" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ98">
-        <v>1</v>
-      </c>
       <c r="AK98" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="99" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM98">
+        <v>1</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" spans="1:40">
       <c r="A99">
         <v>999995</v>
       </c>
@@ -7803,29 +7899,29 @@
       <c r="Z99">
         <v>100</v>
       </c>
-      <c r="AB99">
+      <c r="AC99">
         <v>35</v>
       </c>
-      <c r="AC99">
-        <v>1</v>
-      </c>
       <c r="AD99">
         <v>1</v>
       </c>
       <c r="AE99">
+        <v>1</v>
+      </c>
+      <c r="AH99">
         <v>999995</v>
       </c>
-      <c r="AH99" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ99">
-        <v>1</v>
-      </c>
       <c r="AK99" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="100" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM99">
+        <v>1</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:40">
       <c r="A100">
         <v>999996</v>
       </c>
@@ -7856,29 +7952,29 @@
       <c r="Z100">
         <v>100</v>
       </c>
-      <c r="AB100">
+      <c r="AC100">
         <v>35</v>
       </c>
-      <c r="AC100">
-        <v>1</v>
-      </c>
       <c r="AD100">
         <v>1</v>
       </c>
       <c r="AE100">
+        <v>1</v>
+      </c>
+      <c r="AH100">
         <v>999996</v>
       </c>
-      <c r="AH100" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ100">
-        <v>1</v>
-      </c>
       <c r="AK100" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="101" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM100">
+        <v>1</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:40">
       <c r="A101">
         <v>999997</v>
       </c>
@@ -7909,29 +8005,29 @@
       <c r="Z101">
         <v>100</v>
       </c>
-      <c r="AB101">
+      <c r="AC101">
         <v>35</v>
       </c>
-      <c r="AC101">
-        <v>1</v>
-      </c>
       <c r="AD101">
         <v>1</v>
       </c>
       <c r="AE101">
+        <v>1</v>
+      </c>
+      <c r="AH101">
         <v>999997</v>
       </c>
-      <c r="AH101" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ101">
-        <v>1</v>
-      </c>
       <c r="AK101" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM101">
+        <v>1</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:40">
       <c r="A102">
         <v>999998</v>
       </c>
@@ -7962,29 +8058,29 @@
       <c r="Z102">
         <v>100</v>
       </c>
-      <c r="AB102">
+      <c r="AC102">
         <v>35</v>
       </c>
-      <c r="AC102">
-        <v>1</v>
-      </c>
       <c r="AD102">
         <v>1</v>
       </c>
       <c r="AE102">
+        <v>1</v>
+      </c>
+      <c r="AH102">
         <v>999998</v>
       </c>
-      <c r="AH102" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ102">
-        <v>1</v>
-      </c>
       <c r="AK102" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="103" customFormat="1" spans="1:37">
+        <v>155</v>
+      </c>
+      <c r="AM102">
+        <v>1</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:40">
       <c r="A103">
         <v>999999</v>
       </c>
@@ -8015,26 +8111,26 @@
       <c r="Z103">
         <v>100</v>
       </c>
-      <c r="AB103">
+      <c r="AC103">
         <v>35</v>
       </c>
-      <c r="AC103">
-        <v>1</v>
-      </c>
       <c r="AD103">
         <v>1</v>
       </c>
       <c r="AE103">
+        <v>1</v>
+      </c>
+      <c r="AH103">
         <v>999999</v>
       </c>
-      <c r="AH103" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ103">
-        <v>1</v>
-      </c>
       <c r="AK103" t="s">
-        <v>148</v>
+        <v>155</v>
+      </c>
+      <c r="AM103">
+        <v>1</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1"/>
@@ -8058,7 +8154,7 @@
     <row r="172" ht="12" customHeight="1"/>
     <row r="173" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK103" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN103" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="149">
   <si>
     <t>id</t>
   </si>
@@ -191,7 +191,7 @@
     <t>可装备类型</t>
   </si>
   <si>
-    <t>可装备武器类型</t>
+    <t>可装备武器类型（1法杖 2单手剑 3双手剑 4刀盾 5大剑 6大盾 7弓 8投掷物）</t>
   </si>
   <si>
     <t>等待动画名字</t>
@@ -311,30 +311,18 @@
     <t>创建角色-兽人</t>
   </si>
   <si>
-    <t>ui_research_43</t>
-  </si>
-  <si>
     <t>人类战士</t>
   </si>
   <si>
     <t>1,2,3,10,</t>
   </si>
   <si>
-    <t>ui_research_42</t>
-  </si>
-  <si>
     <t>人类弓箭手</t>
   </si>
   <si>
-    <t>ui_research_48</t>
-  </si>
-  <si>
     <t>人类魔法师（火）</t>
   </si>
   <si>
-    <t>ui_research_47</t>
-  </si>
-  <si>
     <t>人类魔法师（冰）</t>
   </si>
   <si>
@@ -365,15 +353,9 @@
     <t>1,6</t>
   </si>
   <si>
-    <t>ui_research_51</t>
-  </si>
-  <si>
     <t>守护史莱姆</t>
   </si>
   <si>
-    <t>ui_research_54</t>
-  </si>
-  <si>
     <t>自爆史莱姆</t>
   </si>
   <si>
@@ -383,9 +365,6 @@
     <t>烂泥史莱姆</t>
   </si>
   <si>
-    <t>ui_research_53</t>
-  </si>
-  <si>
     <t>毒液史莱姆</t>
   </si>
   <si>
@@ -395,21 +374,12 @@
     <t>1,2,3,6</t>
   </si>
   <si>
-    <t>ui_research_45</t>
-  </si>
-  <si>
     <t>愈之魅魔</t>
   </si>
   <si>
-    <t>ui_research_52</t>
-  </si>
-  <si>
     <t>惑之魅魔</t>
   </si>
   <si>
-    <t>ui_research_49</t>
-  </si>
-  <si>
     <t>奥之魅魔</t>
   </si>
   <si>
@@ -440,9 +410,6 @@
     <t>2000100001,2000200001,</t>
   </si>
   <si>
-    <t>ui_research_44</t>
-  </si>
-  <si>
     <t>Card_Scene_7</t>
   </si>
   <si>
@@ -479,10 +446,19 @@
     <t>兽人魔法师（冰）</t>
   </si>
   <si>
-    <t>人类-战士</t>
+    <t>人类-冒险者</t>
+  </si>
+  <si>
+    <t>人类-持盾战士</t>
   </si>
   <si>
     <t>人类-弓箭手</t>
+  </si>
+  <si>
+    <t>人类-强弓手</t>
+  </si>
+  <si>
+    <t>人类-连射手</t>
   </si>
   <si>
     <t>人类-魔法师（火）</t>
@@ -513,10 +489,38 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -986,144 +990,165 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1474,7 +1499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN173"/>
+  <dimension ref="A1:AN176"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="23.375" customWidth="1"/>
@@ -1614,10 +1639,10 @@
       <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AK1" t="s">
@@ -1736,10 +1761,10 @@
       <c r="AH2" t="s">
         <v>40</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="AK2" t="s">
@@ -1858,10 +1883,10 @@
       <c r="AH3" t="s">
         <v>77</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AI3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>79</v>
       </c>
       <c r="AK3" t="s">
@@ -1899,6 +1924,9 @@
       <c r="AA4">
         <v>100</v>
       </c>
+      <c r="AE4" s="1">
+        <v>10</v>
+      </c>
       <c r="AG4">
         <v>1</v>
       </c>
@@ -1939,6 +1967,9 @@
       </c>
       <c r="AA5">
         <v>100</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>1</v>
@@ -1978,6 +2009,9 @@
       <c r="AA6">
         <v>100</v>
       </c>
+      <c r="AE6" s="1">
+        <v>10</v>
+      </c>
       <c r="AG6">
         <v>1</v>
       </c>
@@ -2019,6 +2053,9 @@
       <c r="AA7">
         <v>100</v>
       </c>
+      <c r="AE7" s="1">
+        <v>10</v>
+      </c>
       <c r="AG7">
         <v>1</v>
       </c>
@@ -2060,6 +2097,9 @@
       <c r="AA8">
         <v>100</v>
       </c>
+      <c r="AE8" s="1">
+        <v>10</v>
+      </c>
       <c r="AG8">
         <v>1</v>
       </c>
@@ -2101,6 +2141,9 @@
       <c r="AA9">
         <v>100</v>
       </c>
+      <c r="AE9" s="1">
+        <v>10</v>
+      </c>
       <c r="AG9">
         <v>1</v>
       </c>
@@ -2142,6 +2185,9 @@
       <c r="AA10">
         <v>100</v>
       </c>
+      <c r="AE10" s="1">
+        <v>10</v>
+      </c>
       <c r="AG10">
         <v>1</v>
       </c>
@@ -2161,3015 +2207,3001 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:40">
-      <c r="A11">
+    <row r="11" s="1" customFormat="1" spans="1:40">
+      <c r="A11" s="1">
         <v>1001</v>
       </c>
-      <c r="B11"/>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="G11">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
         <v>1000001</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>100001</v>
       </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>0.5</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>0.5</v>
-      </c>
-      <c r="X11">
-        <v>0.5</v>
-      </c>
-      <c r="Z11">
-        <v>100</v>
-      </c>
-      <c r="AC11">
-        <v>10</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>0.2</v>
-      </c>
-      <c r="AH11">
-        <v>1</v>
-      </c>
-      <c r="AI11">
+      <c r="S11" s="1">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="1">
         <v>1000001</v>
       </c>
-      <c r="AJ11" s="1" t="s">
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL11" s="5">
+        <v>300100001</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>1001</v>
+      </c>
+      <c r="AN11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AK11" t="s">
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:40">
+      <c r="A12" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7</v>
+      </c>
+      <c r="P12" s="1">
+        <v>200001</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AL11" s="1">
-        <v>300100001</v>
-      </c>
-      <c r="AM11">
-        <v>1001</v>
-      </c>
-      <c r="AN11" t="s">
+      <c r="AL12" s="5">
+        <v>300100002</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>1002</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:40">
+      <c r="A13" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:40">
-      <c r="A12">
-        <v>1002</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="G12">
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1">
+        <v>201001</v>
+      </c>
+      <c r="S13" s="1">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U13" s="1">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="1">
         <v>1000001</v>
       </c>
-      <c r="I12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12">
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL13" s="5">
+        <v>300100003</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>1003</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:40">
+      <c r="A14" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>201002</v>
+      </c>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="1">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>1</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL14" s="5">
+        <v>300100004</v>
+      </c>
+      <c r="AM14" s="1">
+        <v>1004</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="12" customHeight="1" spans="1:40">
+      <c r="A15" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B15" s="1">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>21010001</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P15" s="1">
+        <v>100001</v>
+      </c>
+      <c r="S15" s="1">
+        <v>2</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U15" s="1">
+        <v>1</v>
+      </c>
+      <c r="V15" s="1">
+        <v>1</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>2</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>300200001</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>2001</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:40">
+      <c r="A16" s="1">
+        <v>2002</v>
+      </c>
+      <c r="B16" s="1">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>21000001</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="1">
+        <v>8</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>200001</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S16" s="1">
+        <v>2</v>
+      </c>
+      <c r="T16" s="1">
+        <v>10</v>
+      </c>
+      <c r="U16" s="1">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1">
+        <v>1</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>2</v>
+      </c>
+      <c r="AI16" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL16" s="1">
+        <v>300200002</v>
+      </c>
+      <c r="AM16" s="1">
+        <v>2002</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:40">
+      <c r="A17" s="1">
+        <v>2003</v>
+      </c>
+      <c r="B17" s="1">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="H17" s="1">
+        <v>21010002</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P17" s="1">
+        <v>201001</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S17" s="1">
+        <v>2</v>
+      </c>
+      <c r="T17" s="1">
+        <v>10</v>
+      </c>
+      <c r="U17" s="1">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>50</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>2</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL17" s="1">
+        <v>300200003</v>
+      </c>
+      <c r="AM17" s="1">
+        <v>2003</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:40">
+      <c r="A18" s="1">
+        <v>2004</v>
+      </c>
+      <c r="B18" s="1">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>21010003</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="1">
+        <v>201002</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S18" s="1">
+        <v>2</v>
+      </c>
+      <c r="T18" s="1">
+        <v>10</v>
+      </c>
+      <c r="U18" s="1">
+        <v>1</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>50</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>2</v>
+      </c>
+      <c r="AI18" s="1">
+        <v>2000001</v>
+      </c>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL18" s="1">
+        <v>300200004</v>
+      </c>
+      <c r="AM18" s="1">
+        <v>2004</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:40">
+      <c r="A19" s="1">
+        <v>3001</v>
+      </c>
+      <c r="B19" s="1">
+        <v>30</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S19" s="1">
+        <v>2</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U19" s="1">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1">
+        <v>1</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>120</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>500</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>3000001</v>
+      </c>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL19" s="1">
+        <v>300300001</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>3001</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:40">
+      <c r="A20" s="1">
+        <v>3002</v>
+      </c>
+      <c r="B20" s="1">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="1">
+        <v>300001</v>
+      </c>
+      <c r="R20" s="1">
+        <v>11</v>
+      </c>
+      <c r="S20" s="1">
+        <v>2</v>
+      </c>
+      <c r="T20" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U20" s="1">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>120</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>500</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI20" s="1">
+        <v>3000001</v>
+      </c>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL20" s="1">
+        <v>300300002</v>
+      </c>
+      <c r="AM20" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:40">
+      <c r="A21" s="1">
+        <v>3003</v>
+      </c>
+      <c r="B21" s="1">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1">
+        <v>400001</v>
+      </c>
+      <c r="R21" s="1">
+        <v>11</v>
+      </c>
+      <c r="S21" s="1">
+        <v>2</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U21" s="1">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1</v>
+      </c>
+      <c r="W21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>120</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>50</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="1">
+        <v>3000001</v>
+      </c>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL21" s="1">
+        <v>300300003</v>
+      </c>
+      <c r="AM21" s="1">
+        <v>3003</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:40">
+      <c r="A22" s="1">
+        <v>3004</v>
+      </c>
+      <c r="B22" s="1">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1">
+        <v>400002</v>
+      </c>
+      <c r="R22" s="1">
+        <v>11</v>
+      </c>
+      <c r="S22" s="1">
+        <v>2</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U22" s="1">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1">
+        <v>1</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>120</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>50</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI22" s="1">
+        <v>3000001</v>
+      </c>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL22" s="1">
+        <v>300300004</v>
+      </c>
+      <c r="AM22" s="1">
+        <v>3004</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:40">
+      <c r="A23" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B23" s="1">
+        <v>30</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>41000002</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P23" s="1">
+        <v>101001</v>
+      </c>
+      <c r="S23" s="1">
+        <v>2</v>
+      </c>
+      <c r="T23" s="1">
+        <v>3</v>
+      </c>
+      <c r="U23" s="1">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1">
+        <v>1</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>50</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI23" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL23" s="1">
+        <v>300400001</v>
+      </c>
+      <c r="AM23" s="1">
+        <v>4001</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:40">
+      <c r="A24" s="1">
+        <v>4002</v>
+      </c>
+      <c r="B24" s="1">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P24" s="1">
+        <v>500001</v>
+      </c>
+      <c r="R24" s="1">
+        <v>12</v>
+      </c>
+      <c r="S24" s="1">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1">
+        <v>1</v>
+      </c>
+      <c r="U24" s="1">
+        <v>1</v>
+      </c>
+      <c r="V24" s="1">
+        <v>1</v>
+      </c>
+      <c r="W24" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>50</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH24" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI24" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL24" s="1">
+        <v>300400002</v>
+      </c>
+      <c r="AM24" s="1">
+        <v>4002</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:40">
+      <c r="A25" s="1">
+        <v>4003</v>
+      </c>
+      <c r="B25" s="1">
+        <v>30</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P25" s="1">
+        <v>600001</v>
+      </c>
+      <c r="R25" s="1">
+        <v>32</v>
+      </c>
+      <c r="S25" s="1">
+        <v>2</v>
+      </c>
+      <c r="T25" s="1">
+        <v>6</v>
+      </c>
+      <c r="U25" s="1">
+        <v>1</v>
+      </c>
+      <c r="V25" s="1">
+        <v>1</v>
+      </c>
+      <c r="W25" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>50</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL25" s="1">
+        <v>300400003</v>
+      </c>
+      <c r="AM25" s="1">
+        <v>4003</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:40">
+      <c r="A26" s="1">
+        <v>4004</v>
+      </c>
+      <c r="B26" s="1">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P26" s="1">
+        <v>202001</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="R26" s="1">
+        <v>30</v>
+      </c>
+      <c r="S26" s="1">
+        <v>2</v>
+      </c>
+      <c r="T26" s="1">
+        <v>10</v>
+      </c>
+      <c r="U26" s="1">
+        <v>1</v>
+      </c>
+      <c r="V26" s="1">
+        <v>1</v>
+      </c>
+      <c r="W26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X26" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>50</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC26" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH26" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI26" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL26" s="1">
+        <v>300400004</v>
+      </c>
+      <c r="AM26" s="1">
+        <v>4004</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:40">
+      <c r="A27" s="1">
+        <v>4005</v>
+      </c>
+      <c r="B27" s="1">
+        <v>30</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P27" s="1">
+        <v>500002</v>
+      </c>
+      <c r="R27" s="1">
+        <v>13</v>
+      </c>
+      <c r="S27" s="1">
+        <v>1</v>
+      </c>
+      <c r="T27" s="1">
+        <v>1</v>
+      </c>
+      <c r="U27" s="1">
+        <v>1</v>
+      </c>
+      <c r="V27" s="1">
+        <v>1</v>
+      </c>
+      <c r="W27" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X27" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>50</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH27" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI27" s="1">
+        <v>4000001</v>
+      </c>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL27" s="1">
+        <v>300400005</v>
+      </c>
+      <c r="AM27" s="1">
+        <v>4005</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:40">
+      <c r="A28" s="1">
+        <v>5001</v>
+      </c>
+      <c r="B28" s="1">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P28" s="1">
+        <v>101002</v>
+      </c>
+      <c r="R28" s="1">
+        <v>11</v>
+      </c>
+      <c r="S28" s="1">
+        <v>2</v>
+      </c>
+      <c r="T28" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U28" s="1">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1">
+        <v>1</v>
+      </c>
+      <c r="W28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X28" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>60</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>300</v>
+      </c>
+      <c r="AC28" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD28" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI28" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL28" s="5">
+        <v>300500001</v>
+      </c>
+      <c r="AM28" s="1">
+        <v>5001</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:40">
+      <c r="A29" s="1">
+        <v>5002</v>
+      </c>
+      <c r="B29" s="1">
+        <v>30</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="H29" s="1">
+        <v>51010001</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J29" s="1">
+        <v>8</v>
+      </c>
+      <c r="P29" s="1">
+        <v>203001</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="R29" s="1">
+        <v>1</v>
+      </c>
+      <c r="S29" s="1">
+        <v>2</v>
+      </c>
+      <c r="T29" s="1">
+        <v>10</v>
+      </c>
+      <c r="U29" s="1">
+        <v>1</v>
+      </c>
+      <c r="V29" s="1">
+        <v>1</v>
+      </c>
+      <c r="W29" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X29" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>60</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>300</v>
+      </c>
+      <c r="AC29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL29" s="5">
+        <v>300500002</v>
+      </c>
+      <c r="AM29" s="1">
+        <v>5002</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:40">
+      <c r="A30" s="1">
+        <v>5003</v>
+      </c>
+      <c r="B30" s="1">
+        <v>30</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P30" s="1">
+        <v>700001</v>
+      </c>
+      <c r="R30" s="1">
+        <v>41</v>
+      </c>
+      <c r="S30" s="1">
+        <v>2</v>
+      </c>
+      <c r="T30" s="1">
+        <v>6</v>
+      </c>
+      <c r="U30" s="1">
+        <v>1</v>
+      </c>
+      <c r="V30" s="1">
+        <v>1</v>
+      </c>
+      <c r="W30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>150</v>
+      </c>
+      <c r="AC30" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH30" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI30" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL30" s="5">
+        <v>300500003</v>
+      </c>
+      <c r="AM30" s="1">
+        <v>5003</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:40">
+      <c r="A31" s="1">
+        <v>5004</v>
+      </c>
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P31" s="1">
+        <v>700002</v>
+      </c>
+      <c r="R31" s="1">
+        <v>41</v>
+      </c>
+      <c r="S31" s="1">
+        <v>2</v>
+      </c>
+      <c r="T31" s="1">
+        <v>6</v>
+      </c>
+      <c r="U31" s="1">
+        <v>1</v>
+      </c>
+      <c r="V31" s="1">
+        <v>1</v>
+      </c>
+      <c r="W31" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X31" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z31" s="1">
+        <v>150</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH31" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI31" s="1">
+        <v>5000001</v>
+      </c>
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL31" s="5">
+        <v>300500004</v>
+      </c>
+      <c r="AM31" s="1">
+        <v>5004</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:40">
+      <c r="A32" s="1">
+        <v>6001</v>
+      </c>
+      <c r="B32" s="1">
+        <v>30</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J32" s="1">
+        <v>3</v>
+      </c>
+      <c r="P32" s="1">
+        <v>200001</v>
+      </c>
+      <c r="S32" s="1">
+        <v>2</v>
+      </c>
+      <c r="T32" s="1">
+        <v>6</v>
+      </c>
+      <c r="U32" s="1">
+        <v>1</v>
+      </c>
+      <c r="V32" s="1">
+        <v>1</v>
+      </c>
+      <c r="W32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>80</v>
+      </c>
+      <c r="AC32" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH32" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI32" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="AJ32" s="5"/>
+      <c r="AK32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL32" s="5">
+        <v>300600001</v>
+      </c>
+      <c r="AM32" s="1">
+        <v>6001</v>
+      </c>
+      <c r="AN32" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:40">
+      <c r="A33" s="1">
+        <v>6002</v>
+      </c>
+      <c r="B33" s="1">
+        <v>30</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="H33" s="1">
+        <v>61010002</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="1">
         <v>7</v>
       </c>
-      <c r="P12">
+      <c r="N33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P33" s="1">
+        <v>204001</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S33" s="1">
+        <v>2</v>
+      </c>
+      <c r="T33" s="1">
+        <v>10</v>
+      </c>
+      <c r="U33" s="1">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1">
+        <v>1</v>
+      </c>
+      <c r="W33" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z33" s="1">
+        <v>80</v>
+      </c>
+      <c r="AC33" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH33" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI33" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="AJ33" s="5"/>
+      <c r="AK33" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL33" s="5">
+        <v>300600002</v>
+      </c>
+      <c r="AM33" s="1">
+        <v>6002</v>
+      </c>
+      <c r="AN33" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:40">
+      <c r="A34" s="1">
+        <v>6003</v>
+      </c>
+      <c r="B34" s="1">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="1">
+        <v>8</v>
+      </c>
+      <c r="P34" s="1">
         <v>200001</v>
       </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <v>0.5</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>0.5</v>
-      </c>
-      <c r="X12">
-        <v>0.5</v>
-      </c>
-      <c r="Z12">
-        <v>100</v>
-      </c>
-      <c r="AC12">
-        <v>10</v>
-      </c>
-      <c r="AD12">
-        <v>1</v>
-      </c>
-      <c r="AE12">
-        <v>0.2</v>
-      </c>
-      <c r="AH12">
-        <v>1</v>
-      </c>
-      <c r="AI12">
+      <c r="S34" s="1">
+        <v>2</v>
+      </c>
+      <c r="T34" s="1">
+        <v>6</v>
+      </c>
+      <c r="U34" s="1">
+        <v>1</v>
+      </c>
+      <c r="V34" s="1">
+        <v>1</v>
+      </c>
+      <c r="W34" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>300</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>500</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH34" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI34" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="AJ34" s="5"/>
+      <c r="AK34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL34" s="5">
+        <v>300600003</v>
+      </c>
+      <c r="AM34" s="1">
+        <v>6003</v>
+      </c>
+      <c r="AN34" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:40">
+      <c r="A35" s="1">
+        <v>6004</v>
+      </c>
+      <c r="B35" s="1">
+        <v>30</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="H35" s="1">
+        <v>61010003</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P35" s="1">
+        <v>204002</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S35" s="1">
+        <v>2</v>
+      </c>
+      <c r="T35" s="1">
+        <v>6</v>
+      </c>
+      <c r="U35" s="1">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1">
+        <v>1</v>
+      </c>
+      <c r="W35" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X35" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC35" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD35" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH35" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI35" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="AJ35" s="5"/>
+      <c r="AK35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL35" s="5">
+        <v>300600004</v>
+      </c>
+      <c r="AM35" s="1">
+        <v>6004</v>
+      </c>
+      <c r="AN35" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:40">
+      <c r="A36" s="1">
+        <v>6005</v>
+      </c>
+      <c r="B36" s="1">
+        <v>30</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="H36" s="1">
+        <v>61010003</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P36" s="1">
+        <v>204003</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S36" s="1">
+        <v>2</v>
+      </c>
+      <c r="T36" s="1">
+        <v>6</v>
+      </c>
+      <c r="U36" s="1">
+        <v>1</v>
+      </c>
+      <c r="V36" s="1">
+        <v>1</v>
+      </c>
+      <c r="W36" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X36" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>40</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH36" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI36" s="1">
+        <v>6000001</v>
+      </c>
+      <c r="AJ36" s="5"/>
+      <c r="AK36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL36" s="5">
+        <v>300600005</v>
+      </c>
+      <c r="AM36" s="1">
+        <v>6005</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:40">
+      <c r="A37" s="1">
+        <v>7001</v>
+      </c>
+      <c r="B37" s="1">
+        <v>30</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P37" s="1">
+        <v>200001</v>
+      </c>
+      <c r="S37" s="1">
+        <v>2</v>
+      </c>
+      <c r="T37" s="1">
+        <v>6</v>
+      </c>
+      <c r="U37" s="1">
+        <v>1</v>
+      </c>
+      <c r="V37" s="1">
+        <v>1</v>
+      </c>
+      <c r="W37" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X37" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>120</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>12</v>
+      </c>
+      <c r="AD37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH37" s="1">
+        <v>7</v>
+      </c>
+      <c r="AI37" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="AJ37" s="5"/>
+      <c r="AK37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL37" s="5">
+        <v>300700001</v>
+      </c>
+      <c r="AM37" s="1">
+        <v>7001</v>
+      </c>
+      <c r="AN37" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:40">
+      <c r="A38" s="1">
+        <v>7002</v>
+      </c>
+      <c r="B38" s="1">
+        <v>30</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="H38" s="1">
+        <v>71000001</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J38" s="1">
+        <v>8</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P38" s="1">
+        <v>205001</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S38" s="1">
+        <v>2</v>
+      </c>
+      <c r="T38" s="1">
+        <v>10</v>
+      </c>
+      <c r="U38" s="1">
+        <v>1</v>
+      </c>
+      <c r="V38" s="1">
+        <v>1</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>120</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH38" s="1">
+        <v>7</v>
+      </c>
+      <c r="AI38" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="AJ38" s="5"/>
+      <c r="AK38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL38" s="5">
+        <v>300700002</v>
+      </c>
+      <c r="AM38" s="1">
+        <v>7002</v>
+      </c>
+      <c r="AN38" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:40">
+      <c r="A39" s="1">
+        <v>7003</v>
+      </c>
+      <c r="B39" s="1">
+        <v>30</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="H39" s="1">
+        <v>71010004</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P39" s="1">
+        <v>205002</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S39" s="1">
+        <v>2</v>
+      </c>
+      <c r="T39" s="1">
+        <v>6</v>
+      </c>
+      <c r="U39" s="1">
+        <v>1</v>
+      </c>
+      <c r="V39" s="1">
+        <v>1</v>
+      </c>
+      <c r="W39" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X39" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z39" s="1">
+        <v>60</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH39" s="1">
+        <v>7</v>
+      </c>
+      <c r="AI39" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="AJ39" s="5"/>
+      <c r="AK39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL39" s="5">
+        <v>300700003</v>
+      </c>
+      <c r="AM39" s="1">
+        <v>7003</v>
+      </c>
+      <c r="AN39" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:40">
+      <c r="A40" s="1">
+        <v>7004</v>
+      </c>
+      <c r="B40" s="1">
+        <v>30</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="H40" s="1">
+        <v>71010004</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P40" s="1">
+        <v>205003</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="S40" s="1">
+        <v>2</v>
+      </c>
+      <c r="T40" s="1">
+        <v>6</v>
+      </c>
+      <c r="U40" s="1">
+        <v>1</v>
+      </c>
+      <c r="V40" s="1">
+        <v>1</v>
+      </c>
+      <c r="W40" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="X40" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>45</v>
+      </c>
+      <c r="Z40" s="1">
+        <v>60</v>
+      </c>
+      <c r="AC40" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH40" s="1">
+        <v>7</v>
+      </c>
+      <c r="AI40" s="1">
+        <v>7000001</v>
+      </c>
+      <c r="AJ40" s="5"/>
+      <c r="AK40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL40" s="5">
+        <v>300700004</v>
+      </c>
+      <c r="AM40" s="1">
+        <v>7004</v>
+      </c>
+      <c r="AN40" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="1:40">
+      <c r="A41" s="2">
+        <v>101001</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2">
         <v>1000001</v>
       </c>
-      <c r="AJ12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK12" t="s">
+      <c r="I41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J41" s="2">
+        <v>2</v>
+      </c>
+      <c r="P41" s="2">
+        <v>100001</v>
+      </c>
+      <c r="S41" s="2">
+        <v>1</v>
+      </c>
+      <c r="T41" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U41" s="2">
+        <v>1</v>
+      </c>
+      <c r="V41" s="2">
+        <v>1</v>
+      </c>
+      <c r="W41" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X41" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z41" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD41" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH41" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ41" s="7"/>
+      <c r="AK41" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AL12" s="1">
-        <v>300100002</v>
-      </c>
-      <c r="AM12">
-        <v>1002</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:40">
-      <c r="A13">
-        <v>1003</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="G13">
+      <c r="AM41" s="2">
+        <v>101001</v>
+      </c>
+      <c r="AN41" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="1:40">
+      <c r="A42" s="2">
+        <v>101002</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2">
         <v>1000001</v>
       </c>
-      <c r="I13" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="P13">
+      <c r="I42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J42" s="2">
+        <v>4</v>
+      </c>
+      <c r="P42" s="2">
+        <v>100001</v>
+      </c>
+      <c r="S42" s="2">
+        <v>1</v>
+      </c>
+      <c r="T42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U42" s="2">
+        <v>1</v>
+      </c>
+      <c r="V42" s="2">
+        <v>1</v>
+      </c>
+      <c r="W42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>100</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC42" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD42" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH42" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ42" s="7"/>
+      <c r="AK42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM42" s="2">
+        <v>101002</v>
+      </c>
+      <c r="AN42" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="1:40">
+      <c r="A43" s="2">
+        <v>102001</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J43" s="2">
+        <v>7</v>
+      </c>
+      <c r="P43" s="2">
+        <v>200001</v>
+      </c>
+      <c r="S43" s="2">
+        <v>1</v>
+      </c>
+      <c r="T43" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U43" s="2">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2">
+        <v>1</v>
+      </c>
+      <c r="W43" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X43" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC43" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH43" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ43" s="7"/>
+      <c r="AK43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM43" s="2">
+        <v>102001</v>
+      </c>
+      <c r="AN43" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="1:40">
+      <c r="A44" s="2">
+        <v>102002</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44" s="2">
+        <v>7</v>
+      </c>
+      <c r="P44" s="2">
+        <v>200001</v>
+      </c>
+      <c r="S44" s="2">
+        <v>1</v>
+      </c>
+      <c r="T44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U44" s="2">
+        <v>1</v>
+      </c>
+      <c r="V44" s="2">
+        <v>1</v>
+      </c>
+      <c r="W44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC44" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH44" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI44" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ44" s="7"/>
+      <c r="AK44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM44" s="2">
+        <v>102002</v>
+      </c>
+      <c r="AN44" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="1:40">
+      <c r="A45" s="2">
+        <v>102003</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="2">
+        <v>7</v>
+      </c>
+      <c r="P45" s="2">
+        <v>200001</v>
+      </c>
+      <c r="S45" s="2">
+        <v>1</v>
+      </c>
+      <c r="T45" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U45" s="2">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2">
+        <v>1</v>
+      </c>
+      <c r="W45" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X45" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z45" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI45" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ45" s="7"/>
+      <c r="AK45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM45" s="2">
+        <v>102003</v>
+      </c>
+      <c r="AN45" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="1:40">
+      <c r="A46" s="2">
+        <v>103001</v>
+      </c>
+      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="P46" s="2">
         <v>201001</v>
       </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>0.5</v>
-      </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
-      </c>
-      <c r="W13">
-        <v>0.5</v>
-      </c>
-      <c r="X13">
-        <v>0.5</v>
-      </c>
-      <c r="Z13">
-        <v>100</v>
-      </c>
-      <c r="AC13">
-        <v>10</v>
-      </c>
-      <c r="AD13">
-        <v>1</v>
-      </c>
-      <c r="AE13">
-        <v>0.2</v>
-      </c>
-      <c r="AH13">
-        <v>1</v>
-      </c>
-      <c r="AI13">
+      <c r="S46" s="2">
+        <v>1</v>
+      </c>
+      <c r="T46" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U46" s="2">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2">
+        <v>1</v>
+      </c>
+      <c r="W46" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X46" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="2">
         <v>1000001</v>
       </c>
-      <c r="AJ13" s="1" t="s">
+      <c r="AJ46" s="7"/>
+      <c r="AK46" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM46" s="2">
+        <v>103001</v>
+      </c>
+      <c r="AN46" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:40">
+      <c r="A47" s="2">
+        <v>103002</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" s="2">
+        <v>1</v>
+      </c>
+      <c r="P47" s="2">
+        <v>201002</v>
+      </c>
+      <c r="S47" s="2">
+        <v>1</v>
+      </c>
+      <c r="T47" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U47" s="2">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2">
+        <v>1</v>
+      </c>
+      <c r="W47" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="X47" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Z47" s="2">
+        <v>100</v>
+      </c>
+      <c r="AC47" s="2">
+        <v>10</v>
+      </c>
+      <c r="AD47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="6">
+        <v>10</v>
+      </c>
+      <c r="AH47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI47" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="AJ47" s="7"/>
+      <c r="AK47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM47" s="2">
+        <v>103002</v>
+      </c>
+      <c r="AN47" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:40">
+      <c r="A48" s="8">
+        <v>900001</v>
+      </c>
+      <c r="B48" s="9">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9">
+        <v>9</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="H48" s="9">
+        <v>21010001</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J48" s="9">
+        <v>2</v>
+      </c>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AK13" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL13" s="1">
-        <v>300100003</v>
-      </c>
-      <c r="AM13">
-        <v>1003</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:40">
-      <c r="A14">
-        <v>1004</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>1000001</v>
-      </c>
-      <c r="I14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>201002</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <v>0.5</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-      <c r="W14">
-        <v>0.5</v>
-      </c>
-      <c r="X14">
-        <v>0.5</v>
-      </c>
-      <c r="Z14">
-        <v>100</v>
-      </c>
-      <c r="AC14">
-        <v>10</v>
-      </c>
-      <c r="AD14">
-        <v>1</v>
-      </c>
-      <c r="AE14">
-        <v>0.2</v>
-      </c>
-      <c r="AH14">
-        <v>1</v>
-      </c>
-      <c r="AI14">
-        <v>1000001</v>
-      </c>
-      <c r="AJ14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>300100004</v>
-      </c>
-      <c r="AM14">
-        <v>1004</v>
-      </c>
-      <c r="AN14" t="s">
+      <c r="O48" s="9"/>
+      <c r="P48" s="9">
+        <v>100001</v>
+      </c>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9">
+        <v>2</v>
+      </c>
+      <c r="T48" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U48" s="9">
+        <v>1</v>
+      </c>
+      <c r="V48" s="9">
+        <v>1</v>
+      </c>
+      <c r="W48" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X48" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y48" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z48" s="9">
+        <v>1000</v>
+      </c>
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD48" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="9"/>
+      <c r="AH48" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI48" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="AJ48" s="8"/>
+      <c r="AK48" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL48" s="9">
+        <v>300200001</v>
+      </c>
+      <c r="AM48" s="8">
+        <v>900001</v>
+      </c>
+      <c r="AN48" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:40">
+      <c r="A49" s="8">
+        <v>900002</v>
+      </c>
+      <c r="B49" s="9">
+        <v>2</v>
+      </c>
+      <c r="C49" s="9">
+        <v>9</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="H49" s="9">
+        <v>21000001</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="9">
+        <v>8</v>
+      </c>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9">
+        <v>200001</v>
+      </c>
+      <c r="Q49" s="9" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="1:40">
-      <c r="A15">
-        <v>2001</v>
-      </c>
-      <c r="B15">
-        <v>30</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="G15">
+      <c r="R49" s="9"/>
+      <c r="S49" s="9">
+        <v>2</v>
+      </c>
+      <c r="T49" s="9">
+        <v>10</v>
+      </c>
+      <c r="U49" s="9">
+        <v>1</v>
+      </c>
+      <c r="V49" s="9">
+        <v>1</v>
+      </c>
+      <c r="W49" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X49" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y49" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z49" s="9">
+        <v>1000</v>
+      </c>
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF49" s="9"/>
+      <c r="AG49" s="9"/>
+      <c r="AH49" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI49" s="9">
         <v>2000001</v>
       </c>
-      <c r="H15">
-        <v>21010001</v>
-      </c>
-      <c r="I15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="N15" t="s">
-        <v>102</v>
-      </c>
-      <c r="P15">
-        <v>100001</v>
-      </c>
-      <c r="S15">
-        <v>2</v>
-      </c>
-      <c r="T15">
-        <v>0.5</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-      <c r="W15">
-        <v>0.5</v>
-      </c>
-      <c r="X15">
-        <v>0.5</v>
-      </c>
-      <c r="Y15">
-        <v>10</v>
-      </c>
-      <c r="Z15">
-        <v>100</v>
-      </c>
-      <c r="AC15">
-        <v>10</v>
-      </c>
-      <c r="AD15">
-        <v>1</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>2</v>
-      </c>
-      <c r="AI15">
-        <v>2000001</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK15" t="s">
+      <c r="AJ49" s="8"/>
+      <c r="AK49" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AL15">
-        <v>300200001</v>
-      </c>
-      <c r="AM15">
-        <v>2001</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40">
-      <c r="A16">
-        <v>2002</v>
-      </c>
-      <c r="B16">
-        <v>40</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>2000001</v>
-      </c>
-      <c r="H16">
-        <v>21000001</v>
-      </c>
-      <c r="I16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J16">
-        <v>8</v>
-      </c>
-      <c r="N16" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16">
-        <v>200001</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>105</v>
-      </c>
-      <c r="S16">
-        <v>2</v>
-      </c>
-      <c r="T16">
-        <v>10</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-      <c r="W16">
-        <v>0.5</v>
-      </c>
-      <c r="X16">
-        <v>0.5</v>
-      </c>
-      <c r="Y16">
-        <v>10</v>
-      </c>
-      <c r="Z16">
-        <v>100</v>
-      </c>
-      <c r="AC16">
-        <v>10</v>
-      </c>
-      <c r="AD16">
-        <v>1</v>
-      </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-      <c r="AH16">
-        <v>2</v>
-      </c>
-      <c r="AI16">
-        <v>2000001</v>
-      </c>
-      <c r="AJ16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL16">
+      <c r="AL49" s="9">
         <v>300200002</v>
       </c>
-      <c r="AM16">
-        <v>2002</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40">
-      <c r="A17">
-        <v>2003</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>2000001</v>
-      </c>
-      <c r="H17">
-        <v>21010002</v>
-      </c>
-      <c r="I17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17">
-        <v>201001</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>105</v>
-      </c>
-      <c r="S17">
-        <v>2</v>
-      </c>
-      <c r="T17">
-        <v>10</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
-      </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>0.5</v>
-      </c>
-      <c r="X17">
-        <v>0.5</v>
-      </c>
-      <c r="Y17">
-        <v>20</v>
-      </c>
-      <c r="Z17">
-        <v>50</v>
-      </c>
-      <c r="AC17">
-        <v>6</v>
-      </c>
-      <c r="AD17">
-        <v>1</v>
-      </c>
-      <c r="AE17">
-        <v>1</v>
-      </c>
-      <c r="AH17">
-        <v>2</v>
-      </c>
-      <c r="AI17">
-        <v>2000001</v>
-      </c>
-      <c r="AJ17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL17">
-        <v>300200003</v>
-      </c>
-      <c r="AM17">
-        <v>2003</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:40">
-      <c r="A18">
-        <v>2004</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2000001</v>
-      </c>
-      <c r="H18">
-        <v>21010003</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="s">
-        <v>107</v>
-      </c>
-      <c r="P18">
-        <v>201002</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>105</v>
-      </c>
-      <c r="S18">
-        <v>2</v>
-      </c>
-      <c r="T18">
-        <v>10</v>
-      </c>
-      <c r="U18">
-        <v>1</v>
-      </c>
-      <c r="V18">
-        <v>1</v>
-      </c>
-      <c r="W18">
-        <v>0.5</v>
-      </c>
-      <c r="X18">
-        <v>0.5</v>
-      </c>
-      <c r="Y18">
-        <v>20</v>
-      </c>
-      <c r="Z18">
-        <v>50</v>
-      </c>
-      <c r="AC18">
-        <v>3</v>
-      </c>
-      <c r="AD18">
-        <v>1</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AH18">
-        <v>2</v>
-      </c>
-      <c r="AI18">
-        <v>2000001</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL18">
-        <v>300200004</v>
-      </c>
-      <c r="AM18">
-        <v>2004</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:40">
-      <c r="A19">
-        <v>3001</v>
-      </c>
-      <c r="B19">
-        <v>30</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>110</v>
-      </c>
-      <c r="S19">
-        <v>2</v>
-      </c>
-      <c r="T19">
-        <v>0.5</v>
-      </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19">
-        <v>0.5</v>
-      </c>
-      <c r="X19">
-        <v>0.5</v>
-      </c>
-      <c r="Y19">
-        <v>120</v>
-      </c>
-      <c r="Z19">
-        <v>100</v>
-      </c>
-      <c r="AB19">
-        <v>500</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-      <c r="AH19">
-        <v>3</v>
-      </c>
-      <c r="AI19">
-        <v>3000001</v>
-      </c>
-      <c r="AJ19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL19">
-        <v>300300001</v>
-      </c>
-      <c r="AM19">
-        <v>3001</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:40">
-      <c r="A20">
-        <v>3002</v>
-      </c>
-      <c r="B20">
-        <v>30</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>110</v>
-      </c>
-      <c r="N20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P20">
-        <v>300001</v>
-      </c>
-      <c r="R20">
-        <v>11</v>
-      </c>
-      <c r="S20">
-        <v>2</v>
-      </c>
-      <c r="T20">
-        <v>1.5</v>
-      </c>
-      <c r="U20">
-        <v>1</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>0.5</v>
-      </c>
-      <c r="X20">
-        <v>0.15</v>
-      </c>
-      <c r="Y20">
-        <v>120</v>
-      </c>
-      <c r="Z20">
-        <v>100</v>
-      </c>
-      <c r="AC20">
-        <v>500</v>
-      </c>
-      <c r="AD20">
-        <v>1</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-      <c r="AH20">
-        <v>3</v>
-      </c>
-      <c r="AI20">
-        <v>3000001</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL20">
-        <v>300300002</v>
-      </c>
-      <c r="AM20">
-        <v>3002</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:40">
-      <c r="A21">
-        <v>3003</v>
-      </c>
-      <c r="B21">
-        <v>30</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" t="s">
-        <v>107</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-      <c r="P21">
-        <v>400001</v>
-      </c>
-      <c r="R21">
-        <v>11</v>
-      </c>
-      <c r="S21">
-        <v>2</v>
-      </c>
-      <c r="T21">
-        <v>0.5</v>
-      </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>0.5</v>
-      </c>
-      <c r="X21">
-        <v>0.5</v>
-      </c>
-      <c r="Y21">
-        <v>120</v>
-      </c>
-      <c r="Z21">
-        <v>50</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>1</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AH21">
-        <v>3</v>
-      </c>
-      <c r="AI21">
-        <v>3000001</v>
-      </c>
-      <c r="AJ21" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL21">
-        <v>300300003</v>
-      </c>
-      <c r="AM21">
-        <v>3003</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:40">
-      <c r="A22">
-        <v>3004</v>
-      </c>
-      <c r="B22">
-        <v>30</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="I22" t="s">
-        <v>110</v>
-      </c>
-      <c r="N22" t="s">
-        <v>107</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>400002</v>
-      </c>
-      <c r="R22">
-        <v>11</v>
-      </c>
-      <c r="S22">
-        <v>2</v>
-      </c>
-      <c r="T22">
-        <v>0.5</v>
-      </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22">
-        <v>0.5</v>
-      </c>
-      <c r="X22">
-        <v>0.5</v>
-      </c>
-      <c r="Y22">
-        <v>120</v>
-      </c>
-      <c r="Z22">
-        <v>50</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>1</v>
-      </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AH22">
-        <v>3</v>
-      </c>
-      <c r="AI22">
-        <v>3000001</v>
-      </c>
-      <c r="AJ22" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL22">
-        <v>300300004</v>
-      </c>
-      <c r="AM22">
-        <v>3004</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:40">
-      <c r="A23">
-        <v>4001</v>
-      </c>
-      <c r="B23">
-        <v>30</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>4000001</v>
-      </c>
-      <c r="H23">
-        <v>41000002</v>
-      </c>
-      <c r="I23" t="s">
-        <v>95</v>
-      </c>
-      <c r="J23">
-        <v>2</v>
-      </c>
-      <c r="N23" t="s">
-        <v>102</v>
-      </c>
-      <c r="P23">
-        <v>101001</v>
-      </c>
-      <c r="S23">
-        <v>2</v>
-      </c>
-      <c r="T23">
-        <v>3</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>0.5</v>
-      </c>
-      <c r="X23">
-        <v>0.5</v>
-      </c>
-      <c r="Y23">
-        <v>50</v>
-      </c>
-      <c r="Z23">
-        <v>100</v>
-      </c>
-      <c r="AC23">
-        <v>6</v>
-      </c>
-      <c r="AD23">
-        <v>1</v>
-      </c>
-      <c r="AE23">
-        <v>1</v>
-      </c>
-      <c r="AH23">
-        <v>4</v>
-      </c>
-      <c r="AI23">
-        <v>4000001</v>
-      </c>
-      <c r="AJ23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL23">
-        <v>300400001</v>
-      </c>
-      <c r="AM23">
-        <v>4001</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:40">
-      <c r="A24">
-        <v>4002</v>
-      </c>
-      <c r="B24">
-        <v>30</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>4000001</v>
-      </c>
-      <c r="I24" t="s">
-        <v>120</v>
-      </c>
-      <c r="P24">
-        <v>500001</v>
-      </c>
-      <c r="R24">
-        <v>12</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>0.5</v>
-      </c>
-      <c r="X24">
-        <v>0.5</v>
-      </c>
-      <c r="Y24">
-        <v>50</v>
-      </c>
-      <c r="Z24">
-        <v>100</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>1</v>
-      </c>
-      <c r="AH24">
-        <v>4</v>
-      </c>
-      <c r="AI24">
-        <v>4000001</v>
-      </c>
-      <c r="AJ24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL24">
-        <v>300400002</v>
-      </c>
-      <c r="AM24">
-        <v>4002</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:40">
-      <c r="A25">
-        <v>4003</v>
-      </c>
-      <c r="B25">
-        <v>30</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>4000001</v>
-      </c>
-      <c r="I25" t="s">
-        <v>120</v>
-      </c>
-      <c r="P25">
-        <v>600001</v>
-      </c>
-      <c r="R25">
-        <v>32</v>
-      </c>
-      <c r="S25">
-        <v>2</v>
-      </c>
-      <c r="T25">
-        <v>6</v>
-      </c>
-      <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-      <c r="W25">
-        <v>0.5</v>
-      </c>
-      <c r="X25">
-        <v>0.5</v>
-      </c>
-      <c r="Y25">
-        <v>50</v>
-      </c>
-      <c r="Z25">
-        <v>100</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>1</v>
-      </c>
-      <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AH25">
-        <v>4</v>
-      </c>
-      <c r="AI25">
-        <v>4000001</v>
-      </c>
-      <c r="AJ25" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL25">
-        <v>300400003</v>
-      </c>
-      <c r="AM25">
-        <v>4003</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:40">
-      <c r="A26">
-        <v>4004</v>
-      </c>
-      <c r="B26">
-        <v>30</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>4000001</v>
-      </c>
-      <c r="I26" t="s">
-        <v>120</v>
-      </c>
-      <c r="P26">
-        <v>202001</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>105</v>
-      </c>
-      <c r="R26">
-        <v>30</v>
-      </c>
-      <c r="S26">
-        <v>2</v>
-      </c>
-      <c r="T26">
-        <v>10</v>
-      </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-      <c r="W26">
-        <v>0.5</v>
-      </c>
-      <c r="X26">
-        <v>0.5</v>
-      </c>
-      <c r="Y26">
-        <v>50</v>
-      </c>
-      <c r="Z26">
-        <v>100</v>
-      </c>
-      <c r="AC26">
-        <v>3</v>
-      </c>
-      <c r="AD26">
-        <v>1</v>
-      </c>
-      <c r="AE26">
-        <v>1</v>
-      </c>
-      <c r="AH26">
-        <v>4</v>
-      </c>
-      <c r="AI26">
-        <v>4000001</v>
-      </c>
-      <c r="AJ26" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL26">
-        <v>300400004</v>
-      </c>
-      <c r="AM26">
-        <v>4004</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:40">
-      <c r="A27">
-        <v>4005</v>
-      </c>
-      <c r="B27">
-        <v>30</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>4000001</v>
-      </c>
-      <c r="I27" t="s">
-        <v>120</v>
-      </c>
-      <c r="P27">
-        <v>500002</v>
-      </c>
-      <c r="R27">
-        <v>13</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27">
-        <v>1</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>0.5</v>
-      </c>
-      <c r="X27">
-        <v>0.5</v>
-      </c>
-      <c r="Y27">
-        <v>50</v>
-      </c>
-      <c r="Z27">
-        <v>100</v>
-      </c>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AD27">
-        <v>1</v>
-      </c>
-      <c r="AE27">
-        <v>1</v>
-      </c>
-      <c r="AH27">
-        <v>4</v>
-      </c>
-      <c r="AI27">
-        <v>4000001</v>
-      </c>
-      <c r="AJ27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL27">
-        <v>300400005</v>
-      </c>
-      <c r="AM27">
-        <v>4005</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:40">
-      <c r="A28">
-        <v>5001</v>
-      </c>
-      <c r="B28">
-        <v>30</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>5000001</v>
-      </c>
-      <c r="I28" t="s">
-        <v>128</v>
-      </c>
-      <c r="P28">
-        <v>101002</v>
-      </c>
-      <c r="R28">
-        <v>11</v>
-      </c>
-      <c r="S28">
-        <v>2</v>
-      </c>
-      <c r="T28">
-        <v>1.5</v>
-      </c>
-      <c r="U28">
-        <v>1</v>
-      </c>
-      <c r="V28">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>0.5</v>
-      </c>
-      <c r="X28">
-        <v>0.5</v>
-      </c>
-      <c r="Y28">
-        <v>60</v>
-      </c>
-      <c r="Z28">
-        <v>300</v>
-      </c>
-      <c r="AC28">
-        <v>3</v>
-      </c>
-      <c r="AD28">
-        <v>1</v>
-      </c>
-      <c r="AE28">
-        <v>1</v>
-      </c>
-      <c r="AH28">
-        <v>5</v>
-      </c>
-      <c r="AI28">
-        <v>5000001</v>
-      </c>
-      <c r="AJ28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL28" s="1">
-        <v>300500001</v>
-      </c>
-      <c r="AM28">
-        <v>5001</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:40">
-      <c r="A29">
-        <v>5002</v>
-      </c>
-      <c r="B29">
-        <v>30</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>5000001</v>
-      </c>
-      <c r="H29">
-        <v>51010001</v>
-      </c>
-      <c r="I29" t="s">
-        <v>130</v>
-      </c>
-      <c r="J29">
-        <v>8</v>
-      </c>
-      <c r="P29">
-        <v>203001</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>131</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>2</v>
-      </c>
-      <c r="T29">
-        <v>10</v>
-      </c>
-      <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-      <c r="W29">
-        <v>0.5</v>
-      </c>
-      <c r="X29">
-        <v>0.5</v>
-      </c>
-      <c r="Y29">
-        <v>60</v>
-      </c>
-      <c r="Z29">
-        <v>300</v>
-      </c>
-      <c r="AC29">
-        <v>10</v>
-      </c>
-      <c r="AD29">
-        <v>1</v>
-      </c>
-      <c r="AE29">
-        <v>1</v>
-      </c>
-      <c r="AH29">
-        <v>5</v>
-      </c>
-      <c r="AI29">
-        <v>5000001</v>
-      </c>
-      <c r="AJ29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL29" s="1">
-        <v>300500002</v>
-      </c>
-      <c r="AM29">
-        <v>5002</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:40">
-      <c r="A30">
-        <v>5003</v>
-      </c>
-      <c r="B30">
-        <v>30</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>5000001</v>
-      </c>
-      <c r="I30" t="s">
-        <v>128</v>
-      </c>
-      <c r="P30">
-        <v>700001</v>
-      </c>
-      <c r="R30">
-        <v>41</v>
-      </c>
-      <c r="S30">
-        <v>2</v>
-      </c>
-      <c r="T30">
-        <v>6</v>
-      </c>
-      <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="V30">
-        <v>1</v>
-      </c>
-      <c r="W30">
-        <v>0.5</v>
-      </c>
-      <c r="X30">
-        <v>0.5</v>
-      </c>
-      <c r="Y30">
-        <v>45</v>
-      </c>
-      <c r="Z30">
-        <v>150</v>
-      </c>
-      <c r="AC30">
-        <v>6</v>
-      </c>
-      <c r="AD30">
-        <v>1</v>
-      </c>
-      <c r="AE30">
-        <v>1</v>
-      </c>
-      <c r="AH30">
-        <v>5</v>
-      </c>
-      <c r="AI30">
-        <v>5000001</v>
-      </c>
-      <c r="AJ30" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL30" s="1">
-        <v>300500003</v>
-      </c>
-      <c r="AM30">
-        <v>5003</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:40">
-      <c r="A31">
-        <v>5004</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>5000001</v>
-      </c>
-      <c r="I31" t="s">
-        <v>128</v>
-      </c>
-      <c r="P31">
-        <v>700002</v>
-      </c>
-      <c r="R31">
-        <v>41</v>
-      </c>
-      <c r="S31">
-        <v>2</v>
-      </c>
-      <c r="T31">
-        <v>6</v>
-      </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="W31">
-        <v>0.5</v>
-      </c>
-      <c r="X31">
-        <v>0.5</v>
-      </c>
-      <c r="Y31">
-        <v>45</v>
-      </c>
-      <c r="Z31">
-        <v>150</v>
-      </c>
-      <c r="AC31">
-        <v>3</v>
-      </c>
-      <c r="AD31">
-        <v>1</v>
-      </c>
-      <c r="AE31">
-        <v>1</v>
-      </c>
-      <c r="AH31">
-        <v>5</v>
-      </c>
-      <c r="AI31">
-        <v>5000001</v>
-      </c>
-      <c r="AJ31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL31" s="1">
-        <v>300500004</v>
-      </c>
-      <c r="AM31">
-        <v>5004</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:40">
-      <c r="A32">
-        <v>6001</v>
-      </c>
-      <c r="B32">
-        <v>30</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32">
-        <v>6000001</v>
-      </c>
-      <c r="I32" t="s">
-        <v>95</v>
-      </c>
-      <c r="J32">
-        <v>3</v>
-      </c>
-      <c r="P32">
-        <v>200001</v>
-      </c>
-      <c r="S32">
-        <v>2</v>
-      </c>
-      <c r="T32">
-        <v>6</v>
-      </c>
-      <c r="U32">
-        <v>1</v>
-      </c>
-      <c r="V32">
-        <v>1</v>
-      </c>
-      <c r="W32">
-        <v>0.5</v>
-      </c>
-      <c r="X32">
-        <v>0.5</v>
-      </c>
-      <c r="Y32">
-        <v>30</v>
-      </c>
-      <c r="Z32">
-        <v>80</v>
-      </c>
-      <c r="AC32">
-        <v>5</v>
-      </c>
-      <c r="AD32">
-        <v>1</v>
-      </c>
-      <c r="AE32">
-        <v>1</v>
-      </c>
-      <c r="AH32">
-        <v>6</v>
-      </c>
-      <c r="AI32">
-        <v>6000001</v>
-      </c>
-      <c r="AJ32" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL32" s="1">
-        <v>300600001</v>
-      </c>
-      <c r="AM32">
-        <v>6001</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:40">
-      <c r="A33">
-        <v>6002</v>
-      </c>
-      <c r="B33">
-        <v>30</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>6000001</v>
-      </c>
-      <c r="H33">
-        <v>61010002</v>
-      </c>
-      <c r="I33" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33">
-        <v>7</v>
-      </c>
-      <c r="N33" t="s">
-        <v>102</v>
-      </c>
-      <c r="P33">
-        <v>204001</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>139</v>
-      </c>
-      <c r="S33">
-        <v>2</v>
-      </c>
-      <c r="T33">
-        <v>10</v>
-      </c>
-      <c r="U33">
-        <v>1</v>
-      </c>
-      <c r="V33">
-        <v>1</v>
-      </c>
-      <c r="W33">
-        <v>0.5</v>
-      </c>
-      <c r="X33">
-        <v>0.5</v>
-      </c>
-      <c r="Y33">
-        <v>30</v>
-      </c>
-      <c r="Z33">
-        <v>80</v>
-      </c>
-      <c r="AC33">
-        <v>10</v>
-      </c>
-      <c r="AD33">
-        <v>1</v>
-      </c>
-      <c r="AE33">
-        <v>1</v>
-      </c>
-      <c r="AH33">
-        <v>6</v>
-      </c>
-      <c r="AI33">
-        <v>6000001</v>
-      </c>
-      <c r="AJ33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL33" s="1">
-        <v>300600002</v>
-      </c>
-      <c r="AM33">
-        <v>6002</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:40">
-      <c r="A34">
-        <v>6003</v>
-      </c>
-      <c r="B34">
-        <v>30</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="G34">
-        <v>6000001</v>
-      </c>
-      <c r="I34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34">
-        <v>8</v>
-      </c>
-      <c r="P34">
-        <v>200001</v>
-      </c>
-      <c r="S34">
-        <v>2</v>
-      </c>
-      <c r="T34">
-        <v>6</v>
-      </c>
-      <c r="U34">
-        <v>1</v>
-      </c>
-      <c r="V34">
-        <v>1</v>
-      </c>
-      <c r="W34">
-        <v>0.5</v>
-      </c>
-      <c r="X34">
-        <v>0.5</v>
-      </c>
-      <c r="Y34">
-        <v>300</v>
-      </c>
-      <c r="Z34">
-        <v>100</v>
-      </c>
-      <c r="AC34">
-        <v>500</v>
-      </c>
-      <c r="AD34">
-        <v>1</v>
-      </c>
-      <c r="AE34">
-        <v>1</v>
-      </c>
-      <c r="AH34">
-        <v>6</v>
-      </c>
-      <c r="AI34">
-        <v>6000001</v>
-      </c>
-      <c r="AJ34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL34" s="1">
-        <v>300600003</v>
-      </c>
-      <c r="AM34">
-        <v>6003</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:40">
-      <c r="A35">
-        <v>6004</v>
-      </c>
-      <c r="B35">
-        <v>30</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="G35">
-        <v>6000001</v>
-      </c>
-      <c r="H35">
-        <v>61010003</v>
-      </c>
-      <c r="I35" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="N35" t="s">
-        <v>107</v>
-      </c>
-      <c r="P35">
-        <v>204002</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>139</v>
-      </c>
-      <c r="S35">
-        <v>2</v>
-      </c>
-      <c r="T35">
-        <v>6</v>
-      </c>
-      <c r="U35">
-        <v>1</v>
-      </c>
-      <c r="V35">
-        <v>1</v>
-      </c>
-      <c r="W35">
-        <v>0.5</v>
-      </c>
-      <c r="X35">
-        <v>0.5</v>
-      </c>
-      <c r="Y35">
-        <v>20</v>
-      </c>
-      <c r="Z35">
-        <v>40</v>
-      </c>
-      <c r="AC35">
-        <v>6</v>
-      </c>
-      <c r="AD35">
-        <v>1</v>
-      </c>
-      <c r="AE35">
-        <v>1</v>
-      </c>
-      <c r="AH35">
-        <v>6</v>
-      </c>
-      <c r="AI35">
-        <v>6000001</v>
-      </c>
-      <c r="AJ35" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL35" s="1">
-        <v>300600004</v>
-      </c>
-      <c r="AM35">
-        <v>6004</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:40">
-      <c r="A36">
-        <v>6005</v>
-      </c>
-      <c r="B36">
-        <v>30</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="G36">
-        <v>6000001</v>
-      </c>
-      <c r="H36">
-        <v>61010003</v>
-      </c>
-      <c r="I36" t="s">
-        <v>95</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
-        <v>107</v>
-      </c>
-      <c r="P36">
-        <v>204003</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>139</v>
-      </c>
-      <c r="S36">
-        <v>2</v>
-      </c>
-      <c r="T36">
-        <v>6</v>
-      </c>
-      <c r="U36">
-        <v>1</v>
-      </c>
-      <c r="V36">
-        <v>1</v>
-      </c>
-      <c r="W36">
-        <v>0.5</v>
-      </c>
-      <c r="X36">
-        <v>0.5</v>
-      </c>
-      <c r="Y36">
-        <v>20</v>
-      </c>
-      <c r="Z36">
-        <v>40</v>
-      </c>
-      <c r="AC36">
-        <v>3</v>
-      </c>
-      <c r="AD36">
-        <v>1</v>
-      </c>
-      <c r="AE36">
-        <v>1</v>
-      </c>
-      <c r="AH36">
-        <v>6</v>
-      </c>
-      <c r="AI36">
-        <v>6000001</v>
-      </c>
-      <c r="AJ36" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL36" s="1">
-        <v>300600005</v>
-      </c>
-      <c r="AM36">
-        <v>6005</v>
-      </c>
-      <c r="AN36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:40">
-      <c r="A37">
-        <v>7001</v>
-      </c>
-      <c r="B37">
-        <v>30</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
-        <v>144</v>
-      </c>
-      <c r="G37">
-        <v>7000001</v>
-      </c>
-      <c r="I37" t="s">
-        <v>120</v>
-      </c>
-      <c r="P37">
-        <v>200001</v>
-      </c>
-      <c r="S37">
-        <v>2</v>
-      </c>
-      <c r="T37">
-        <v>6</v>
-      </c>
-      <c r="U37">
-        <v>1</v>
-      </c>
-      <c r="V37">
-        <v>1</v>
-      </c>
-      <c r="W37">
-        <v>0.5</v>
-      </c>
-      <c r="X37">
-        <v>0.5</v>
-      </c>
-      <c r="Y37">
-        <v>45</v>
-      </c>
-      <c r="Z37">
-        <v>120</v>
-      </c>
-      <c r="AC37">
-        <v>12</v>
-      </c>
-      <c r="AD37">
-        <v>1</v>
-      </c>
-      <c r="AE37">
-        <v>1</v>
-      </c>
-      <c r="AH37">
-        <v>7</v>
-      </c>
-      <c r="AI37">
-        <v>7000001</v>
-      </c>
-      <c r="AJ37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK37" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL37" s="1">
-        <v>300700001</v>
-      </c>
-      <c r="AM37">
-        <v>7001</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:40">
-      <c r="A38">
-        <v>7002</v>
-      </c>
-      <c r="B38">
-        <v>30</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="G38">
-        <v>7000001</v>
-      </c>
-      <c r="H38">
-        <v>71000001</v>
-      </c>
-      <c r="I38" t="s">
-        <v>130</v>
-      </c>
-      <c r="J38">
-        <v>8</v>
-      </c>
-      <c r="N38" t="s">
-        <v>107</v>
-      </c>
-      <c r="P38">
-        <v>205001</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>105</v>
-      </c>
-      <c r="S38">
-        <v>2</v>
-      </c>
-      <c r="T38">
-        <v>10</v>
-      </c>
-      <c r="U38">
-        <v>1</v>
-      </c>
-      <c r="V38">
-        <v>1</v>
-      </c>
-      <c r="W38">
-        <v>0.5</v>
-      </c>
-      <c r="X38">
-        <v>0.5</v>
-      </c>
-      <c r="Y38">
-        <v>45</v>
-      </c>
-      <c r="Z38">
-        <v>120</v>
-      </c>
-      <c r="AC38">
-        <v>3</v>
-      </c>
-      <c r="AD38">
-        <v>1</v>
-      </c>
-      <c r="AE38">
-        <v>1</v>
-      </c>
-      <c r="AH38">
-        <v>7</v>
-      </c>
-      <c r="AI38">
-        <v>7000001</v>
-      </c>
-      <c r="AJ38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL38" s="1">
-        <v>300700002</v>
-      </c>
-      <c r="AM38">
-        <v>7002</v>
-      </c>
-      <c r="AN38" t="s">
+      <c r="AM49" s="8">
+        <v>900002</v>
+      </c>
+      <c r="AN49" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:40">
-      <c r="A39">
-        <v>7003</v>
-      </c>
-      <c r="B39">
-        <v>30</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="G39">
-        <v>7000001</v>
-      </c>
-      <c r="H39">
-        <v>71010004</v>
-      </c>
-      <c r="I39" t="s">
-        <v>95</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="N39" t="s">
-        <v>102</v>
-      </c>
-      <c r="P39">
-        <v>205002</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>105</v>
-      </c>
-      <c r="S39">
-        <v>2</v>
-      </c>
-      <c r="T39">
-        <v>6</v>
-      </c>
-      <c r="U39">
-        <v>1</v>
-      </c>
-      <c r="V39">
-        <v>1</v>
-      </c>
-      <c r="W39">
-        <v>0.5</v>
-      </c>
-      <c r="X39">
-        <v>0.5</v>
-      </c>
-      <c r="Y39">
-        <v>45</v>
-      </c>
-      <c r="Z39">
-        <v>60</v>
-      </c>
-      <c r="AC39">
-        <v>6</v>
-      </c>
-      <c r="AD39">
-        <v>1</v>
-      </c>
-      <c r="AE39">
-        <v>1</v>
-      </c>
-      <c r="AH39">
-        <v>7</v>
-      </c>
-      <c r="AI39">
-        <v>7000001</v>
-      </c>
-      <c r="AJ39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK39" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL39" s="1">
-        <v>300700003</v>
-      </c>
-      <c r="AM39">
-        <v>7003</v>
-      </c>
-      <c r="AN39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:40">
-      <c r="A40">
-        <v>7004</v>
-      </c>
-      <c r="B40">
-        <v>30</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="G40">
-        <v>7000001</v>
-      </c>
-      <c r="H40">
-        <v>71010004</v>
-      </c>
-      <c r="I40" t="s">
-        <v>95</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="N40" t="s">
-        <v>102</v>
-      </c>
-      <c r="P40">
-        <v>205003</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>105</v>
-      </c>
-      <c r="S40">
-        <v>2</v>
-      </c>
-      <c r="T40">
-        <v>6</v>
-      </c>
-      <c r="U40">
-        <v>1</v>
-      </c>
-      <c r="V40">
-        <v>1</v>
-      </c>
-      <c r="W40">
-        <v>0.5</v>
-      </c>
-      <c r="X40">
-        <v>0.5</v>
-      </c>
-      <c r="Y40">
-        <v>45</v>
-      </c>
-      <c r="Z40">
-        <v>60</v>
-      </c>
-      <c r="AC40">
-        <v>3</v>
-      </c>
-      <c r="AD40">
-        <v>1</v>
-      </c>
-      <c r="AE40">
-        <v>1</v>
-      </c>
-      <c r="AH40">
-        <v>7</v>
-      </c>
-      <c r="AI40">
-        <v>7000001</v>
-      </c>
-      <c r="AJ40" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL40" s="1">
-        <v>300700004</v>
-      </c>
-      <c r="AM40">
-        <v>7004</v>
-      </c>
-      <c r="AN40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:40">
-      <c r="A41">
-        <v>101001</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-      <c r="G41">
-        <v>1000001</v>
-      </c>
-      <c r="I41" t="s">
-        <v>95</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="P41">
-        <v>100001</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="T41">
-        <v>0.5</v>
-      </c>
-      <c r="U41">
-        <v>1</v>
-      </c>
-      <c r="V41">
-        <v>1</v>
-      </c>
-      <c r="W41">
-        <v>0.5</v>
-      </c>
-      <c r="X41">
-        <v>0.5</v>
-      </c>
-      <c r="Z41">
-        <v>100</v>
-      </c>
-      <c r="AC41">
-        <v>10</v>
-      </c>
-      <c r="AD41">
-        <v>1</v>
-      </c>
-      <c r="AE41">
-        <v>0.2</v>
-      </c>
-      <c r="AH41">
-        <v>1</v>
-      </c>
-      <c r="AI41">
-        <v>1000001</v>
-      </c>
-      <c r="AJ41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM41">
-        <v>101001</v>
-      </c>
-      <c r="AN41" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:40">
-      <c r="A42">
-        <v>102001</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-      <c r="G42">
-        <v>1000001</v>
-      </c>
-      <c r="I42" t="s">
-        <v>95</v>
-      </c>
-      <c r="J42">
-        <v>7</v>
-      </c>
-      <c r="P42">
-        <v>200001</v>
-      </c>
-      <c r="S42">
-        <v>1</v>
-      </c>
-      <c r="T42">
-        <v>0.5</v>
-      </c>
-      <c r="U42">
-        <v>1</v>
-      </c>
-      <c r="V42">
-        <v>1</v>
-      </c>
-      <c r="W42">
-        <v>0.5</v>
-      </c>
-      <c r="X42">
-        <v>0.5</v>
-      </c>
-      <c r="Z42">
-        <v>100</v>
-      </c>
-      <c r="AC42">
-        <v>10</v>
-      </c>
-      <c r="AD42">
-        <v>1</v>
-      </c>
-      <c r="AE42">
-        <v>0.2</v>
-      </c>
-      <c r="AH42">
-        <v>1</v>
-      </c>
-      <c r="AI42">
-        <v>1000001</v>
-      </c>
-      <c r="AJ42" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM42">
-        <v>102001</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:40">
-      <c r="A43">
-        <v>103001</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-      <c r="G43">
-        <v>1000001</v>
-      </c>
-      <c r="I43" t="s">
-        <v>95</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="P43">
-        <v>201001</v>
-      </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="T43">
-        <v>0.5</v>
-      </c>
-      <c r="U43">
-        <v>1</v>
-      </c>
-      <c r="V43">
-        <v>1</v>
-      </c>
-      <c r="W43">
-        <v>0.5</v>
-      </c>
-      <c r="X43">
-        <v>0.5</v>
-      </c>
-      <c r="Z43">
-        <v>100</v>
-      </c>
-      <c r="AC43">
-        <v>10</v>
-      </c>
-      <c r="AD43">
-        <v>1</v>
-      </c>
-      <c r="AE43">
-        <v>0.2</v>
-      </c>
-      <c r="AH43">
-        <v>1</v>
-      </c>
-      <c r="AI43">
-        <v>1000001</v>
-      </c>
-      <c r="AJ43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK43" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM43">
-        <v>103001</v>
-      </c>
-      <c r="AN43" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:40">
-      <c r="A44">
-        <v>103002</v>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>1000001</v>
-      </c>
-      <c r="I44" t="s">
-        <v>95</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>201002</v>
-      </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="T44">
-        <v>0.5</v>
-      </c>
-      <c r="U44">
-        <v>1</v>
-      </c>
-      <c r="V44">
-        <v>1</v>
-      </c>
-      <c r="W44">
-        <v>0.5</v>
-      </c>
-      <c r="X44">
-        <v>0.5</v>
-      </c>
-      <c r="Z44">
-        <v>100</v>
-      </c>
-      <c r="AC44">
-        <v>10</v>
-      </c>
-      <c r="AD44">
-        <v>1</v>
-      </c>
-      <c r="AE44">
-        <v>0.2</v>
-      </c>
-      <c r="AH44">
-        <v>1</v>
-      </c>
-      <c r="AI44">
-        <v>1000001</v>
-      </c>
-      <c r="AJ44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK44" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM44">
-        <v>103002</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:40">
-      <c r="A45" s="1">
-        <v>900001</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>9</v>
-      </c>
-      <c r="G45">
-        <v>2000001</v>
-      </c>
-      <c r="H45">
-        <v>21010001</v>
-      </c>
-      <c r="I45" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45">
-        <v>2</v>
-      </c>
-      <c r="N45" t="s">
-        <v>102</v>
-      </c>
-      <c r="P45">
-        <v>100001</v>
-      </c>
-      <c r="S45">
-        <v>2</v>
-      </c>
-      <c r="T45">
-        <v>0.5</v>
-      </c>
-      <c r="U45">
-        <v>1</v>
-      </c>
-      <c r="V45">
-        <v>1</v>
-      </c>
-      <c r="W45">
-        <v>0.5</v>
-      </c>
-      <c r="X45">
-        <v>0.5</v>
-      </c>
-      <c r="Y45">
-        <v>10</v>
-      </c>
-      <c r="Z45">
-        <v>100</v>
-      </c>
-      <c r="AC45">
-        <v>100</v>
-      </c>
-      <c r="AD45">
-        <v>1</v>
-      </c>
-      <c r="AE45">
-        <v>1</v>
-      </c>
-      <c r="AH45">
-        <v>2</v>
-      </c>
-      <c r="AI45">
-        <v>2000001</v>
-      </c>
-      <c r="AJ45" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK45" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL45">
-        <v>300200001</v>
-      </c>
-      <c r="AM45" s="1">
-        <v>900001</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:40">
-      <c r="A46" s="1">
-        <v>900002</v>
-      </c>
-      <c r="B46">
-        <v>2</v>
-      </c>
-      <c r="C46">
-        <v>9</v>
-      </c>
-      <c r="G46">
-        <v>2000001</v>
-      </c>
-      <c r="H46">
-        <v>21000001</v>
-      </c>
-      <c r="I46" t="s">
-        <v>95</v>
-      </c>
-      <c r="J46">
-        <v>8</v>
-      </c>
-      <c r="N46" t="s">
-        <v>104</v>
-      </c>
-      <c r="P46">
-        <v>200001</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>105</v>
-      </c>
-      <c r="S46">
-        <v>2</v>
-      </c>
-      <c r="T46">
-        <v>10</v>
-      </c>
-      <c r="U46">
-        <v>1</v>
-      </c>
-      <c r="V46">
-        <v>1</v>
-      </c>
-      <c r="W46">
-        <v>0.5</v>
-      </c>
-      <c r="X46">
-        <v>0.5</v>
-      </c>
-      <c r="Y46">
-        <v>10</v>
-      </c>
-      <c r="Z46">
-        <v>100</v>
-      </c>
-      <c r="AC46">
-        <v>100</v>
-      </c>
-      <c r="AD46">
-        <v>1</v>
-      </c>
-      <c r="AE46">
-        <v>1</v>
-      </c>
-      <c r="AH46">
-        <v>2</v>
-      </c>
-      <c r="AI46">
-        <v>2000001</v>
-      </c>
-      <c r="AJ46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK46" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL46">
-        <v>300200002</v>
-      </c>
-      <c r="AM46" s="1">
-        <v>900002</v>
-      </c>
-      <c r="AN46" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:40">
-      <c r="A47" s="1">
+    <row r="50" customFormat="1" spans="1:40">
+      <c r="A50" s="3">
         <v>989996</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="P47">
-        <v>200001</v>
-      </c>
-      <c r="S47">
-        <v>2</v>
-      </c>
-      <c r="T47">
-        <v>6</v>
-      </c>
-      <c r="U47">
-        <v>1</v>
-      </c>
-      <c r="V47">
-        <v>1</v>
-      </c>
-      <c r="W47">
-        <v>0.5</v>
-      </c>
-      <c r="X47">
-        <v>0.5</v>
-      </c>
-      <c r="Z47">
-        <v>100</v>
-      </c>
-      <c r="AC47">
-        <v>35</v>
-      </c>
-      <c r="AD47">
-        <v>1</v>
-      </c>
-      <c r="AE47">
-        <v>1</v>
-      </c>
-      <c r="AH47" s="1">
-        <v>989996</v>
-      </c>
-      <c r="AI47" s="2"/>
-      <c r="AJ47" s="2"/>
-      <c r="AK47" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM47">
-        <v>1</v>
-      </c>
-      <c r="AN47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:40">
-      <c r="A48" s="1">
-        <v>989997</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="P48">
-        <v>200001</v>
-      </c>
-      <c r="S48">
-        <v>2</v>
-      </c>
-      <c r="T48">
-        <v>6</v>
-      </c>
-      <c r="U48">
-        <v>1</v>
-      </c>
-      <c r="V48">
-        <v>1</v>
-      </c>
-      <c r="W48">
-        <v>0.5</v>
-      </c>
-      <c r="X48">
-        <v>0.5</v>
-      </c>
-      <c r="Z48">
-        <v>100</v>
-      </c>
-      <c r="AC48">
-        <v>35</v>
-      </c>
-      <c r="AD48">
-        <v>1</v>
-      </c>
-      <c r="AE48">
-        <v>1</v>
-      </c>
-      <c r="AH48" s="1">
-        <v>989997</v>
-      </c>
-      <c r="AI48" s="2"/>
-      <c r="AJ48" s="2"/>
-      <c r="AK48" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM48">
-        <v>1</v>
-      </c>
-      <c r="AN48" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:40">
-      <c r="A49" s="1">
-        <v>989998</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="P49">
-        <v>200001</v>
-      </c>
-      <c r="S49">
-        <v>2</v>
-      </c>
-      <c r="T49">
-        <v>6</v>
-      </c>
-      <c r="U49">
-        <v>1</v>
-      </c>
-      <c r="V49">
-        <v>1</v>
-      </c>
-      <c r="W49">
-        <v>0.5</v>
-      </c>
-      <c r="X49">
-        <v>0.5</v>
-      </c>
-      <c r="Z49">
-        <v>100</v>
-      </c>
-      <c r="AC49">
-        <v>35</v>
-      </c>
-      <c r="AD49">
-        <v>1</v>
-      </c>
-      <c r="AE49">
-        <v>1</v>
-      </c>
-      <c r="AH49" s="1">
-        <v>989998</v>
-      </c>
-      <c r="AI49" s="2"/>
-      <c r="AJ49" s="2"/>
-      <c r="AK49" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM49">
-        <v>1</v>
-      </c>
-      <c r="AN49" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:40">
-      <c r="A50" s="1">
-        <v>989999</v>
-      </c>
-      <c r="B50" s="2"/>
+      <c r="B50" s="4"/>
       <c r="C50">
         <v>1</v>
       </c>
@@ -5203,27 +5235,29 @@
       <c r="AD50">
         <v>1</v>
       </c>
-      <c r="AE50">
-        <v>1</v>
-      </c>
-      <c r="AH50">
-        <v>989999</v>
-      </c>
+      <c r="AE50" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>989996</v>
+      </c>
+      <c r="AI50" s="4"/>
+      <c r="AJ50" s="4"/>
       <c r="AK50" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM50">
         <v>1</v>
       </c>
       <c r="AN50" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:40">
-      <c r="A51" s="1">
-        <v>999947</v>
-      </c>
-      <c r="B51" s="2"/>
+      <c r="A51" s="3">
+        <v>989997</v>
+      </c>
+      <c r="B51" s="4"/>
       <c r="C51">
         <v>1</v>
       </c>
@@ -5257,29 +5291,29 @@
       <c r="AD51">
         <v>1</v>
       </c>
-      <c r="AE51">
-        <v>1</v>
-      </c>
-      <c r="AH51" s="1">
-        <v>999947</v>
-      </c>
-      <c r="AI51" s="2"/>
-      <c r="AJ51" s="2"/>
+      <c r="AE51" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>989997</v>
+      </c>
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
       <c r="AK51" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM51">
         <v>1</v>
       </c>
       <c r="AN51" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:40">
-      <c r="A52" s="1">
-        <v>999948</v>
-      </c>
-      <c r="B52" s="2"/>
+      <c r="A52" s="3">
+        <v>989998</v>
+      </c>
+      <c r="B52" s="4"/>
       <c r="C52">
         <v>1</v>
       </c>
@@ -5313,29 +5347,29 @@
       <c r="AD52">
         <v>1</v>
       </c>
-      <c r="AE52">
-        <v>1</v>
-      </c>
-      <c r="AH52" s="1">
-        <v>999948</v>
-      </c>
-      <c r="AI52" s="2"/>
-      <c r="AJ52" s="2"/>
+      <c r="AE52" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>989998</v>
+      </c>
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
       <c r="AK52" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM52">
         <v>1</v>
       </c>
       <c r="AN52" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:40">
-      <c r="A53" s="1">
-        <v>999949</v>
-      </c>
-      <c r="B53" s="2"/>
+      <c r="A53" s="3">
+        <v>989999</v>
+      </c>
+      <c r="B53" s="4"/>
       <c r="C53">
         <v>1</v>
       </c>
@@ -5369,29 +5403,27 @@
       <c r="AD53">
         <v>1</v>
       </c>
-      <c r="AE53">
-        <v>1</v>
-      </c>
-      <c r="AH53" s="1">
-        <v>999949</v>
-      </c>
-      <c r="AI53" s="2"/>
-      <c r="AJ53" s="2"/>
+      <c r="AE53" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH53">
+        <v>989999</v>
+      </c>
       <c r="AK53" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM53">
         <v>1</v>
       </c>
       <c r="AN53" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:40">
-      <c r="A54" s="1">
-        <v>999950</v>
-      </c>
-      <c r="B54" s="2"/>
+      <c r="A54" s="3">
+        <v>999947</v>
+      </c>
+      <c r="B54" s="4"/>
       <c r="C54">
         <v>1</v>
       </c>
@@ -5425,29 +5457,29 @@
       <c r="AD54">
         <v>1</v>
       </c>
-      <c r="AE54">
-        <v>1</v>
-      </c>
-      <c r="AH54" s="1">
-        <v>999950</v>
-      </c>
-      <c r="AI54" s="2"/>
-      <c r="AJ54" s="2"/>
+      <c r="AE54" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>999947</v>
+      </c>
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
       <c r="AK54" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM54">
         <v>1</v>
       </c>
       <c r="AN54" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:40">
-      <c r="A55" s="1">
-        <v>999951</v>
-      </c>
-      <c r="B55" s="2"/>
+      <c r="A55" s="3">
+        <v>999948</v>
+      </c>
+      <c r="B55" s="4"/>
       <c r="C55">
         <v>1</v>
       </c>
@@ -5481,29 +5513,29 @@
       <c r="AD55">
         <v>1</v>
       </c>
-      <c r="AE55">
-        <v>1</v>
-      </c>
-      <c r="AH55" s="1">
-        <v>999951</v>
-      </c>
-      <c r="AI55" s="2"/>
-      <c r="AJ55" s="2"/>
+      <c r="AE55" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH55" s="3">
+        <v>999948</v>
+      </c>
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
       <c r="AK55" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
       <c r="AN55" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:40">
-      <c r="A56" s="1">
-        <v>999952</v>
-      </c>
-      <c r="B56" s="2"/>
+      <c r="A56" s="3">
+        <v>999949</v>
+      </c>
+      <c r="B56" s="4"/>
       <c r="C56">
         <v>1</v>
       </c>
@@ -5537,29 +5569,29 @@
       <c r="AD56">
         <v>1</v>
       </c>
-      <c r="AE56">
-        <v>1</v>
-      </c>
-      <c r="AH56" s="1">
-        <v>999952</v>
-      </c>
-      <c r="AI56" s="2"/>
-      <c r="AJ56" s="2"/>
+      <c r="AE56" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH56" s="3">
+        <v>999949</v>
+      </c>
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
       <c r="AK56" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
       <c r="AN56" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:40">
-      <c r="A57" s="1">
-        <v>999953</v>
-      </c>
-      <c r="B57" s="2"/>
+      <c r="A57" s="3">
+        <v>999950</v>
+      </c>
+      <c r="B57" s="4"/>
       <c r="C57">
         <v>1</v>
       </c>
@@ -5593,29 +5625,29 @@
       <c r="AD57">
         <v>1</v>
       </c>
-      <c r="AE57">
-        <v>1</v>
-      </c>
-      <c r="AH57" s="1">
-        <v>999953</v>
-      </c>
-      <c r="AI57" s="2"/>
-      <c r="AJ57" s="2"/>
+      <c r="AE57" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>999950</v>
+      </c>
+      <c r="AI57" s="4"/>
+      <c r="AJ57" s="4"/>
       <c r="AK57" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
       <c r="AN57" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:40">
-      <c r="A58" s="1">
-        <v>999954</v>
-      </c>
-      <c r="B58" s="2"/>
+      <c r="A58" s="3">
+        <v>999951</v>
+      </c>
+      <c r="B58" s="4"/>
       <c r="C58">
         <v>1</v>
       </c>
@@ -5649,29 +5681,29 @@
       <c r="AD58">
         <v>1</v>
       </c>
-      <c r="AE58">
-        <v>1</v>
-      </c>
-      <c r="AH58" s="1">
-        <v>999954</v>
-      </c>
-      <c r="AI58" s="2"/>
-      <c r="AJ58" s="2"/>
+      <c r="AE58" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>999951</v>
+      </c>
+      <c r="AI58" s="4"/>
+      <c r="AJ58" s="4"/>
       <c r="AK58" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
       <c r="AN58" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:40">
-      <c r="A59" s="1">
-        <v>999955</v>
-      </c>
-      <c r="B59" s="2"/>
+      <c r="A59" s="3">
+        <v>999952</v>
+      </c>
+      <c r="B59" s="4"/>
       <c r="C59">
         <v>1</v>
       </c>
@@ -5705,29 +5737,29 @@
       <c r="AD59">
         <v>1</v>
       </c>
-      <c r="AE59">
-        <v>1</v>
-      </c>
-      <c r="AH59" s="1">
-        <v>999955</v>
-      </c>
-      <c r="AI59" s="2"/>
-      <c r="AJ59" s="2"/>
+      <c r="AE59" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>999952</v>
+      </c>
+      <c r="AI59" s="4"/>
+      <c r="AJ59" s="4"/>
       <c r="AK59" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
       <c r="AN59" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:40">
-      <c r="A60" s="1">
-        <v>999956</v>
-      </c>
-      <c r="B60" s="2"/>
+      <c r="A60" s="3">
+        <v>999953</v>
+      </c>
+      <c r="B60" s="4"/>
       <c r="C60">
         <v>1</v>
       </c>
@@ -5761,29 +5793,29 @@
       <c r="AD60">
         <v>1</v>
       </c>
-      <c r="AE60">
-        <v>1</v>
-      </c>
-      <c r="AH60" s="1">
-        <v>999956</v>
-      </c>
-      <c r="AI60" s="2"/>
-      <c r="AJ60" s="2"/>
+      <c r="AE60" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH60" s="3">
+        <v>999953</v>
+      </c>
+      <c r="AI60" s="4"/>
+      <c r="AJ60" s="4"/>
       <c r="AK60" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
       <c r="AN60" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:40">
-      <c r="A61" s="1">
-        <v>999957</v>
-      </c>
-      <c r="B61" s="2"/>
+      <c r="A61" s="3">
+        <v>999954</v>
+      </c>
+      <c r="B61" s="4"/>
       <c r="C61">
         <v>1</v>
       </c>
@@ -5817,29 +5849,29 @@
       <c r="AD61">
         <v>1</v>
       </c>
-      <c r="AE61">
-        <v>1</v>
-      </c>
-      <c r="AH61" s="1">
-        <v>999957</v>
-      </c>
-      <c r="AI61" s="2"/>
-      <c r="AJ61" s="2"/>
+      <c r="AE61" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>999954</v>
+      </c>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
       <c r="AK61" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
       <c r="AN61" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:40">
-      <c r="A62" s="1">
-        <v>999958</v>
-      </c>
-      <c r="B62" s="2"/>
+      <c r="A62" s="3">
+        <v>999955</v>
+      </c>
+      <c r="B62" s="4"/>
       <c r="C62">
         <v>1</v>
       </c>
@@ -5873,29 +5905,29 @@
       <c r="AD62">
         <v>1</v>
       </c>
-      <c r="AE62">
-        <v>1</v>
-      </c>
-      <c r="AH62" s="1">
-        <v>999958</v>
-      </c>
-      <c r="AI62" s="2"/>
-      <c r="AJ62" s="2"/>
+      <c r="AE62" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>999955</v>
+      </c>
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
       <c r="AK62" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
       <c r="AN62" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:40">
-      <c r="A63" s="1">
-        <v>999959</v>
-      </c>
-      <c r="B63" s="2"/>
+      <c r="A63" s="3">
+        <v>999956</v>
+      </c>
+      <c r="B63" s="4"/>
       <c r="C63">
         <v>1</v>
       </c>
@@ -5929,29 +5961,29 @@
       <c r="AD63">
         <v>1</v>
       </c>
-      <c r="AE63">
-        <v>1</v>
-      </c>
-      <c r="AH63" s="1">
-        <v>999959</v>
-      </c>
-      <c r="AI63" s="2"/>
-      <c r="AJ63" s="2"/>
+      <c r="AE63" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>999956</v>
+      </c>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
       <c r="AK63" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
       <c r="AN63" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:40">
-      <c r="A64" s="1">
-        <v>999960</v>
-      </c>
-      <c r="B64" s="2"/>
+      <c r="A64" s="3">
+        <v>999957</v>
+      </c>
+      <c r="B64" s="4"/>
       <c r="C64">
         <v>1</v>
       </c>
@@ -5985,29 +6017,29 @@
       <c r="AD64">
         <v>1</v>
       </c>
-      <c r="AE64">
-        <v>1</v>
-      </c>
-      <c r="AH64" s="1">
-        <v>999960</v>
-      </c>
-      <c r="AI64" s="2"/>
-      <c r="AJ64" s="2"/>
+      <c r="AE64" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>999957</v>
+      </c>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
       <c r="AK64" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
       <c r="AN64" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:40">
-      <c r="A65" s="1">
-        <v>999961</v>
-      </c>
-      <c r="B65" s="2"/>
+      <c r="A65" s="3">
+        <v>999958</v>
+      </c>
+      <c r="B65" s="4"/>
       <c r="C65">
         <v>1</v>
       </c>
@@ -6041,29 +6073,29 @@
       <c r="AD65">
         <v>1</v>
       </c>
-      <c r="AE65">
-        <v>1</v>
-      </c>
-      <c r="AH65" s="1">
-        <v>999961</v>
-      </c>
-      <c r="AI65" s="2"/>
-      <c r="AJ65" s="2"/>
+      <c r="AE65" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>999958</v>
+      </c>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
       <c r="AK65" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
       <c r="AN65" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:40">
-      <c r="A66" s="1">
-        <v>999962</v>
-      </c>
-      <c r="B66" s="2"/>
+      <c r="A66" s="3">
+        <v>999959</v>
+      </c>
+      <c r="B66" s="4"/>
       <c r="C66">
         <v>1</v>
       </c>
@@ -6097,29 +6129,29 @@
       <c r="AD66">
         <v>1</v>
       </c>
-      <c r="AE66">
-        <v>1</v>
-      </c>
-      <c r="AH66" s="1">
-        <v>999962</v>
-      </c>
-      <c r="AI66" s="2"/>
-      <c r="AJ66" s="2"/>
+      <c r="AE66" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH66" s="3">
+        <v>999959</v>
+      </c>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
       <c r="AK66" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
       <c r="AN66" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:40">
-      <c r="A67" s="1">
-        <v>999963</v>
-      </c>
-      <c r="B67" s="2"/>
+      <c r="A67" s="3">
+        <v>999960</v>
+      </c>
+      <c r="B67" s="4"/>
       <c r="C67">
         <v>1</v>
       </c>
@@ -6153,29 +6185,29 @@
       <c r="AD67">
         <v>1</v>
       </c>
-      <c r="AE67">
-        <v>1</v>
-      </c>
-      <c r="AH67" s="1">
-        <v>999963</v>
-      </c>
-      <c r="AI67" s="2"/>
-      <c r="AJ67" s="2"/>
+      <c r="AE67" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH67" s="3">
+        <v>999960</v>
+      </c>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
       <c r="AK67" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
       <c r="AN67" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:40">
-      <c r="A68" s="1">
-        <v>999964</v>
-      </c>
-      <c r="B68" s="2"/>
+      <c r="A68" s="3">
+        <v>999961</v>
+      </c>
+      <c r="B68" s="4"/>
       <c r="C68">
         <v>1</v>
       </c>
@@ -6209,29 +6241,29 @@
       <c r="AD68">
         <v>1</v>
       </c>
-      <c r="AE68">
-        <v>1</v>
-      </c>
-      <c r="AH68" s="1">
-        <v>999964</v>
-      </c>
-      <c r="AI68" s="2"/>
-      <c r="AJ68" s="2"/>
+      <c r="AE68" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>999961</v>
+      </c>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
       <c r="AK68" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
       <c r="AN68" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:40">
-      <c r="A69" s="1">
-        <v>999965</v>
-      </c>
-      <c r="B69" s="2"/>
+      <c r="A69" s="3">
+        <v>999962</v>
+      </c>
+      <c r="B69" s="4"/>
       <c r="C69">
         <v>1</v>
       </c>
@@ -6265,29 +6297,29 @@
       <c r="AD69">
         <v>1</v>
       </c>
-      <c r="AE69">
-        <v>1</v>
-      </c>
-      <c r="AH69" s="1">
-        <v>999965</v>
-      </c>
-      <c r="AI69" s="2"/>
-      <c r="AJ69" s="2"/>
+      <c r="AE69" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>999962</v>
+      </c>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
       <c r="AK69" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
       <c r="AN69" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:40">
-      <c r="A70" s="1">
-        <v>999966</v>
-      </c>
-      <c r="B70" s="2"/>
+      <c r="A70" s="3">
+        <v>999963</v>
+      </c>
+      <c r="B70" s="4"/>
       <c r="C70">
         <v>1</v>
       </c>
@@ -6321,29 +6353,29 @@
       <c r="AD70">
         <v>1</v>
       </c>
-      <c r="AE70">
-        <v>1</v>
-      </c>
-      <c r="AH70" s="1">
-        <v>999966</v>
-      </c>
-      <c r="AI70" s="2"/>
-      <c r="AJ70" s="2"/>
+      <c r="AE70" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>999963</v>
+      </c>
+      <c r="AI70" s="4"/>
+      <c r="AJ70" s="4"/>
       <c r="AK70" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
       <c r="AN70" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:40">
-      <c r="A71" s="1">
-        <v>999967</v>
-      </c>
-      <c r="B71" s="2"/>
+      <c r="A71" s="3">
+        <v>999964</v>
+      </c>
+      <c r="B71" s="4"/>
       <c r="C71">
         <v>1</v>
       </c>
@@ -6377,29 +6409,29 @@
       <c r="AD71">
         <v>1</v>
       </c>
-      <c r="AE71">
-        <v>1</v>
-      </c>
-      <c r="AH71" s="1">
-        <v>999967</v>
-      </c>
-      <c r="AI71" s="2"/>
-      <c r="AJ71" s="2"/>
+      <c r="AE71" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>999964</v>
+      </c>
+      <c r="AI71" s="4"/>
+      <c r="AJ71" s="4"/>
       <c r="AK71" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
       <c r="AN71" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:40">
-      <c r="A72" s="1">
-        <v>999968</v>
-      </c>
-      <c r="B72" s="2"/>
+      <c r="A72" s="3">
+        <v>999965</v>
+      </c>
+      <c r="B72" s="4"/>
       <c r="C72">
         <v>1</v>
       </c>
@@ -6433,29 +6465,29 @@
       <c r="AD72">
         <v>1</v>
       </c>
-      <c r="AE72">
-        <v>1</v>
-      </c>
-      <c r="AH72" s="1">
-        <v>999968</v>
-      </c>
-      <c r="AI72" s="2"/>
-      <c r="AJ72" s="2"/>
+      <c r="AE72" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3">
+        <v>999965</v>
+      </c>
+      <c r="AI72" s="4"/>
+      <c r="AJ72" s="4"/>
       <c r="AK72" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
       <c r="AN72" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:40">
-      <c r="A73" s="1">
-        <v>999969</v>
-      </c>
-      <c r="B73" s="2"/>
+      <c r="A73" s="3">
+        <v>999966</v>
+      </c>
+      <c r="B73" s="4"/>
       <c r="C73">
         <v>1</v>
       </c>
@@ -6489,29 +6521,29 @@
       <c r="AD73">
         <v>1</v>
       </c>
-      <c r="AE73">
-        <v>1</v>
-      </c>
-      <c r="AH73" s="1">
-        <v>999969</v>
-      </c>
-      <c r="AI73" s="2"/>
-      <c r="AJ73" s="2"/>
+      <c r="AE73" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>999966</v>
+      </c>
+      <c r="AI73" s="4"/>
+      <c r="AJ73" s="4"/>
       <c r="AK73" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
       <c r="AN73" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:40">
-      <c r="A74" s="1">
-        <v>999970</v>
-      </c>
-      <c r="B74" s="2"/>
+      <c r="A74" s="3">
+        <v>999967</v>
+      </c>
+      <c r="B74" s="4"/>
       <c r="C74">
         <v>1</v>
       </c>
@@ -6545,29 +6577,29 @@
       <c r="AD74">
         <v>1</v>
       </c>
-      <c r="AE74">
-        <v>1</v>
-      </c>
-      <c r="AH74" s="1">
-        <v>999970</v>
-      </c>
-      <c r="AI74" s="2"/>
-      <c r="AJ74" s="2"/>
+      <c r="AE74" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>999967</v>
+      </c>
+      <c r="AI74" s="4"/>
+      <c r="AJ74" s="4"/>
       <c r="AK74" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
       <c r="AN74" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:40">
-      <c r="A75" s="1">
-        <v>999971</v>
-      </c>
-      <c r="B75" s="2"/>
+      <c r="A75" s="3">
+        <v>999968</v>
+      </c>
+      <c r="B75" s="4"/>
       <c r="C75">
         <v>1</v>
       </c>
@@ -6601,29 +6633,29 @@
       <c r="AD75">
         <v>1</v>
       </c>
-      <c r="AE75">
-        <v>1</v>
-      </c>
-      <c r="AH75" s="1">
-        <v>999971</v>
-      </c>
-      <c r="AI75" s="2"/>
-      <c r="AJ75" s="2"/>
+      <c r="AE75" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>999968</v>
+      </c>
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
       <c r="AK75" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
       <c r="AN75" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:40">
-      <c r="A76" s="1">
-        <v>999972</v>
-      </c>
-      <c r="B76" s="2"/>
+      <c r="A76" s="3">
+        <v>999969</v>
+      </c>
+      <c r="B76" s="4"/>
       <c r="C76">
         <v>1</v>
       </c>
@@ -6657,29 +6689,29 @@
       <c r="AD76">
         <v>1</v>
       </c>
-      <c r="AE76">
-        <v>1</v>
-      </c>
-      <c r="AH76" s="1">
-        <v>999972</v>
-      </c>
-      <c r="AI76" s="2"/>
-      <c r="AJ76" s="2"/>
+      <c r="AE76" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH76" s="3">
+        <v>999969</v>
+      </c>
+      <c r="AI76" s="4"/>
+      <c r="AJ76" s="4"/>
       <c r="AK76" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
       <c r="AN76" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:40">
-      <c r="A77" s="1">
-        <v>999973</v>
-      </c>
-      <c r="B77" s="2"/>
+      <c r="A77" s="3">
+        <v>999970</v>
+      </c>
+      <c r="B77" s="4"/>
       <c r="C77">
         <v>1</v>
       </c>
@@ -6713,29 +6745,29 @@
       <c r="AD77">
         <v>1</v>
       </c>
-      <c r="AE77">
-        <v>1</v>
-      </c>
-      <c r="AH77" s="1">
-        <v>999973</v>
-      </c>
-      <c r="AI77" s="2"/>
-      <c r="AJ77" s="2"/>
+      <c r="AE77" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>999970</v>
+      </c>
+      <c r="AI77" s="4"/>
+      <c r="AJ77" s="4"/>
       <c r="AK77" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
       <c r="AN77" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:40">
-      <c r="A78" s="1">
-        <v>999974</v>
-      </c>
-      <c r="B78" s="2"/>
+      <c r="A78" s="3">
+        <v>999971</v>
+      </c>
+      <c r="B78" s="4"/>
       <c r="C78">
         <v>1</v>
       </c>
@@ -6769,29 +6801,29 @@
       <c r="AD78">
         <v>1</v>
       </c>
-      <c r="AE78">
-        <v>1</v>
-      </c>
-      <c r="AH78" s="1">
-        <v>999974</v>
-      </c>
-      <c r="AI78" s="2"/>
-      <c r="AJ78" s="2"/>
+      <c r="AE78" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH78" s="3">
+        <v>999971</v>
+      </c>
+      <c r="AI78" s="4"/>
+      <c r="AJ78" s="4"/>
       <c r="AK78" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
       <c r="AN78" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:40">
-      <c r="A79" s="1">
-        <v>999975</v>
-      </c>
-      <c r="B79" s="2"/>
+      <c r="A79" s="3">
+        <v>999972</v>
+      </c>
+      <c r="B79" s="4"/>
       <c r="C79">
         <v>1</v>
       </c>
@@ -6825,29 +6857,29 @@
       <c r="AD79">
         <v>1</v>
       </c>
-      <c r="AE79">
-        <v>1</v>
-      </c>
-      <c r="AH79" s="1">
-        <v>999975</v>
-      </c>
-      <c r="AI79" s="2"/>
-      <c r="AJ79" s="2"/>
+      <c r="AE79" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH79" s="3">
+        <v>999972</v>
+      </c>
+      <c r="AI79" s="4"/>
+      <c r="AJ79" s="4"/>
       <c r="AK79" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
       <c r="AN79" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:40">
-      <c r="A80" s="1">
-        <v>999976</v>
-      </c>
-      <c r="B80" s="2"/>
+      <c r="A80" s="3">
+        <v>999973</v>
+      </c>
+      <c r="B80" s="4"/>
       <c r="C80">
         <v>1</v>
       </c>
@@ -6881,29 +6913,29 @@
       <c r="AD80">
         <v>1</v>
       </c>
-      <c r="AE80">
-        <v>1</v>
-      </c>
-      <c r="AH80" s="1">
-        <v>999976</v>
-      </c>
-      <c r="AI80" s="2"/>
-      <c r="AJ80" s="2"/>
+      <c r="AE80" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH80" s="3">
+        <v>999973</v>
+      </c>
+      <c r="AI80" s="4"/>
+      <c r="AJ80" s="4"/>
       <c r="AK80" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
       <c r="AN80" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:40">
-      <c r="A81" s="1">
-        <v>999977</v>
-      </c>
-      <c r="B81" s="2"/>
+      <c r="A81" s="3">
+        <v>999974</v>
+      </c>
+      <c r="B81" s="4"/>
       <c r="C81">
         <v>1</v>
       </c>
@@ -6937,29 +6969,29 @@
       <c r="AD81">
         <v>1</v>
       </c>
-      <c r="AE81">
-        <v>1</v>
-      </c>
-      <c r="AH81" s="1">
-        <v>999977</v>
-      </c>
-      <c r="AI81" s="2"/>
-      <c r="AJ81" s="2"/>
+      <c r="AE81" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>999974</v>
+      </c>
+      <c r="AI81" s="4"/>
+      <c r="AJ81" s="4"/>
       <c r="AK81" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
       <c r="AN81" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:40">
-      <c r="A82" s="1">
-        <v>999978</v>
-      </c>
-      <c r="B82" s="2"/>
+      <c r="A82" s="3">
+        <v>999975</v>
+      </c>
+      <c r="B82" s="4"/>
       <c r="C82">
         <v>1</v>
       </c>
@@ -6993,29 +7025,29 @@
       <c r="AD82">
         <v>1</v>
       </c>
-      <c r="AE82">
-        <v>1</v>
-      </c>
-      <c r="AH82" s="1">
-        <v>999978</v>
-      </c>
-      <c r="AI82" s="2"/>
-      <c r="AJ82" s="2"/>
+      <c r="AE82" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH82" s="3">
+        <v>999975</v>
+      </c>
+      <c r="AI82" s="4"/>
+      <c r="AJ82" s="4"/>
       <c r="AK82" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
       <c r="AN82" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:40">
-      <c r="A83" s="1">
-        <v>999979</v>
-      </c>
-      <c r="B83" s="2"/>
+      <c r="A83" s="3">
+        <v>999976</v>
+      </c>
+      <c r="B83" s="4"/>
       <c r="C83">
         <v>1</v>
       </c>
@@ -7049,29 +7081,29 @@
       <c r="AD83">
         <v>1</v>
       </c>
-      <c r="AE83">
-        <v>1</v>
-      </c>
-      <c r="AH83" s="1">
-        <v>999979</v>
-      </c>
-      <c r="AI83" s="2"/>
-      <c r="AJ83" s="2"/>
+      <c r="AE83" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>999976</v>
+      </c>
+      <c r="AI83" s="4"/>
+      <c r="AJ83" s="4"/>
       <c r="AK83" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
       <c r="AN83" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:40">
-      <c r="A84" s="1">
-        <v>999980</v>
-      </c>
-      <c r="B84" s="2"/>
+      <c r="A84" s="3">
+        <v>999977</v>
+      </c>
+      <c r="B84" s="4"/>
       <c r="C84">
         <v>1</v>
       </c>
@@ -7105,29 +7137,29 @@
       <c r="AD84">
         <v>1</v>
       </c>
-      <c r="AE84">
-        <v>1</v>
-      </c>
-      <c r="AH84" s="1">
-        <v>999980</v>
-      </c>
-      <c r="AI84" s="2"/>
-      <c r="AJ84" s="2"/>
+      <c r="AE84" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>999977</v>
+      </c>
+      <c r="AI84" s="4"/>
+      <c r="AJ84" s="4"/>
       <c r="AK84" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
       <c r="AN84" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:40">
-      <c r="A85" s="1">
-        <v>999981</v>
-      </c>
-      <c r="B85" s="2"/>
+      <c r="A85" s="3">
+        <v>999978</v>
+      </c>
+      <c r="B85" s="4"/>
       <c r="C85">
         <v>1</v>
       </c>
@@ -7161,28 +7193,29 @@
       <c r="AD85">
         <v>1</v>
       </c>
-      <c r="AE85">
-        <v>1</v>
-      </c>
-      <c r="AH85" s="1">
-        <v>999981</v>
-      </c>
-      <c r="AI85" s="2"/>
-      <c r="AJ85" s="2"/>
+      <c r="AE85" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>999978</v>
+      </c>
+      <c r="AI85" s="4"/>
+      <c r="AJ85" s="4"/>
       <c r="AK85" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
       <c r="AN85" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:40">
-      <c r="A86">
-        <v>999982</v>
-      </c>
+      <c r="A86" s="3">
+        <v>999979</v>
+      </c>
+      <c r="B86" s="4"/>
       <c r="C86">
         <v>1</v>
       </c>
@@ -7216,26 +7249,29 @@
       <c r="AD86">
         <v>1</v>
       </c>
-      <c r="AE86">
-        <v>1</v>
-      </c>
-      <c r="AH86">
-        <v>999982</v>
-      </c>
+      <c r="AE86" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>999979</v>
+      </c>
+      <c r="AI86" s="4"/>
+      <c r="AJ86" s="4"/>
       <c r="AK86" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
       <c r="AN86" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:40">
-      <c r="A87">
-        <v>999983</v>
-      </c>
+      <c r="A87" s="3">
+        <v>999980</v>
+      </c>
+      <c r="B87" s="4"/>
       <c r="C87">
         <v>1</v>
       </c>
@@ -7269,26 +7305,29 @@
       <c r="AD87">
         <v>1</v>
       </c>
-      <c r="AE87">
-        <v>1</v>
-      </c>
-      <c r="AH87">
-        <v>999983</v>
-      </c>
+      <c r="AE87" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>999980</v>
+      </c>
+      <c r="AI87" s="4"/>
+      <c r="AJ87" s="4"/>
       <c r="AK87" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
       <c r="AN87" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:40">
-      <c r="A88">
-        <v>999984</v>
-      </c>
+      <c r="A88" s="3">
+        <v>999981</v>
+      </c>
+      <c r="B88" s="4"/>
       <c r="C88">
         <v>1</v>
       </c>
@@ -7322,25 +7361,27 @@
       <c r="AD88">
         <v>1</v>
       </c>
-      <c r="AE88">
-        <v>1</v>
-      </c>
-      <c r="AH88">
-        <v>999984</v>
-      </c>
+      <c r="AE88" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>999981</v>
+      </c>
+      <c r="AI88" s="4"/>
+      <c r="AJ88" s="4"/>
       <c r="AK88" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
       <c r="AN88" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:40">
       <c r="A89">
-        <v>999985</v>
+        <v>999982</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7375,25 +7416,25 @@
       <c r="AD89">
         <v>1</v>
       </c>
-      <c r="AE89">
-        <v>1</v>
+      <c r="AE89" s="1">
+        <v>10</v>
       </c>
       <c r="AH89">
-        <v>999985</v>
+        <v>999982</v>
       </c>
       <c r="AK89" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
       <c r="AN89" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:40">
       <c r="A90">
-        <v>999986</v>
+        <v>999983</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7428,25 +7469,25 @@
       <c r="AD90">
         <v>1</v>
       </c>
-      <c r="AE90">
-        <v>1</v>
+      <c r="AE90" s="1">
+        <v>10</v>
       </c>
       <c r="AH90">
-        <v>999986</v>
+        <v>999983</v>
       </c>
       <c r="AK90" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
       <c r="AN90" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:40">
       <c r="A91">
-        <v>999987</v>
+        <v>999984</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7481,25 +7522,25 @@
       <c r="AD91">
         <v>1</v>
       </c>
-      <c r="AE91">
-        <v>1</v>
+      <c r="AE91" s="1">
+        <v>10</v>
       </c>
       <c r="AH91">
-        <v>999987</v>
+        <v>999984</v>
       </c>
       <c r="AK91" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
       <c r="AN91" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:40">
       <c r="A92">
-        <v>999988</v>
+        <v>999985</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7534,25 +7575,25 @@
       <c r="AD92">
         <v>1</v>
       </c>
-      <c r="AE92">
-        <v>1</v>
+      <c r="AE92" s="1">
+        <v>10</v>
       </c>
       <c r="AH92">
-        <v>999988</v>
+        <v>999985</v>
       </c>
       <c r="AK92" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
       <c r="AN92" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:40">
       <c r="A93">
-        <v>999989</v>
+        <v>999986</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7587,25 +7628,25 @@
       <c r="AD93">
         <v>1</v>
       </c>
-      <c r="AE93">
-        <v>1</v>
+      <c r="AE93" s="1">
+        <v>10</v>
       </c>
       <c r="AH93">
-        <v>999989</v>
+        <v>999986</v>
       </c>
       <c r="AK93" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
       <c r="AN93" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:40">
       <c r="A94">
-        <v>999990</v>
+        <v>999987</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7640,25 +7681,25 @@
       <c r="AD94">
         <v>1</v>
       </c>
-      <c r="AE94">
-        <v>1</v>
+      <c r="AE94" s="1">
+        <v>10</v>
       </c>
       <c r="AH94">
-        <v>999990</v>
+        <v>999987</v>
       </c>
       <c r="AK94" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
       <c r="AN94" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:40">
       <c r="A95">
-        <v>999991</v>
+        <v>999988</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7693,25 +7734,25 @@
       <c r="AD95">
         <v>1</v>
       </c>
-      <c r="AE95">
-        <v>1</v>
+      <c r="AE95" s="1">
+        <v>10</v>
       </c>
       <c r="AH95">
-        <v>999991</v>
+        <v>999988</v>
       </c>
       <c r="AK95" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
       <c r="AN95" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:40">
       <c r="A96">
-        <v>999992</v>
+        <v>999989</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7746,25 +7787,25 @@
       <c r="AD96">
         <v>1</v>
       </c>
-      <c r="AE96">
-        <v>1</v>
+      <c r="AE96" s="1">
+        <v>10</v>
       </c>
       <c r="AH96">
-        <v>999992</v>
+        <v>999989</v>
       </c>
       <c r="AK96" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
       <c r="AN96" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:40">
       <c r="A97">
-        <v>999993</v>
+        <v>999990</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7799,25 +7840,25 @@
       <c r="AD97">
         <v>1</v>
       </c>
-      <c r="AE97">
-        <v>1</v>
+      <c r="AE97" s="1">
+        <v>10</v>
       </c>
       <c r="AH97">
-        <v>999993</v>
+        <v>999990</v>
       </c>
       <c r="AK97" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
       <c r="AN97" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:40">
       <c r="A98">
-        <v>999994</v>
+        <v>999991</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7852,25 +7893,25 @@
       <c r="AD98">
         <v>1</v>
       </c>
-      <c r="AE98">
-        <v>1</v>
+      <c r="AE98" s="1">
+        <v>10</v>
       </c>
       <c r="AH98">
-        <v>999994</v>
+        <v>999991</v>
       </c>
       <c r="AK98" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
       <c r="AN98" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:40">
       <c r="A99">
-        <v>999995</v>
+        <v>999992</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7905,25 +7946,25 @@
       <c r="AD99">
         <v>1</v>
       </c>
-      <c r="AE99">
-        <v>1</v>
+      <c r="AE99" s="1">
+        <v>10</v>
       </c>
       <c r="AH99">
-        <v>999995</v>
+        <v>999992</v>
       </c>
       <c r="AK99" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
       <c r="AN99" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:40">
       <c r="A100">
-        <v>999996</v>
+        <v>999993</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7958,25 +7999,25 @@
       <c r="AD100">
         <v>1</v>
       </c>
-      <c r="AE100">
-        <v>1</v>
+      <c r="AE100" s="1">
+        <v>10</v>
       </c>
       <c r="AH100">
-        <v>999996</v>
+        <v>999993</v>
       </c>
       <c r="AK100" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
       <c r="AN100" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:40">
       <c r="A101">
-        <v>999997</v>
+        <v>999994</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -8011,25 +8052,25 @@
       <c r="AD101">
         <v>1</v>
       </c>
-      <c r="AE101">
-        <v>1</v>
+      <c r="AE101" s="1">
+        <v>10</v>
       </c>
       <c r="AH101">
-        <v>999997</v>
+        <v>999994</v>
       </c>
       <c r="AK101" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
       <c r="AN101" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:40">
       <c r="A102">
-        <v>999998</v>
+        <v>999995</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -8064,25 +8105,25 @@
       <c r="AD102">
         <v>1</v>
       </c>
-      <c r="AE102">
-        <v>1</v>
+      <c r="AE102" s="1">
+        <v>10</v>
       </c>
       <c r="AH102">
-        <v>999998</v>
+        <v>999995</v>
       </c>
       <c r="AK102" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
       <c r="AN102" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:40">
       <c r="A103">
-        <v>999999</v>
+        <v>999996</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -8117,25 +8158,181 @@
       <c r="AD103">
         <v>1</v>
       </c>
-      <c r="AE103">
-        <v>1</v>
+      <c r="AE103" s="1">
+        <v>10</v>
       </c>
       <c r="AH103">
+        <v>999996</v>
+      </c>
+      <c r="AK103" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM103">
+        <v>1</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" spans="1:40">
+      <c r="A104">
+        <v>999997</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="P104">
+        <v>200001</v>
+      </c>
+      <c r="S104">
+        <v>2</v>
+      </c>
+      <c r="T104">
+        <v>6</v>
+      </c>
+      <c r="U104">
+        <v>1</v>
+      </c>
+      <c r="V104">
+        <v>1</v>
+      </c>
+      <c r="W104">
+        <v>0.5</v>
+      </c>
+      <c r="X104">
+        <v>0.5</v>
+      </c>
+      <c r="Z104">
+        <v>100</v>
+      </c>
+      <c r="AC104">
+        <v>35</v>
+      </c>
+      <c r="AD104">
+        <v>1</v>
+      </c>
+      <c r="AE104" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH104">
+        <v>999997</v>
+      </c>
+      <c r="AK104" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM104">
+        <v>1</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" spans="1:40">
+      <c r="A105">
+        <v>999998</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="P105">
+        <v>200001</v>
+      </c>
+      <c r="S105">
+        <v>2</v>
+      </c>
+      <c r="T105">
+        <v>6</v>
+      </c>
+      <c r="U105">
+        <v>1</v>
+      </c>
+      <c r="V105">
+        <v>1</v>
+      </c>
+      <c r="W105">
+        <v>0.5</v>
+      </c>
+      <c r="X105">
+        <v>0.5</v>
+      </c>
+      <c r="Z105">
+        <v>100</v>
+      </c>
+      <c r="AC105">
+        <v>35</v>
+      </c>
+      <c r="AD105">
+        <v>1</v>
+      </c>
+      <c r="AE105" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH105">
+        <v>999998</v>
+      </c>
+      <c r="AK105" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM105">
+        <v>1</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="1:40">
+      <c r="A106">
         <v>999999</v>
       </c>
-      <c r="AK103" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM103">
-        <v>1</v>
-      </c>
-      <c r="AN103" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1"/>
-    <row r="124" ht="15" customHeight="1"/>
-    <row r="125" ht="15" customHeight="1"/>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="P106">
+        <v>200001</v>
+      </c>
+      <c r="S106">
+        <v>2</v>
+      </c>
+      <c r="T106">
+        <v>6</v>
+      </c>
+      <c r="U106">
+        <v>1</v>
+      </c>
+      <c r="V106">
+        <v>1</v>
+      </c>
+      <c r="W106">
+        <v>0.5</v>
+      </c>
+      <c r="X106">
+        <v>0.5</v>
+      </c>
+      <c r="Z106">
+        <v>100</v>
+      </c>
+      <c r="AC106">
+        <v>35</v>
+      </c>
+      <c r="AD106">
+        <v>1</v>
+      </c>
+      <c r="AE106" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH106">
+        <v>999999</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM106">
+        <v>1</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>148</v>
+      </c>
+    </row>
     <row r="126" ht="15" customHeight="1"/>
     <row r="127" ht="15" customHeight="1"/>
     <row r="128" ht="15" customHeight="1"/>
@@ -8144,17 +8341,20 @@
     <row r="131" ht="15" customHeight="1"/>
     <row r="132" ht="15" customHeight="1"/>
     <row r="133" ht="15" customHeight="1"/>
-    <row r="165" ht="12" customHeight="1"/>
-    <row r="166" ht="12" customHeight="1"/>
-    <row r="167" ht="12" customHeight="1"/>
+    <row r="134" ht="15" customHeight="1"/>
+    <row r="135" ht="15" customHeight="1"/>
+    <row r="136" ht="15" customHeight="1"/>
     <row r="168" ht="12" customHeight="1"/>
     <row r="169" ht="12" customHeight="1"/>
     <row r="170" ht="12" customHeight="1"/>
     <row r="171" ht="12" customHeight="1"/>
     <row r="172" ht="12" customHeight="1"/>
     <row r="173" ht="12" customHeight="1"/>
+    <row r="174" ht="12" customHeight="1"/>
+    <row r="175" ht="12" customHeight="1"/>
+    <row r="176" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN103" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN106" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -10,7 +10,7 @@
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="154">
   <si>
     <t>id</t>
   </si>
@@ -449,9 +449,18 @@
     <t>人类-冒险者</t>
   </si>
   <si>
+    <t>Attack5</t>
+  </si>
+  <si>
     <t>人类-持盾战士</t>
   </si>
   <si>
+    <t>Attack4</t>
+  </si>
+  <si>
+    <t>0,0.6,0</t>
+  </si>
+  <si>
     <t>人类-弓箭手</t>
   </si>
   <si>
@@ -464,7 +473,13 @@
     <t>人类-魔法师（火）</t>
   </si>
   <si>
+    <t>人类-魔法师（水）</t>
+  </si>
+  <si>
     <t>人类-魔法师（冰）</t>
+  </si>
+  <si>
+    <t>人类-魔法师（雷）</t>
   </si>
   <si>
     <t>测试骷髅战士</t>
@@ -1142,7 +1157,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1499,17 +1514,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN176"/>
+  <dimension ref="A1:AN178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="23.375" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="23.375" customWidth="1"/>
     <col min="3" max="3" width="33.25" customWidth="1"/>
     <col min="4" max="4" width="19.375" customWidth="1"/>
     <col min="5" max="6" width="24.875" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="24.875" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="10" max="10" width="33.5" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
     <col min="12" max="12" width="11.125" customWidth="1"/>
     <col min="13" max="13" width="11.875" customWidth="1"/>
@@ -1521,7 +1537,8 @@
     <col min="19" max="19" width="35.875" customWidth="1"/>
     <col min="20" max="20" width="21.5" customWidth="1"/>
     <col min="21" max="22" width="29.625" customWidth="1"/>
-    <col min="23" max="24" width="20.25" customWidth="1"/>
+    <col min="23" max="23" width="20.25" customWidth="1"/>
+    <col min="24" max="24" width="46.875" customWidth="1"/>
     <col min="25" max="25" width="11.125" customWidth="1"/>
     <col min="26" max="27" width="11.75" customWidth="1"/>
     <col min="28" max="28" width="6.375" customWidth="1"/>
@@ -4543,775 +4560,986 @@
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:40">
-      <c r="A41" s="2">
+      <c r="A41" s="6">
         <v>101001</v>
       </c>
-      <c r="C41" s="2">
-        <v>2</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6">
+        <v>2</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6">
         <v>1000001</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J41" s="2">
-        <v>2</v>
-      </c>
-      <c r="P41" s="2">
+      <c r="J41" s="6">
+        <v>2</v>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6">
         <v>100001</v>
       </c>
-      <c r="S41" s="2">
-        <v>1</v>
-      </c>
-      <c r="T41" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U41" s="2">
-        <v>1</v>
-      </c>
-      <c r="V41" s="2">
-        <v>1</v>
-      </c>
-      <c r="W41" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X41" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z41" s="2">
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6">
+        <v>1</v>
+      </c>
+      <c r="T41" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="U41" s="6">
+        <v>1</v>
+      </c>
+      <c r="V41" s="6">
+        <v>1</v>
+      </c>
+      <c r="W41" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X41" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6">
         <v>100</v>
       </c>
-      <c r="AC41" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD41" s="2">
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD41" s="6">
         <v>1</v>
       </c>
       <c r="AE41" s="6">
         <v>10</v>
       </c>
-      <c r="AH41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="2">
+      <c r="AF41" s="6"/>
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="6">
         <v>1000001</v>
       </c>
       <c r="AJ41" s="7"/>
-      <c r="AK41" s="2" t="s">
+      <c r="AK41" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="AM41" s="2">
+      <c r="AL41" s="6"/>
+      <c r="AM41" s="6">
         <v>101001</v>
       </c>
-      <c r="AN41" s="2" t="s">
+      <c r="AN41" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:40">
-      <c r="A42" s="2">
+      <c r="A42" s="6">
         <v>101002</v>
       </c>
-      <c r="C42" s="2">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6">
+        <v>2</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6">
         <v>1000001</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="6">
         <v>4</v>
       </c>
-      <c r="P42" s="2">
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6">
         <v>100001</v>
       </c>
-      <c r="S42" s="2">
-        <v>1</v>
-      </c>
-      <c r="T42" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U42" s="2">
-        <v>1</v>
-      </c>
-      <c r="V42" s="2">
-        <v>1</v>
-      </c>
-      <c r="W42" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X42" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z42" s="2">
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6">
+        <v>1</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="U42" s="6">
+        <v>1</v>
+      </c>
+      <c r="V42" s="6">
+        <v>1</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X42" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6">
         <v>100</v>
       </c>
-      <c r="AB42" s="2">
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6">
         <v>100</v>
       </c>
-      <c r="AC42" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD42" s="2">
+      <c r="AC42" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD42" s="6">
         <v>1</v>
       </c>
       <c r="AE42" s="6">
         <v>10</v>
       </c>
-      <c r="AH42" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="2">
+      <c r="AF42" s="6"/>
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
         <v>1000001</v>
       </c>
       <c r="AJ42" s="7"/>
-      <c r="AK42" s="2" t="s">
+      <c r="AK42" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="AM42" s="2">
+      <c r="AL42" s="6"/>
+      <c r="AM42" s="6">
         <v>101002</v>
       </c>
-      <c r="AN42" s="2" t="s">
-        <v>139</v>
+      <c r="AN42" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" spans="1:40">
-      <c r="A43" s="2">
+      <c r="A43" s="6">
         <v>102001</v>
       </c>
-      <c r="C43" s="2">
-        <v>2</v>
-      </c>
-      <c r="G43" s="2">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6">
+        <v>2</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6">
         <v>1000001</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="6">
         <v>7</v>
       </c>
-      <c r="P43" s="2">
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6">
         <v>200001</v>
       </c>
-      <c r="S43" s="2">
-        <v>1</v>
-      </c>
-      <c r="T43" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U43" s="2">
-        <v>1</v>
-      </c>
-      <c r="V43" s="2">
-        <v>1</v>
-      </c>
-      <c r="W43" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X43" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z43" s="2">
+      <c r="Q43" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6">
+        <v>1</v>
+      </c>
+      <c r="T43" s="6">
+        <v>10</v>
+      </c>
+      <c r="U43" s="6">
+        <v>1</v>
+      </c>
+      <c r="V43" s="6">
+        <v>1</v>
+      </c>
+      <c r="W43" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X43" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6">
+        <v>70</v>
+      </c>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF43" s="6"/>
+      <c r="AG43" s="6"/>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ43" s="7"/>
+      <c r="AK43" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL43" s="6"/>
+      <c r="AM43" s="6">
+        <v>102001</v>
+      </c>
+      <c r="AN43" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="1:40">
+      <c r="A44" s="6">
+        <v>102002</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44" s="6">
+        <v>7</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6">
+        <v>205001</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6">
+        <v>1</v>
+      </c>
+      <c r="T44" s="6">
+        <v>10</v>
+      </c>
+      <c r="U44" s="6">
+        <v>1</v>
+      </c>
+      <c r="V44" s="6">
+        <v>1</v>
+      </c>
+      <c r="W44" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X44" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="6">
+        <v>70</v>
+      </c>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF44" s="6"/>
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI44" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ44" s="7"/>
+      <c r="AK44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL44" s="6"/>
+      <c r="AM44" s="6">
+        <v>102002</v>
+      </c>
+      <c r="AN44" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="1:40">
+      <c r="A45" s="6">
+        <v>102003</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6">
+        <v>2</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="6">
+        <v>7</v>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6">
+        <v>204001</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R45" s="6"/>
+      <c r="S45" s="6">
+        <v>1</v>
+      </c>
+      <c r="T45" s="6">
+        <v>10</v>
+      </c>
+      <c r="U45" s="6">
+        <v>1</v>
+      </c>
+      <c r="V45" s="6">
+        <v>1</v>
+      </c>
+      <c r="W45" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X45" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="6">
+        <v>70</v>
+      </c>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE45" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF45" s="6"/>
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI45" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ45" s="7"/>
+      <c r="AK45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL45" s="6"/>
+      <c r="AM45" s="6">
+        <v>102003</v>
+      </c>
+      <c r="AN45" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="1:40">
+      <c r="A46" s="6">
+        <v>103001</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6">
+        <v>2</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="6">
+        <v>1</v>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6">
+        <v>200002</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6">
+        <v>1</v>
+      </c>
+      <c r="T46" s="6">
+        <v>10</v>
+      </c>
+      <c r="U46" s="6">
+        <v>1</v>
+      </c>
+      <c r="V46" s="6">
+        <v>1</v>
+      </c>
+      <c r="W46" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X46" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF46" s="6"/>
+      <c r="AG46" s="6"/>
+      <c r="AH46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ46" s="7"/>
+      <c r="AK46" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL46" s="6"/>
+      <c r="AM46" s="6">
+        <v>103001</v>
+      </c>
+      <c r="AN46" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:40">
+      <c r="A47" s="6">
+        <v>103002</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6">
+        <v>2</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" s="6">
+        <v>1</v>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6">
+        <v>200003</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6">
+        <v>1</v>
+      </c>
+      <c r="T47" s="6">
+        <v>10</v>
+      </c>
+      <c r="U47" s="6">
+        <v>1</v>
+      </c>
+      <c r="V47" s="6">
+        <v>1</v>
+      </c>
+      <c r="W47" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X47" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD47" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF47" s="6"/>
+      <c r="AG47" s="6"/>
+      <c r="AH47" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI47" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ47" s="7"/>
+      <c r="AK47" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL47" s="6"/>
+      <c r="AM47" s="6">
+        <v>103002</v>
+      </c>
+      <c r="AN47" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:40">
+      <c r="A48" s="6">
+        <v>103003</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6">
+        <v>2</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J48" s="6">
+        <v>1</v>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6">
+        <v>200004</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6">
+        <v>1</v>
+      </c>
+      <c r="T48" s="6">
+        <v>10</v>
+      </c>
+      <c r="U48" s="6">
+        <v>1</v>
+      </c>
+      <c r="V48" s="6">
+        <v>1</v>
+      </c>
+      <c r="W48" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X48" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD48" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF48" s="6"/>
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI48" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ48" s="7"/>
+      <c r="AK48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL48" s="6"/>
+      <c r="AM48" s="6">
+        <v>103003</v>
+      </c>
+      <c r="AN48" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:40">
+      <c r="A49" s="6">
+        <v>103004</v>
+      </c>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6">
+        <v>2</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="6">
+        <v>1</v>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6">
+        <v>200005</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6">
+        <v>1</v>
+      </c>
+      <c r="T49" s="6">
+        <v>10</v>
+      </c>
+      <c r="U49" s="6">
+        <v>1</v>
+      </c>
+      <c r="V49" s="6">
+        <v>1</v>
+      </c>
+      <c r="W49" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X49" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y49" s="6"/>
+      <c r="Z49" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA49" s="6"/>
+      <c r="AB49" s="6"/>
+      <c r="AC49" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD49" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF49" s="6"/>
+      <c r="AG49" s="6"/>
+      <c r="AH49" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI49" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ49" s="7"/>
+      <c r="AK49" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL49" s="6"/>
+      <c r="AM49" s="6">
+        <v>103004</v>
+      </c>
+      <c r="AN49" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:40">
+      <c r="A50" s="8">
+        <v>900001</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9">
+        <v>9</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="H50" s="9">
+        <v>21010001</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J50" s="9">
+        <v>2</v>
+      </c>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9">
+        <v>100001</v>
+      </c>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="9">
+        <v>2</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U50" s="9">
+        <v>1</v>
+      </c>
+      <c r="V50" s="9">
+        <v>1</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AA50" s="9"/>
+      <c r="AB50" s="9"/>
+      <c r="AC50" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD50" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF50" s="9"/>
+      <c r="AG50" s="9"/>
+      <c r="AH50" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="AJ50" s="8"/>
+      <c r="AK50" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL50" s="9">
+        <v>300200001</v>
+      </c>
+      <c r="AM50" s="8">
+        <v>900001</v>
+      </c>
+      <c r="AN50" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:40">
+      <c r="A51" s="8">
+        <v>900002</v>
+      </c>
+      <c r="B51" s="9">
+        <v>2</v>
+      </c>
+      <c r="C51" s="9">
+        <v>9</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9">
+        <v>2000001</v>
+      </c>
+      <c r="H51" s="9">
+        <v>21000001</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J51" s="9">
+        <v>8</v>
+      </c>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AC43" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE43" s="6">
-        <v>10</v>
-      </c>
-      <c r="AH43" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI43" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="AJ43" s="7"/>
-      <c r="AK43" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM43" s="2">
-        <v>102001</v>
-      </c>
-      <c r="AN43" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="1:40">
-      <c r="A44" s="2">
-        <v>102002</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2</v>
-      </c>
-      <c r="G44" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J44" s="2">
-        <v>7</v>
-      </c>
-      <c r="P44" s="2">
+      <c r="O51" s="9"/>
+      <c r="P51" s="9">
         <v>200001</v>
       </c>
-      <c r="S44" s="2">
-        <v>1</v>
-      </c>
-      <c r="T44" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U44" s="2">
-        <v>1</v>
-      </c>
-      <c r="V44" s="2">
-        <v>1</v>
-      </c>
-      <c r="W44" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X44" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z44" s="2">
-        <v>100</v>
-      </c>
-      <c r="AC44" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD44" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="6">
-        <v>10</v>
-      </c>
-      <c r="AH44" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI44" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="AJ44" s="7"/>
-      <c r="AK44" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM44" s="2">
-        <v>102002</v>
-      </c>
-      <c r="AN44" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:40">
-      <c r="A45" s="2">
-        <v>102003</v>
-      </c>
-      <c r="C45" s="2">
-        <v>2</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J45" s="2">
-        <v>7</v>
-      </c>
-      <c r="P45" s="2">
-        <v>200001</v>
-      </c>
-      <c r="S45" s="2">
-        <v>1</v>
-      </c>
-      <c r="T45" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U45" s="2">
-        <v>1</v>
-      </c>
-      <c r="V45" s="2">
-        <v>1</v>
-      </c>
-      <c r="W45" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X45" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z45" s="2">
-        <v>100</v>
-      </c>
-      <c r="AC45" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE45" s="6">
-        <v>10</v>
-      </c>
-      <c r="AH45" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI45" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="AJ45" s="7"/>
-      <c r="AK45" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM45" s="2">
-        <v>102003</v>
-      </c>
-      <c r="AN45" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:40">
-      <c r="A46" s="2">
-        <v>103001</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J46" s="2">
-        <v>1</v>
-      </c>
-      <c r="P46" s="2">
-        <v>201001</v>
-      </c>
-      <c r="S46" s="2">
-        <v>1</v>
-      </c>
-      <c r="T46" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U46" s="2">
-        <v>1</v>
-      </c>
-      <c r="V46" s="2">
-        <v>1</v>
-      </c>
-      <c r="W46" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X46" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z46" s="2">
-        <v>100</v>
-      </c>
-      <c r="AC46" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE46" s="6">
-        <v>10</v>
-      </c>
-      <c r="AH46" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI46" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="AJ46" s="7"/>
-      <c r="AK46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM46" s="2">
-        <v>103001</v>
-      </c>
-      <c r="AN46" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:40">
-      <c r="A47" s="2">
-        <v>103002</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2</v>
-      </c>
-      <c r="G47" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J47" s="2">
-        <v>1</v>
-      </c>
-      <c r="P47" s="2">
-        <v>201002</v>
-      </c>
-      <c r="S47" s="2">
-        <v>1</v>
-      </c>
-      <c r="T47" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="U47" s="2">
-        <v>1</v>
-      </c>
-      <c r="V47" s="2">
-        <v>1</v>
-      </c>
-      <c r="W47" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="X47" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Z47" s="2">
-        <v>100</v>
-      </c>
-      <c r="AC47" s="2">
-        <v>10</v>
-      </c>
-      <c r="AD47" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE47" s="6">
-        <v>10</v>
-      </c>
-      <c r="AH47" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI47" s="2">
-        <v>1000001</v>
-      </c>
-      <c r="AJ47" s="7"/>
-      <c r="AK47" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM47" s="2">
-        <v>103002</v>
-      </c>
-      <c r="AN47" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:40">
-      <c r="A48" s="8">
-        <v>900001</v>
-      </c>
-      <c r="B48" s="9">
-        <v>1</v>
-      </c>
-      <c r="C48" s="9">
-        <v>9</v>
-      </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9">
+      <c r="Q51" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9">
+        <v>2</v>
+      </c>
+      <c r="T51" s="9">
+        <v>10</v>
+      </c>
+      <c r="U51" s="9">
+        <v>1</v>
+      </c>
+      <c r="V51" s="9">
+        <v>1</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>10000</v>
+      </c>
+      <c r="AA51" s="9"/>
+      <c r="AB51" s="9"/>
+      <c r="AC51" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD51" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF51" s="9"/>
+      <c r="AG51" s="9"/>
+      <c r="AH51" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI51" s="9">
         <v>2000001</v>
       </c>
-      <c r="H48" s="9">
-        <v>21010001</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="J48" s="9">
-        <v>2</v>
-      </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9">
-        <v>100001</v>
-      </c>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9">
-        <v>2</v>
-      </c>
-      <c r="T48" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="U48" s="9">
-        <v>1</v>
-      </c>
-      <c r="V48" s="9">
-        <v>1</v>
-      </c>
-      <c r="W48" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="X48" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y48" s="9">
-        <v>10</v>
-      </c>
-      <c r="Z48" s="9">
-        <v>1000</v>
-      </c>
-      <c r="AA48" s="9"/>
-      <c r="AB48" s="9"/>
-      <c r="AC48" s="9">
-        <v>1</v>
-      </c>
-      <c r="AD48" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="1">
-        <v>10</v>
-      </c>
-      <c r="AF48" s="9"/>
-      <c r="AG48" s="9"/>
-      <c r="AH48" s="9">
-        <v>2</v>
-      </c>
-      <c r="AI48" s="9">
-        <v>2000001</v>
-      </c>
-      <c r="AJ48" s="8"/>
-      <c r="AK48" s="9" t="s">
+      <c r="AJ51" s="8"/>
+      <c r="AK51" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AL48" s="9">
-        <v>300200001</v>
-      </c>
-      <c r="AM48" s="8">
-        <v>900001</v>
-      </c>
-      <c r="AN48" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:40">
-      <c r="A49" s="8">
+      <c r="AL51" s="9">
+        <v>300200002</v>
+      </c>
+      <c r="AM51" s="8">
         <v>900002</v>
       </c>
-      <c r="B49" s="9">
-        <v>2</v>
-      </c>
-      <c r="C49" s="9">
-        <v>9</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9">
-        <v>2000001</v>
-      </c>
-      <c r="H49" s="9">
-        <v>21000001</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="J49" s="9">
-        <v>8</v>
-      </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9">
-        <v>200001</v>
-      </c>
-      <c r="Q49" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9">
-        <v>2</v>
-      </c>
-      <c r="T49" s="9">
-        <v>10</v>
-      </c>
-      <c r="U49" s="9">
-        <v>1</v>
-      </c>
-      <c r="V49" s="9">
-        <v>1</v>
-      </c>
-      <c r="W49" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="X49" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y49" s="9">
-        <v>10</v>
-      </c>
-      <c r="Z49" s="9">
-        <v>1000</v>
-      </c>
-      <c r="AA49" s="9"/>
-      <c r="AB49" s="9"/>
-      <c r="AC49" s="9">
-        <v>1</v>
-      </c>
-      <c r="AD49" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE49" s="1">
-        <v>10</v>
-      </c>
-      <c r="AF49" s="9"/>
-      <c r="AG49" s="9"/>
-      <c r="AH49" s="9">
-        <v>2</v>
-      </c>
-      <c r="AI49" s="9">
-        <v>2000001</v>
-      </c>
-      <c r="AJ49" s="8"/>
-      <c r="AK49" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL49" s="9">
-        <v>300200002</v>
-      </c>
-      <c r="AM49" s="8">
-        <v>900002</v>
-      </c>
-      <c r="AN49" s="9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:40">
-      <c r="A50" s="3">
-        <v>989996</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>200001</v>
-      </c>
-      <c r="S50">
-        <v>2</v>
-      </c>
-      <c r="T50">
-        <v>6</v>
-      </c>
-      <c r="U50">
-        <v>1</v>
-      </c>
-      <c r="V50">
-        <v>1</v>
-      </c>
-      <c r="W50">
-        <v>0.5</v>
-      </c>
-      <c r="X50">
-        <v>0.5</v>
-      </c>
-      <c r="Z50">
-        <v>100</v>
-      </c>
-      <c r="AC50">
-        <v>35</v>
-      </c>
-      <c r="AD50">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH50" s="3">
-        <v>989996</v>
-      </c>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" t="s">
-        <v>147</v>
-      </c>
-      <c r="AM50">
-        <v>1</v>
-      </c>
-      <c r="AN50" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:40">
-      <c r="A51" s="3">
-        <v>989997</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="P51">
-        <v>200001</v>
-      </c>
-      <c r="S51">
-        <v>2</v>
-      </c>
-      <c r="T51">
-        <v>6</v>
-      </c>
-      <c r="U51">
-        <v>1</v>
-      </c>
-      <c r="V51">
-        <v>1</v>
-      </c>
-      <c r="W51">
-        <v>0.5</v>
-      </c>
-      <c r="X51">
-        <v>0.5</v>
-      </c>
-      <c r="Z51">
-        <v>100</v>
-      </c>
-      <c r="AC51">
-        <v>35</v>
-      </c>
-      <c r="AD51">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH51" s="3">
-        <v>989997</v>
-      </c>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" t="s">
-        <v>147</v>
-      </c>
-      <c r="AM51">
-        <v>1</v>
-      </c>
-      <c r="AN51" t="s">
-        <v>148</v>
+      <c r="AN51" s="9" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:40">
       <c r="A52" s="3">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52">
@@ -5351,23 +5579,23 @@
         <v>10</v>
       </c>
       <c r="AH52" s="3">
-        <v>989998</v>
+        <v>989996</v>
       </c>
       <c r="AI52" s="4"/>
       <c r="AJ52" s="4"/>
       <c r="AK52" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM52">
         <v>1</v>
       </c>
       <c r="AN52" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:40">
       <c r="A53" s="3">
-        <v>989999</v>
+        <v>989997</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53">
@@ -5406,22 +5634,24 @@
       <c r="AE53" s="1">
         <v>10</v>
       </c>
-      <c r="AH53">
-        <v>989999</v>
-      </c>
+      <c r="AH53" s="3">
+        <v>989997</v>
+      </c>
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
       <c r="AK53" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM53">
         <v>1</v>
       </c>
       <c r="AN53" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:40">
       <c r="A54" s="3">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54">
@@ -5461,23 +5691,23 @@
         <v>10</v>
       </c>
       <c r="AH54" s="3">
-        <v>999947</v>
+        <v>989998</v>
       </c>
       <c r="AI54" s="4"/>
       <c r="AJ54" s="4"/>
       <c r="AK54" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM54">
         <v>1</v>
       </c>
       <c r="AN54" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:40">
       <c r="A55" s="3">
-        <v>999948</v>
+        <v>989999</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55">
@@ -5516,24 +5746,22 @@
       <c r="AE55" s="1">
         <v>10</v>
       </c>
-      <c r="AH55" s="3">
-        <v>999948</v>
-      </c>
-      <c r="AI55" s="4"/>
-      <c r="AJ55" s="4"/>
+      <c r="AH55">
+        <v>989999</v>
+      </c>
       <c r="AK55" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
       <c r="AN55" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:40">
       <c r="A56" s="3">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56">
@@ -5573,23 +5801,23 @@
         <v>10</v>
       </c>
       <c r="AH56" s="3">
-        <v>999949</v>
+        <v>999947</v>
       </c>
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
       <c r="AK56" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
       <c r="AN56" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:40">
       <c r="A57" s="3">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57">
@@ -5629,23 +5857,23 @@
         <v>10</v>
       </c>
       <c r="AH57" s="3">
-        <v>999950</v>
+        <v>999948</v>
       </c>
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
       <c r="AK57" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
       <c r="AN57" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:40">
       <c r="A58" s="3">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58">
@@ -5685,23 +5913,23 @@
         <v>10</v>
       </c>
       <c r="AH58" s="3">
-        <v>999951</v>
+        <v>999949</v>
       </c>
       <c r="AI58" s="4"/>
       <c r="AJ58" s="4"/>
       <c r="AK58" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
       <c r="AN58" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:40">
       <c r="A59" s="3">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59">
@@ -5741,23 +5969,23 @@
         <v>10</v>
       </c>
       <c r="AH59" s="3">
-        <v>999952</v>
+        <v>999950</v>
       </c>
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
       <c r="AK59" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
       <c r="AN59" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:40">
       <c r="A60" s="3">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60">
@@ -5797,23 +6025,23 @@
         <v>10</v>
       </c>
       <c r="AH60" s="3">
-        <v>999953</v>
+        <v>999951</v>
       </c>
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
       <c r="AK60" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
       <c r="AN60" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:40">
       <c r="A61" s="3">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61">
@@ -5853,23 +6081,23 @@
         <v>10</v>
       </c>
       <c r="AH61" s="3">
-        <v>999954</v>
+        <v>999952</v>
       </c>
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
       <c r="AK61" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
       <c r="AN61" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:40">
       <c r="A62" s="3">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62">
@@ -5909,23 +6137,23 @@
         <v>10</v>
       </c>
       <c r="AH62" s="3">
-        <v>999955</v>
+        <v>999953</v>
       </c>
       <c r="AI62" s="4"/>
       <c r="AJ62" s="4"/>
       <c r="AK62" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
       <c r="AN62" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:40">
       <c r="A63" s="3">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63">
@@ -5965,23 +6193,23 @@
         <v>10</v>
       </c>
       <c r="AH63" s="3">
-        <v>999956</v>
+        <v>999954</v>
       </c>
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4"/>
       <c r="AK63" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
       <c r="AN63" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:40">
       <c r="A64" s="3">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64">
@@ -6021,23 +6249,23 @@
         <v>10</v>
       </c>
       <c r="AH64" s="3">
-        <v>999957</v>
+        <v>999955</v>
       </c>
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
       <c r="AK64" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
       <c r="AN64" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:40">
       <c r="A65" s="3">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65">
@@ -6077,23 +6305,23 @@
         <v>10</v>
       </c>
       <c r="AH65" s="3">
-        <v>999958</v>
+        <v>999956</v>
       </c>
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
       <c r="AK65" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
       <c r="AN65" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:40">
       <c r="A66" s="3">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66">
@@ -6133,23 +6361,23 @@
         <v>10</v>
       </c>
       <c r="AH66" s="3">
-        <v>999959</v>
+        <v>999957</v>
       </c>
       <c r="AI66" s="4"/>
       <c r="AJ66" s="4"/>
       <c r="AK66" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
       <c r="AN66" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:40">
       <c r="A67" s="3">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67">
@@ -6189,23 +6417,23 @@
         <v>10</v>
       </c>
       <c r="AH67" s="3">
-        <v>999960</v>
+        <v>999958</v>
       </c>
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4"/>
       <c r="AK67" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
       <c r="AN67" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:40">
       <c r="A68" s="3">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68">
@@ -6245,23 +6473,23 @@
         <v>10</v>
       </c>
       <c r="AH68" s="3">
-        <v>999961</v>
+        <v>999959</v>
       </c>
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4"/>
       <c r="AK68" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
       <c r="AN68" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:40">
       <c r="A69" s="3">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69">
@@ -6301,23 +6529,23 @@
         <v>10</v>
       </c>
       <c r="AH69" s="3">
-        <v>999962</v>
+        <v>999960</v>
       </c>
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
       <c r="AK69" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
       <c r="AN69" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:40">
       <c r="A70" s="3">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70">
@@ -6357,23 +6585,23 @@
         <v>10</v>
       </c>
       <c r="AH70" s="3">
-        <v>999963</v>
+        <v>999961</v>
       </c>
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
       <c r="AK70" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
       <c r="AN70" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:40">
       <c r="A71" s="3">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71">
@@ -6413,23 +6641,23 @@
         <v>10</v>
       </c>
       <c r="AH71" s="3">
-        <v>999964</v>
+        <v>999962</v>
       </c>
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
       <c r="AK71" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
       <c r="AN71" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:40">
       <c r="A72" s="3">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72">
@@ -6469,23 +6697,23 @@
         <v>10</v>
       </c>
       <c r="AH72" s="3">
-        <v>999965</v>
+        <v>999963</v>
       </c>
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
       <c r="AK72" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
       <c r="AN72" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:40">
       <c r="A73" s="3">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73">
@@ -6525,23 +6753,23 @@
         <v>10</v>
       </c>
       <c r="AH73" s="3">
-        <v>999966</v>
+        <v>999964</v>
       </c>
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
       <c r="AK73" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
       <c r="AN73" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:40">
       <c r="A74" s="3">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74">
@@ -6581,23 +6809,23 @@
         <v>10</v>
       </c>
       <c r="AH74" s="3">
-        <v>999967</v>
+        <v>999965</v>
       </c>
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
       <c r="AK74" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
       <c r="AN74" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:40">
       <c r="A75" s="3">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75">
@@ -6637,23 +6865,23 @@
         <v>10</v>
       </c>
       <c r="AH75" s="3">
-        <v>999968</v>
+        <v>999966</v>
       </c>
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
       <c r="AK75" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
       <c r="AN75" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:40">
       <c r="A76" s="3">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76">
@@ -6693,23 +6921,23 @@
         <v>10</v>
       </c>
       <c r="AH76" s="3">
-        <v>999969</v>
+        <v>999967</v>
       </c>
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
       <c r="AK76" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
       <c r="AN76" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:40">
       <c r="A77" s="3">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77">
@@ -6749,23 +6977,23 @@
         <v>10</v>
       </c>
       <c r="AH77" s="3">
-        <v>999970</v>
+        <v>999968</v>
       </c>
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
       <c r="AK77" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
       <c r="AN77" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:40">
       <c r="A78" s="3">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78">
@@ -6805,23 +7033,23 @@
         <v>10</v>
       </c>
       <c r="AH78" s="3">
-        <v>999971</v>
+        <v>999969</v>
       </c>
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
       <c r="AK78" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
       <c r="AN78" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:40">
       <c r="A79" s="3">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79">
@@ -6861,23 +7089,23 @@
         <v>10</v>
       </c>
       <c r="AH79" s="3">
-        <v>999972</v>
+        <v>999970</v>
       </c>
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
       <c r="AK79" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
       <c r="AN79" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:40">
       <c r="A80" s="3">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80">
@@ -6917,23 +7145,23 @@
         <v>10</v>
       </c>
       <c r="AH80" s="3">
-        <v>999973</v>
+        <v>999971</v>
       </c>
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
       <c r="AK80" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
       <c r="AN80" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:40">
       <c r="A81" s="3">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81">
@@ -6973,23 +7201,23 @@
         <v>10</v>
       </c>
       <c r="AH81" s="3">
-        <v>999974</v>
+        <v>999972</v>
       </c>
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
       <c r="AK81" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
       <c r="AN81" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:40">
       <c r="A82" s="3">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82">
@@ -7029,23 +7257,23 @@
         <v>10</v>
       </c>
       <c r="AH82" s="3">
-        <v>999975</v>
+        <v>999973</v>
       </c>
       <c r="AI82" s="4"/>
       <c r="AJ82" s="4"/>
       <c r="AK82" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
       <c r="AN82" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:40">
       <c r="A83" s="3">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83">
@@ -7085,23 +7313,23 @@
         <v>10</v>
       </c>
       <c r="AH83" s="3">
-        <v>999976</v>
+        <v>999974</v>
       </c>
       <c r="AI83" s="4"/>
       <c r="AJ83" s="4"/>
       <c r="AK83" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
       <c r="AN83" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:40">
       <c r="A84" s="3">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84">
@@ -7141,23 +7369,23 @@
         <v>10</v>
       </c>
       <c r="AH84" s="3">
-        <v>999977</v>
+        <v>999975</v>
       </c>
       <c r="AI84" s="4"/>
       <c r="AJ84" s="4"/>
       <c r="AK84" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
       <c r="AN84" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:40">
       <c r="A85" s="3">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85">
@@ -7197,23 +7425,23 @@
         <v>10</v>
       </c>
       <c r="AH85" s="3">
-        <v>999978</v>
+        <v>999976</v>
       </c>
       <c r="AI85" s="4"/>
       <c r="AJ85" s="4"/>
       <c r="AK85" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
       <c r="AN85" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:40">
       <c r="A86" s="3">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86">
@@ -7253,23 +7481,23 @@
         <v>10</v>
       </c>
       <c r="AH86" s="3">
-        <v>999979</v>
+        <v>999977</v>
       </c>
       <c r="AI86" s="4"/>
       <c r="AJ86" s="4"/>
       <c r="AK86" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
       <c r="AN86" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:40">
       <c r="A87" s="3">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87">
@@ -7309,23 +7537,23 @@
         <v>10</v>
       </c>
       <c r="AH87" s="3">
-        <v>999980</v>
+        <v>999978</v>
       </c>
       <c r="AI87" s="4"/>
       <c r="AJ87" s="4"/>
       <c r="AK87" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
       <c r="AN87" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:40">
       <c r="A88" s="3">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88">
@@ -7365,24 +7593,25 @@
         <v>10</v>
       </c>
       <c r="AH88" s="3">
-        <v>999981</v>
+        <v>999979</v>
       </c>
       <c r="AI88" s="4"/>
       <c r="AJ88" s="4"/>
       <c r="AK88" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
       <c r="AN88" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:40">
-      <c r="A89">
-        <v>999982</v>
-      </c>
+      <c r="A89" s="3">
+        <v>999980</v>
+      </c>
+      <c r="B89" s="4"/>
       <c r="C89">
         <v>1</v>
       </c>
@@ -7419,23 +7648,26 @@
       <c r="AE89" s="1">
         <v>10</v>
       </c>
-      <c r="AH89">
-        <v>999982</v>
-      </c>
+      <c r="AH89" s="3">
+        <v>999980</v>
+      </c>
+      <c r="AI89" s="4"/>
+      <c r="AJ89" s="4"/>
       <c r="AK89" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
       <c r="AN89" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:40">
-      <c r="A90">
-        <v>999983</v>
-      </c>
+      <c r="A90" s="3">
+        <v>999981</v>
+      </c>
+      <c r="B90" s="4"/>
       <c r="C90">
         <v>1</v>
       </c>
@@ -7472,22 +7704,24 @@
       <c r="AE90" s="1">
         <v>10</v>
       </c>
-      <c r="AH90">
-        <v>999983</v>
-      </c>
+      <c r="AH90" s="3">
+        <v>999981</v>
+      </c>
+      <c r="AI90" s="4"/>
+      <c r="AJ90" s="4"/>
       <c r="AK90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
       <c r="AN90" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:40">
       <c r="A91">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7526,21 +7760,21 @@
         <v>10</v>
       </c>
       <c r="AH91">
-        <v>999984</v>
+        <v>999982</v>
       </c>
       <c r="AK91" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
       <c r="AN91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:40">
       <c r="A92">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7579,21 +7813,21 @@
         <v>10</v>
       </c>
       <c r="AH92">
-        <v>999985</v>
+        <v>999983</v>
       </c>
       <c r="AK92" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
       <c r="AN92" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:40">
       <c r="A93">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7632,21 +7866,21 @@
         <v>10</v>
       </c>
       <c r="AH93">
-        <v>999986</v>
+        <v>999984</v>
       </c>
       <c r="AK93" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
       <c r="AN93" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:40">
       <c r="A94">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7685,21 +7919,21 @@
         <v>10</v>
       </c>
       <c r="AH94">
-        <v>999987</v>
+        <v>999985</v>
       </c>
       <c r="AK94" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
       <c r="AN94" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:40">
       <c r="A95">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7738,21 +7972,21 @@
         <v>10</v>
       </c>
       <c r="AH95">
-        <v>999988</v>
+        <v>999986</v>
       </c>
       <c r="AK95" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
       <c r="AN95" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:40">
       <c r="A96">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7791,21 +8025,21 @@
         <v>10</v>
       </c>
       <c r="AH96">
-        <v>999989</v>
+        <v>999987</v>
       </c>
       <c r="AK96" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
       <c r="AN96" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:40">
       <c r="A97">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7844,21 +8078,21 @@
         <v>10</v>
       </c>
       <c r="AH97">
-        <v>999990</v>
+        <v>999988</v>
       </c>
       <c r="AK97" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
       <c r="AN97" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:40">
       <c r="A98">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7897,21 +8131,21 @@
         <v>10</v>
       </c>
       <c r="AH98">
-        <v>999991</v>
+        <v>999989</v>
       </c>
       <c r="AK98" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
       <c r="AN98" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:40">
       <c r="A99">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7950,21 +8184,21 @@
         <v>10</v>
       </c>
       <c r="AH99">
-        <v>999992</v>
+        <v>999990</v>
       </c>
       <c r="AK99" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
       <c r="AN99" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:40">
       <c r="A100">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -8003,21 +8237,21 @@
         <v>10</v>
       </c>
       <c r="AH100">
-        <v>999993</v>
+        <v>999991</v>
       </c>
       <c r="AK100" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
       <c r="AN100" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:40">
       <c r="A101">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -8056,21 +8290,21 @@
         <v>10</v>
       </c>
       <c r="AH101">
-        <v>999994</v>
+        <v>999992</v>
       </c>
       <c r="AK101" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
       <c r="AN101" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:40">
       <c r="A102">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -8109,21 +8343,21 @@
         <v>10</v>
       </c>
       <c r="AH102">
-        <v>999995</v>
+        <v>999993</v>
       </c>
       <c r="AK102" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
       <c r="AN102" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:40">
       <c r="A103">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -8162,21 +8396,21 @@
         <v>10</v>
       </c>
       <c r="AH103">
-        <v>999996</v>
+        <v>999994</v>
       </c>
       <c r="AK103" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM103">
         <v>1</v>
       </c>
       <c r="AN103" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:40">
       <c r="A104">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -8215,21 +8449,21 @@
         <v>10</v>
       </c>
       <c r="AH104">
-        <v>999997</v>
+        <v>999995</v>
       </c>
       <c r="AK104" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM104">
         <v>1</v>
       </c>
       <c r="AN104" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:40">
       <c r="A105">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -8268,21 +8502,21 @@
         <v>10</v>
       </c>
       <c r="AH105">
-        <v>999998</v>
+        <v>999996</v>
       </c>
       <c r="AK105" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AM105">
         <v>1</v>
       </c>
       <c r="AN105" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:40">
       <c r="A106">
-        <v>999999</v>
+        <v>999997</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -8321,20 +8555,124 @@
         <v>10</v>
       </c>
       <c r="AH106">
+        <v>999997</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM106">
+        <v>1</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="1:40">
+      <c r="A107">
+        <v>999998</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="P107">
+        <v>200001</v>
+      </c>
+      <c r="S107">
+        <v>2</v>
+      </c>
+      <c r="T107">
+        <v>6</v>
+      </c>
+      <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107">
+        <v>1</v>
+      </c>
+      <c r="W107">
+        <v>0.5</v>
+      </c>
+      <c r="X107">
+        <v>0.5</v>
+      </c>
+      <c r="Z107">
+        <v>100</v>
+      </c>
+      <c r="AC107">
+        <v>35</v>
+      </c>
+      <c r="AD107">
+        <v>1</v>
+      </c>
+      <c r="AE107" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH107">
+        <v>999998</v>
+      </c>
+      <c r="AK107" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM107">
+        <v>1</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" spans="1:40">
+      <c r="A108">
         <v>999999</v>
       </c>
-      <c r="AK106" t="s">
-        <v>147</v>
-      </c>
-      <c r="AM106">
-        <v>1</v>
-      </c>
-      <c r="AN106" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="126" ht="15" customHeight="1"/>
-    <row r="127" ht="15" customHeight="1"/>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="P108">
+        <v>200001</v>
+      </c>
+      <c r="S108">
+        <v>2</v>
+      </c>
+      <c r="T108">
+        <v>6</v>
+      </c>
+      <c r="U108">
+        <v>1</v>
+      </c>
+      <c r="V108">
+        <v>1</v>
+      </c>
+      <c r="W108">
+        <v>0.5</v>
+      </c>
+      <c r="X108">
+        <v>0.5</v>
+      </c>
+      <c r="Z108">
+        <v>100</v>
+      </c>
+      <c r="AC108">
+        <v>35</v>
+      </c>
+      <c r="AD108">
+        <v>1</v>
+      </c>
+      <c r="AE108" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH108">
+        <v>999999</v>
+      </c>
+      <c r="AK108" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM108">
+        <v>1</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>153</v>
+      </c>
+    </row>
     <row r="128" ht="15" customHeight="1"/>
     <row r="129" ht="15" customHeight="1"/>
     <row r="130" ht="15" customHeight="1"/>
@@ -8344,8 +8682,8 @@
     <row r="134" ht="15" customHeight="1"/>
     <row r="135" ht="15" customHeight="1"/>
     <row r="136" ht="15" customHeight="1"/>
-    <row r="168" ht="12" customHeight="1"/>
-    <row r="169" ht="12" customHeight="1"/>
+    <row r="137" ht="15" customHeight="1"/>
+    <row r="138" ht="15" customHeight="1"/>
     <row r="170" ht="12" customHeight="1"/>
     <row r="171" ht="12" customHeight="1"/>
     <row r="172" ht="12" customHeight="1"/>
@@ -8353,8 +8691,10 @@
     <row r="174" ht="12" customHeight="1"/>
     <row r="175" ht="12" customHeight="1"/>
     <row r="176" ht="12" customHeight="1"/>
+    <row r="177" ht="12" customHeight="1"/>
+    <row r="178" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN106" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN108" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
@@ -3694,7 +3694,7 @@
         <v>118</v>
       </c>
       <c r="P30" s="1">
-        <v>700001</v>
+        <v>101003</v>
       </c>
       <c r="R30" s="1">
         <v>41</v>
@@ -3769,7 +3769,7 @@
         <v>118</v>
       </c>
       <c r="P31" s="1">
-        <v>700002</v>
+        <v>101004</v>
       </c>
       <c r="R31" s="1">
         <v>41</v>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="O49" s="6"/>
       <c r="P49" s="6">
-        <v>200005</v>
+        <v>800001</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>142</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -10,7 +10,7 @@
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CreatureInfo!$A$1:$AN$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="158">
   <si>
     <t>id</t>
   </si>
@@ -480,6 +480,18 @@
   </si>
   <si>
     <t>人类-魔法师（雷）</t>
+  </si>
+  <si>
+    <t>0,10,0</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（火）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（水）</t>
+  </si>
+  <si>
+    <t>人类-大魔法师（冰）</t>
   </si>
   <si>
     <t>测试骷髅战士</t>
@@ -1135,7 +1147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1158,6 +1170,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1514,7 +1529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN178"/>
+  <dimension ref="A1:AN181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5347,367 +5362,463 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:40">
-      <c r="A50" s="8">
+    <row r="50" s="2" customFormat="1" spans="1:40">
+      <c r="A50" s="6">
+        <v>103101</v>
+      </c>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6">
+        <v>2</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J50" s="6">
+        <v>1</v>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O50" s="6"/>
+      <c r="P50" s="8">
+        <v>700001</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6">
+        <v>1</v>
+      </c>
+      <c r="T50" s="6">
+        <v>10</v>
+      </c>
+      <c r="U50" s="6">
+        <v>1</v>
+      </c>
+      <c r="V50" s="6">
+        <v>1</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X50" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF50" s="6"/>
+      <c r="AG50" s="6"/>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ50" s="7"/>
+      <c r="AK50" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL50" s="6"/>
+      <c r="AM50" s="6">
+        <v>103101</v>
+      </c>
+      <c r="AN50" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:40">
+      <c r="A51" s="6">
+        <v>103102</v>
+      </c>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6">
+        <v>2</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J51" s="6">
+        <v>1</v>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O51" s="6"/>
+      <c r="P51" s="8">
+        <v>700002</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6">
+        <v>1</v>
+      </c>
+      <c r="T51" s="6">
+        <v>10</v>
+      </c>
+      <c r="U51" s="6">
+        <v>1</v>
+      </c>
+      <c r="V51" s="6">
+        <v>1</v>
+      </c>
+      <c r="W51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF51" s="6"/>
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ51" s="7"/>
+      <c r="AK51" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL51" s="6"/>
+      <c r="AM51" s="6">
+        <v>103102</v>
+      </c>
+      <c r="AN51" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" spans="1:40">
+      <c r="A52" s="6">
+        <v>103103</v>
+      </c>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J52" s="6">
+        <v>1</v>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O52" s="6"/>
+      <c r="P52" s="8">
+        <v>700003</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6">
+        <v>1</v>
+      </c>
+      <c r="T52" s="6">
+        <v>10</v>
+      </c>
+      <c r="U52" s="6">
+        <v>1</v>
+      </c>
+      <c r="V52" s="6">
+        <v>1</v>
+      </c>
+      <c r="W52" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="X52" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6">
+        <v>50</v>
+      </c>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6">
+        <v>10</v>
+      </c>
+      <c r="AD52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>1000001</v>
+      </c>
+      <c r="AJ52" s="7"/>
+      <c r="AK52" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL52" s="6"/>
+      <c r="AM52" s="6">
+        <v>103103</v>
+      </c>
+      <c r="AN52" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:40">
+      <c r="A53" s="9">
         <v>900001</v>
       </c>
-      <c r="B50" s="9">
-        <v>1</v>
-      </c>
-      <c r="C50" s="9">
+      <c r="B53" s="10">
+        <v>1</v>
+      </c>
+      <c r="C53" s="10">
         <v>9</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9">
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10">
         <v>2000001</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H53" s="10">
         <v>21010001</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I53" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="J50" s="9">
-        <v>2</v>
-      </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9" t="s">
+      <c r="J53" s="10">
+        <v>2</v>
+      </c>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9">
+      <c r="O53" s="10"/>
+      <c r="P53" s="10">
         <v>100001</v>
       </c>
-      <c r="Q50" s="9"/>
-      <c r="R50" s="9"/>
-      <c r="S50" s="9">
-        <v>2</v>
-      </c>
-      <c r="T50" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="U50" s="9">
-        <v>1</v>
-      </c>
-      <c r="V50" s="9">
-        <v>1</v>
-      </c>
-      <c r="W50" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="X50" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y50" s="9">
-        <v>10</v>
-      </c>
-      <c r="Z50" s="9">
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10">
+        <v>2</v>
+      </c>
+      <c r="T53" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="U53" s="10">
+        <v>1</v>
+      </c>
+      <c r="V53" s="10">
+        <v>1</v>
+      </c>
+      <c r="W53" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="X53" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Y53" s="10">
+        <v>10</v>
+      </c>
+      <c r="Z53" s="10">
         <v>10000</v>
       </c>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9">
-        <v>1</v>
-      </c>
-      <c r="AD50" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE50" s="1">
-        <v>10</v>
-      </c>
-      <c r="AF50" s="9"/>
-      <c r="AG50" s="9"/>
-      <c r="AH50" s="9">
-        <v>2</v>
-      </c>
-      <c r="AI50" s="9">
+      <c r="AA53" s="10"/>
+      <c r="AB53" s="10"/>
+      <c r="AC53" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD53" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF53" s="10"/>
+      <c r="AG53" s="10"/>
+      <c r="AH53" s="10">
+        <v>2</v>
+      </c>
+      <c r="AI53" s="10">
         <v>2000001</v>
       </c>
-      <c r="AJ50" s="8"/>
-      <c r="AK50" s="9" t="s">
+      <c r="AJ53" s="9"/>
+      <c r="AK53" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AL50" s="9">
+      <c r="AL53" s="10">
         <v>300200001</v>
       </c>
-      <c r="AM50" s="8">
+      <c r="AM53" s="9">
         <v>900001</v>
       </c>
-      <c r="AN50" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:40">
-      <c r="A51" s="8">
+      <c r="AN53" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:40">
+      <c r="A54" s="9">
         <v>900002</v>
       </c>
-      <c r="B51" s="9">
-        <v>2</v>
-      </c>
-      <c r="C51" s="9">
+      <c r="B54" s="10">
+        <v>2</v>
+      </c>
+      <c r="C54" s="10">
         <v>9</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9">
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10">
         <v>2000001</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H54" s="10">
         <v>21000001</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I54" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J54" s="10">
         <v>8</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9" t="s">
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9">
+      <c r="O54" s="10"/>
+      <c r="P54" s="10">
         <v>200001</v>
       </c>
-      <c r="Q51" s="9" t="s">
+      <c r="Q54" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9">
-        <v>2</v>
-      </c>
-      <c r="T51" s="9">
-        <v>10</v>
-      </c>
-      <c r="U51" s="9">
-        <v>1</v>
-      </c>
-      <c r="V51" s="9">
-        <v>1</v>
-      </c>
-      <c r="W51" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="X51" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y51" s="9">
-        <v>10</v>
-      </c>
-      <c r="Z51" s="9">
+      <c r="R54" s="10"/>
+      <c r="S54" s="10">
+        <v>2</v>
+      </c>
+      <c r="T54" s="10">
+        <v>10</v>
+      </c>
+      <c r="U54" s="10">
+        <v>1</v>
+      </c>
+      <c r="V54" s="10">
+        <v>1</v>
+      </c>
+      <c r="W54" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="X54" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Y54" s="10">
+        <v>10</v>
+      </c>
+      <c r="Z54" s="10">
         <v>10000</v>
       </c>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9">
-        <v>1</v>
-      </c>
-      <c r="AD51" s="9">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="1">
-        <v>10</v>
-      </c>
-      <c r="AF51" s="9"/>
-      <c r="AG51" s="9"/>
-      <c r="AH51" s="9">
-        <v>2</v>
-      </c>
-      <c r="AI51" s="9">
+      <c r="AA54" s="10"/>
+      <c r="AB54" s="10"/>
+      <c r="AC54" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD54" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>10</v>
+      </c>
+      <c r="AF54" s="10"/>
+      <c r="AG54" s="10"/>
+      <c r="AH54" s="10">
+        <v>2</v>
+      </c>
+      <c r="AI54" s="10">
         <v>2000001</v>
       </c>
-      <c r="AJ51" s="8"/>
-      <c r="AK51" s="9" t="s">
+      <c r="AJ54" s="9"/>
+      <c r="AK54" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AL51" s="9">
+      <c r="AL54" s="10">
         <v>300200002</v>
       </c>
-      <c r="AM51" s="8">
+      <c r="AM54" s="9">
         <v>900002</v>
       </c>
-      <c r="AN51" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:40">
-      <c r="A52" s="3">
-        <v>989996</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="P52">
-        <v>200001</v>
-      </c>
-      <c r="S52">
-        <v>2</v>
-      </c>
-      <c r="T52">
-        <v>6</v>
-      </c>
-      <c r="U52">
-        <v>1</v>
-      </c>
-      <c r="V52">
-        <v>1</v>
-      </c>
-      <c r="W52">
-        <v>0.5</v>
-      </c>
-      <c r="X52">
-        <v>0.5</v>
-      </c>
-      <c r="Z52">
-        <v>100</v>
-      </c>
-      <c r="AC52">
-        <v>35</v>
-      </c>
-      <c r="AD52">
-        <v>1</v>
-      </c>
-      <c r="AE52" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>989996</v>
-      </c>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM52">
-        <v>1</v>
-      </c>
-      <c r="AN52" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:40">
-      <c r="A53" s="3">
-        <v>989997</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="P53">
-        <v>200001</v>
-      </c>
-      <c r="S53">
-        <v>2</v>
-      </c>
-      <c r="T53">
-        <v>6</v>
-      </c>
-      <c r="U53">
-        <v>1</v>
-      </c>
-      <c r="V53">
-        <v>1</v>
-      </c>
-      <c r="W53">
-        <v>0.5</v>
-      </c>
-      <c r="X53">
-        <v>0.5</v>
-      </c>
-      <c r="Z53">
-        <v>100</v>
-      </c>
-      <c r="AC53">
-        <v>35</v>
-      </c>
-      <c r="AD53">
-        <v>1</v>
-      </c>
-      <c r="AE53" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH53" s="3">
-        <v>989997</v>
-      </c>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM53">
-        <v>1</v>
-      </c>
-      <c r="AN53" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:40">
-      <c r="A54" s="3">
-        <v>989998</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="P54">
-        <v>200001</v>
-      </c>
-      <c r="S54">
-        <v>2</v>
-      </c>
-      <c r="T54">
-        <v>6</v>
-      </c>
-      <c r="U54">
-        <v>1</v>
-      </c>
-      <c r="V54">
-        <v>1</v>
-      </c>
-      <c r="W54">
-        <v>0.5</v>
-      </c>
-      <c r="X54">
-        <v>0.5</v>
-      </c>
-      <c r="Z54">
-        <v>100</v>
-      </c>
-      <c r="AC54">
-        <v>35</v>
-      </c>
-      <c r="AD54">
-        <v>1</v>
-      </c>
-      <c r="AE54" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>989998</v>
-      </c>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM54">
-        <v>1</v>
-      </c>
-      <c r="AN54" t="s">
-        <v>153</v>
+      <c r="AN54" s="10" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:40">
       <c r="A55" s="3">
-        <v>989999</v>
+        <v>989996</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55">
@@ -5746,22 +5857,24 @@
       <c r="AE55" s="1">
         <v>10</v>
       </c>
-      <c r="AH55">
-        <v>989999</v>
-      </c>
+      <c r="AH55" s="3">
+        <v>989996</v>
+      </c>
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
       <c r="AK55" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
       <c r="AN55" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:40">
       <c r="A56" s="3">
-        <v>999947</v>
+        <v>989997</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56">
@@ -5801,23 +5914,23 @@
         <v>10</v>
       </c>
       <c r="AH56" s="3">
-        <v>999947</v>
+        <v>989997</v>
       </c>
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
       <c r="AK56" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
       <c r="AN56" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:40">
       <c r="A57" s="3">
-        <v>999948</v>
+        <v>989998</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57">
@@ -5857,23 +5970,23 @@
         <v>10</v>
       </c>
       <c r="AH57" s="3">
-        <v>999948</v>
+        <v>989998</v>
       </c>
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
       <c r="AK57" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
       <c r="AN57" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:40">
       <c r="A58" s="3">
-        <v>999949</v>
+        <v>989999</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58">
@@ -5912,24 +6025,22 @@
       <c r="AE58" s="1">
         <v>10</v>
       </c>
-      <c r="AH58" s="3">
-        <v>999949</v>
-      </c>
-      <c r="AI58" s="4"/>
-      <c r="AJ58" s="4"/>
+      <c r="AH58">
+        <v>989999</v>
+      </c>
       <c r="AK58" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
       <c r="AN58" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:40">
       <c r="A59" s="3">
-        <v>999950</v>
+        <v>999947</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59">
@@ -5969,23 +6080,23 @@
         <v>10</v>
       </c>
       <c r="AH59" s="3">
-        <v>999950</v>
+        <v>999947</v>
       </c>
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
       <c r="AK59" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
       <c r="AN59" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:40">
       <c r="A60" s="3">
-        <v>999951</v>
+        <v>999948</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60">
@@ -6025,23 +6136,23 @@
         <v>10</v>
       </c>
       <c r="AH60" s="3">
-        <v>999951</v>
+        <v>999948</v>
       </c>
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
       <c r="AK60" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
       <c r="AN60" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:40">
       <c r="A61" s="3">
-        <v>999952</v>
+        <v>999949</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61">
@@ -6081,23 +6192,23 @@
         <v>10</v>
       </c>
       <c r="AH61" s="3">
-        <v>999952</v>
+        <v>999949</v>
       </c>
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
       <c r="AK61" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
       <c r="AN61" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:40">
       <c r="A62" s="3">
-        <v>999953</v>
+        <v>999950</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62">
@@ -6137,23 +6248,23 @@
         <v>10</v>
       </c>
       <c r="AH62" s="3">
-        <v>999953</v>
+        <v>999950</v>
       </c>
       <c r="AI62" s="4"/>
       <c r="AJ62" s="4"/>
       <c r="AK62" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
       <c r="AN62" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:40">
       <c r="A63" s="3">
-        <v>999954</v>
+        <v>999951</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63">
@@ -6193,23 +6304,23 @@
         <v>10</v>
       </c>
       <c r="AH63" s="3">
-        <v>999954</v>
+        <v>999951</v>
       </c>
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4"/>
       <c r="AK63" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
       <c r="AN63" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:40">
       <c r="A64" s="3">
-        <v>999955</v>
+        <v>999952</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64">
@@ -6249,23 +6360,23 @@
         <v>10</v>
       </c>
       <c r="AH64" s="3">
-        <v>999955</v>
+        <v>999952</v>
       </c>
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
       <c r="AK64" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
       <c r="AN64" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:40">
       <c r="A65" s="3">
-        <v>999956</v>
+        <v>999953</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65">
@@ -6305,23 +6416,23 @@
         <v>10</v>
       </c>
       <c r="AH65" s="3">
-        <v>999956</v>
+        <v>999953</v>
       </c>
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
       <c r="AK65" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
       <c r="AN65" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:40">
       <c r="A66" s="3">
-        <v>999957</v>
+        <v>999954</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66">
@@ -6361,23 +6472,23 @@
         <v>10</v>
       </c>
       <c r="AH66" s="3">
-        <v>999957</v>
+        <v>999954</v>
       </c>
       <c r="AI66" s="4"/>
       <c r="AJ66" s="4"/>
       <c r="AK66" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
       <c r="AN66" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:40">
       <c r="A67" s="3">
-        <v>999958</v>
+        <v>999955</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67">
@@ -6417,23 +6528,23 @@
         <v>10</v>
       </c>
       <c r="AH67" s="3">
-        <v>999958</v>
+        <v>999955</v>
       </c>
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4"/>
       <c r="AK67" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
       <c r="AN67" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:40">
       <c r="A68" s="3">
-        <v>999959</v>
+        <v>999956</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68">
@@ -6473,23 +6584,23 @@
         <v>10</v>
       </c>
       <c r="AH68" s="3">
-        <v>999959</v>
+        <v>999956</v>
       </c>
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4"/>
       <c r="AK68" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
       <c r="AN68" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:40">
       <c r="A69" s="3">
-        <v>999960</v>
+        <v>999957</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69">
@@ -6529,23 +6640,23 @@
         <v>10</v>
       </c>
       <c r="AH69" s="3">
-        <v>999960</v>
+        <v>999957</v>
       </c>
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
       <c r="AK69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
       <c r="AN69" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:40">
       <c r="A70" s="3">
-        <v>999961</v>
+        <v>999958</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70">
@@ -6585,23 +6696,23 @@
         <v>10</v>
       </c>
       <c r="AH70" s="3">
-        <v>999961</v>
+        <v>999958</v>
       </c>
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
       <c r="AK70" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
       <c r="AN70" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:40">
       <c r="A71" s="3">
-        <v>999962</v>
+        <v>999959</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71">
@@ -6641,23 +6752,23 @@
         <v>10</v>
       </c>
       <c r="AH71" s="3">
-        <v>999962</v>
+        <v>999959</v>
       </c>
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
       <c r="AK71" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
       <c r="AN71" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:40">
       <c r="A72" s="3">
-        <v>999963</v>
+        <v>999960</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72">
@@ -6697,23 +6808,23 @@
         <v>10</v>
       </c>
       <c r="AH72" s="3">
-        <v>999963</v>
+        <v>999960</v>
       </c>
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
       <c r="AK72" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
       <c r="AN72" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:40">
       <c r="A73" s="3">
-        <v>999964</v>
+        <v>999961</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73">
@@ -6753,23 +6864,23 @@
         <v>10</v>
       </c>
       <c r="AH73" s="3">
-        <v>999964</v>
+        <v>999961</v>
       </c>
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
       <c r="AK73" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
       <c r="AN73" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:40">
       <c r="A74" s="3">
-        <v>999965</v>
+        <v>999962</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74">
@@ -6809,23 +6920,23 @@
         <v>10</v>
       </c>
       <c r="AH74" s="3">
-        <v>999965</v>
+        <v>999962</v>
       </c>
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
       <c r="AK74" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
       <c r="AN74" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:40">
       <c r="A75" s="3">
-        <v>999966</v>
+        <v>999963</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75">
@@ -6865,23 +6976,23 @@
         <v>10</v>
       </c>
       <c r="AH75" s="3">
-        <v>999966</v>
+        <v>999963</v>
       </c>
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
       <c r="AK75" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
       <c r="AN75" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:40">
       <c r="A76" s="3">
-        <v>999967</v>
+        <v>999964</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76">
@@ -6921,23 +7032,23 @@
         <v>10</v>
       </c>
       <c r="AH76" s="3">
-        <v>999967</v>
+        <v>999964</v>
       </c>
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
       <c r="AK76" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
       <c r="AN76" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:40">
       <c r="A77" s="3">
-        <v>999968</v>
+        <v>999965</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77">
@@ -6977,23 +7088,23 @@
         <v>10</v>
       </c>
       <c r="AH77" s="3">
-        <v>999968</v>
+        <v>999965</v>
       </c>
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
       <c r="AK77" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
       <c r="AN77" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:40">
       <c r="A78" s="3">
-        <v>999969</v>
+        <v>999966</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78">
@@ -7033,23 +7144,23 @@
         <v>10</v>
       </c>
       <c r="AH78" s="3">
-        <v>999969</v>
+        <v>999966</v>
       </c>
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
       <c r="AK78" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
       <c r="AN78" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:40">
       <c r="A79" s="3">
-        <v>999970</v>
+        <v>999967</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79">
@@ -7089,23 +7200,23 @@
         <v>10</v>
       </c>
       <c r="AH79" s="3">
-        <v>999970</v>
+        <v>999967</v>
       </c>
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
       <c r="AK79" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
       <c r="AN79" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:40">
       <c r="A80" s="3">
-        <v>999971</v>
+        <v>999968</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80">
@@ -7145,23 +7256,23 @@
         <v>10</v>
       </c>
       <c r="AH80" s="3">
-        <v>999971</v>
+        <v>999968</v>
       </c>
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
       <c r="AK80" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
       <c r="AN80" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:40">
       <c r="A81" s="3">
-        <v>999972</v>
+        <v>999969</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81">
@@ -7201,23 +7312,23 @@
         <v>10</v>
       </c>
       <c r="AH81" s="3">
-        <v>999972</v>
+        <v>999969</v>
       </c>
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
       <c r="AK81" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
       <c r="AN81" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:40">
       <c r="A82" s="3">
-        <v>999973</v>
+        <v>999970</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82">
@@ -7257,23 +7368,23 @@
         <v>10</v>
       </c>
       <c r="AH82" s="3">
-        <v>999973</v>
+        <v>999970</v>
       </c>
       <c r="AI82" s="4"/>
       <c r="AJ82" s="4"/>
       <c r="AK82" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
       <c r="AN82" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:40">
       <c r="A83" s="3">
-        <v>999974</v>
+        <v>999971</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83">
@@ -7313,23 +7424,23 @@
         <v>10</v>
       </c>
       <c r="AH83" s="3">
-        <v>999974</v>
+        <v>999971</v>
       </c>
       <c r="AI83" s="4"/>
       <c r="AJ83" s="4"/>
       <c r="AK83" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
       <c r="AN83" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:40">
       <c r="A84" s="3">
-        <v>999975</v>
+        <v>999972</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84">
@@ -7369,23 +7480,23 @@
         <v>10</v>
       </c>
       <c r="AH84" s="3">
-        <v>999975</v>
+        <v>999972</v>
       </c>
       <c r="AI84" s="4"/>
       <c r="AJ84" s="4"/>
       <c r="AK84" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
       <c r="AN84" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:40">
       <c r="A85" s="3">
-        <v>999976</v>
+        <v>999973</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85">
@@ -7425,23 +7536,23 @@
         <v>10</v>
       </c>
       <c r="AH85" s="3">
-        <v>999976</v>
+        <v>999973</v>
       </c>
       <c r="AI85" s="4"/>
       <c r="AJ85" s="4"/>
       <c r="AK85" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
       <c r="AN85" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:40">
       <c r="A86" s="3">
-        <v>999977</v>
+        <v>999974</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86">
@@ -7481,23 +7592,23 @@
         <v>10</v>
       </c>
       <c r="AH86" s="3">
-        <v>999977</v>
+        <v>999974</v>
       </c>
       <c r="AI86" s="4"/>
       <c r="AJ86" s="4"/>
       <c r="AK86" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
       <c r="AN86" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:40">
       <c r="A87" s="3">
-        <v>999978</v>
+        <v>999975</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87">
@@ -7537,23 +7648,23 @@
         <v>10</v>
       </c>
       <c r="AH87" s="3">
-        <v>999978</v>
+        <v>999975</v>
       </c>
       <c r="AI87" s="4"/>
       <c r="AJ87" s="4"/>
       <c r="AK87" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
       <c r="AN87" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:40">
       <c r="A88" s="3">
-        <v>999979</v>
+        <v>999976</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88">
@@ -7593,23 +7704,23 @@
         <v>10</v>
       </c>
       <c r="AH88" s="3">
-        <v>999979</v>
+        <v>999976</v>
       </c>
       <c r="AI88" s="4"/>
       <c r="AJ88" s="4"/>
       <c r="AK88" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
       <c r="AN88" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:40">
       <c r="A89" s="3">
-        <v>999980</v>
+        <v>999977</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89">
@@ -7649,23 +7760,23 @@
         <v>10</v>
       </c>
       <c r="AH89" s="3">
-        <v>999980</v>
+        <v>999977</v>
       </c>
       <c r="AI89" s="4"/>
       <c r="AJ89" s="4"/>
       <c r="AK89" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
       <c r="AN89" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:40">
       <c r="A90" s="3">
-        <v>999981</v>
+        <v>999978</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90">
@@ -7705,24 +7816,25 @@
         <v>10</v>
       </c>
       <c r="AH90" s="3">
-        <v>999981</v>
+        <v>999978</v>
       </c>
       <c r="AI90" s="4"/>
       <c r="AJ90" s="4"/>
       <c r="AK90" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
       <c r="AN90" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:40">
-      <c r="A91">
-        <v>999982</v>
-      </c>
+      <c r="A91" s="3">
+        <v>999979</v>
+      </c>
+      <c r="B91" s="4"/>
       <c r="C91">
         <v>1</v>
       </c>
@@ -7759,23 +7871,26 @@
       <c r="AE91" s="1">
         <v>10</v>
       </c>
-      <c r="AH91">
-        <v>999982</v>
-      </c>
+      <c r="AH91" s="3">
+        <v>999979</v>
+      </c>
+      <c r="AI91" s="4"/>
+      <c r="AJ91" s="4"/>
       <c r="AK91" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
       <c r="AN91" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:40">
-      <c r="A92">
-        <v>999983</v>
-      </c>
+      <c r="A92" s="3">
+        <v>999980</v>
+      </c>
+      <c r="B92" s="4"/>
       <c r="C92">
         <v>1</v>
       </c>
@@ -7812,23 +7927,26 @@
       <c r="AE92" s="1">
         <v>10</v>
       </c>
-      <c r="AH92">
-        <v>999983</v>
-      </c>
+      <c r="AH92" s="3">
+        <v>999980</v>
+      </c>
+      <c r="AI92" s="4"/>
+      <c r="AJ92" s="4"/>
       <c r="AK92" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
       <c r="AN92" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:40">
-      <c r="A93">
-        <v>999984</v>
-      </c>
+      <c r="A93" s="3">
+        <v>999981</v>
+      </c>
+      <c r="B93" s="4"/>
       <c r="C93">
         <v>1</v>
       </c>
@@ -7865,22 +7983,24 @@
       <c r="AE93" s="1">
         <v>10</v>
       </c>
-      <c r="AH93">
-        <v>999984</v>
-      </c>
+      <c r="AH93" s="3">
+        <v>999981</v>
+      </c>
+      <c r="AI93" s="4"/>
+      <c r="AJ93" s="4"/>
       <c r="AK93" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
       <c r="AN93" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:40">
       <c r="A94">
-        <v>999985</v>
+        <v>999982</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7919,21 +8039,21 @@
         <v>10</v>
       </c>
       <c r="AH94">
-        <v>999985</v>
+        <v>999982</v>
       </c>
       <c r="AK94" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
       <c r="AN94" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:40">
       <c r="A95">
-        <v>999986</v>
+        <v>999983</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7972,21 +8092,21 @@
         <v>10</v>
       </c>
       <c r="AH95">
-        <v>999986</v>
+        <v>999983</v>
       </c>
       <c r="AK95" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
       <c r="AN95" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:40">
       <c r="A96">
-        <v>999987</v>
+        <v>999984</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -8025,21 +8145,21 @@
         <v>10</v>
       </c>
       <c r="AH96">
-        <v>999987</v>
+        <v>999984</v>
       </c>
       <c r="AK96" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
       <c r="AN96" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:40">
       <c r="A97">
-        <v>999988</v>
+        <v>999985</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -8078,21 +8198,21 @@
         <v>10</v>
       </c>
       <c r="AH97">
-        <v>999988</v>
+        <v>999985</v>
       </c>
       <c r="AK97" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
       <c r="AN97" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:40">
       <c r="A98">
-        <v>999989</v>
+        <v>999986</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -8131,21 +8251,21 @@
         <v>10</v>
       </c>
       <c r="AH98">
-        <v>999989</v>
+        <v>999986</v>
       </c>
       <c r="AK98" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
       <c r="AN98" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:40">
       <c r="A99">
-        <v>999990</v>
+        <v>999987</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -8184,21 +8304,21 @@
         <v>10</v>
       </c>
       <c r="AH99">
-        <v>999990</v>
+        <v>999987</v>
       </c>
       <c r="AK99" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
       <c r="AN99" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:40">
       <c r="A100">
-        <v>999991</v>
+        <v>999988</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -8237,21 +8357,21 @@
         <v>10</v>
       </c>
       <c r="AH100">
-        <v>999991</v>
+        <v>999988</v>
       </c>
       <c r="AK100" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
       <c r="AN100" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:40">
       <c r="A101">
-        <v>999992</v>
+        <v>999989</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -8290,21 +8410,21 @@
         <v>10</v>
       </c>
       <c r="AH101">
-        <v>999992</v>
+        <v>999989</v>
       </c>
       <c r="AK101" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
       <c r="AN101" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:40">
       <c r="A102">
-        <v>999993</v>
+        <v>999990</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -8343,21 +8463,21 @@
         <v>10</v>
       </c>
       <c r="AH102">
-        <v>999993</v>
+        <v>999990</v>
       </c>
       <c r="AK102" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
       <c r="AN102" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:40">
       <c r="A103">
-        <v>999994</v>
+        <v>999991</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -8396,21 +8516,21 @@
         <v>10</v>
       </c>
       <c r="AH103">
-        <v>999994</v>
+        <v>999991</v>
       </c>
       <c r="AK103" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM103">
         <v>1</v>
       </c>
       <c r="AN103" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:40">
       <c r="A104">
-        <v>999995</v>
+        <v>999992</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -8449,21 +8569,21 @@
         <v>10</v>
       </c>
       <c r="AH104">
-        <v>999995</v>
+        <v>999992</v>
       </c>
       <c r="AK104" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM104">
         <v>1</v>
       </c>
       <c r="AN104" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:40">
       <c r="A105">
-        <v>999996</v>
+        <v>999993</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -8502,21 +8622,21 @@
         <v>10</v>
       </c>
       <c r="AH105">
-        <v>999996</v>
+        <v>999993</v>
       </c>
       <c r="AK105" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM105">
         <v>1</v>
       </c>
       <c r="AN105" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:40">
       <c r="A106">
-        <v>999997</v>
+        <v>999994</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -8555,21 +8675,21 @@
         <v>10</v>
       </c>
       <c r="AH106">
-        <v>999997</v>
+        <v>999994</v>
       </c>
       <c r="AK106" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM106">
         <v>1</v>
       </c>
       <c r="AN106" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:40">
       <c r="A107">
-        <v>999998</v>
+        <v>999995</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -8608,21 +8728,21 @@
         <v>10</v>
       </c>
       <c r="AH107">
-        <v>999998</v>
+        <v>999995</v>
       </c>
       <c r="AK107" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AM107">
         <v>1</v>
       </c>
       <c r="AN107" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:40">
       <c r="A108">
-        <v>999999</v>
+        <v>999996</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -8661,21 +8781,177 @@
         <v>10</v>
       </c>
       <c r="AH108">
+        <v>999996</v>
+      </c>
+      <c r="AK108" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM108">
+        <v>1</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" spans="1:40">
+      <c r="A109">
+        <v>999997</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="P109">
+        <v>200001</v>
+      </c>
+      <c r="S109">
+        <v>2</v>
+      </c>
+      <c r="T109">
+        <v>6</v>
+      </c>
+      <c r="U109">
+        <v>1</v>
+      </c>
+      <c r="V109">
+        <v>1</v>
+      </c>
+      <c r="W109">
+        <v>0.5</v>
+      </c>
+      <c r="X109">
+        <v>0.5</v>
+      </c>
+      <c r="Z109">
+        <v>100</v>
+      </c>
+      <c r="AC109">
+        <v>35</v>
+      </c>
+      <c r="AD109">
+        <v>1</v>
+      </c>
+      <c r="AE109" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH109">
+        <v>999997</v>
+      </c>
+      <c r="AK109" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM109">
+        <v>1</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" spans="1:40">
+      <c r="A110">
+        <v>999998</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="P110">
+        <v>200001</v>
+      </c>
+      <c r="S110">
+        <v>2</v>
+      </c>
+      <c r="T110">
+        <v>6</v>
+      </c>
+      <c r="U110">
+        <v>1</v>
+      </c>
+      <c r="V110">
+        <v>1</v>
+      </c>
+      <c r="W110">
+        <v>0.5</v>
+      </c>
+      <c r="X110">
+        <v>0.5</v>
+      </c>
+      <c r="Z110">
+        <v>100</v>
+      </c>
+      <c r="AC110">
+        <v>35</v>
+      </c>
+      <c r="AD110">
+        <v>1</v>
+      </c>
+      <c r="AE110" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH110">
+        <v>999998</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM110">
+        <v>1</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" spans="1:40">
+      <c r="A111">
         <v>999999</v>
       </c>
-      <c r="AK108" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM108">
-        <v>1</v>
-      </c>
-      <c r="AN108" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="128" ht="15" customHeight="1"/>
-    <row r="129" ht="15" customHeight="1"/>
-    <row r="130" ht="15" customHeight="1"/>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="P111">
+        <v>200001</v>
+      </c>
+      <c r="S111">
+        <v>2</v>
+      </c>
+      <c r="T111">
+        <v>6</v>
+      </c>
+      <c r="U111">
+        <v>1</v>
+      </c>
+      <c r="V111">
+        <v>1</v>
+      </c>
+      <c r="W111">
+        <v>0.5</v>
+      </c>
+      <c r="X111">
+        <v>0.5</v>
+      </c>
+      <c r="Z111">
+        <v>100</v>
+      </c>
+      <c r="AC111">
+        <v>35</v>
+      </c>
+      <c r="AD111">
+        <v>1</v>
+      </c>
+      <c r="AE111" s="1">
+        <v>10</v>
+      </c>
+      <c r="AH111">
+        <v>999999</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM111">
+        <v>1</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>157</v>
+      </c>
+    </row>
     <row r="131" ht="15" customHeight="1"/>
     <row r="132" ht="15" customHeight="1"/>
     <row r="133" ht="15" customHeight="1"/>
@@ -8684,17 +8960,20 @@
     <row r="136" ht="15" customHeight="1"/>
     <row r="137" ht="15" customHeight="1"/>
     <row r="138" ht="15" customHeight="1"/>
-    <row r="170" ht="12" customHeight="1"/>
-    <row r="171" ht="12" customHeight="1"/>
-    <row r="172" ht="12" customHeight="1"/>
+    <row r="139" ht="15" customHeight="1"/>
+    <row r="140" ht="15" customHeight="1"/>
+    <row r="141" ht="15" customHeight="1"/>
     <row r="173" ht="12" customHeight="1"/>
     <row r="174" ht="12" customHeight="1"/>
     <row r="175" ht="12" customHeight="1"/>
     <row r="176" ht="12" customHeight="1"/>
     <row r="177" ht="12" customHeight="1"/>
     <row r="178" ht="12" customHeight="1"/>
+    <row r="179" ht="12" customHeight="1"/>
+    <row r="180" ht="12" customHeight="1"/>
+    <row r="181" ht="12" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN108" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AN111" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -482,7 +482,7 @@
     <t>人类-魔法师（雷）</t>
   </si>
   <si>
-    <t>0,10,0</t>
+    <t>0,6,0</t>
   </si>
   <si>
     <t>人类-大魔法师（火）</t>
@@ -1147,7 +1147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1170,9 +1170,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5390,7 +5387,7 @@
         <v>98</v>
       </c>
       <c r="O50" s="6"/>
-      <c r="P50" s="8">
+      <c r="P50" s="6">
         <v>700001</v>
       </c>
       <c r="Q50" s="6" t="s">
@@ -5478,7 +5475,7 @@
         <v>98</v>
       </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="8">
+      <c r="P51" s="6">
         <v>700002</v>
       </c>
       <c r="Q51" s="6" t="s">
@@ -5566,7 +5563,7 @@
         <v>98</v>
       </c>
       <c r="O52" s="6"/>
-      <c r="P52" s="8">
+      <c r="P52" s="6">
         <v>700003</v>
       </c>
       <c r="Q52" s="6" t="s">
@@ -5627,192 +5624,192 @@
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:40">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>900001</v>
       </c>
-      <c r="B53" s="10">
-        <v>1</v>
-      </c>
-      <c r="C53" s="10">
+      <c r="B53" s="9">
+        <v>1</v>
+      </c>
+      <c r="C53" s="9">
         <v>9</v>
       </c>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10">
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9">
         <v>2000001</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="9">
         <v>21010001</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="J53" s="10">
-        <v>2</v>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10" t="s">
+      <c r="J53" s="9">
+        <v>2</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10">
+      <c r="O53" s="9"/>
+      <c r="P53" s="9">
         <v>100001</v>
       </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10">
-        <v>2</v>
-      </c>
-      <c r="T53" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="U53" s="10">
-        <v>1</v>
-      </c>
-      <c r="V53" s="10">
-        <v>1</v>
-      </c>
-      <c r="W53" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="X53" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Y53" s="10">
-        <v>10</v>
-      </c>
-      <c r="Z53" s="10">
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9">
+        <v>2</v>
+      </c>
+      <c r="T53" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U53" s="9">
+        <v>1</v>
+      </c>
+      <c r="V53" s="9">
+        <v>1</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z53" s="9">
         <v>10000</v>
       </c>
-      <c r="AA53" s="10"/>
-      <c r="AB53" s="10"/>
-      <c r="AC53" s="10">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="10">
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD53" s="9">
         <v>1</v>
       </c>
       <c r="AE53" s="1">
         <v>10</v>
       </c>
-      <c r="AF53" s="10"/>
-      <c r="AG53" s="10"/>
-      <c r="AH53" s="10">
-        <v>2</v>
-      </c>
-      <c r="AI53" s="10">
+      <c r="AF53" s="9"/>
+      <c r="AG53" s="9"/>
+      <c r="AH53" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI53" s="9">
         <v>2000001</v>
       </c>
-      <c r="AJ53" s="9"/>
-      <c r="AK53" s="10" t="s">
+      <c r="AJ53" s="8"/>
+      <c r="AK53" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AL53" s="10">
+      <c r="AL53" s="9">
         <v>300200001</v>
       </c>
-      <c r="AM53" s="9">
+      <c r="AM53" s="8">
         <v>900001</v>
       </c>
-      <c r="AN53" s="10" t="s">
+      <c r="AN53" s="9" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:40">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>900002</v>
       </c>
-      <c r="B54" s="10">
-        <v>2</v>
-      </c>
-      <c r="C54" s="10">
+      <c r="B54" s="9">
+        <v>2</v>
+      </c>
+      <c r="C54" s="9">
         <v>9</v>
       </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10">
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9">
         <v>2000001</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="9">
         <v>21000001</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="J54" s="10">
+      <c r="J54" s="9">
         <v>8</v>
       </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10" t="s">
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10">
+      <c r="O54" s="9"/>
+      <c r="P54" s="9">
         <v>200001</v>
       </c>
-      <c r="Q54" s="10" t="s">
+      <c r="Q54" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="R54" s="10"/>
-      <c r="S54" s="10">
-        <v>2</v>
-      </c>
-      <c r="T54" s="10">
-        <v>10</v>
-      </c>
-      <c r="U54" s="10">
-        <v>1</v>
-      </c>
-      <c r="V54" s="10">
-        <v>1</v>
-      </c>
-      <c r="W54" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="X54" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Y54" s="10">
-        <v>10</v>
-      </c>
-      <c r="Z54" s="10">
+      <c r="R54" s="9"/>
+      <c r="S54" s="9">
+        <v>2</v>
+      </c>
+      <c r="T54" s="9">
+        <v>10</v>
+      </c>
+      <c r="U54" s="9">
+        <v>1</v>
+      </c>
+      <c r="V54" s="9">
+        <v>1</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="X54" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>10</v>
+      </c>
+      <c r="Z54" s="9">
         <v>10000</v>
       </c>
-      <c r="AA54" s="10"/>
-      <c r="AB54" s="10"/>
-      <c r="AC54" s="10">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="10">
+      <c r="AA54" s="9"/>
+      <c r="AB54" s="9"/>
+      <c r="AC54" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD54" s="9">
         <v>1</v>
       </c>
       <c r="AE54" s="1">
         <v>10</v>
       </c>
-      <c r="AF54" s="10"/>
-      <c r="AG54" s="10"/>
-      <c r="AH54" s="10">
-        <v>2</v>
-      </c>
-      <c r="AI54" s="10">
+      <c r="AF54" s="9"/>
+      <c r="AG54" s="9"/>
+      <c r="AH54" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI54" s="9">
         <v>2000001</v>
       </c>
-      <c r="AJ54" s="9"/>
-      <c r="AK54" s="10" t="s">
+      <c r="AJ54" s="8"/>
+      <c r="AK54" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AL54" s="10">
+      <c r="AL54" s="9">
         <v>300200002</v>
       </c>
-      <c r="AM54" s="9">
+      <c r="AM54" s="8">
         <v>900002</v>
       </c>
-      <c r="AN54" s="10" t="s">
+      <c r="AN54" s="9" t="s">
         <v>155</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
@@ -1548,9 +1548,10 @@
     <col min="18" max="18" width="20.375" customWidth="1"/>
     <col min="19" max="19" width="35.875" customWidth="1"/>
     <col min="20" max="20" width="21.5" customWidth="1"/>
-    <col min="21" max="22" width="29.625" customWidth="1"/>
+    <col min="21" max="21" width="29.625" customWidth="1"/>
+    <col min="22" max="22" width="17.125" customWidth="1"/>
     <col min="23" max="23" width="20.25" customWidth="1"/>
-    <col min="24" max="24" width="46.875" customWidth="1"/>
+    <col min="24" max="24" width="18.25" customWidth="1"/>
     <col min="25" max="25" width="11.125" customWidth="1"/>
     <col min="26" max="27" width="11.75" customWidth="1"/>
     <col min="28" max="28" width="6.375" customWidth="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="164">
   <si>
     <t>id</t>
   </si>
@@ -311,15 +311,24 @@
     <t>创建角色-兽人</t>
   </si>
   <si>
+    <t>ui_class_3</t>
+  </si>
+  <si>
     <t>人类战士</t>
   </si>
   <si>
     <t>1,2,3,10,</t>
   </si>
   <si>
+    <t>ui_class_6</t>
+  </si>
+  <si>
     <t>人类弓箭手</t>
   </si>
   <si>
+    <t>ui_class_2</t>
+  </si>
+  <si>
     <t>人类魔法师（火）</t>
   </si>
   <si>
@@ -410,6 +419,9 @@
     <t>2000100001,2000200001,</t>
   </si>
   <si>
+    <t>ui_class_1</t>
+  </si>
+  <si>
     <t>Card_Scene_7</t>
   </si>
   <si>
@@ -452,6 +464,9 @@
     <t>Attack5</t>
   </si>
   <si>
+    <t>ui_class_7</t>
+  </si>
+  <si>
     <t>人类-持盾战士</t>
   </si>
   <si>
@@ -483,6 +498,9 @@
   </si>
   <si>
     <t>0,6,0</t>
+  </si>
+  <si>
+    <t>ui_class_5</t>
   </si>
   <si>
     <t>人类-大魔法师（火）</t>
@@ -2287,7 +2305,9 @@
       <c r="AI11" s="1">
         <v>1000001</v>
       </c>
-      <c r="AJ11" s="5"/>
+      <c r="AJ11" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AK11" s="1" t="s">
         <v>84</v>
       </c>
@@ -2298,7 +2318,7 @@
         <v>1001</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:40">
@@ -2312,7 +2332,7 @@
         <v>1000001</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J12" s="1">
         <v>7</v>
@@ -2356,7 +2376,9 @@
       <c r="AI12" s="1">
         <v>1000001</v>
       </c>
-      <c r="AJ12" s="5"/>
+      <c r="AJ12" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="AK12" s="1" t="s">
         <v>84</v>
       </c>
@@ -2367,7 +2389,7 @@
         <v>1002</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:40">
@@ -2381,7 +2403,7 @@
         <v>1000001</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -2425,7 +2447,9 @@
       <c r="AI13" s="1">
         <v>1000001</v>
       </c>
-      <c r="AJ13" s="5"/>
+      <c r="AJ13" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK13" s="1" t="s">
         <v>84</v>
       </c>
@@ -2436,7 +2460,7 @@
         <v>1003</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:40">
@@ -2450,7 +2474,7 @@
         <v>1000001</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -2494,7 +2518,9 @@
       <c r="AI14" s="1">
         <v>1000001</v>
       </c>
-      <c r="AJ14" s="5"/>
+      <c r="AJ14" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK14" s="1" t="s">
         <v>84</v>
       </c>
@@ -2505,7 +2531,7 @@
         <v>1004</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="12" customHeight="1" spans="1:40">
@@ -2525,13 +2551,13 @@
         <v>21010001</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J15" s="1">
         <v>2</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P15" s="1">
         <v>100001</v>
@@ -2575,7 +2601,9 @@
       <c r="AI15" s="1">
         <v>2000001</v>
       </c>
-      <c r="AJ15" s="5"/>
+      <c r="AJ15" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AK15" s="1" t="s">
         <v>86</v>
       </c>
@@ -2586,7 +2614,7 @@
         <v>2001</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:40">
@@ -2606,19 +2634,19 @@
         <v>21000001</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J16" s="1">
         <v>8</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P16" s="1">
         <v>200001</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S16" s="1">
         <v>2</v>
@@ -2659,7 +2687,9 @@
       <c r="AI16" s="1">
         <v>2000001</v>
       </c>
-      <c r="AJ16" s="5"/>
+      <c r="AJ16" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="AK16" s="1" t="s">
         <v>86</v>
       </c>
@@ -2670,7 +2700,7 @@
         <v>2002</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:40">
@@ -2690,19 +2720,19 @@
         <v>21010002</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P17" s="1">
         <v>201001</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S17" s="1">
         <v>2</v>
@@ -2743,7 +2773,9 @@
       <c r="AI17" s="1">
         <v>2000001</v>
       </c>
-      <c r="AJ17" s="5"/>
+      <c r="AJ17" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK17" s="1" t="s">
         <v>86</v>
       </c>
@@ -2754,7 +2786,7 @@
         <v>2003</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:40">
@@ -2774,19 +2806,19 @@
         <v>21010003</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P18" s="1">
         <v>201002</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S18" s="1">
         <v>2</v>
@@ -2827,7 +2859,9 @@
       <c r="AI18" s="1">
         <v>2000001</v>
       </c>
-      <c r="AJ18" s="5"/>
+      <c r="AJ18" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK18" s="1" t="s">
         <v>86</v>
       </c>
@@ -2838,7 +2872,7 @@
         <v>2004</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:40">
@@ -2852,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="S19" s="1">
         <v>2</v>
@@ -2907,7 +2941,7 @@
         <v>3001</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:40">
@@ -2921,10 +2955,10 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P20" s="1">
         <v>300001</v>
@@ -2982,7 +3016,7 @@
         <v>3002</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:40">
@@ -2996,13 +3030,13 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="O21" s="1">
         <v>1</v>
@@ -3063,7 +3097,7 @@
         <v>3003</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:40">
@@ -3077,13 +3111,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -3144,7 +3178,7 @@
         <v>3004</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:40">
@@ -3164,13 +3198,13 @@
         <v>41000002</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" s="1">
         <v>2</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P23" s="1">
         <v>101001</v>
@@ -3214,7 +3248,9 @@
       <c r="AI23" s="1">
         <v>4000001</v>
       </c>
-      <c r="AJ23" s="5"/>
+      <c r="AJ23" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AK23" s="1" t="s">
         <v>86</v>
       </c>
@@ -3225,7 +3261,7 @@
         <v>4001</v>
       </c>
       <c r="AN23" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:40">
@@ -3242,7 +3278,7 @@
         <v>4000001</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P24" s="1">
         <v>500001</v>
@@ -3300,7 +3336,7 @@
         <v>4002</v>
       </c>
       <c r="AN24" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:40">
@@ -3317,7 +3353,7 @@
         <v>4000001</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P25" s="1">
         <v>600001</v>
@@ -3375,7 +3411,7 @@
         <v>4003</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:40">
@@ -3392,13 +3428,13 @@
         <v>4000001</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P26" s="1">
         <v>202001</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="R26" s="1">
         <v>30</v>
@@ -3453,7 +3489,7 @@
         <v>4004</v>
       </c>
       <c r="AN26" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:40">
@@ -3470,7 +3506,7 @@
         <v>4000001</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P27" s="1">
         <v>500002</v>
@@ -3528,7 +3564,7 @@
         <v>4005</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:40">
@@ -3545,7 +3581,7 @@
         <v>5000001</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P28" s="1">
         <v>101002</v>
@@ -3592,7 +3628,9 @@
       <c r="AI28" s="1">
         <v>5000001</v>
       </c>
-      <c r="AJ28" s="5"/>
+      <c r="AJ28" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AK28" s="1" t="s">
         <v>86</v>
       </c>
@@ -3603,7 +3641,7 @@
         <v>5001</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:40">
@@ -3623,7 +3661,7 @@
         <v>51010001</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J29" s="1">
         <v>8</v>
@@ -3632,7 +3670,7 @@
         <v>203001</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="R29" s="1">
         <v>1</v>
@@ -3687,7 +3725,7 @@
         <v>5002</v>
       </c>
       <c r="AN29" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:40">
@@ -3704,7 +3742,7 @@
         <v>5000001</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P30" s="1">
         <v>101003</v>
@@ -3751,7 +3789,9 @@
       <c r="AI30" s="1">
         <v>5000001</v>
       </c>
-      <c r="AJ30" s="5"/>
+      <c r="AJ30" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK30" s="1" t="s">
         <v>86</v>
       </c>
@@ -3762,7 +3802,7 @@
         <v>5003</v>
       </c>
       <c r="AN30" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:40">
@@ -3779,7 +3819,7 @@
         <v>5000001</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P31" s="1">
         <v>101004</v>
@@ -3826,7 +3866,9 @@
       <c r="AI31" s="1">
         <v>5000001</v>
       </c>
-      <c r="AJ31" s="5"/>
+      <c r="AJ31" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK31" s="1" t="s">
         <v>86</v>
       </c>
@@ -3837,7 +3879,7 @@
         <v>5004</v>
       </c>
       <c r="AN31" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:40">
@@ -3851,13 +3893,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G32" s="1">
         <v>6000001</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J32" s="1">
         <v>3</v>
@@ -3904,9 +3946,11 @@
       <c r="AI32" s="1">
         <v>6000001</v>
       </c>
-      <c r="AJ32" s="5"/>
+      <c r="AJ32" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="AK32" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AL32" s="5">
         <v>300600001</v>
@@ -3915,7 +3959,7 @@
         <v>6001</v>
       </c>
       <c r="AN32" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:40">
@@ -3935,19 +3979,19 @@
         <v>61010002</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J33" s="1">
         <v>7</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P33" s="1">
         <v>204001</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -3988,9 +4032,11 @@
       <c r="AI33" s="1">
         <v>6000001</v>
       </c>
-      <c r="AJ33" s="5"/>
+      <c r="AJ33" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="AK33" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AL33" s="5">
         <v>300600002</v>
@@ -3999,7 +4045,7 @@
         <v>6002</v>
       </c>
       <c r="AN33" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:40">
@@ -4016,7 +4062,7 @@
         <v>6000001</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J34" s="1">
         <v>8</v>
@@ -4065,7 +4111,7 @@
       </c>
       <c r="AJ34" s="5"/>
       <c r="AK34" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AL34" s="5">
         <v>300600003</v>
@@ -4074,7 +4120,7 @@
         <v>6003</v>
       </c>
       <c r="AN34" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:40">
@@ -4094,19 +4140,19 @@
         <v>61010003</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P35" s="1">
         <v>204002</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="S35" s="1">
         <v>2</v>
@@ -4147,9 +4193,11 @@
       <c r="AI35" s="1">
         <v>6000001</v>
       </c>
-      <c r="AJ35" s="5"/>
+      <c r="AJ35" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK35" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AL35" s="5">
         <v>300600004</v>
@@ -4158,7 +4206,7 @@
         <v>6004</v>
       </c>
       <c r="AN35" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:40">
@@ -4178,19 +4226,19 @@
         <v>61010003</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P36" s="1">
         <v>204003</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="S36" s="1">
         <v>2</v>
@@ -4231,9 +4279,11 @@
       <c r="AI36" s="1">
         <v>6000001</v>
       </c>
-      <c r="AJ36" s="5"/>
+      <c r="AJ36" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK36" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AL36" s="5">
         <v>300600005</v>
@@ -4242,7 +4292,7 @@
         <v>6005</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:40">
@@ -4256,13 +4306,13 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G37" s="1">
         <v>7000001</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P37" s="1">
         <v>200001</v>
@@ -4306,7 +4356,9 @@
       <c r="AI37" s="1">
         <v>7000001</v>
       </c>
-      <c r="AJ37" s="5"/>
+      <c r="AJ37" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AK37" s="1" t="s">
         <v>86</v>
       </c>
@@ -4317,7 +4369,7 @@
         <v>7001</v>
       </c>
       <c r="AN37" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:40">
@@ -4337,19 +4389,19 @@
         <v>71000001</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J38" s="1">
         <v>8</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P38" s="1">
         <v>205001</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S38" s="1">
         <v>2</v>
@@ -4401,7 +4453,7 @@
         <v>7002</v>
       </c>
       <c r="AN38" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:40">
@@ -4421,19 +4473,19 @@
         <v>71010004</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P39" s="1">
         <v>205002</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S39" s="1">
         <v>2</v>
@@ -4474,7 +4526,9 @@
       <c r="AI39" s="1">
         <v>7000001</v>
       </c>
-      <c r="AJ39" s="5"/>
+      <c r="AJ39" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK39" s="1" t="s">
         <v>86</v>
       </c>
@@ -4485,7 +4539,7 @@
         <v>7003</v>
       </c>
       <c r="AN39" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:40">
@@ -4505,19 +4559,19 @@
         <v>71010004</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J40" s="1">
         <v>1</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P40" s="1">
         <v>205003</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S40" s="1">
         <v>2</v>
@@ -4558,7 +4612,9 @@
       <c r="AI40" s="1">
         <v>7000001</v>
       </c>
-      <c r="AJ40" s="5"/>
+      <c r="AJ40" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="AK40" s="1" t="s">
         <v>86</v>
       </c>
@@ -4569,7 +4625,7 @@
         <v>7004</v>
       </c>
       <c r="AN40" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:40">
@@ -4588,7 +4644,7 @@
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J41" s="6">
         <v>2</v>
@@ -4644,7 +4700,9 @@
       <c r="AI41" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ41" s="7"/>
+      <c r="AJ41" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="AK41" s="6" t="s">
         <v>84</v>
       </c>
@@ -4653,7 +4711,7 @@
         <v>101001</v>
       </c>
       <c r="AN41" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:40">
@@ -4672,7 +4730,7 @@
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J42" s="6">
         <v>4</v>
@@ -4681,7 +4739,7 @@
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="6">
@@ -4732,7 +4790,9 @@
       <c r="AI42" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ42" s="7"/>
+      <c r="AJ42" s="7" t="s">
+        <v>144</v>
+      </c>
       <c r="AK42" s="6" t="s">
         <v>84</v>
       </c>
@@ -4741,7 +4801,7 @@
         <v>101002</v>
       </c>
       <c r="AN42" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" spans="1:40">
@@ -4760,7 +4820,7 @@
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J43" s="6">
         <v>7</v>
@@ -4769,14 +4829,14 @@
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="O43" s="6"/>
       <c r="P43" s="6">
         <v>200001</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R43" s="6"/>
       <c r="S43" s="6">
@@ -4820,7 +4880,9 @@
       <c r="AI43" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ43" s="7"/>
+      <c r="AJ43" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="AK43" s="6" t="s">
         <v>84</v>
       </c>
@@ -4829,7 +4891,7 @@
         <v>102001</v>
       </c>
       <c r="AN43" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" spans="1:40">
@@ -4848,7 +4910,7 @@
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J44" s="6">
         <v>7</v>
@@ -4857,14 +4919,14 @@
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="6">
         <v>205001</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R44" s="6"/>
       <c r="S44" s="6">
@@ -4908,7 +4970,9 @@
       <c r="AI44" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ44" s="7"/>
+      <c r="AJ44" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="AK44" s="6" t="s">
         <v>84</v>
       </c>
@@ -4917,7 +4981,7 @@
         <v>102002</v>
       </c>
       <c r="AN44" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:40">
@@ -4936,7 +5000,7 @@
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J45" s="6">
         <v>7</v>
@@ -4945,14 +5009,14 @@
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="6">
         <v>204001</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R45" s="6"/>
       <c r="S45" s="6">
@@ -4996,7 +5060,9 @@
       <c r="AI45" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ45" s="7"/>
+      <c r="AJ45" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="AK45" s="6" t="s">
         <v>84</v>
       </c>
@@ -5005,7 +5071,7 @@
         <v>102003</v>
       </c>
       <c r="AN45" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:40">
@@ -5024,7 +5090,7 @@
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J46" s="6">
         <v>1</v>
@@ -5033,14 +5099,14 @@
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O46" s="6"/>
       <c r="P46" s="6">
         <v>200002</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R46" s="6"/>
       <c r="S46" s="6">
@@ -5084,7 +5150,9 @@
       <c r="AI46" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ46" s="7"/>
+      <c r="AJ46" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="AK46" s="6" t="s">
         <v>84</v>
       </c>
@@ -5093,7 +5161,7 @@
         <v>103001</v>
       </c>
       <c r="AN46" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:40">
@@ -5112,7 +5180,7 @@
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J47" s="6">
         <v>1</v>
@@ -5121,14 +5189,14 @@
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O47" s="6"/>
       <c r="P47" s="6">
         <v>200003</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R47" s="6"/>
       <c r="S47" s="6">
@@ -5172,7 +5240,9 @@
       <c r="AI47" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ47" s="7"/>
+      <c r="AJ47" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="AK47" s="6" t="s">
         <v>84</v>
       </c>
@@ -5181,7 +5251,7 @@
         <v>103002</v>
       </c>
       <c r="AN47" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:40">
@@ -5200,7 +5270,7 @@
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J48" s="6">
         <v>1</v>
@@ -5209,14 +5279,14 @@
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O48" s="6"/>
       <c r="P48" s="6">
         <v>200004</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R48" s="6"/>
       <c r="S48" s="6">
@@ -5260,7 +5330,9 @@
       <c r="AI48" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ48" s="7"/>
+      <c r="AJ48" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="AK48" s="6" t="s">
         <v>84</v>
       </c>
@@ -5269,7 +5341,7 @@
         <v>103003</v>
       </c>
       <c r="AN48" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:40">
@@ -5288,7 +5360,7 @@
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J49" s="6">
         <v>1</v>
@@ -5297,14 +5369,14 @@
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O49" s="6"/>
       <c r="P49" s="6">
         <v>800001</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="R49" s="6"/>
       <c r="S49" s="6">
@@ -5348,7 +5420,9 @@
       <c r="AI49" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ49" s="7"/>
+      <c r="AJ49" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="AK49" s="6" t="s">
         <v>84</v>
       </c>
@@ -5357,7 +5431,7 @@
         <v>103004</v>
       </c>
       <c r="AN49" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:40">
@@ -5376,7 +5450,7 @@
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J50" s="6">
         <v>1</v>
@@ -5385,14 +5459,14 @@
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O50" s="6"/>
       <c r="P50" s="6">
         <v>700001</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="R50" s="6"/>
       <c r="S50" s="6">
@@ -5436,7 +5510,9 @@
       <c r="AI50" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ50" s="7"/>
+      <c r="AJ50" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="AK50" s="6" t="s">
         <v>84</v>
       </c>
@@ -5445,7 +5521,7 @@
         <v>103101</v>
       </c>
       <c r="AN50" s="6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:40">
@@ -5464,7 +5540,7 @@
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J51" s="6">
         <v>1</v>
@@ -5473,14 +5549,14 @@
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O51" s="6"/>
       <c r="P51" s="6">
         <v>700002</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="R51" s="6"/>
       <c r="S51" s="6">
@@ -5524,7 +5600,9 @@
       <c r="AI51" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ51" s="7"/>
+      <c r="AJ51" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="AK51" s="6" t="s">
         <v>84</v>
       </c>
@@ -5533,7 +5611,7 @@
         <v>103102</v>
       </c>
       <c r="AN51" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:40">
@@ -5552,7 +5630,7 @@
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J52" s="6">
         <v>1</v>
@@ -5561,14 +5639,14 @@
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O52" s="6"/>
       <c r="P52" s="6">
         <v>700003</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="6">
@@ -5612,7 +5690,9 @@
       <c r="AI52" s="6">
         <v>1000001</v>
       </c>
-      <c r="AJ52" s="7"/>
+      <c r="AJ52" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="AK52" s="6" t="s">
         <v>84</v>
       </c>
@@ -5621,7 +5701,7 @@
         <v>103103</v>
       </c>
       <c r="AN52" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:40">
@@ -5644,7 +5724,7 @@
         <v>21010001</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J53" s="9">
         <v>2</v>
@@ -5653,7 +5733,7 @@
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
       <c r="N53" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9">
@@ -5704,7 +5784,9 @@
       <c r="AI53" s="9">
         <v>2000001</v>
       </c>
-      <c r="AJ53" s="8"/>
+      <c r="AJ53" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="AK53" s="9" t="s">
         <v>86</v>
       </c>
@@ -5715,7 +5797,7 @@
         <v>900001</v>
       </c>
       <c r="AN53" s="9" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:40">
@@ -5738,7 +5820,7 @@
         <v>21000001</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J54" s="9">
         <v>8</v>
@@ -5747,14 +5829,14 @@
       <c r="L54" s="9"/>
       <c r="M54" s="9"/>
       <c r="N54" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O54" s="9"/>
       <c r="P54" s="9">
         <v>200001</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9">
@@ -5800,7 +5882,9 @@
       <c r="AI54" s="9">
         <v>2000001</v>
       </c>
-      <c r="AJ54" s="8"/>
+      <c r="AJ54" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="AK54" s="9" t="s">
         <v>86</v>
       </c>
@@ -5811,7 +5895,7 @@
         <v>900002</v>
       </c>
       <c r="AN54" s="9" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:40">
@@ -5861,13 +5945,13 @@
       <c r="AI55" s="4"/>
       <c r="AJ55" s="4"/>
       <c r="AK55" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
       <c r="AN55" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:40">
@@ -5917,13 +6001,13 @@
       <c r="AI56" s="4"/>
       <c r="AJ56" s="4"/>
       <c r="AK56" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
       <c r="AN56" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:40">
@@ -5973,13 +6057,13 @@
       <c r="AI57" s="4"/>
       <c r="AJ57" s="4"/>
       <c r="AK57" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
       <c r="AN57" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:40">
@@ -6027,13 +6111,13 @@
         <v>989999</v>
       </c>
       <c r="AK58" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
       <c r="AN58" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:40">
@@ -6083,13 +6167,13 @@
       <c r="AI59" s="4"/>
       <c r="AJ59" s="4"/>
       <c r="AK59" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
       <c r="AN59" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:40">
@@ -6139,13 +6223,13 @@
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
       <c r="AK60" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
       <c r="AN60" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:40">
@@ -6195,13 +6279,13 @@
       <c r="AI61" s="4"/>
       <c r="AJ61" s="4"/>
       <c r="AK61" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
       <c r="AN61" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:40">
@@ -6251,13 +6335,13 @@
       <c r="AI62" s="4"/>
       <c r="AJ62" s="4"/>
       <c r="AK62" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
       <c r="AN62" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:40">
@@ -6307,13 +6391,13 @@
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4"/>
       <c r="AK63" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
       <c r="AN63" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:40">
@@ -6363,13 +6447,13 @@
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4"/>
       <c r="AK64" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
       <c r="AN64" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:40">
@@ -6419,13 +6503,13 @@
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4"/>
       <c r="AK65" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
       <c r="AN65" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:40">
@@ -6475,13 +6559,13 @@
       <c r="AI66" s="4"/>
       <c r="AJ66" s="4"/>
       <c r="AK66" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
       <c r="AN66" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:40">
@@ -6531,13 +6615,13 @@
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4"/>
       <c r="AK67" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
       <c r="AN67" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:40">
@@ -6587,13 +6671,13 @@
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4"/>
       <c r="AK68" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
       <c r="AN68" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:40">
@@ -6643,13 +6727,13 @@
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4"/>
       <c r="AK69" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
       <c r="AN69" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:40">
@@ -6699,13 +6783,13 @@
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4"/>
       <c r="AK70" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
       <c r="AN70" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:40">
@@ -6755,13 +6839,13 @@
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
       <c r="AK71" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
       <c r="AN71" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:40">
@@ -6811,13 +6895,13 @@
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
       <c r="AK72" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
       <c r="AN72" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:40">
@@ -6867,13 +6951,13 @@
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
       <c r="AK73" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
       <c r="AN73" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:40">
@@ -6923,13 +7007,13 @@
       <c r="AI74" s="4"/>
       <c r="AJ74" s="4"/>
       <c r="AK74" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
       <c r="AN74" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:40">
@@ -6979,13 +7063,13 @@
       <c r="AI75" s="4"/>
       <c r="AJ75" s="4"/>
       <c r="AK75" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
       <c r="AN75" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:40">
@@ -7035,13 +7119,13 @@
       <c r="AI76" s="4"/>
       <c r="AJ76" s="4"/>
       <c r="AK76" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
       <c r="AN76" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:40">
@@ -7091,13 +7175,13 @@
       <c r="AI77" s="4"/>
       <c r="AJ77" s="4"/>
       <c r="AK77" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
       <c r="AN77" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:40">
@@ -7147,13 +7231,13 @@
       <c r="AI78" s="4"/>
       <c r="AJ78" s="4"/>
       <c r="AK78" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
       <c r="AN78" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:40">
@@ -7203,13 +7287,13 @@
       <c r="AI79" s="4"/>
       <c r="AJ79" s="4"/>
       <c r="AK79" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
       <c r="AN79" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:40">
@@ -7259,13 +7343,13 @@
       <c r="AI80" s="4"/>
       <c r="AJ80" s="4"/>
       <c r="AK80" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
       <c r="AN80" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:40">
@@ -7315,13 +7399,13 @@
       <c r="AI81" s="4"/>
       <c r="AJ81" s="4"/>
       <c r="AK81" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
       <c r="AN81" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:40">
@@ -7371,13 +7455,13 @@
       <c r="AI82" s="4"/>
       <c r="AJ82" s="4"/>
       <c r="AK82" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
       <c r="AN82" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:40">
@@ -7427,13 +7511,13 @@
       <c r="AI83" s="4"/>
       <c r="AJ83" s="4"/>
       <c r="AK83" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
       <c r="AN83" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:40">
@@ -7483,13 +7567,13 @@
       <c r="AI84" s="4"/>
       <c r="AJ84" s="4"/>
       <c r="AK84" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
       <c r="AN84" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:40">
@@ -7539,13 +7623,13 @@
       <c r="AI85" s="4"/>
       <c r="AJ85" s="4"/>
       <c r="AK85" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
       <c r="AN85" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:40">
@@ -7595,13 +7679,13 @@
       <c r="AI86" s="4"/>
       <c r="AJ86" s="4"/>
       <c r="AK86" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
       <c r="AN86" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:40">
@@ -7651,13 +7735,13 @@
       <c r="AI87" s="4"/>
       <c r="AJ87" s="4"/>
       <c r="AK87" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
       <c r="AN87" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:40">
@@ -7707,13 +7791,13 @@
       <c r="AI88" s="4"/>
       <c r="AJ88" s="4"/>
       <c r="AK88" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
       <c r="AN88" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:40">
@@ -7763,13 +7847,13 @@
       <c r="AI89" s="4"/>
       <c r="AJ89" s="4"/>
       <c r="AK89" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
       <c r="AN89" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:40">
@@ -7819,13 +7903,13 @@
       <c r="AI90" s="4"/>
       <c r="AJ90" s="4"/>
       <c r="AK90" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
       <c r="AN90" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:40">
@@ -7875,13 +7959,13 @@
       <c r="AI91" s="4"/>
       <c r="AJ91" s="4"/>
       <c r="AK91" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
       <c r="AN91" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:40">
@@ -7931,13 +8015,13 @@
       <c r="AI92" s="4"/>
       <c r="AJ92" s="4"/>
       <c r="AK92" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
       <c r="AN92" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:40">
@@ -7987,13 +8071,13 @@
       <c r="AI93" s="4"/>
       <c r="AJ93" s="4"/>
       <c r="AK93" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
       <c r="AN93" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:40">
@@ -8040,13 +8124,13 @@
         <v>999982</v>
       </c>
       <c r="AK94" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
       <c r="AN94" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:40">
@@ -8093,13 +8177,13 @@
         <v>999983</v>
       </c>
       <c r="AK95" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
       <c r="AN95" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:40">
@@ -8146,13 +8230,13 @@
         <v>999984</v>
       </c>
       <c r="AK96" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
       <c r="AN96" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:40">
@@ -8199,13 +8283,13 @@
         <v>999985</v>
       </c>
       <c r="AK97" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
       <c r="AN97" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:40">
@@ -8252,13 +8336,13 @@
         <v>999986</v>
       </c>
       <c r="AK98" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
       <c r="AN98" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:40">
@@ -8305,13 +8389,13 @@
         <v>999987</v>
       </c>
       <c r="AK99" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
       <c r="AN99" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:40">
@@ -8358,13 +8442,13 @@
         <v>999988</v>
       </c>
       <c r="AK100" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
       <c r="AN100" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:40">
@@ -8411,13 +8495,13 @@
         <v>999989</v>
       </c>
       <c r="AK101" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
       <c r="AN101" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:40">
@@ -8464,13 +8548,13 @@
         <v>999990</v>
       </c>
       <c r="AK102" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
       <c r="AN102" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:40">
@@ -8517,13 +8601,13 @@
         <v>999991</v>
       </c>
       <c r="AK103" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM103">
         <v>1</v>
       </c>
       <c r="AN103" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:40">
@@ -8570,13 +8654,13 @@
         <v>999992</v>
       </c>
       <c r="AK104" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM104">
         <v>1</v>
       </c>
       <c r="AN104" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:40">
@@ -8623,13 +8707,13 @@
         <v>999993</v>
       </c>
       <c r="AK105" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM105">
         <v>1</v>
       </c>
       <c r="AN105" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:40">
@@ -8676,13 +8760,13 @@
         <v>999994</v>
       </c>
       <c r="AK106" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM106">
         <v>1</v>
       </c>
       <c r="AN106" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:40">
@@ -8729,13 +8813,13 @@
         <v>999995</v>
       </c>
       <c r="AK107" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM107">
         <v>1</v>
       </c>
       <c r="AN107" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:40">
@@ -8782,13 +8866,13 @@
         <v>999996</v>
       </c>
       <c r="AK108" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM108">
         <v>1</v>
       </c>
       <c r="AN108" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:40">
@@ -8835,13 +8919,13 @@
         <v>999997</v>
       </c>
       <c r="AK109" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM109">
         <v>1</v>
       </c>
       <c r="AN109" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:40">
@@ -8888,13 +8972,13 @@
         <v>999998</v>
       </c>
       <c r="AK110" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM110">
         <v>1</v>
       </c>
       <c r="AN110" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:40">
@@ -8941,13 +9025,13 @@
         <v>999999</v>
       </c>
       <c r="AK111" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AM111">
         <v>1</v>
       </c>
       <c r="AN111" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
@@ -2667,10 +2667,10 @@
         <v>0.5</v>
       </c>
       <c r="Y16" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Z16" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AC16" s="1">
         <v>10</v>
@@ -2753,13 +2753,13 @@
         <v>0.5</v>
       </c>
       <c r="Y17" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Z17" s="1">
         <v>50</v>
       </c>
       <c r="AC17" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD17" s="1">
         <v>1</v>
@@ -2839,13 +2839,13 @@
         <v>0.5</v>
       </c>
       <c r="Y18" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Z18" s="1">
         <v>50</v>
       </c>
       <c r="AC18" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD18" s="1">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -35,7 +35,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>create_mana</t>
+    <t>create_mp</t>
   </si>
   <si>
     <t>creature_type</t>
@@ -251,7 +251,7 @@
     <t>攻击力</t>
   </si>
   <si>
-    <t>攻击间隔</t>
+    <t>攻击速度</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -2259,7 +2259,9 @@
       <c r="A11" s="1">
         <v>1001</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1">
+        <v>10</v>
+      </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
@@ -2325,6 +2327,9 @@
       <c r="A12" s="1">
         <v>1002</v>
       </c>
+      <c r="B12" s="1">
+        <v>15</v>
+      </c>
       <c r="C12" s="1">
         <v>2</v>
       </c>
@@ -2396,6 +2401,9 @@
       <c r="A13" s="1">
         <v>1003</v>
       </c>
+      <c r="B13" s="1">
+        <v>20</v>
+      </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
@@ -2467,6 +2475,9 @@
       <c r="A14" s="1">
         <v>1004</v>
       </c>
+      <c r="B14" s="1">
+        <v>20</v>
+      </c>
       <c r="C14" s="1">
         <v>2</v>
       </c>
@@ -2539,7 +2550,7 @@
         <v>2001</v>
       </c>
       <c r="B15" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
@@ -2622,7 +2633,7 @@
         <v>2002</v>
       </c>
       <c r="B16" s="1">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
@@ -2708,7 +2719,7 @@
         <v>2003</v>
       </c>
       <c r="B17" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -2794,7 +2805,7 @@
         <v>2004</v>
       </c>
       <c r="B18" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
@@ -2880,7 +2891,7 @@
         <v>3001</v>
       </c>
       <c r="B19" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -2949,7 +2960,7 @@
         <v>3002</v>
       </c>
       <c r="B20" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -3024,7 +3035,7 @@
         <v>3003</v>
       </c>
       <c r="B21" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
@@ -3105,7 +3116,7 @@
         <v>3004</v>
       </c>
       <c r="B22" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -3186,7 +3197,7 @@
         <v>4001</v>
       </c>
       <c r="B23" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -3269,7 +3280,7 @@
         <v>4002</v>
       </c>
       <c r="B24" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -3344,7 +3355,7 @@
         <v>4003</v>
       </c>
       <c r="B25" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
@@ -3419,7 +3430,7 @@
         <v>4004</v>
       </c>
       <c r="B26" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -3497,7 +3508,7 @@
         <v>4005</v>
       </c>
       <c r="B27" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -3572,7 +3583,7 @@
         <v>5001</v>
       </c>
       <c r="B28" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
@@ -3649,7 +3660,7 @@
         <v>5002</v>
       </c>
       <c r="B29" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
@@ -3733,7 +3744,7 @@
         <v>5003</v>
       </c>
       <c r="B30" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
@@ -3810,7 +3821,7 @@
         <v>5004</v>
       </c>
       <c r="B31" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
@@ -3887,7 +3898,7 @@
         <v>6001</v>
       </c>
       <c r="B32" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
@@ -3967,7 +3978,7 @@
         <v>6002</v>
       </c>
       <c r="B33" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
@@ -4053,7 +4064,7 @@
         <v>6003</v>
       </c>
       <c r="B34" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
@@ -4128,7 +4139,7 @@
         <v>6004</v>
       </c>
       <c r="B35" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
@@ -4214,7 +4225,7 @@
         <v>6005</v>
       </c>
       <c r="B36" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
@@ -4300,7 +4311,7 @@
         <v>7001</v>
       </c>
       <c r="B37" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
@@ -4377,7 +4388,7 @@
         <v>7002</v>
       </c>
       <c r="B38" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C38" s="1">
         <v>1</v>
@@ -4461,7 +4472,7 @@
         <v>7003</v>
       </c>
       <c r="B39" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
@@ -4547,7 +4558,7 @@
         <v>7004</v>
       </c>
       <c r="B40" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="AD11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="1">
         <v>10</v>
@@ -2370,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="AD12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="1">
         <v>10</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="AD13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="1">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="AD14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="1">
         <v>10</v>
@@ -2601,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="AD15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="1">
         <v>10</v>
@@ -2687,7 +2687,7 @@
         <v>10</v>
       </c>
       <c r="AD16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="1">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="AD17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="1">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="AD18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="1">
         <v>10</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="1">
         <v>10</v>
@@ -3005,7 +3005,7 @@
         <v>500</v>
       </c>
       <c r="AD20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="1">
         <v>10</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="1">
         <v>10</v>
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="1">
         <v>10</v>
@@ -3248,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="AD23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" s="1">
         <v>10</v>
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="AD24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="1">
         <v>10</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="AD25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="1">
         <v>10</v>
@@ -3478,7 +3478,7 @@
         <v>3</v>
       </c>
       <c r="AD26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="1">
         <v>10</v>
@@ -3553,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="AD27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="1">
         <v>10</v>
@@ -3628,7 +3628,7 @@
         <v>3</v>
       </c>
       <c r="AD28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28" s="1">
         <v>10</v>
@@ -3714,7 +3714,7 @@
         <v>10</v>
       </c>
       <c r="AD29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="1">
         <v>10</v>
@@ -3789,7 +3789,7 @@
         <v>6</v>
       </c>
       <c r="AD30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="1">
         <v>10</v>
@@ -3866,7 +3866,7 @@
         <v>3</v>
       </c>
       <c r="AD31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="1">
         <v>10</v>
@@ -3946,7 +3946,7 @@
         <v>5</v>
       </c>
       <c r="AD32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="1">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>10</v>
       </c>
       <c r="AD33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE33" s="1">
         <v>10</v>
@@ -4109,7 +4109,7 @@
         <v>500</v>
       </c>
       <c r="AD34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" s="1">
         <v>10</v>
@@ -4193,7 +4193,7 @@
         <v>6</v>
       </c>
       <c r="AD35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="1">
         <v>10</v>
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="AD36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" s="1">
         <v>10</v>
@@ -4356,7 +4356,7 @@
         <v>12</v>
       </c>
       <c r="AD37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" s="1">
         <v>10</v>
@@ -4442,7 +4442,7 @@
         <v>3</v>
       </c>
       <c r="AD38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="1">
         <v>10</v>
@@ -4526,7 +4526,7 @@
         <v>6</v>
       </c>
       <c r="AD39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE39" s="1">
         <v>10</v>
@@ -4612,7 +4612,7 @@
         <v>3</v>
       </c>
       <c r="AD40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="1">
         <v>10</v>
@@ -4697,8 +4697,8 @@
       <c r="AC41" s="6">
         <v>10</v>
       </c>
-      <c r="AD41" s="6">
-        <v>1</v>
+      <c r="AD41" s="1">
+        <v>0</v>
       </c>
       <c r="AE41" s="6">
         <v>10</v>
@@ -4787,8 +4787,8 @@
       <c r="AC42" s="6">
         <v>10</v>
       </c>
-      <c r="AD42" s="6">
-        <v>1</v>
+      <c r="AD42" s="1">
+        <v>0</v>
       </c>
       <c r="AE42" s="6">
         <v>10</v>
@@ -4877,8 +4877,8 @@
       <c r="AC43" s="6">
         <v>10</v>
       </c>
-      <c r="AD43" s="6">
-        <v>1</v>
+      <c r="AD43" s="1">
+        <v>0</v>
       </c>
       <c r="AE43" s="6">
         <v>10</v>
@@ -4967,8 +4967,8 @@
       <c r="AC44" s="6">
         <v>10</v>
       </c>
-      <c r="AD44" s="6">
-        <v>1</v>
+      <c r="AD44" s="1">
+        <v>0</v>
       </c>
       <c r="AE44" s="6">
         <v>10</v>
@@ -5057,8 +5057,8 @@
       <c r="AC45" s="6">
         <v>10</v>
       </c>
-      <c r="AD45" s="6">
-        <v>1</v>
+      <c r="AD45" s="1">
+        <v>0</v>
       </c>
       <c r="AE45" s="6">
         <v>10</v>
@@ -5147,8 +5147,8 @@
       <c r="AC46" s="6">
         <v>10</v>
       </c>
-      <c r="AD46" s="6">
-        <v>1</v>
+      <c r="AD46" s="1">
+        <v>0</v>
       </c>
       <c r="AE46" s="6">
         <v>10</v>
@@ -5237,8 +5237,8 @@
       <c r="AC47" s="6">
         <v>10</v>
       </c>
-      <c r="AD47" s="6">
-        <v>1</v>
+      <c r="AD47" s="1">
+        <v>0</v>
       </c>
       <c r="AE47" s="6">
         <v>10</v>
@@ -5327,8 +5327,8 @@
       <c r="AC48" s="6">
         <v>10</v>
       </c>
-      <c r="AD48" s="6">
-        <v>1</v>
+      <c r="AD48" s="1">
+        <v>0</v>
       </c>
       <c r="AE48" s="6">
         <v>10</v>
@@ -5417,8 +5417,8 @@
       <c r="AC49" s="6">
         <v>10</v>
       </c>
-      <c r="AD49" s="6">
-        <v>1</v>
+      <c r="AD49" s="1">
+        <v>0</v>
       </c>
       <c r="AE49" s="6">
         <v>10</v>
@@ -5507,8 +5507,8 @@
       <c r="AC50" s="6">
         <v>10</v>
       </c>
-      <c r="AD50" s="6">
-        <v>1</v>
+      <c r="AD50" s="1">
+        <v>0</v>
       </c>
       <c r="AE50" s="6">
         <v>10</v>
@@ -5597,8 +5597,8 @@
       <c r="AC51" s="6">
         <v>10</v>
       </c>
-      <c r="AD51" s="6">
-        <v>1</v>
+      <c r="AD51" s="1">
+        <v>0</v>
       </c>
       <c r="AE51" s="6">
         <v>10</v>
@@ -5687,8 +5687,8 @@
       <c r="AC52" s="6">
         <v>10</v>
       </c>
-      <c r="AD52" s="6">
-        <v>1</v>
+      <c r="AD52" s="1">
+        <v>0</v>
       </c>
       <c r="AE52" s="6">
         <v>10</v>
@@ -5781,8 +5781,8 @@
       <c r="AC53" s="9">
         <v>1</v>
       </c>
-      <c r="AD53" s="9">
-        <v>1</v>
+      <c r="AD53" s="1">
+        <v>0</v>
       </c>
       <c r="AE53" s="1">
         <v>10</v>
@@ -5879,8 +5879,8 @@
       <c r="AC54" s="9">
         <v>1</v>
       </c>
-      <c r="AD54" s="9">
-        <v>1</v>
+      <c r="AD54" s="1">
+        <v>0</v>
       </c>
       <c r="AE54" s="1">
         <v>10</v>
@@ -5944,8 +5944,8 @@
       <c r="AC55">
         <v>35</v>
       </c>
-      <c r="AD55">
-        <v>1</v>
+      <c r="AD55" s="1">
+        <v>0</v>
       </c>
       <c r="AE55" s="1">
         <v>10</v>
@@ -6000,8 +6000,8 @@
       <c r="AC56">
         <v>35</v>
       </c>
-      <c r="AD56">
-        <v>1</v>
+      <c r="AD56" s="1">
+        <v>0</v>
       </c>
       <c r="AE56" s="1">
         <v>10</v>
@@ -6056,8 +6056,8 @@
       <c r="AC57">
         <v>35</v>
       </c>
-      <c r="AD57">
-        <v>1</v>
+      <c r="AD57" s="1">
+        <v>0</v>
       </c>
       <c r="AE57" s="1">
         <v>10</v>
@@ -6112,8 +6112,8 @@
       <c r="AC58">
         <v>35</v>
       </c>
-      <c r="AD58">
-        <v>1</v>
+      <c r="AD58" s="1">
+        <v>0</v>
       </c>
       <c r="AE58" s="1">
         <v>10</v>
@@ -6166,8 +6166,8 @@
       <c r="AC59">
         <v>35</v>
       </c>
-      <c r="AD59">
-        <v>1</v>
+      <c r="AD59" s="1">
+        <v>0</v>
       </c>
       <c r="AE59" s="1">
         <v>10</v>
@@ -6222,8 +6222,8 @@
       <c r="AC60">
         <v>35</v>
       </c>
-      <c r="AD60">
-        <v>1</v>
+      <c r="AD60" s="1">
+        <v>0</v>
       </c>
       <c r="AE60" s="1">
         <v>10</v>
@@ -6278,8 +6278,8 @@
       <c r="AC61">
         <v>35</v>
       </c>
-      <c r="AD61">
-        <v>1</v>
+      <c r="AD61" s="1">
+        <v>0</v>
       </c>
       <c r="AE61" s="1">
         <v>10</v>
@@ -6334,8 +6334,8 @@
       <c r="AC62">
         <v>35</v>
       </c>
-      <c r="AD62">
-        <v>1</v>
+      <c r="AD62" s="1">
+        <v>0</v>
       </c>
       <c r="AE62" s="1">
         <v>10</v>
@@ -6390,8 +6390,8 @@
       <c r="AC63">
         <v>35</v>
       </c>
-      <c r="AD63">
-        <v>1</v>
+      <c r="AD63" s="1">
+        <v>0</v>
       </c>
       <c r="AE63" s="1">
         <v>10</v>
@@ -6446,8 +6446,8 @@
       <c r="AC64">
         <v>35</v>
       </c>
-      <c r="AD64">
-        <v>1</v>
+      <c r="AD64" s="1">
+        <v>0</v>
       </c>
       <c r="AE64" s="1">
         <v>10</v>
@@ -6502,8 +6502,8 @@
       <c r="AC65">
         <v>35</v>
       </c>
-      <c r="AD65">
-        <v>1</v>
+      <c r="AD65" s="1">
+        <v>0</v>
       </c>
       <c r="AE65" s="1">
         <v>10</v>
@@ -6558,8 +6558,8 @@
       <c r="AC66">
         <v>35</v>
       </c>
-      <c r="AD66">
-        <v>1</v>
+      <c r="AD66" s="1">
+        <v>0</v>
       </c>
       <c r="AE66" s="1">
         <v>10</v>
@@ -6614,8 +6614,8 @@
       <c r="AC67">
         <v>35</v>
       </c>
-      <c r="AD67">
-        <v>1</v>
+      <c r="AD67" s="1">
+        <v>0</v>
       </c>
       <c r="AE67" s="1">
         <v>10</v>
@@ -6670,8 +6670,8 @@
       <c r="AC68">
         <v>35</v>
       </c>
-      <c r="AD68">
-        <v>1</v>
+      <c r="AD68" s="1">
+        <v>0</v>
       </c>
       <c r="AE68" s="1">
         <v>10</v>
@@ -6726,8 +6726,8 @@
       <c r="AC69">
         <v>35</v>
       </c>
-      <c r="AD69">
-        <v>1</v>
+      <c r="AD69" s="1">
+        <v>0</v>
       </c>
       <c r="AE69" s="1">
         <v>10</v>
@@ -6782,8 +6782,8 @@
       <c r="AC70">
         <v>35</v>
       </c>
-      <c r="AD70">
-        <v>1</v>
+      <c r="AD70" s="1">
+        <v>0</v>
       </c>
       <c r="AE70" s="1">
         <v>10</v>
@@ -6838,8 +6838,8 @@
       <c r="AC71">
         <v>35</v>
       </c>
-      <c r="AD71">
-        <v>1</v>
+      <c r="AD71" s="1">
+        <v>0</v>
       </c>
       <c r="AE71" s="1">
         <v>10</v>
@@ -6894,8 +6894,8 @@
       <c r="AC72">
         <v>35</v>
       </c>
-      <c r="AD72">
-        <v>1</v>
+      <c r="AD72" s="1">
+        <v>0</v>
       </c>
       <c r="AE72" s="1">
         <v>10</v>
@@ -6950,8 +6950,8 @@
       <c r="AC73">
         <v>35</v>
       </c>
-      <c r="AD73">
-        <v>1</v>
+      <c r="AD73" s="1">
+        <v>0</v>
       </c>
       <c r="AE73" s="1">
         <v>10</v>
@@ -7006,8 +7006,8 @@
       <c r="AC74">
         <v>35</v>
       </c>
-      <c r="AD74">
-        <v>1</v>
+      <c r="AD74" s="1">
+        <v>0</v>
       </c>
       <c r="AE74" s="1">
         <v>10</v>
@@ -7062,8 +7062,8 @@
       <c r="AC75">
         <v>35</v>
       </c>
-      <c r="AD75">
-        <v>1</v>
+      <c r="AD75" s="1">
+        <v>0</v>
       </c>
       <c r="AE75" s="1">
         <v>10</v>
@@ -7118,8 +7118,8 @@
       <c r="AC76">
         <v>35</v>
       </c>
-      <c r="AD76">
-        <v>1</v>
+      <c r="AD76" s="1">
+        <v>0</v>
       </c>
       <c r="AE76" s="1">
         <v>10</v>
@@ -7174,8 +7174,8 @@
       <c r="AC77">
         <v>35</v>
       </c>
-      <c r="AD77">
-        <v>1</v>
+      <c r="AD77" s="1">
+        <v>0</v>
       </c>
       <c r="AE77" s="1">
         <v>10</v>
@@ -7230,8 +7230,8 @@
       <c r="AC78">
         <v>35</v>
       </c>
-      <c r="AD78">
-        <v>1</v>
+      <c r="AD78" s="1">
+        <v>0</v>
       </c>
       <c r="AE78" s="1">
         <v>10</v>
@@ -7286,8 +7286,8 @@
       <c r="AC79">
         <v>35</v>
       </c>
-      <c r="AD79">
-        <v>1</v>
+      <c r="AD79" s="1">
+        <v>0</v>
       </c>
       <c r="AE79" s="1">
         <v>10</v>
@@ -7342,8 +7342,8 @@
       <c r="AC80">
         <v>35</v>
       </c>
-      <c r="AD80">
-        <v>1</v>
+      <c r="AD80" s="1">
+        <v>0</v>
       </c>
       <c r="AE80" s="1">
         <v>10</v>
@@ -7398,8 +7398,8 @@
       <c r="AC81">
         <v>35</v>
       </c>
-      <c r="AD81">
-        <v>1</v>
+      <c r="AD81" s="1">
+        <v>0</v>
       </c>
       <c r="AE81" s="1">
         <v>10</v>
@@ -7454,8 +7454,8 @@
       <c r="AC82">
         <v>35</v>
       </c>
-      <c r="AD82">
-        <v>1</v>
+      <c r="AD82" s="1">
+        <v>0</v>
       </c>
       <c r="AE82" s="1">
         <v>10</v>
@@ -7510,8 +7510,8 @@
       <c r="AC83">
         <v>35</v>
       </c>
-      <c r="AD83">
-        <v>1</v>
+      <c r="AD83" s="1">
+        <v>0</v>
       </c>
       <c r="AE83" s="1">
         <v>10</v>
@@ -7566,8 +7566,8 @@
       <c r="AC84">
         <v>35</v>
       </c>
-      <c r="AD84">
-        <v>1</v>
+      <c r="AD84" s="1">
+        <v>0</v>
       </c>
       <c r="AE84" s="1">
         <v>10</v>
@@ -7622,8 +7622,8 @@
       <c r="AC85">
         <v>35</v>
       </c>
-      <c r="AD85">
-        <v>1</v>
+      <c r="AD85" s="1">
+        <v>0</v>
       </c>
       <c r="AE85" s="1">
         <v>10</v>
@@ -7678,8 +7678,8 @@
       <c r="AC86">
         <v>35</v>
       </c>
-      <c r="AD86">
-        <v>1</v>
+      <c r="AD86" s="1">
+        <v>0</v>
       </c>
       <c r="AE86" s="1">
         <v>10</v>
@@ -7734,8 +7734,8 @@
       <c r="AC87">
         <v>35</v>
       </c>
-      <c r="AD87">
-        <v>1</v>
+      <c r="AD87" s="1">
+        <v>0</v>
       </c>
       <c r="AE87" s="1">
         <v>10</v>
@@ -7790,8 +7790,8 @@
       <c r="AC88">
         <v>35</v>
       </c>
-      <c r="AD88">
-        <v>1</v>
+      <c r="AD88" s="1">
+        <v>0</v>
       </c>
       <c r="AE88" s="1">
         <v>10</v>
@@ -7846,8 +7846,8 @@
       <c r="AC89">
         <v>35</v>
       </c>
-      <c r="AD89">
-        <v>1</v>
+      <c r="AD89" s="1">
+        <v>0</v>
       </c>
       <c r="AE89" s="1">
         <v>10</v>
@@ -7902,8 +7902,8 @@
       <c r="AC90">
         <v>35</v>
       </c>
-      <c r="AD90">
-        <v>1</v>
+      <c r="AD90" s="1">
+        <v>0</v>
       </c>
       <c r="AE90" s="1">
         <v>10</v>
@@ -7958,8 +7958,8 @@
       <c r="AC91">
         <v>35</v>
       </c>
-      <c r="AD91">
-        <v>1</v>
+      <c r="AD91" s="1">
+        <v>0</v>
       </c>
       <c r="AE91" s="1">
         <v>10</v>
@@ -8014,8 +8014,8 @@
       <c r="AC92">
         <v>35</v>
       </c>
-      <c r="AD92">
-        <v>1</v>
+      <c r="AD92" s="1">
+        <v>0</v>
       </c>
       <c r="AE92" s="1">
         <v>10</v>
@@ -8070,8 +8070,8 @@
       <c r="AC93">
         <v>35</v>
       </c>
-      <c r="AD93">
-        <v>1</v>
+      <c r="AD93" s="1">
+        <v>0</v>
       </c>
       <c r="AE93" s="1">
         <v>10</v>
@@ -8125,8 +8125,8 @@
       <c r="AC94">
         <v>35</v>
       </c>
-      <c r="AD94">
-        <v>1</v>
+      <c r="AD94" s="1">
+        <v>0</v>
       </c>
       <c r="AE94" s="1">
         <v>10</v>
@@ -8178,8 +8178,8 @@
       <c r="AC95">
         <v>35</v>
       </c>
-      <c r="AD95">
-        <v>1</v>
+      <c r="AD95" s="1">
+        <v>0</v>
       </c>
       <c r="AE95" s="1">
         <v>10</v>
@@ -8231,8 +8231,8 @@
       <c r="AC96">
         <v>35</v>
       </c>
-      <c r="AD96">
-        <v>1</v>
+      <c r="AD96" s="1">
+        <v>0</v>
       </c>
       <c r="AE96" s="1">
         <v>10</v>
@@ -8284,8 +8284,8 @@
       <c r="AC97">
         <v>35</v>
       </c>
-      <c r="AD97">
-        <v>1</v>
+      <c r="AD97" s="1">
+        <v>0</v>
       </c>
       <c r="AE97" s="1">
         <v>10</v>
@@ -8337,8 +8337,8 @@
       <c r="AC98">
         <v>35</v>
       </c>
-      <c r="AD98">
-        <v>1</v>
+      <c r="AD98" s="1">
+        <v>0</v>
       </c>
       <c r="AE98" s="1">
         <v>10</v>
@@ -8390,8 +8390,8 @@
       <c r="AC99">
         <v>35</v>
       </c>
-      <c r="AD99">
-        <v>1</v>
+      <c r="AD99" s="1">
+        <v>0</v>
       </c>
       <c r="AE99" s="1">
         <v>10</v>
@@ -8443,8 +8443,8 @@
       <c r="AC100">
         <v>35</v>
       </c>
-      <c r="AD100">
-        <v>1</v>
+      <c r="AD100" s="1">
+        <v>0</v>
       </c>
       <c r="AE100" s="1">
         <v>10</v>
@@ -8496,8 +8496,8 @@
       <c r="AC101">
         <v>35</v>
       </c>
-      <c r="AD101">
-        <v>1</v>
+      <c r="AD101" s="1">
+        <v>0</v>
       </c>
       <c r="AE101" s="1">
         <v>10</v>
@@ -8549,8 +8549,8 @@
       <c r="AC102">
         <v>35</v>
       </c>
-      <c r="AD102">
-        <v>1</v>
+      <c r="AD102" s="1">
+        <v>0</v>
       </c>
       <c r="AE102" s="1">
         <v>10</v>
@@ -8602,8 +8602,8 @@
       <c r="AC103">
         <v>35</v>
       </c>
-      <c r="AD103">
-        <v>1</v>
+      <c r="AD103" s="1">
+        <v>0</v>
       </c>
       <c r="AE103" s="1">
         <v>10</v>
@@ -8655,8 +8655,8 @@
       <c r="AC104">
         <v>35</v>
       </c>
-      <c r="AD104">
-        <v>1</v>
+      <c r="AD104" s="1">
+        <v>0</v>
       </c>
       <c r="AE104" s="1">
         <v>10</v>
@@ -8708,8 +8708,8 @@
       <c r="AC105">
         <v>35</v>
       </c>
-      <c r="AD105">
-        <v>1</v>
+      <c r="AD105" s="1">
+        <v>0</v>
       </c>
       <c r="AE105" s="1">
         <v>10</v>
@@ -8761,8 +8761,8 @@
       <c r="AC106">
         <v>35</v>
       </c>
-      <c r="AD106">
-        <v>1</v>
+      <c r="AD106" s="1">
+        <v>0</v>
       </c>
       <c r="AE106" s="1">
         <v>10</v>
@@ -8814,8 +8814,8 @@
       <c r="AC107">
         <v>35</v>
       </c>
-      <c r="AD107">
-        <v>1</v>
+      <c r="AD107" s="1">
+        <v>0</v>
       </c>
       <c r="AE107" s="1">
         <v>10</v>
@@ -8867,8 +8867,8 @@
       <c r="AC108">
         <v>35</v>
       </c>
-      <c r="AD108">
-        <v>1</v>
+      <c r="AD108" s="1">
+        <v>0</v>
       </c>
       <c r="AE108" s="1">
         <v>10</v>
@@ -8920,8 +8920,8 @@
       <c r="AC109">
         <v>35</v>
       </c>
-      <c r="AD109">
-        <v>1</v>
+      <c r="AD109" s="1">
+        <v>0</v>
       </c>
       <c r="AE109" s="1">
         <v>10</v>
@@ -8973,8 +8973,8 @@
       <c r="AC110">
         <v>35</v>
       </c>
-      <c r="AD110">
-        <v>1</v>
+      <c r="AD110" s="1">
+        <v>0</v>
       </c>
       <c r="AE110" s="1">
         <v>10</v>
@@ -9026,8 +9026,8 @@
       <c r="AC111">
         <v>35</v>
       </c>
-      <c r="AD111">
-        <v>1</v>
+      <c r="AD111" s="1">
+        <v>0</v>
       </c>
       <c r="AE111" s="1">
         <v>10</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1970,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE4" s="1">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE5" s="1">
         <v>10</v>
@@ -2055,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="AA6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE6" s="1">
         <v>10</v>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="AA7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE7" s="1">
         <v>10</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="AA8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE8" s="1">
         <v>10</v>
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE9" s="1">
         <v>10</v>
@@ -2231,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="AA10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AE10" s="1">
         <v>10</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14505" windowHeight="10410"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="168">
   <si>
     <t>id</t>
   </si>
@@ -149,6 +149,9 @@
     <t>name[language]</t>
   </si>
   <si>
+    <t>body_size</t>
+  </si>
+  <si>
     <t>remark</t>
   </si>
   <si>
@@ -281,12 +284,18 @@
     <t>名字-中文</t>
   </si>
   <si>
+    <t>体型大小（空或0=默认1倍；"0.9,1.1"=区间随机；"1.1"=固定倍数；最终在目标大小基础上相乘）</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
     <t>Card_Scene_2</t>
   </si>
   <si>
+    <t>0.9,1.1</t>
+  </si>
+  <si>
     <t>创建角色-人类</t>
   </si>
   <si>
@@ -294,6 +303,9 @@
   </si>
   <si>
     <t>创建角色-骷髅</t>
+  </si>
+  <si>
+    <t>Card_Scene_6</t>
   </si>
   <si>
     <t>创建角色-史莱姆</t>
@@ -1530,7 +1542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN181"/>
+  <dimension ref="A1:AO181"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.375" style="3" customWidth="1"/>
@@ -1567,11 +1579,11 @@
     <col min="35" max="35" width="34" style="3" customWidth="1"/>
     <col min="36" max="36" width="16" style="3" customWidth="1"/>
     <col min="37" max="38" width="13.75" style="3" customWidth="1"/>
-    <col min="39" max="39" width="16" style="3" customWidth="1"/>
-    <col min="40" max="40" width="42.875" style="3" customWidth="1"/>
+    <col min="39" max="39" width="12.875" style="3" customWidth="1"/>
+    <col min="40" max="40" width="58.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1692,252 +1704,261 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:40">
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="AI2" t="s">
         <v>41</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="AJ2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL2" t="s">
         <v>41</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AM2" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="AN2" t="s">
         <v>43</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AO2" t="s">
         <v>43</v>
       </c>
-      <c r="V2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40">
+    </row>
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40">
+        <v>84</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1972,16 +1993,19 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AM4">
         <v>1</v>
       </c>
-      <c r="AN4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40">
+      <c r="AN4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2016,16 +2040,19 @@
         <v>2</v>
       </c>
       <c r="AK5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM5">
         <v>2</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AN5" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:40">
+      <c r="AO5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2057,16 +2084,19 @@
         <v>3</v>
       </c>
       <c r="AK6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AM6">
         <v>3</v>
       </c>
-      <c r="AN6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40">
+      <c r="AN6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41">
       <c r="A7">
         <v>4</v>
       </c>
@@ -2101,16 +2131,19 @@
         <v>4</v>
       </c>
       <c r="AK7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM7">
         <v>4</v>
       </c>
-      <c r="AN7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:40">
+      <c r="AN7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2145,16 +2178,19 @@
         <v>5</v>
       </c>
       <c r="AK8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM8">
         <v>5</v>
       </c>
-      <c r="AN8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:40">
+      <c r="AN8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41">
       <c r="A9">
         <v>6</v>
       </c>
@@ -2189,16 +2225,19 @@
         <v>6</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM9">
         <v>6</v>
       </c>
-      <c r="AN9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:40">
+      <c r="AN9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41">
       <c r="A10">
         <v>7</v>
       </c>
@@ -2233,16 +2272,19 @@
         <v>7</v>
       </c>
       <c r="AK10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AM10">
         <v>7</v>
       </c>
-      <c r="AN10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:40">
+      <c r="AN10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:41">
       <c r="A11" s="1">
         <v>1001</v>
       </c>
@@ -2295,10 +2337,10 @@
         <v>1000001</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK11" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL11" s="1">
         <v>300100001</v>
@@ -2306,11 +2348,14 @@
       <c r="AM11" s="1">
         <v>1001</v>
       </c>
-      <c r="AN11" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:40">
+      <c r="AN11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:41">
       <c r="A12" s="1">
         <v>1002</v>
       </c>
@@ -2324,7 +2369,7 @@
         <v>1000001</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J12" s="1">
         <v>7</v>
@@ -2369,10 +2414,10 @@
         <v>1000001</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL12" s="1">
         <v>300100002</v>
@@ -2380,11 +2425,14 @@
       <c r="AM12" s="1">
         <v>1002</v>
       </c>
-      <c r="AN12" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:40">
+      <c r="AN12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:41">
       <c r="A13" s="1">
         <v>1003</v>
       </c>
@@ -2398,7 +2446,7 @@
         <v>1000001</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -2443,10 +2491,10 @@
         <v>1000001</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL13" s="1">
         <v>300100003</v>
@@ -2454,11 +2502,14 @@
       <c r="AM13" s="1">
         <v>1003</v>
       </c>
-      <c r="AN13" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:40">
+      <c r="AN13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:41">
       <c r="A14" s="1">
         <v>1004</v>
       </c>
@@ -2472,7 +2523,7 @@
         <v>1000001</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -2517,10 +2568,10 @@
         <v>1000001</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL14" s="1">
         <v>300100004</v>
@@ -2528,11 +2579,14 @@
       <c r="AM14" s="1">
         <v>1004</v>
       </c>
-      <c r="AN14" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="12" customHeight="1" spans="1:40">
+      <c r="AN14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="12" customHeight="1" spans="1:41">
       <c r="A15" s="1">
         <v>2001</v>
       </c>
@@ -2549,13 +2603,13 @@
         <v>21010001</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J15" s="1">
         <v>2</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P15" s="1">
         <v>100001</v>
@@ -2600,10 +2654,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL15" s="1">
         <v>300200001</v>
@@ -2611,11 +2665,14 @@
       <c r="AM15" s="1">
         <v>2001</v>
       </c>
-      <c r="AN15" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:40">
+      <c r="AN15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:41">
       <c r="A16" s="1">
         <v>2002</v>
       </c>
@@ -2632,19 +2689,19 @@
         <v>21000001</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J16" s="1">
         <v>8</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P16" s="1">
         <v>200001</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S16" s="1">
         <v>2</v>
@@ -2686,10 +2743,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL16" s="1">
         <v>300200002</v>
@@ -2697,11 +2754,14 @@
       <c r="AM16" s="1">
         <v>2002</v>
       </c>
-      <c r="AN16" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:40">
+      <c r="AN16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:41">
       <c r="A17" s="1">
         <v>2003</v>
       </c>
@@ -2718,19 +2778,19 @@
         <v>21010002</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J17" s="1">
         <v>1</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P17" s="1">
         <v>201001</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S17" s="1">
         <v>2</v>
@@ -2772,10 +2832,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL17" s="1">
         <v>300200003</v>
@@ -2783,11 +2843,14 @@
       <c r="AM17" s="1">
         <v>2003</v>
       </c>
-      <c r="AN17" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:40">
+      <c r="AN17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:41">
       <c r="A18" s="1">
         <v>2004</v>
       </c>
@@ -2804,19 +2867,19 @@
         <v>21010003</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P18" s="1">
         <v>201002</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S18" s="1">
         <v>2</v>
@@ -2858,10 +2921,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ18" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL18" s="1">
         <v>300200004</v>
@@ -2869,11 +2932,14 @@
       <c r="AM18" s="1">
         <v>2004</v>
       </c>
-      <c r="AN18" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:40">
+      <c r="AN18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:41">
       <c r="A19" s="1">
         <v>3001</v>
       </c>
@@ -2884,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="S19" s="1">
         <v>2</v>
@@ -2930,7 +2996,7 @@
       </c>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AL19" s="1">
         <v>300300001</v>
@@ -2938,11 +3004,14 @@
       <c r="AM19" s="1">
         <v>3001</v>
       </c>
-      <c r="AN19" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:40">
+      <c r="AN19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:41">
       <c r="A20" s="1">
         <v>3002</v>
       </c>
@@ -2953,10 +3022,10 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P20" s="1">
         <v>300001</v>
@@ -3005,7 +3074,7 @@
       </c>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AL20" s="1">
         <v>300300002</v>
@@ -3013,11 +3082,14 @@
       <c r="AM20" s="1">
         <v>3002</v>
       </c>
-      <c r="AN20" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:40">
+      <c r="AN20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:41">
       <c r="A21" s="1">
         <v>3003</v>
       </c>
@@ -3028,13 +3100,13 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O21" s="1">
         <v>1</v>
@@ -3086,7 +3158,7 @@
       </c>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AL21" s="1">
         <v>300300003</v>
@@ -3094,11 +3166,14 @@
       <c r="AM21" s="1">
         <v>3003</v>
       </c>
-      <c r="AN21" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:40">
+      <c r="AN21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:41">
       <c r="A22" s="1">
         <v>3004</v>
       </c>
@@ -3109,13 +3184,13 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O22" s="1">
         <v>1</v>
@@ -3167,7 +3242,7 @@
       </c>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AL22" s="1">
         <v>300300004</v>
@@ -3175,11 +3250,14 @@
       <c r="AM22" s="1">
         <v>3004</v>
       </c>
-      <c r="AN22" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:40">
+      <c r="AN22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:41">
       <c r="A23" s="1">
         <v>4001</v>
       </c>
@@ -3196,13 +3274,13 @@
         <v>41000002</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J23" s="1">
         <v>2</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P23" s="1">
         <v>101001</v>
@@ -3247,10 +3325,10 @@
         <v>4000001</v>
       </c>
       <c r="AJ23" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK23" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL23" s="1">
         <v>300400001</v>
@@ -3258,11 +3336,14 @@
       <c r="AM23" s="1">
         <v>4001</v>
       </c>
-      <c r="AN23" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:40">
+      <c r="AN23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:41">
       <c r="A24" s="1">
         <v>4002</v>
       </c>
@@ -3276,7 +3357,7 @@
         <v>4000001</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P24" s="1">
         <v>500001</v>
@@ -3325,7 +3406,7 @@
       </c>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL24" s="1">
         <v>300400002</v>
@@ -3333,11 +3414,14 @@
       <c r="AM24" s="1">
         <v>4002</v>
       </c>
-      <c r="AN24" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:40">
+      <c r="AN24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:41">
       <c r="A25" s="1">
         <v>4003</v>
       </c>
@@ -3351,7 +3435,7 @@
         <v>4000001</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P25" s="1">
         <v>600001</v>
@@ -3400,7 +3484,7 @@
       </c>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL25" s="1">
         <v>300400003</v>
@@ -3408,11 +3492,14 @@
       <c r="AM25" s="1">
         <v>4003</v>
       </c>
-      <c r="AN25" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:40">
+      <c r="AN25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:41">
       <c r="A26" s="1">
         <v>4004</v>
       </c>
@@ -3426,13 +3513,13 @@
         <v>4000001</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P26" s="1">
         <v>202001</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="R26" s="1">
         <v>30</v>
@@ -3478,7 +3565,7 @@
       </c>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL26" s="1">
         <v>300400004</v>
@@ -3486,11 +3573,14 @@
       <c r="AM26" s="1">
         <v>4004</v>
       </c>
-      <c r="AN26" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:40">
+      <c r="AN26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:41">
       <c r="A27" s="1">
         <v>4005</v>
       </c>
@@ -3504,7 +3594,7 @@
         <v>4000001</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P27" s="1">
         <v>500002</v>
@@ -3553,7 +3643,7 @@
       </c>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL27" s="1">
         <v>300400005</v>
@@ -3561,11 +3651,14 @@
       <c r="AM27" s="1">
         <v>4005</v>
       </c>
-      <c r="AN27" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:40">
+      <c r="AN27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:41">
       <c r="A28" s="1">
         <v>5001</v>
       </c>
@@ -3579,7 +3672,7 @@
         <v>5000001</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P28" s="1">
         <v>101002</v>
@@ -3627,10 +3720,10 @@
         <v>5000001</v>
       </c>
       <c r="AJ28" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL28" s="1">
         <v>300500001</v>
@@ -3638,11 +3731,14 @@
       <c r="AM28" s="1">
         <v>5001</v>
       </c>
-      <c r="AN28" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:40">
+      <c r="AN28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:41">
       <c r="A29" s="1">
         <v>5002</v>
       </c>
@@ -3659,7 +3755,7 @@
         <v>51010001</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J29" s="1">
         <v>8</v>
@@ -3668,7 +3764,7 @@
         <v>203001</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="R29" s="1">
         <v>1</v>
@@ -3714,7 +3810,7 @@
       </c>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL29" s="1">
         <v>300500002</v>
@@ -3722,11 +3818,14 @@
       <c r="AM29" s="1">
         <v>5002</v>
       </c>
-      <c r="AN29" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:40">
+      <c r="AN29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO29" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:41">
       <c r="A30" s="1">
         <v>5003</v>
       </c>
@@ -3740,7 +3839,7 @@
         <v>5000001</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P30" s="1">
         <v>101003</v>
@@ -3788,10 +3887,10 @@
         <v>5000001</v>
       </c>
       <c r="AJ30" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL30" s="1">
         <v>300500003</v>
@@ -3799,11 +3898,14 @@
       <c r="AM30" s="1">
         <v>5003</v>
       </c>
-      <c r="AN30" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:40">
+      <c r="AN30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO30" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:41">
       <c r="A31" s="1">
         <v>5004</v>
       </c>
@@ -3817,7 +3919,7 @@
         <v>5000001</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P31" s="1">
         <v>101004</v>
@@ -3865,10 +3967,10 @@
         <v>5000001</v>
       </c>
       <c r="AJ31" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL31" s="1">
         <v>300500004</v>
@@ -3876,11 +3978,14 @@
       <c r="AM31" s="1">
         <v>5004</v>
       </c>
-      <c r="AN31" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:40">
+      <c r="AN31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO31" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:41">
       <c r="A32" s="1">
         <v>6001</v>
       </c>
@@ -3891,13 +3996,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G32" s="1">
         <v>6000001</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J32" s="1">
         <v>3</v>
@@ -3945,10 +4050,10 @@
         <v>6000001</v>
       </c>
       <c r="AJ32" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL32" s="1">
         <v>300600001</v>
@@ -3956,11 +4061,14 @@
       <c r="AM32" s="1">
         <v>6001</v>
       </c>
-      <c r="AN32" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:40">
+      <c r="AN32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:41">
       <c r="A33" s="1">
         <v>6002</v>
       </c>
@@ -3977,19 +4085,19 @@
         <v>61010002</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J33" s="1">
         <v>7</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P33" s="1">
         <v>204001</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -4031,10 +4139,10 @@
         <v>6000001</v>
       </c>
       <c r="AJ33" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK33" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL33" s="1">
         <v>300600002</v>
@@ -4042,11 +4150,14 @@
       <c r="AM33" s="1">
         <v>6002</v>
       </c>
-      <c r="AN33" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:40">
+      <c r="AN33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:41">
       <c r="A34" s="1">
         <v>6003</v>
       </c>
@@ -4060,7 +4171,7 @@
         <v>6000001</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J34" s="1">
         <v>8</v>
@@ -4109,7 +4220,7 @@
       </c>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL34" s="1">
         <v>300600003</v>
@@ -4117,11 +4228,14 @@
       <c r="AM34" s="1">
         <v>6003</v>
       </c>
-      <c r="AN34" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:40">
+      <c r="AN34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO34" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:41">
       <c r="A35" s="1">
         <v>6004</v>
       </c>
@@ -4138,19 +4252,19 @@
         <v>61010003</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J35" s="1">
         <v>1</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P35" s="1">
         <v>204002</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="S35" s="1">
         <v>2</v>
@@ -4192,10 +4306,10 @@
         <v>6000001</v>
       </c>
       <c r="AJ35" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK35" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL35" s="1">
         <v>300600004</v>
@@ -4203,11 +4317,14 @@
       <c r="AM35" s="1">
         <v>6004</v>
       </c>
-      <c r="AN35" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:40">
+      <c r="AN35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO35" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:41">
       <c r="A36" s="1">
         <v>6005</v>
       </c>
@@ -4224,19 +4341,19 @@
         <v>61010003</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J36" s="1">
         <v>1</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P36" s="1">
         <v>204003</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="S36" s="1">
         <v>2</v>
@@ -4278,10 +4395,10 @@
         <v>6000001</v>
       </c>
       <c r="AJ36" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AL36" s="1">
         <v>300600005</v>
@@ -4289,11 +4406,14 @@
       <c r="AM36" s="1">
         <v>6005</v>
       </c>
-      <c r="AN36" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:40">
+      <c r="AN36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO36" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:41">
       <c r="A37" s="1">
         <v>7001</v>
       </c>
@@ -4304,13 +4424,13 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G37" s="1">
         <v>7000001</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P37" s="1">
         <v>200001</v>
@@ -4355,10 +4475,10 @@
         <v>7000001</v>
       </c>
       <c r="AJ37" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL37" s="1">
         <v>300700001</v>
@@ -4366,11 +4486,14 @@
       <c r="AM37" s="1">
         <v>7001</v>
       </c>
-      <c r="AN37" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:40">
+      <c r="AN37" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:41">
       <c r="A38" s="1">
         <v>7002</v>
       </c>
@@ -4387,19 +4510,19 @@
         <v>71000001</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J38" s="1">
         <v>8</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P38" s="1">
         <v>205001</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S38" s="1">
         <v>2</v>
@@ -4442,7 +4565,7 @@
       </c>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL38" s="1">
         <v>300700002</v>
@@ -4450,11 +4573,14 @@
       <c r="AM38" s="1">
         <v>7002</v>
       </c>
-      <c r="AN38" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:40">
+      <c r="AN38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO38" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:41">
       <c r="A39" s="1">
         <v>7003</v>
       </c>
@@ -4471,19 +4597,19 @@
         <v>71010004</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P39" s="1">
         <v>205002</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S39" s="1">
         <v>2</v>
@@ -4525,10 +4651,10 @@
         <v>7000001</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK39" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL39" s="1">
         <v>300700003</v>
@@ -4536,11 +4662,14 @@
       <c r="AM39" s="1">
         <v>7003</v>
       </c>
-      <c r="AN39" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:40">
+      <c r="AN39" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO39" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:41">
       <c r="A40" s="1">
         <v>7004</v>
       </c>
@@ -4557,19 +4686,19 @@
         <v>71010004</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J40" s="1">
         <v>1</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P40" s="1">
         <v>205003</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="S40" s="1">
         <v>2</v>
@@ -4611,10 +4740,10 @@
         <v>7000001</v>
       </c>
       <c r="AJ40" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK40" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL40" s="1">
         <v>300700004</v>
@@ -4622,11 +4751,14 @@
       <c r="AM40" s="1">
         <v>7004</v>
       </c>
-      <c r="AN40" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:40">
+      <c r="AN40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO40" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" spans="1:41">
       <c r="A41" s="4">
         <v>101001</v>
       </c>
@@ -4642,7 +4774,7 @@
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J41" s="4">
         <v>2</v>
@@ -4699,20 +4831,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ41" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK41" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL41" s="4"/>
       <c r="AM41" s="4">
         <v>101001</v>
       </c>
-      <c r="AN41" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:40">
+      <c r="AO41" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" s="2" customFormat="1" spans="1:41">
       <c r="A42" s="4">
         <v>101002</v>
       </c>
@@ -4728,7 +4860,7 @@
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J42" s="4">
         <v>4</v>
@@ -4737,7 +4869,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O42" s="4"/>
       <c r="P42" s="4">
@@ -4789,20 +4921,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ42" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AK42" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL42" s="4"/>
       <c r="AM42" s="4">
         <v>101002</v>
       </c>
-      <c r="AN42" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="1:40">
+      <c r="AO42" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" spans="1:41">
       <c r="A43" s="4">
         <v>102001</v>
       </c>
@@ -4818,7 +4950,7 @@
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J43" s="4">
         <v>7</v>
@@ -4827,14 +4959,14 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O43" s="4"/>
       <c r="P43" s="4">
         <v>200001</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4">
@@ -4879,20 +5011,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ43" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK43" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL43" s="4"/>
       <c r="AM43" s="4">
         <v>102001</v>
       </c>
-      <c r="AN43" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="1:40">
+      <c r="AO43" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" spans="1:41">
       <c r="A44" s="4">
         <v>102002</v>
       </c>
@@ -4908,7 +5040,7 @@
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J44" s="4">
         <v>7</v>
@@ -4917,14 +5049,14 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O44" s="4"/>
       <c r="P44" s="4">
         <v>205001</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R44" s="4"/>
       <c r="S44" s="4">
@@ -4969,20 +5101,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ44" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK44" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL44" s="4"/>
       <c r="AM44" s="4">
         <v>102002</v>
       </c>
-      <c r="AN44" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:40">
+      <c r="AO44" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="1:41">
       <c r="A45" s="4">
         <v>102003</v>
       </c>
@@ -4998,7 +5130,7 @@
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J45" s="4">
         <v>7</v>
@@ -5007,14 +5139,14 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="O45" s="4"/>
       <c r="P45" s="4">
         <v>204001</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4">
@@ -5059,20 +5191,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ45" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK45" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL45" s="4"/>
       <c r="AM45" s="4">
         <v>102003</v>
       </c>
-      <c r="AN45" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:40">
+      <c r="AO45" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="1:41">
       <c r="A46" s="4">
         <v>103001</v>
       </c>
@@ -5088,7 +5220,7 @@
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J46" s="4">
         <v>1</v>
@@ -5097,14 +5229,14 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O46" s="4"/>
       <c r="P46" s="4">
         <v>200002</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4">
@@ -5149,20 +5281,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ46" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK46" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL46" s="4"/>
       <c r="AM46" s="4">
         <v>103001</v>
       </c>
-      <c r="AN46" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:40">
+      <c r="AO46" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:41">
       <c r="A47" s="4">
         <v>103002</v>
       </c>
@@ -5178,7 +5310,7 @@
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J47" s="4">
         <v>1</v>
@@ -5187,14 +5319,14 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O47" s="4"/>
       <c r="P47" s="4">
         <v>200003</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4">
@@ -5239,20 +5371,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ47" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK47" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL47" s="4"/>
       <c r="AM47" s="4">
         <v>103002</v>
       </c>
-      <c r="AN47" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:40">
+      <c r="AO47" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:41">
       <c r="A48" s="4">
         <v>103003</v>
       </c>
@@ -5268,7 +5400,7 @@
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J48" s="4">
         <v>1</v>
@@ -5277,14 +5409,14 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O48" s="4"/>
       <c r="P48" s="4">
         <v>200004</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4">
@@ -5329,20 +5461,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ48" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK48" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL48" s="4"/>
       <c r="AM48" s="4">
         <v>103003</v>
       </c>
-      <c r="AN48" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:40">
+      <c r="AO48" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:41">
       <c r="A49" s="4">
         <v>103004</v>
       </c>
@@ -5358,7 +5490,7 @@
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J49" s="4">
         <v>1</v>
@@ -5367,14 +5499,14 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O49" s="4"/>
       <c r="P49" s="4">
         <v>800001</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4">
@@ -5419,20 +5551,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ49" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AK49" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL49" s="4"/>
       <c r="AM49" s="4">
         <v>103004</v>
       </c>
-      <c r="AN49" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:40">
+      <c r="AO49" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:41">
       <c r="A50" s="4">
         <v>103101</v>
       </c>
@@ -5448,7 +5580,7 @@
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J50" s="4">
         <v>1</v>
@@ -5457,14 +5589,14 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O50" s="4"/>
       <c r="P50" s="4">
         <v>700001</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4">
@@ -5509,20 +5641,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ50" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AK50" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL50" s="4"/>
       <c r="AM50" s="4">
         <v>103101</v>
       </c>
-      <c r="AN50" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:40">
+      <c r="AO50" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:41">
       <c r="A51" s="4">
         <v>103102</v>
       </c>
@@ -5538,7 +5670,7 @@
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J51" s="4">
         <v>1</v>
@@ -5547,14 +5679,14 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O51" s="4"/>
       <c r="P51" s="4">
         <v>700002</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4">
@@ -5599,20 +5731,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ51" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AK51" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL51" s="4"/>
       <c r="AM51" s="4">
         <v>103102</v>
       </c>
-      <c r="AN51" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:40">
+      <c r="AO51" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" spans="1:41">
       <c r="A52" s="4">
         <v>103103</v>
       </c>
@@ -5628,7 +5760,7 @@
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J52" s="4">
         <v>1</v>
@@ -5637,14 +5769,14 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O52" s="4"/>
       <c r="P52" s="4">
         <v>700003</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R52" s="4"/>
       <c r="S52" s="4">
@@ -5689,20 +5821,20 @@
         <v>1000001</v>
       </c>
       <c r="AJ52" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AK52" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL52" s="4"/>
       <c r="AM52" s="4">
         <v>103103</v>
       </c>
-      <c r="AN52" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:40">
+      <c r="AO52" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:41">
       <c r="A53" s="5">
         <v>900001</v>
       </c>
@@ -5722,7 +5854,7 @@
         <v>21010001</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J53" s="5">
         <v>2</v>
@@ -5731,7 +5863,7 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O53" s="5"/>
       <c r="P53" s="5">
@@ -5783,10 +5915,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ53" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AK53" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL53" s="5">
         <v>300200001</v>
@@ -5794,11 +5926,11 @@
       <c r="AM53" s="5">
         <v>900001</v>
       </c>
-      <c r="AN53" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="54" spans="1:40">
+      <c r="AO53" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:41">
       <c r="A54" s="5">
         <v>900002</v>
       </c>
@@ -5818,7 +5950,7 @@
         <v>21000001</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J54" s="5">
         <v>8</v>
@@ -5827,14 +5959,14 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O54" s="5"/>
       <c r="P54" s="5">
         <v>200001</v>
       </c>
       <c r="Q54" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="R54" s="5"/>
       <c r="S54" s="5">
@@ -5881,10 +6013,10 @@
         <v>2000001</v>
       </c>
       <c r="AJ54" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK54" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL54" s="5">
         <v>300200002</v>
@@ -5892,11 +6024,11 @@
       <c r="AM54" s="5">
         <v>900002</v>
       </c>
-      <c r="AN54" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55" spans="1:40">
+      <c r="AO54" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:41">
       <c r="A55">
         <v>989996</v>
       </c>
@@ -5943,16 +6075,16 @@
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
-      <c r="AN55" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="56" spans="1:40">
+      <c r="AO55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:41">
       <c r="A56">
         <v>989997</v>
       </c>
@@ -5999,16 +6131,16 @@
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
-      <c r="AN56" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="57" spans="1:40">
+      <c r="AO56" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:41">
       <c r="A57">
         <v>989998</v>
       </c>
@@ -6055,16 +6187,16 @@
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
-      <c r="AN57" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="58" spans="1:40">
+      <c r="AO57" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" spans="1:41">
       <c r="A58">
         <v>989999</v>
       </c>
@@ -6109,16 +6241,16 @@
         <v>989999</v>
       </c>
       <c r="AK58" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
-      <c r="AN58" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="59" spans="1:40">
+      <c r="AO58" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:41">
       <c r="A59">
         <v>999947</v>
       </c>
@@ -6165,16 +6297,16 @@
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
-      <c r="AN59" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="60" spans="1:40">
+      <c r="AO59" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:41">
       <c r="A60">
         <v>999948</v>
       </c>
@@ -6221,16 +6353,16 @@
       <c r="AI60"/>
       <c r="AJ60"/>
       <c r="AK60" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
-      <c r="AN60" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" spans="1:40">
+      <c r="AO60" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:41">
       <c r="A61">
         <v>999949</v>
       </c>
@@ -6277,16 +6409,16 @@
       <c r="AI61"/>
       <c r="AJ61"/>
       <c r="AK61" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
-      <c r="AN61" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="62" spans="1:40">
+      <c r="AO61" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:41">
       <c r="A62">
         <v>999950</v>
       </c>
@@ -6333,16 +6465,16 @@
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
-      <c r="AN62" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="63" spans="1:40">
+      <c r="AO62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:41">
       <c r="A63">
         <v>999951</v>
       </c>
@@ -6389,16 +6521,16 @@
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
-      <c r="AN63" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="64" spans="1:40">
+      <c r="AO63" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:41">
       <c r="A64">
         <v>999952</v>
       </c>
@@ -6445,16 +6577,16 @@
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
-      <c r="AN64" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="65" spans="1:40">
+      <c r="AO64" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:41">
       <c r="A65">
         <v>999953</v>
       </c>
@@ -6501,16 +6633,16 @@
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
-      <c r="AN65" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="66" spans="1:40">
+      <c r="AO65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:41">
       <c r="A66">
         <v>999954</v>
       </c>
@@ -6557,16 +6689,16 @@
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
-      <c r="AN66" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="67" spans="1:40">
+      <c r="AO66" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:41">
       <c r="A67">
         <v>999955</v>
       </c>
@@ -6613,16 +6745,16 @@
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
-      <c r="AN67" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="68" spans="1:40">
+      <c r="AO67" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:41">
       <c r="A68">
         <v>999956</v>
       </c>
@@ -6669,16 +6801,16 @@
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
-      <c r="AN68" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:40">
+      <c r="AO68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41">
       <c r="A69">
         <v>999957</v>
       </c>
@@ -6725,16 +6857,16 @@
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
-      <c r="AN69" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="70" spans="1:40">
+      <c r="AO69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:41">
       <c r="A70">
         <v>999958</v>
       </c>
@@ -6781,16 +6913,16 @@
       <c r="AI70"/>
       <c r="AJ70"/>
       <c r="AK70" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
-      <c r="AN70" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="71" spans="1:40">
+      <c r="AO70" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:41">
       <c r="A71">
         <v>999959</v>
       </c>
@@ -6837,16 +6969,16 @@
       <c r="AI71"/>
       <c r="AJ71"/>
       <c r="AK71" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
-      <c r="AN71" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="72" spans="1:40">
+      <c r="AO71" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:41">
       <c r="A72">
         <v>999960</v>
       </c>
@@ -6893,16 +7025,16 @@
       <c r="AI72"/>
       <c r="AJ72"/>
       <c r="AK72" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
-      <c r="AN72" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="73" spans="1:40">
+      <c r="AO72" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="1:41">
       <c r="A73">
         <v>999961</v>
       </c>
@@ -6949,16 +7081,16 @@
       <c r="AI73"/>
       <c r="AJ73"/>
       <c r="AK73" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
-      <c r="AN73" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="74" spans="1:40">
+      <c r="AO73" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:41">
       <c r="A74">
         <v>999962</v>
       </c>
@@ -7005,16 +7137,16 @@
       <c r="AI74"/>
       <c r="AJ74"/>
       <c r="AK74" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
-      <c r="AN74" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="75" spans="1:40">
+      <c r="AO74" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="75" spans="1:41">
       <c r="A75">
         <v>999963</v>
       </c>
@@ -7061,16 +7193,16 @@
       <c r="AI75"/>
       <c r="AJ75"/>
       <c r="AK75" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
-      <c r="AN75" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="76" spans="1:40">
+      <c r="AO75" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="76" spans="1:41">
       <c r="A76">
         <v>999964</v>
       </c>
@@ -7117,16 +7249,16 @@
       <c r="AI76"/>
       <c r="AJ76"/>
       <c r="AK76" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
-      <c r="AN76" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="77" spans="1:40">
+      <c r="AO76" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="77" spans="1:41">
       <c r="A77">
         <v>999965</v>
       </c>
@@ -7173,16 +7305,16 @@
       <c r="AI77"/>
       <c r="AJ77"/>
       <c r="AK77" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
-      <c r="AN77" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="78" spans="1:40">
+      <c r="AO77" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" spans="1:41">
       <c r="A78">
         <v>999966</v>
       </c>
@@ -7229,16 +7361,16 @@
       <c r="AI78"/>
       <c r="AJ78"/>
       <c r="AK78" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
-      <c r="AN78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="79" spans="1:40">
+      <c r="AO78" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79" spans="1:41">
       <c r="A79">
         <v>999967</v>
       </c>
@@ -7285,16 +7417,16 @@
       <c r="AI79"/>
       <c r="AJ79"/>
       <c r="AK79" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
-      <c r="AN79" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="80" spans="1:40">
+      <c r="AO79" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="80" spans="1:41">
       <c r="A80">
         <v>999968</v>
       </c>
@@ -7341,16 +7473,16 @@
       <c r="AI80"/>
       <c r="AJ80"/>
       <c r="AK80" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
-      <c r="AN80" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="1:40">
+      <c r="AO80" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="81" spans="1:41">
       <c r="A81">
         <v>999969</v>
       </c>
@@ -7397,16 +7529,16 @@
       <c r="AI81"/>
       <c r="AJ81"/>
       <c r="AK81" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
-      <c r="AN81" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="82" spans="1:40">
+      <c r="AO81" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="82" spans="1:41">
       <c r="A82">
         <v>999970</v>
       </c>
@@ -7453,16 +7585,16 @@
       <c r="AI82"/>
       <c r="AJ82"/>
       <c r="AK82" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
-      <c r="AN82" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="1:40">
+      <c r="AO82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:41">
       <c r="A83">
         <v>999971</v>
       </c>
@@ -7509,16 +7641,16 @@
       <c r="AI83"/>
       <c r="AJ83"/>
       <c r="AK83" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
-      <c r="AN83" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="84" spans="1:40">
+      <c r="AO83" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:41">
       <c r="A84">
         <v>999972</v>
       </c>
@@ -7565,16 +7697,16 @@
       <c r="AI84"/>
       <c r="AJ84"/>
       <c r="AK84" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
-      <c r="AN84" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="85" spans="1:40">
+      <c r="AO84" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85" spans="1:41">
       <c r="A85">
         <v>999973</v>
       </c>
@@ -7621,16 +7753,16 @@
       <c r="AI85"/>
       <c r="AJ85"/>
       <c r="AK85" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
-      <c r="AN85" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="86" spans="1:40">
+      <c r="AO85" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:41">
       <c r="A86">
         <v>999974</v>
       </c>
@@ -7677,16 +7809,16 @@
       <c r="AI86"/>
       <c r="AJ86"/>
       <c r="AK86" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
-      <c r="AN86" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="87" spans="1:40">
+      <c r="AO86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:41">
       <c r="A87">
         <v>999975</v>
       </c>
@@ -7733,16 +7865,16 @@
       <c r="AI87"/>
       <c r="AJ87"/>
       <c r="AK87" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
-      <c r="AN87" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:40">
+      <c r="AO87" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="88" spans="1:41">
       <c r="A88">
         <v>999976</v>
       </c>
@@ -7789,16 +7921,16 @@
       <c r="AI88"/>
       <c r="AJ88"/>
       <c r="AK88" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
-      <c r="AN88" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="89" spans="1:40">
+      <c r="AO88" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="89" spans="1:41">
       <c r="A89">
         <v>999977</v>
       </c>
@@ -7845,16 +7977,16 @@
       <c r="AI89"/>
       <c r="AJ89"/>
       <c r="AK89" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
-      <c r="AN89" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="90" spans="1:40">
+      <c r="AO89" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="90" spans="1:41">
       <c r="A90">
         <v>999978</v>
       </c>
@@ -7901,16 +8033,16 @@
       <c r="AI90"/>
       <c r="AJ90"/>
       <c r="AK90" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
-      <c r="AN90" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="91" spans="1:40">
+      <c r="AO90" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="91" spans="1:41">
       <c r="A91">
         <v>999979</v>
       </c>
@@ -7957,16 +8089,16 @@
       <c r="AI91"/>
       <c r="AJ91"/>
       <c r="AK91" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
-      <c r="AN91" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="92" spans="1:40">
+      <c r="AO91" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="92" spans="1:41">
       <c r="A92">
         <v>999980</v>
       </c>
@@ -8013,16 +8145,16 @@
       <c r="AI92"/>
       <c r="AJ92"/>
       <c r="AK92" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
-      <c r="AN92" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="93" spans="1:40">
+      <c r="AO92" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:41">
       <c r="A93">
         <v>999981</v>
       </c>
@@ -8069,16 +8201,16 @@
       <c r="AI93"/>
       <c r="AJ93"/>
       <c r="AK93" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
-      <c r="AN93" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="94" spans="1:40">
+      <c r="AO93" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="94" spans="1:41">
       <c r="A94">
         <v>999982</v>
       </c>
@@ -8122,16 +8254,16 @@
         <v>999982</v>
       </c>
       <c r="AK94" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
-      <c r="AN94" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="95" spans="1:40">
+      <c r="AO94" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" spans="1:41">
       <c r="A95">
         <v>999983</v>
       </c>
@@ -8175,16 +8307,16 @@
         <v>999983</v>
       </c>
       <c r="AK95" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
-      <c r="AN95" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="96" spans="1:40">
+      <c r="AO95" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="96" spans="1:41">
       <c r="A96">
         <v>999984</v>
       </c>
@@ -8228,16 +8360,16 @@
         <v>999984</v>
       </c>
       <c r="AK96" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
-      <c r="AN96" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="97" spans="1:40">
+      <c r="AO96" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="97" spans="1:41">
       <c r="A97">
         <v>999985</v>
       </c>
@@ -8281,16 +8413,16 @@
         <v>999985</v>
       </c>
       <c r="AK97" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
-      <c r="AN97" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="98" spans="1:40">
+      <c r="AO97" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="98" spans="1:41">
       <c r="A98">
         <v>999986</v>
       </c>
@@ -8334,16 +8466,16 @@
         <v>999986</v>
       </c>
       <c r="AK98" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
-      <c r="AN98" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="99" spans="1:40">
+      <c r="AO98" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="99" spans="1:41">
       <c r="A99">
         <v>999987</v>
       </c>
@@ -8387,16 +8519,16 @@
         <v>999987</v>
       </c>
       <c r="AK99" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
-      <c r="AN99" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="100" spans="1:40">
+      <c r="AO99" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="100" spans="1:41">
       <c r="A100">
         <v>999988</v>
       </c>
@@ -8440,16 +8572,16 @@
         <v>999988</v>
       </c>
       <c r="AK100" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
-      <c r="AN100" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="101" spans="1:40">
+      <c r="AO100" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:41">
       <c r="A101">
         <v>999989</v>
       </c>
@@ -8493,16 +8625,16 @@
         <v>999989</v>
       </c>
       <c r="AK101" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
-      <c r="AN101" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="102" spans="1:40">
+      <c r="AO101" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="102" spans="1:41">
       <c r="A102">
         <v>999990</v>
       </c>
@@ -8546,16 +8678,16 @@
         <v>999990</v>
       </c>
       <c r="AK102" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
-      <c r="AN102" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="103" spans="1:40">
+      <c r="AO102" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="103" spans="1:41">
       <c r="A103">
         <v>999991</v>
       </c>
@@ -8599,16 +8731,16 @@
         <v>999991</v>
       </c>
       <c r="AK103" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM103">
         <v>1</v>
       </c>
-      <c r="AN103" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="104" spans="1:40">
+      <c r="AO103" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:41">
       <c r="A104">
         <v>999992</v>
       </c>
@@ -8652,16 +8784,16 @@
         <v>999992</v>
       </c>
       <c r="AK104" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM104">
         <v>1</v>
       </c>
-      <c r="AN104" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="1:40">
+      <c r="AO104" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="105" spans="1:41">
       <c r="A105">
         <v>999993</v>
       </c>
@@ -8705,16 +8837,16 @@
         <v>999993</v>
       </c>
       <c r="AK105" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM105">
         <v>1</v>
       </c>
-      <c r="AN105" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="106" spans="1:40">
+      <c r="AO105" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106" spans="1:41">
       <c r="A106">
         <v>999994</v>
       </c>
@@ -8758,16 +8890,16 @@
         <v>999994</v>
       </c>
       <c r="AK106" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM106">
         <v>1</v>
       </c>
-      <c r="AN106" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="107" spans="1:40">
+      <c r="AO106" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:41">
       <c r="A107">
         <v>999995</v>
       </c>
@@ -8811,16 +8943,16 @@
         <v>999995</v>
       </c>
       <c r="AK107" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM107">
         <v>1</v>
       </c>
-      <c r="AN107" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="108" spans="1:40">
+      <c r="AO107" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:41">
       <c r="A108">
         <v>999996</v>
       </c>
@@ -8864,16 +8996,16 @@
         <v>999996</v>
       </c>
       <c r="AK108" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM108">
         <v>1</v>
       </c>
-      <c r="AN108" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="109" spans="1:40">
+      <c r="AO108" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="109" spans="1:41">
       <c r="A109">
         <v>999997</v>
       </c>
@@ -8917,16 +9049,16 @@
         <v>999997</v>
       </c>
       <c r="AK109" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM109">
         <v>1</v>
       </c>
-      <c r="AN109" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="110" spans="1:40">
+      <c r="AO109" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="110" spans="1:41">
       <c r="A110">
         <v>999998</v>
       </c>
@@ -8970,16 +9102,16 @@
         <v>999998</v>
       </c>
       <c r="AK110" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM110">
         <v>1</v>
       </c>
-      <c r="AN110" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="111" spans="1:40">
+      <c r="AO110" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="111" spans="1:41">
       <c r="A111">
         <v>999999</v>
       </c>
@@ -9023,13 +9155,13 @@
         <v>999999</v>
       </c>
       <c r="AK111" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AM111">
         <v>1</v>
       </c>
-      <c r="AN111" t="s">
-        <v>163</v>
+      <c r="AO111" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="169">
   <si>
     <t>id</t>
   </si>
@@ -374,9 +374,15 @@
     <t>1,6</t>
   </si>
   <si>
+    <t>ui_class_8</t>
+  </si>
+  <si>
     <t>守护史莱姆</t>
   </si>
   <si>
+    <t>ui_class_5</t>
+  </si>
+  <si>
     <t>自爆史莱姆</t>
   </si>
   <si>
@@ -510,9 +516,6 @@
   </si>
   <si>
     <t>0,6,0</t>
-  </si>
-  <si>
-    <t>ui_class_5</t>
   </si>
   <si>
     <t>人类-大魔法师（火）</t>
@@ -2994,7 +2997,9 @@
       <c r="AI19" s="1">
         <v>3000001</v>
       </c>
-      <c r="AJ19" s="1"/>
+      <c r="AJ19" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="AK19" s="1" t="s">
         <v>91</v>
       </c>
@@ -3008,7 +3013,7 @@
         <v>87</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:41">
@@ -3072,7 +3077,9 @@
       <c r="AI20" s="1">
         <v>3000001</v>
       </c>
-      <c r="AJ20" s="1"/>
+      <c r="AJ20" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="AK20" s="1" t="s">
         <v>91</v>
       </c>
@@ -3086,7 +3093,7 @@
         <v>87</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:41">
@@ -3100,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>113</v>
@@ -3156,7 +3163,9 @@
       <c r="AI21" s="1">
         <v>3000001</v>
       </c>
-      <c r="AJ21" s="1"/>
+      <c r="AJ21" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="AK21" s="1" t="s">
         <v>91</v>
       </c>
@@ -3170,7 +3179,7 @@
         <v>87</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:41">
@@ -3184,7 +3193,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>113</v>
@@ -3240,7 +3249,9 @@
       <c r="AI22" s="1">
         <v>3000001</v>
       </c>
-      <c r="AJ22" s="1"/>
+      <c r="AJ22" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="AK22" s="1" t="s">
         <v>91</v>
       </c>
@@ -3254,7 +3265,7 @@
         <v>87</v>
       </c>
       <c r="AO22" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:41">
@@ -3340,7 +3351,7 @@
         <v>87</v>
       </c>
       <c r="AO23" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:41">
@@ -3357,7 +3368,7 @@
         <v>4000001</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P24" s="1">
         <v>500001</v>
@@ -3418,7 +3429,7 @@
         <v>87</v>
       </c>
       <c r="AO24" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:41">
@@ -3435,7 +3446,7 @@
         <v>4000001</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P25" s="1">
         <v>600001</v>
@@ -3496,7 +3507,7 @@
         <v>87</v>
       </c>
       <c r="AO25" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:41">
@@ -3513,7 +3524,7 @@
         <v>4000001</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P26" s="1">
         <v>202001</v>
@@ -3577,7 +3588,7 @@
         <v>87</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:41">
@@ -3594,7 +3605,7 @@
         <v>4000001</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P27" s="1">
         <v>500002</v>
@@ -3655,7 +3666,7 @@
         <v>87</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:41">
@@ -3672,7 +3683,7 @@
         <v>5000001</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P28" s="1">
         <v>101002</v>
@@ -3735,7 +3746,7 @@
         <v>87</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:41">
@@ -3755,7 +3766,7 @@
         <v>51010001</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J29" s="1">
         <v>8</v>
@@ -3764,7 +3775,7 @@
         <v>203001</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R29" s="1">
         <v>1</v>
@@ -3822,7 +3833,7 @@
         <v>87</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:41">
@@ -3839,7 +3850,7 @@
         <v>5000001</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P30" s="1">
         <v>101003</v>
@@ -3902,7 +3913,7 @@
         <v>87</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:41">
@@ -3919,7 +3930,7 @@
         <v>5000001</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P31" s="1">
         <v>101004</v>
@@ -3982,7 +3993,7 @@
         <v>87</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:41">
@@ -3996,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G32" s="1">
         <v>6000001</v>
@@ -4050,10 +4061,10 @@
         <v>6000001</v>
       </c>
       <c r="AJ32" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AK32" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL32" s="1">
         <v>300600001</v>
@@ -4065,7 +4076,7 @@
         <v>87</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:41">
@@ -4097,7 +4108,7 @@
         <v>204001</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S33" s="1">
         <v>2</v>
@@ -4142,7 +4153,7 @@
         <v>100</v>
       </c>
       <c r="AK33" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL33" s="1">
         <v>300600002</v>
@@ -4154,7 +4165,7 @@
         <v>87</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:41">
@@ -4220,7 +4231,7 @@
       </c>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL34" s="1">
         <v>300600003</v>
@@ -4232,7 +4243,7 @@
         <v>87</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:41">
@@ -4264,7 +4275,7 @@
         <v>204002</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S35" s="1">
         <v>2</v>
@@ -4309,7 +4320,7 @@
         <v>102</v>
       </c>
       <c r="AK35" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL35" s="1">
         <v>300600004</v>
@@ -4321,7 +4332,7 @@
         <v>87</v>
       </c>
       <c r="AO35" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:41">
@@ -4353,7 +4364,7 @@
         <v>204003</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S36" s="1">
         <v>2</v>
@@ -4398,7 +4409,7 @@
         <v>102</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AL36" s="1">
         <v>300600005</v>
@@ -4410,7 +4421,7 @@
         <v>87</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:41">
@@ -4424,13 +4435,13 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G37" s="1">
         <v>7000001</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P37" s="1">
         <v>200001</v>
@@ -4490,7 +4501,7 @@
         <v>87</v>
       </c>
       <c r="AO37" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:41">
@@ -4510,7 +4521,7 @@
         <v>71000001</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J38" s="1">
         <v>8</v>
@@ -4577,7 +4588,7 @@
         <v>87</v>
       </c>
       <c r="AO38" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:41">
@@ -4666,7 +4677,7 @@
         <v>87</v>
       </c>
       <c r="AO39" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:41">
@@ -4755,7 +4766,7 @@
         <v>87</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" spans="1:41">
@@ -4841,7 +4852,7 @@
         <v>101001</v>
       </c>
       <c r="AO41" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" spans="1:41">
@@ -4869,7 +4880,7 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O42" s="4"/>
       <c r="P42" s="4">
@@ -4921,7 +4932,7 @@
         <v>1000001</v>
       </c>
       <c r="AJ42" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AK42" s="4" t="s">
         <v>86</v>
@@ -4931,7 +4942,7 @@
         <v>101002</v>
       </c>
       <c r="AO42" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" spans="1:41">
@@ -4959,14 +4970,14 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O43" s="4"/>
       <c r="P43" s="4">
         <v>200001</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4">
@@ -5021,7 +5032,7 @@
         <v>102001</v>
       </c>
       <c r="AO43" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" spans="1:41">
@@ -5049,14 +5060,14 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O44" s="4"/>
       <c r="P44" s="4">
         <v>205001</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R44" s="4"/>
       <c r="S44" s="4">
@@ -5111,7 +5122,7 @@
         <v>102002</v>
       </c>
       <c r="AO44" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:41">
@@ -5139,14 +5150,14 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O45" s="4"/>
       <c r="P45" s="4">
         <v>204001</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4">
@@ -5201,7 +5212,7 @@
         <v>102003</v>
       </c>
       <c r="AO45" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:41">
@@ -5236,7 +5247,7 @@
         <v>200002</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4">
@@ -5291,7 +5302,7 @@
         <v>103001</v>
       </c>
       <c r="AO46" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" spans="1:41">
@@ -5326,7 +5337,7 @@
         <v>200003</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4">
@@ -5381,7 +5392,7 @@
         <v>103002</v>
       </c>
       <c r="AO47" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" spans="1:41">
@@ -5416,7 +5427,7 @@
         <v>200004</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4">
@@ -5471,7 +5482,7 @@
         <v>103003</v>
       </c>
       <c r="AO48" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" s="2" customFormat="1" spans="1:41">
@@ -5506,7 +5517,7 @@
         <v>800001</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4">
@@ -5561,7 +5572,7 @@
         <v>103004</v>
       </c>
       <c r="AO49" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" s="2" customFormat="1" spans="1:41">
@@ -5596,7 +5607,7 @@
         <v>700001</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R50" s="4"/>
       <c r="S50" s="4">
@@ -5641,7 +5652,7 @@
         <v>1000001</v>
       </c>
       <c r="AJ50" s="4" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="AK50" s="4" t="s">
         <v>86</v>
@@ -5651,7 +5662,7 @@
         <v>103101</v>
       </c>
       <c r="AO50" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" s="2" customFormat="1" spans="1:41">
@@ -5686,7 +5697,7 @@
         <v>700002</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4">
@@ -5731,7 +5742,7 @@
         <v>1000001</v>
       </c>
       <c r="AJ51" s="4" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="AK51" s="4" t="s">
         <v>86</v>
@@ -5741,7 +5752,7 @@
         <v>103102</v>
       </c>
       <c r="AO51" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:41">
@@ -5776,7 +5787,7 @@
         <v>700003</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R52" s="4"/>
       <c r="S52" s="4">
@@ -5821,7 +5832,7 @@
         <v>1000001</v>
       </c>
       <c r="AJ52" s="4" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="AK52" s="4" t="s">
         <v>86</v>
@@ -5831,7 +5842,7 @@
         <v>103103</v>
       </c>
       <c r="AO52" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:41">
@@ -5927,7 +5938,7 @@
         <v>900001</v>
       </c>
       <c r="AO53" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:41">
@@ -6025,7 +6036,7 @@
         <v>900002</v>
       </c>
       <c r="AO54" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:41">
@@ -6075,13 +6086,13 @@
       <c r="AI55"/>
       <c r="AJ55"/>
       <c r="AK55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM55">
         <v>1</v>
       </c>
       <c r="AO55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:41">
@@ -6131,13 +6142,13 @@
       <c r="AI56"/>
       <c r="AJ56"/>
       <c r="AK56" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM56">
         <v>1</v>
       </c>
       <c r="AO56" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:41">
@@ -6187,13 +6198,13 @@
       <c r="AI57"/>
       <c r="AJ57"/>
       <c r="AK57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM57">
         <v>1</v>
       </c>
       <c r="AO57" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:41">
@@ -6241,13 +6252,13 @@
         <v>989999</v>
       </c>
       <c r="AK58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM58">
         <v>1</v>
       </c>
       <c r="AO58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:41">
@@ -6297,13 +6308,13 @@
       <c r="AI59"/>
       <c r="AJ59"/>
       <c r="AK59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM59">
         <v>1</v>
       </c>
       <c r="AO59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:41">
@@ -6353,13 +6364,13 @@
       <c r="AI60"/>
       <c r="AJ60"/>
       <c r="AK60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM60">
         <v>1</v>
       </c>
       <c r="AO60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:41">
@@ -6409,13 +6420,13 @@
       <c r="AI61"/>
       <c r="AJ61"/>
       <c r="AK61" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM61">
         <v>1</v>
       </c>
       <c r="AO61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:41">
@@ -6465,13 +6476,13 @@
       <c r="AI62"/>
       <c r="AJ62"/>
       <c r="AK62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM62">
         <v>1</v>
       </c>
       <c r="AO62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:41">
@@ -6521,13 +6532,13 @@
       <c r="AI63"/>
       <c r="AJ63"/>
       <c r="AK63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM63">
         <v>1</v>
       </c>
       <c r="AO63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:41">
@@ -6577,13 +6588,13 @@
       <c r="AI64"/>
       <c r="AJ64"/>
       <c r="AK64" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM64">
         <v>1</v>
       </c>
       <c r="AO64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:41">
@@ -6633,13 +6644,13 @@
       <c r="AI65"/>
       <c r="AJ65"/>
       <c r="AK65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM65">
         <v>1</v>
       </c>
       <c r="AO65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:41">
@@ -6689,13 +6700,13 @@
       <c r="AI66"/>
       <c r="AJ66"/>
       <c r="AK66" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM66">
         <v>1</v>
       </c>
       <c r="AO66" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:41">
@@ -6745,13 +6756,13 @@
       <c r="AI67"/>
       <c r="AJ67"/>
       <c r="AK67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM67">
         <v>1</v>
       </c>
       <c r="AO67" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:41">
@@ -6801,13 +6812,13 @@
       <c r="AI68"/>
       <c r="AJ68"/>
       <c r="AK68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM68">
         <v>1</v>
       </c>
       <c r="AO68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:41">
@@ -6857,13 +6868,13 @@
       <c r="AI69"/>
       <c r="AJ69"/>
       <c r="AK69" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM69">
         <v>1</v>
       </c>
       <c r="AO69" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:41">
@@ -6913,13 +6924,13 @@
       <c r="AI70"/>
       <c r="AJ70"/>
       <c r="AK70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM70">
         <v>1</v>
       </c>
       <c r="AO70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:41">
@@ -6969,13 +6980,13 @@
       <c r="AI71"/>
       <c r="AJ71"/>
       <c r="AK71" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM71">
         <v>1</v>
       </c>
       <c r="AO71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:41">
@@ -7025,13 +7036,13 @@
       <c r="AI72"/>
       <c r="AJ72"/>
       <c r="AK72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM72">
         <v>1</v>
       </c>
       <c r="AO72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:41">
@@ -7081,13 +7092,13 @@
       <c r="AI73"/>
       <c r="AJ73"/>
       <c r="AK73" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM73">
         <v>1</v>
       </c>
       <c r="AO73" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:41">
@@ -7137,13 +7148,13 @@
       <c r="AI74"/>
       <c r="AJ74"/>
       <c r="AK74" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM74">
         <v>1</v>
       </c>
       <c r="AO74" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:41">
@@ -7193,13 +7204,13 @@
       <c r="AI75"/>
       <c r="AJ75"/>
       <c r="AK75" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM75">
         <v>1</v>
       </c>
       <c r="AO75" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:41">
@@ -7249,13 +7260,13 @@
       <c r="AI76"/>
       <c r="AJ76"/>
       <c r="AK76" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM76">
         <v>1</v>
       </c>
       <c r="AO76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:41">
@@ -7305,13 +7316,13 @@
       <c r="AI77"/>
       <c r="AJ77"/>
       <c r="AK77" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM77">
         <v>1</v>
       </c>
       <c r="AO77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:41">
@@ -7361,13 +7372,13 @@
       <c r="AI78"/>
       <c r="AJ78"/>
       <c r="AK78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM78">
         <v>1</v>
       </c>
       <c r="AO78" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:41">
@@ -7417,13 +7428,13 @@
       <c r="AI79"/>
       <c r="AJ79"/>
       <c r="AK79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM79">
         <v>1</v>
       </c>
       <c r="AO79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:41">
@@ -7473,13 +7484,13 @@
       <c r="AI80"/>
       <c r="AJ80"/>
       <c r="AK80" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM80">
         <v>1</v>
       </c>
       <c r="AO80" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:41">
@@ -7529,13 +7540,13 @@
       <c r="AI81"/>
       <c r="AJ81"/>
       <c r="AK81" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM81">
         <v>1</v>
       </c>
       <c r="AO81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:41">
@@ -7585,13 +7596,13 @@
       <c r="AI82"/>
       <c r="AJ82"/>
       <c r="AK82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM82">
         <v>1</v>
       </c>
       <c r="AO82" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:41">
@@ -7641,13 +7652,13 @@
       <c r="AI83"/>
       <c r="AJ83"/>
       <c r="AK83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM83">
         <v>1</v>
       </c>
       <c r="AO83" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:41">
@@ -7697,13 +7708,13 @@
       <c r="AI84"/>
       <c r="AJ84"/>
       <c r="AK84" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM84">
         <v>1</v>
       </c>
       <c r="AO84" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:41">
@@ -7753,13 +7764,13 @@
       <c r="AI85"/>
       <c r="AJ85"/>
       <c r="AK85" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM85">
         <v>1</v>
       </c>
       <c r="AO85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:41">
@@ -7809,13 +7820,13 @@
       <c r="AI86"/>
       <c r="AJ86"/>
       <c r="AK86" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM86">
         <v>1</v>
       </c>
       <c r="AO86" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:41">
@@ -7865,13 +7876,13 @@
       <c r="AI87"/>
       <c r="AJ87"/>
       <c r="AK87" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM87">
         <v>1</v>
       </c>
       <c r="AO87" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="88" spans="1:41">
@@ -7921,13 +7932,13 @@
       <c r="AI88"/>
       <c r="AJ88"/>
       <c r="AK88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM88">
         <v>1</v>
       </c>
       <c r="AO88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="89" spans="1:41">
@@ -7977,13 +7988,13 @@
       <c r="AI89"/>
       <c r="AJ89"/>
       <c r="AK89" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM89">
         <v>1</v>
       </c>
       <c r="AO89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:41">
@@ -8033,13 +8044,13 @@
       <c r="AI90"/>
       <c r="AJ90"/>
       <c r="AK90" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM90">
         <v>1</v>
       </c>
       <c r="AO90" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:41">
@@ -8089,13 +8100,13 @@
       <c r="AI91"/>
       <c r="AJ91"/>
       <c r="AK91" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM91">
         <v>1</v>
       </c>
       <c r="AO91" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:41">
@@ -8145,13 +8156,13 @@
       <c r="AI92"/>
       <c r="AJ92"/>
       <c r="AK92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM92">
         <v>1</v>
       </c>
       <c r="AO92" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:41">
@@ -8201,13 +8212,13 @@
       <c r="AI93"/>
       <c r="AJ93"/>
       <c r="AK93" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM93">
         <v>1</v>
       </c>
       <c r="AO93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:41">
@@ -8254,13 +8265,13 @@
         <v>999982</v>
       </c>
       <c r="AK94" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM94">
         <v>1</v>
       </c>
       <c r="AO94" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:41">
@@ -8307,13 +8318,13 @@
         <v>999983</v>
       </c>
       <c r="AK95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM95">
         <v>1</v>
       </c>
       <c r="AO95" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:41">
@@ -8360,13 +8371,13 @@
         <v>999984</v>
       </c>
       <c r="AK96" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM96">
         <v>1</v>
       </c>
       <c r="AO96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" spans="1:41">
@@ -8413,13 +8424,13 @@
         <v>999985</v>
       </c>
       <c r="AK97" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM97">
         <v>1</v>
       </c>
       <c r="AO97" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:41">
@@ -8466,13 +8477,13 @@
         <v>999986</v>
       </c>
       <c r="AK98" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM98">
         <v>1</v>
       </c>
       <c r="AO98" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:41">
@@ -8519,13 +8530,13 @@
         <v>999987</v>
       </c>
       <c r="AK99" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM99">
         <v>1</v>
       </c>
       <c r="AO99" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="100" spans="1:41">
@@ -8572,13 +8583,13 @@
         <v>999988</v>
       </c>
       <c r="AK100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM100">
         <v>1</v>
       </c>
       <c r="AO100" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:41">
@@ -8625,13 +8636,13 @@
         <v>999989</v>
       </c>
       <c r="AK101" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM101">
         <v>1</v>
       </c>
       <c r="AO101" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="102" spans="1:41">
@@ -8678,13 +8689,13 @@
         <v>999990</v>
       </c>
       <c r="AK102" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM102">
         <v>1</v>
       </c>
       <c r="AO102" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:41">
@@ -8731,13 +8742,13 @@
         <v>999991</v>
       </c>
       <c r="AK103" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM103">
         <v>1</v>
       </c>
       <c r="AO103" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:41">
@@ -8784,13 +8795,13 @@
         <v>999992</v>
       </c>
       <c r="AK104" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM104">
         <v>1</v>
       </c>
       <c r="AO104" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="105" spans="1:41">
@@ -8837,13 +8848,13 @@
         <v>999993</v>
       </c>
       <c r="AK105" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM105">
         <v>1</v>
       </c>
       <c r="AO105" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:41">
@@ -8890,13 +8901,13 @@
         <v>999994</v>
       </c>
       <c r="AK106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM106">
         <v>1</v>
       </c>
       <c r="AO106" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="107" spans="1:41">
@@ -8943,13 +8954,13 @@
         <v>999995</v>
       </c>
       <c r="AK107" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM107">
         <v>1</v>
       </c>
       <c r="AO107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:41">
@@ -8996,13 +9007,13 @@
         <v>999996</v>
       </c>
       <c r="AK108" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM108">
         <v>1</v>
       </c>
       <c r="AO108" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="109" spans="1:41">
@@ -9049,13 +9060,13 @@
         <v>999997</v>
       </c>
       <c r="AK109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM109">
         <v>1</v>
       </c>
       <c r="AO109" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:41">
@@ -9102,13 +9113,13 @@
         <v>999998</v>
       </c>
       <c r="AK110" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM110">
         <v>1</v>
       </c>
       <c r="AO110" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="111" spans="1:41">
@@ -9155,13 +9166,13 @@
         <v>999999</v>
       </c>
       <c r="AK111" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AM111">
         <v>1</v>
       </c>
       <c r="AO111" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1227,7 +1227,7 @@
           <t>attack_search_time</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>attack_search_back</t>
         </is>
@@ -1444,7 +1444,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1661,7 +1661,7 @@
           <t>攻击搜索间隔（搜索敌人间隔）</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="0" t="inlineStr">
         <is>
           <t>攻击搜索身后敌人0否1是（正面无目标时转身攻击身后,范围同正面）</t>
         </is>
@@ -1790,7 +1790,7 @@
       <c r="U4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W4" s="0" t="n">
@@ -1851,7 +1851,7 @@
       <c r="U5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W5" s="0" t="n">
@@ -1909,7 +1909,7 @@
       <c r="U6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W6" s="0" t="n">
@@ -1975,7 +1975,7 @@
       <c r="U7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W7" s="0" t="n">
@@ -2036,7 +2036,7 @@
       <c r="U8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="0" t="n">
@@ -2097,7 +2097,7 @@
       <c r="U9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W9" s="0" t="n">
@@ -2158,7 +2158,7 @@
       <c r="U10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W10" s="0" t="n">
@@ -2226,7 +2226,7 @@
       <c r="U11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W11" s="1" t="n">
@@ -2316,7 +2316,7 @@
       <c r="U12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
+      <c r="V12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W12" s="1" t="n">
@@ -2406,7 +2406,7 @@
       <c r="U13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W13" s="1" t="n">
@@ -2496,7 +2496,7 @@
       <c r="U14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W14" s="1" t="n">
@@ -2594,7 +2594,7 @@
       <c r="U15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V15" s="0" t="n">
         <v>1</v>
       </c>
       <c r="W15" s="1" t="n">
@@ -2700,7 +2700,7 @@
       <c r="U16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W16" s="1" t="n">
@@ -2806,7 +2806,7 @@
       <c r="U17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W17" s="1" t="n">
@@ -2912,7 +2912,7 @@
       <c r="U18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W18" s="1" t="n">
@@ -2996,7 +2996,7 @@
       <c r="U19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W19" s="1" t="n">
@@ -3099,7 +3099,7 @@
       <c r="U20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="1" t="n">
@@ -3207,7 +3207,7 @@
       <c r="U21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V21" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W21" s="1" t="n">
@@ -3315,7 +3315,7 @@
       <c r="U22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="1" t="n">
@@ -3421,7 +3421,7 @@
       <c r="U23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W23" s="1" t="n">
@@ -3514,7 +3514,7 @@
       <c r="U24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W24" s="1" t="n">
@@ -3603,7 +3603,7 @@
       <c r="U25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W25" s="1" t="n">
@@ -3697,7 +3697,7 @@
       <c r="U26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W26" s="1" t="n">
@@ -3786,7 +3786,7 @@
       <c r="U27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W27" s="1" t="n">
@@ -3875,7 +3875,7 @@
       <c r="U28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V28" t="n">
+      <c r="V28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="1" t="n">
@@ -3979,7 +3979,7 @@
       <c r="U29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W29" s="1" t="n">
@@ -4068,7 +4068,7 @@
       <c r="U30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W30" s="1" t="n">
@@ -4161,7 +4161,7 @@
       <c r="U31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W31" s="1" t="n">
@@ -4259,7 +4259,7 @@
       <c r="U32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W32" s="1" t="n">
@@ -4365,7 +4365,7 @@
       <c r="U33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W33" s="1" t="n">
@@ -4458,7 +4458,7 @@
       <c r="U34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="1" t="n">
@@ -4560,7 +4560,7 @@
       <c r="U35" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V35" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W35" s="1" t="n">
@@ -4666,7 +4666,7 @@
       <c r="U36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V36" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W36" s="1" t="n">
@@ -4761,7 +4761,7 @@
       <c r="U37" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V37" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W37" s="1" t="n">
@@ -4867,7 +4867,7 @@
       <c r="U38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V38" t="n">
+      <c r="V38" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W38" s="1" t="n">
@@ -4969,7 +4969,7 @@
       <c r="U39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V39" t="n">
+      <c r="V39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W39" s="1" t="n">
@@ -5075,7 +5075,7 @@
       <c r="U40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="V40" t="n">
+      <c r="V40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W40" s="1" t="n">
@@ -5177,7 +5177,7 @@
       <c r="U41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
+      <c r="V41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W41" s="4" t="n">
@@ -5278,7 +5278,7 @@
       <c r="U42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V42" t="n">
+      <c r="V42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W42" s="4" t="n">
@@ -5385,7 +5385,7 @@
       <c r="U43" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V43" t="n">
+      <c r="V43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W43" s="4" t="n">
@@ -5490,7 +5490,7 @@
       <c r="U44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V44" t="n">
+      <c r="V44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W44" s="4" t="n">
@@ -5595,7 +5595,7 @@
       <c r="U45" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W45" s="4" t="n">
@@ -5700,7 +5700,7 @@
       <c r="U46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V46" t="n">
+      <c r="V46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W46" s="4" t="n">
@@ -5805,7 +5805,7 @@
       <c r="U47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
+      <c r="V47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W47" s="4" t="n">
@@ -5910,7 +5910,7 @@
       <c r="U48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V48" t="n">
+      <c r="V48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W48" s="4" t="n">
@@ -6015,7 +6015,7 @@
       <c r="U49" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
+      <c r="V49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W49" s="4" t="n">
@@ -6103,11 +6103,11 @@
       </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n">
-        <v>700001</v>
+        <v>200002</v>
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>0,6,0</t>
+          <t>0,0.6,0</t>
         </is>
       </c>
       <c r="R50" s="4" t="n"/>
@@ -6120,7 +6120,7 @@
       <c r="U50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
+      <c r="V50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W50" s="4" t="n">
@@ -6208,11 +6208,11 @@
       </c>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n">
-        <v>700002</v>
+        <v>200003</v>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>0,6,0</t>
+          <t>0,0.6,0</t>
         </is>
       </c>
       <c r="R51" s="4" t="n"/>
@@ -6225,7 +6225,7 @@
       <c r="U51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V51" t="n">
+      <c r="V51" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W51" s="4" t="n">
@@ -6330,7 +6330,7 @@
       <c r="U52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V52" t="n">
+      <c r="V52" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W52" s="4" t="n">
@@ -6435,7 +6435,7 @@
       <c r="U53" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V53" t="n">
+      <c r="V53" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W53" s="5" t="n">
@@ -6548,7 +6548,7 @@
       <c r="U54" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V54" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W54" s="5" t="n">
@@ -6627,7 +6627,7 @@
       <c r="U55" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V55" t="n">
+      <c r="V55" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
@@ -6690,7 +6690,7 @@
       <c r="U56" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V56" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
@@ -6753,7 +6753,7 @@
       <c r="U57" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V57" t="n">
+      <c r="V57" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
@@ -6816,7 +6816,7 @@
       <c r="U58" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V58" t="n">
+      <c r="V58" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W58" s="0" t="n">
@@ -6877,7 +6877,7 @@
       <c r="U59" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V59" t="n">
+      <c r="V59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W59" s="0" t="n">
@@ -6940,7 +6940,7 @@
       <c r="U60" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V60" t="n">
+      <c r="V60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W60" s="0" t="n">
@@ -7003,7 +7003,7 @@
       <c r="U61" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V61" t="n">
+      <c r="V61" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
@@ -7066,7 +7066,7 @@
       <c r="U62" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V62" t="n">
+      <c r="V62" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
@@ -7129,7 +7129,7 @@
       <c r="U63" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V63" t="n">
+      <c r="V63" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W63" s="0" t="n">
@@ -7192,7 +7192,7 @@
       <c r="U64" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V64" t="n">
+      <c r="V64" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
@@ -7255,7 +7255,7 @@
       <c r="U65" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
+      <c r="V65" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
@@ -7318,7 +7318,7 @@
       <c r="U66" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V66" t="n">
+      <c r="V66" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
@@ -7381,7 +7381,7 @@
       <c r="U67" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
+      <c r="V67" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
@@ -7444,7 +7444,7 @@
       <c r="U68" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V68" t="n">
+      <c r="V68" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
@@ -7507,7 +7507,7 @@
       <c r="U69" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V69" t="n">
+      <c r="V69" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
@@ -7570,7 +7570,7 @@
       <c r="U70" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V70" t="n">
+      <c r="V70" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
@@ -7633,7 +7633,7 @@
       <c r="U71" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V71" t="n">
+      <c r="V71" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
@@ -7696,7 +7696,7 @@
       <c r="U72" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V72" t="n">
+      <c r="V72" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
@@ -7759,7 +7759,7 @@
       <c r="U73" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
+      <c r="V73" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
@@ -7822,7 +7822,7 @@
       <c r="U74" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V74" t="n">
+      <c r="V74" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
@@ -7885,7 +7885,7 @@
       <c r="U75" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
+      <c r="V75" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
@@ -7948,7 +7948,7 @@
       <c r="U76" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V76" t="n">
+      <c r="V76" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
@@ -8011,7 +8011,7 @@
       <c r="U77" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V77" t="n">
+      <c r="V77" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
@@ -8074,7 +8074,7 @@
       <c r="U78" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V78" t="n">
+      <c r="V78" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
@@ -8137,7 +8137,7 @@
       <c r="U79" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V79" t="n">
+      <c r="V79" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
@@ -8200,7 +8200,7 @@
       <c r="U80" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V80" t="n">
+      <c r="V80" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
@@ -8263,7 +8263,7 @@
       <c r="U81" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V81" t="n">
+      <c r="V81" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
@@ -8326,7 +8326,7 @@
       <c r="U82" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V82" t="n">
+      <c r="V82" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
@@ -8389,7 +8389,7 @@
       <c r="U83" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V83" t="n">
+      <c r="V83" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
@@ -8452,7 +8452,7 @@
       <c r="U84" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V84" t="n">
+      <c r="V84" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
@@ -8515,7 +8515,7 @@
       <c r="U85" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V85" t="n">
+      <c r="V85" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
@@ -8578,7 +8578,7 @@
       <c r="U86" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V86" t="n">
+      <c r="V86" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
@@ -8641,7 +8641,7 @@
       <c r="U87" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V87" t="n">
+      <c r="V87" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
@@ -8704,7 +8704,7 @@
       <c r="U88" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V88" t="n">
+      <c r="V88" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
@@ -8767,7 +8767,7 @@
       <c r="U89" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V89" t="n">
+      <c r="V89" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
@@ -8830,7 +8830,7 @@
       <c r="U90" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V90" t="n">
+      <c r="V90" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
@@ -8893,7 +8893,7 @@
       <c r="U91" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V91" t="n">
+      <c r="V91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
@@ -8956,7 +8956,7 @@
       <c r="U92" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V92" t="n">
+      <c r="V92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
@@ -9019,7 +9019,7 @@
       <c r="U93" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V93" t="n">
+      <c r="V93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
@@ -9081,7 +9081,7 @@
       <c r="U94" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V94" t="n">
+      <c r="V94" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W94" s="0" t="n">
@@ -9141,7 +9141,7 @@
       <c r="U95" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V95" t="n">
+      <c r="V95" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W95" s="0" t="n">
@@ -9201,7 +9201,7 @@
       <c r="U96" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V96" t="n">
+      <c r="V96" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W96" s="0" t="n">
@@ -9261,7 +9261,7 @@
       <c r="U97" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V97" t="n">
+      <c r="V97" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W97" s="0" t="n">
@@ -9321,7 +9321,7 @@
       <c r="U98" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V98" t="n">
+      <c r="V98" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W98" s="0" t="n">
@@ -9381,7 +9381,7 @@
       <c r="U99" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V99" t="n">
+      <c r="V99" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W99" s="0" t="n">
@@ -9441,7 +9441,7 @@
       <c r="U100" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V100" t="n">
+      <c r="V100" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W100" s="0" t="n">
@@ -9501,7 +9501,7 @@
       <c r="U101" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V101" t="n">
+      <c r="V101" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W101" s="0" t="n">
@@ -9561,7 +9561,7 @@
       <c r="U102" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V102" t="n">
+      <c r="V102" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
@@ -9621,7 +9621,7 @@
       <c r="U103" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
+      <c r="V103" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
@@ -9681,7 +9681,7 @@
       <c r="U104" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V104" t="n">
+      <c r="V104" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
@@ -9741,7 +9741,7 @@
       <c r="U105" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V105" t="n">
+      <c r="V105" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
@@ -9801,7 +9801,7 @@
       <c r="U106" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V106" t="n">
+      <c r="V106" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
@@ -9861,7 +9861,7 @@
       <c r="U107" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V107" t="n">
+      <c r="V107" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
@@ -9921,7 +9921,7 @@
       <c r="U108" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V108" t="n">
+      <c r="V108" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
@@ -9981,7 +9981,7 @@
       <c r="U109" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V109" t="n">
+      <c r="V109" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
@@ -10041,7 +10041,7 @@
       <c r="U110" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V110" t="n">
+      <c r="V110" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
@@ -10101,7 +10101,7 @@
       <c r="U111" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="V111" t="n">
+      <c r="V111" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -3009,7 +3009,7 @@
         <v>0.5</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AA19" s="1" t="n">
         <v>100</v>
@@ -3112,7 +3112,7 @@
         <v>0.15</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AA20" s="1" t="n">
         <v>100</v>
@@ -3220,7 +3220,7 @@
         <v>0.5</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AA21" s="1" t="n">
         <v>50</v>
@@ -3328,7 +3328,7 @@
         <v>0.5</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AA22" s="1" t="n">
         <v>50</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -5368,7 +5368,7 @@
       </c>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n">
-        <v>200001</v>
+        <v>210001</v>
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n">
-        <v>205001</v>
+        <v>210001</v>
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n">
-        <v>204001</v>
+        <v>210001</v>
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1787,6 +1787,11 @@
           <t>1,2,3</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0,0.6,0</t>
+        </is>
+      </c>
       <c r="U4" s="0" t="n">
         <v>1</v>
       </c>
@@ -1849,6 +1854,11 @@
       <c r="I5" s="0" t="inlineStr">
         <is>
           <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
         </is>
       </c>
       <c r="U5" s="0" t="n">
@@ -1912,6 +1922,11 @@
           <t>1,6</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
       <c r="U6" s="0" t="n">
         <v>1</v>
       </c>
@@ -1927,7 +1942,7 @@
       <c r="AB6" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AF6" s="1" t="n">
@@ -1981,6 +1996,11 @@
           <t>1,2,3,6</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
       <c r="U7" s="0" t="n">
         <v>1</v>
       </c>
@@ -1996,7 +2016,7 @@
       <c r="AB7" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AF7" s="1" t="n">
@@ -2045,6 +2065,11 @@
           <t>1,2,3,5</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0,0.8,0</t>
+        </is>
+      </c>
       <c r="U8" s="0" t="n">
         <v>1</v>
       </c>
@@ -2060,7 +2085,7 @@
       <c r="AB8" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AF8" s="1" t="n">
@@ -2109,6 +2134,11 @@
           <t>1,2,3</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0,0.3,0</t>
+        </is>
+      </c>
       <c r="U9" s="0" t="n">
         <v>1</v>
       </c>
@@ -2124,7 +2154,7 @@
       <c r="AB9" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AF9" s="1" t="n">
@@ -2173,6 +2203,11 @@
           <t>1,2,3,5,6</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
       <c r="U10" s="0" t="n">
         <v>1</v>
       </c>
@@ -2188,7 +2223,7 @@
       <c r="AB10" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AF10" s="1" t="n">
@@ -5187,7 +5222,7 @@
       <c r="P41" s="4" t="n">
         <v>100001</v>
       </c>
-      <c r="Q41" s="4" t="n"/>
+      <c r="Q41" s="4" t="inlineStr"/>
       <c r="R41" s="4" t="n"/>
       <c r="S41" s="4" t="n">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1787,7 +1787,7 @@
           <t>1,2,3</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="0" t="inlineStr">
         <is>
           <t>0,0.6,0</t>
         </is>
@@ -1856,7 +1856,7 @@
           <t>1,2,3</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="0" t="inlineStr">
         <is>
           <t>0,0.7,0</t>
         </is>
@@ -1922,7 +1922,7 @@
           <t>1,6</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="0" t="inlineStr">
         <is>
           <t>0,0.2,0</t>
         </is>
@@ -1996,7 +1996,7 @@
           <t>1,2,3,6</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="0" t="inlineStr">
         <is>
           <t>0,0.7,0</t>
         </is>
@@ -2065,7 +2065,7 @@
           <t>1,2,3,5</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="0" t="inlineStr">
         <is>
           <t>0,0.8,0</t>
         </is>
@@ -2134,7 +2134,7 @@
           <t>1,2,3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="0" t="inlineStr">
         <is>
           <t>0,0.3,0</t>
         </is>
@@ -2203,7 +2203,7 @@
           <t>1,2,3,5,6</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="0" t="inlineStr">
         <is>
           <t>0,0.7,0</t>
         </is>
@@ -2645,7 +2645,7 @@
         <v>2</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U15" s="1" t="n">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="1" t="n">
         <v>1</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="P17" s="1" t="n">
-        <v>201001</v>
+        <v>201003</v>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="1" t="n">
         <v>1</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AK17" s="1" t="inlineStr">
         <is>
-          <t>ui_class_2</t>
+          <t>ui_class_10</t>
         </is>
       </c>
       <c r="AL17" s="1" t="inlineStr">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="P18" s="1" t="n">
-        <v>201002</v>
+        <v>201004</v>
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="1" t="n">
         <v>1</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AK21" s="1" t="inlineStr">
         <is>
-          <t>ui_class_5</t>
+          <t>ui_class_11</t>
         </is>
       </c>
       <c r="AL21" s="1" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AK22" s="1" t="inlineStr">
         <is>
-          <t>ui_class_5</t>
+          <t>ui_class_12</t>
         </is>
       </c>
       <c r="AL22" s="1" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2270,6 +2270,14 @@
       <c r="G11" s="1" t="n">
         <v>1000001</v>
       </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="P11" s="1" t="n">
         <v>100001</v>
       </c>
@@ -2866,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X17" s="1" t="n">
         <v>0.5</v>
@@ -2881,7 +2889,7 @@
         <v>50</v>
       </c>
       <c r="AD17" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE17" s="1" t="n">
         <v>0</v>
@@ -2972,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X18" s="1" t="n">
         <v>0.5</v>
@@ -2987,7 +2995,7 @@
         <v>50</v>
       </c>
       <c r="AD18" s="1" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE18" s="1" t="n">
         <v>0</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -2279,7 +2279,7 @@
         <v>2</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>100001</v>
+        <v>101005</v>
       </c>
       <c r="S11" s="1" t="n">
         <v>1</v>
@@ -2301,12 +2301,18 @@
       </c>
       <c r="Y11" s="1" t="n">
         <v>0.5</v>
+      </c>
+      <c r="Z11" s="0" t="n">
+        <v>20</v>
       </c>
       <c r="AA11" s="1" t="n">
         <v>100</v>
       </c>
+      <c r="AC11" s="0" t="n">
+        <v>50</v>
+      </c>
       <c r="AD11" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE11" s="1" t="n">
         <v>0</v>
@@ -2392,6 +2398,9 @@
       <c r="Y12" s="1" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z12" s="0" t="n">
+        <v>20</v>
+      </c>
       <c r="AA12" s="1" t="n">
         <v>100</v>
       </c>
@@ -2482,6 +2491,9 @@
       <c r="Y13" s="1" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z13" s="0" t="n">
+        <v>20</v>
+      </c>
       <c r="AA13" s="1" t="n">
         <v>100</v>
       </c>
@@ -2572,6 +2584,9 @@
       <c r="Y14" s="1" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z14" s="0" t="n">
+        <v>20</v>
+      </c>
       <c r="AA14" s="1" t="n">
         <v>100</v>
       </c>
@@ -3398,7 +3413,7 @@
         <v>50</v>
       </c>
       <c r="AD22" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE22" s="1" t="n">
         <v>0</v>
@@ -3498,7 +3513,7 @@
         <v>0.5</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AA23" s="1" t="n">
         <v>100</v>
@@ -3952,13 +3967,13 @@
         <v>0.5</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>300</v>
       </c>
       <c r="AD28" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE28" s="1" t="n">
         <v>0</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>0,2.5,0</t>
+          <t>0,1.5,0</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="Q14" s="0" t="inlineStr">
         <is>
-          <t>0,2.5,0</t>
+          <t>0,1.5,0</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X24" s="1" t="n">
         <v>0.5</v>
@@ -3652,7 +3652,7 @@
         <v>100</v>
       </c>
       <c r="AD24" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE24" s="1" t="n">
         <v>0</v>
@@ -3666,7 +3666,11 @@
       <c r="AJ24" s="1" t="n">
         <v>4000001</v>
       </c>
-      <c r="AK24" s="1" t="n"/>
+      <c r="AK24" s="1" t="inlineStr">
+        <is>
+          <t>ui_class_14</t>
+        </is>
+      </c>
       <c r="AL24" s="1" t="inlineStr">
         <is>
           <t>Card_Scene_1</t>
@@ -3710,6 +3714,11 @@
       <c r="P25" s="1" t="n">
         <v>600001</v>
       </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>0,0.5,0</t>
+        </is>
+      </c>
       <c r="R25" s="1" t="n">
         <v>32</v>
       </c>
@@ -3726,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="1" t="n">
         <v>0.5</v>
@@ -3755,7 +3764,11 @@
       <c r="AJ25" s="1" t="n">
         <v>4000001</v>
       </c>
-      <c r="AK25" s="1" t="n"/>
+      <c r="AK25" s="1" t="inlineStr">
+        <is>
+          <t>ui_class_13</t>
+        </is>
+      </c>
       <c r="AL25" s="1" t="inlineStr">
         <is>
           <t>Card_Scene_1</t>
@@ -3835,7 +3848,7 @@
         <v>100</v>
       </c>
       <c r="AD26" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE26" s="1" t="n">
         <v>0</v>
@@ -3849,7 +3862,11 @@
       <c r="AJ26" s="1" t="n">
         <v>4000001</v>
       </c>
-      <c r="AK26" s="1" t="n"/>
+      <c r="AK26" s="1" t="inlineStr">
+        <is>
+          <t>ui_class_15</t>
+        </is>
+      </c>
       <c r="AL26" s="1" t="inlineStr">
         <is>
           <t>Card_Scene_1</t>
@@ -3938,7 +3955,11 @@
       <c r="AJ27" s="1" t="n">
         <v>4000001</v>
       </c>
-      <c r="AK27" s="1" t="n"/>
+      <c r="AK27" s="1" t="inlineStr">
+        <is>
+          <t>ui_class_8</t>
+        </is>
+      </c>
       <c r="AL27" s="1" t="inlineStr">
         <is>
           <t>Card_Scene_1</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR111"/>
+  <dimension ref="A1:AS111"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -1343,6 +1343,11 @@
           <t>charge_attack</t>
         </is>
       </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>details[language_1]</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1565,6 +1570,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1785,6 +1795,11 @@
       <c r="AR3" s="0" t="inlineStr">
         <is>
           <t>冲锋攻击(0=默认站桩;1=冲锋自爆:放卡后立即向前冲锋,遇敌/冲到路尽头/被打死时原地自爆,冲锋开始后原占位格立即释放)</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>详情描述文本id(取content_1，值=生物自身id，0或空=不显示)</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2304,7 @@
         <v>1000001</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>11000001</v>
+        <v>11000002</v>
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
@@ -2370,6 +2385,9 @@
         <is>
           <t>0.9,1.1</t>
         </is>
+      </c>
+      <c r="AS11" t="n">
+        <v>1001</v>
       </c>
     </row>
     <row r="12" customFormat="1" s="1">
@@ -2480,6 +2498,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS12" t="n">
+        <v>1002</v>
+      </c>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" s="1" t="n">
@@ -2581,6 +2602,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS13" t="n">
+        <v>1003</v>
+      </c>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" s="1" t="n">
@@ -2682,6 +2706,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS14" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="15" ht="12" customFormat="1" customHeight="1" s="1">
       <c r="A15" s="1" t="n">
@@ -2783,6 +2810,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS15" t="n">
+        <v>2001</v>
+      </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" s="1" t="n">
@@ -2889,6 +2919,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS16" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" s="1" t="n">
@@ -2995,6 +3028,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS17" t="n">
+        <v>2003</v>
+      </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="1" t="n">
@@ -3101,6 +3137,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS18" t="n">
+        <v>2004</v>
+      </c>
     </row>
     <row r="19" customFormat="1" s="1">
       <c r="A19" s="1" t="n">
@@ -3193,6 +3232,9 @@
           <t>0,0.2,0</t>
         </is>
       </c>
+      <c r="AS19" t="n">
+        <v>3001</v>
+      </c>
     </row>
     <row r="20" customFormat="1" s="1">
       <c r="A20" s="1" t="n">
@@ -3293,6 +3335,9 @@
           <t>0,0.2,0</t>
         </is>
       </c>
+      <c r="AS20" t="n">
+        <v>3002</v>
+      </c>
     </row>
     <row r="21" customFormat="1" s="1">
       <c r="A21" s="1" t="n">
@@ -3401,6 +3446,9 @@
           <t>0,0.2,0</t>
         </is>
       </c>
+      <c r="AS21" t="n">
+        <v>3003</v>
+      </c>
     </row>
     <row r="22" customFormat="1" s="1">
       <c r="A22" s="1" t="n">
@@ -3509,6 +3557,9 @@
           <t>0,0.2,0</t>
         </is>
       </c>
+      <c r="AS22" t="n">
+        <v>3004</v>
+      </c>
     </row>
     <row r="23" customFormat="1" s="1">
       <c r="A23" s="1" t="n">
@@ -3615,6 +3666,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS23" t="n">
+        <v>4001</v>
+      </c>
     </row>
     <row r="24" customFormat="1" s="1">
       <c r="A24" s="1" t="n">
@@ -3708,6 +3762,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS24" t="n">
+        <v>4002</v>
+      </c>
     </row>
     <row r="25" customFormat="1" s="1">
       <c r="A25" s="1" t="n">
@@ -3806,6 +3863,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS25" t="n">
+        <v>4003</v>
+      </c>
     </row>
     <row r="26" customFormat="1" s="1">
       <c r="A26" s="1" t="n">
@@ -3904,6 +3964,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS26" t="n">
+        <v>4004</v>
+      </c>
     </row>
     <row r="27" customFormat="1" s="1">
       <c r="A27" s="1" t="n">
@@ -3997,6 +4060,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS27" t="n">
+        <v>4005</v>
+      </c>
     </row>
     <row r="28" customFormat="1" s="1">
       <c r="A28" s="1" t="n">
@@ -4090,6 +4156,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS28" t="n">
+        <v>5001</v>
+      </c>
     </row>
     <row r="29" customFormat="1" s="1">
       <c r="A29" s="1" t="n">
@@ -4194,6 +4263,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS29" t="n">
+        <v>5002</v>
+      </c>
     </row>
     <row r="30" customFormat="1" s="1">
       <c r="A30" s="1" t="n">
@@ -4287,6 +4359,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS30" t="n">
+        <v>5003</v>
+      </c>
     </row>
     <row r="31" customFormat="1" s="1">
       <c r="A31" s="1" t="n">
@@ -4380,6 +4455,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS31" t="n">
+        <v>5004</v>
+      </c>
     </row>
     <row r="32" customFormat="1" s="1">
       <c r="A32" s="1" t="n">
@@ -4484,6 +4562,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS32" t="n">
+        <v>6001</v>
+      </c>
     </row>
     <row r="33" customFormat="1" s="1">
       <c r="A33" s="1" t="n">
@@ -4590,6 +4671,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS33" t="n">
+        <v>6002</v>
+      </c>
     </row>
     <row r="34" customFormat="1" s="1">
       <c r="A34" s="1" t="n">
@@ -4689,6 +4773,9 @@
       <c r="AR34" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AS34" t="n">
+        <v>6003</v>
+      </c>
     </row>
     <row r="35" customFormat="1" s="1">
       <c r="A35" s="1" t="n">
@@ -4795,6 +4882,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS35" t="n">
+        <v>6004</v>
+      </c>
     </row>
     <row r="36" customFormat="1" s="1">
       <c r="A36" s="1" t="n">
@@ -4901,6 +4991,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS36" t="n">
+        <v>6005</v>
+      </c>
     </row>
     <row r="37" customFormat="1" s="1">
       <c r="A37" s="1" t="n">
@@ -5002,6 +5095,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS37" t="n">
+        <v>7001</v>
+      </c>
     </row>
     <row r="38" customFormat="1" s="1">
       <c r="A38" s="1" t="n">
@@ -5108,6 +5204,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS38" t="n">
+        <v>7002</v>
+      </c>
     </row>
     <row r="39" customFormat="1" s="1">
       <c r="A39" s="1" t="n">
@@ -5214,6 +5313,9 @@
           <t>0.9,1.1</t>
         </is>
       </c>
+      <c r="AS39" t="n">
+        <v>7003</v>
+      </c>
     </row>
     <row r="40" customFormat="1" s="1">
       <c r="A40" s="1" t="n">
@@ -5319,6 +5421,9 @@
         <is>
           <t>0.9,1.1</t>
         </is>
+      </c>
+      <c r="AS40" t="n">
+        <v>7004</v>
       </c>
     </row>
     <row r="41" customFormat="1" s="2">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -9,7 +9,7 @@
     <sheet name="CreatureInfo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AO$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CreatureInfo'!$A$1:$AN$111</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1119,7 +1119,7 @@
     <col width="16" customWidth="1" style="3" min="37" max="37"/>
     <col width="13.75" customWidth="1" style="3" min="38" max="39"/>
     <col width="12.875" customWidth="1" style="3" min="40" max="40"/>
-    <col width="58.875" customWidth="1" style="3" min="41" max="41"/>
+    <col width="20.375" customWidth="1" style="3" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1325,25 +1325,25 @@
       </c>
       <c r="AO1" s="0" t="inlineStr">
         <is>
+          <t>body_size</t>
+        </is>
+      </c>
+      <c r="AP1" s="0" t="inlineStr">
+        <is>
+          <t>shield_effect_position</t>
+        </is>
+      </c>
+      <c r="AQ1" s="0" t="inlineStr">
+        <is>
+          <t>charge_attack</t>
+        </is>
+      </c>
+      <c r="AR1" s="0" t="inlineStr">
+        <is>
           <t>name[language]</t>
         </is>
       </c>
-      <c r="AP1" s="0" t="inlineStr">
-        <is>
-          <t>body_size</t>
-        </is>
-      </c>
-      <c r="AQ1" s="0" t="inlineStr">
-        <is>
-          <t>shield_effect_position</t>
-        </is>
-      </c>
-      <c r="AR1" s="0" t="inlineStr">
-        <is>
-          <t>charge_attack</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="0" t="inlineStr">
         <is>
           <t>details[language_1]</t>
         </is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="AO2" s="0" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AP2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AQ2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AR2" s="0" t="inlineStr">
+        <is>
           <t>long</t>
         </is>
       </c>
-      <c r="AP2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="AQ2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="AR2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" s="0" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="AO3" s="0" t="inlineStr">
         <is>
+          <t>体型大小（空或0=默认1倍；"0.9,1.1"=区间随机；"1.1"=固定倍数；最终在目标大小基础上相乘）</t>
+        </is>
+      </c>
+      <c r="AP3" s="0" t="inlineStr">
+        <is>
+          <t>护盾受击特效位置偏移(相对生物坐标,空=0,0.5,0)</t>
+        </is>
+      </c>
+      <c r="AQ3" s="0" t="inlineStr">
+        <is>
+          <t>冲锋攻击(0=默认站桩;1=冲锋自爆:放卡后立即向前冲锋,遇敌/冲到路尽头/被打死时原地自爆,冲锋开始后原占位格立即释放)</t>
+        </is>
+      </c>
+      <c r="AR3" s="0" t="inlineStr">
+        <is>
           <t>名字-中文</t>
         </is>
       </c>
-      <c r="AP3" s="0" t="inlineStr">
-        <is>
-          <t>体型大小（空或0=默认1倍；"0.9,1.1"=区间随机；"1.1"=固定倍数；最终在目标大小基础上相乘）</t>
-        </is>
-      </c>
-      <c r="AQ3" s="0" t="inlineStr">
-        <is>
-          <t>护盾受击特效位置偏移(相对生物坐标,空=0,0.5,0)</t>
-        </is>
-      </c>
-      <c r="AR3" s="0" t="inlineStr">
-        <is>
-          <t>冲锋攻击(0=默认站桩;1=冲锋自爆:放卡后立即向前冲锋,遇敌/冲到路尽头/被打死时原地自爆,冲锋开始后原占位格立即释放)</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AS3" s="0" t="inlineStr">
         <is>
           <t>详情描述文本id(取content_1，值=生物自身id，0或空=不显示)</t>
         </is>
@@ -1863,13 +1863,13 @@
           <t>Card_Scene_2</t>
         </is>
       </c>
-      <c r="AO4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP4" s="0" t="inlineStr">
+      <c r="AO4" s="0" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
+      </c>
+      <c r="AR4" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1932,13 +1932,13 @@
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AO5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP5" s="0" t="inlineStr">
+      <c r="AO5" s="0" t="inlineStr">
         <is>
           <t>0.9,1.1</t>
         </is>
+      </c>
+      <c r="AR5" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1998,18 +1998,18 @@
           <t>Card_Scene_6</t>
         </is>
       </c>
-      <c r="AO6" s="0" t="n">
+      <c r="AO6" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AP6" s="0" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
+      <c r="AR6" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="AP6" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AQ6" s="0" t="inlineStr">
-        <is>
-          <t>0,0.2,0</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -2072,13 +2072,13 @@
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AO7" s="0" t="n">
+      <c r="AO7" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR7" s="0" t="n">
         <v>4</v>
-      </c>
-      <c r="AP7" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -2141,13 +2141,13 @@
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AO8" s="0" t="n">
+      <c r="AO8" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR8" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="AP8" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -2210,13 +2210,13 @@
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AO9" s="0" t="n">
+      <c r="AO9" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR9" s="0" t="n">
         <v>6</v>
-      </c>
-      <c r="AP9" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -2279,13 +2279,13 @@
           <t>Card_Scene_1</t>
         </is>
       </c>
-      <c r="AO10" s="0" t="n">
+      <c r="AO10" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR10" s="0" t="n">
         <v>7</v>
-      </c>
-      <c r="AP10" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
       </c>
     </row>
     <row r="11" customFormat="1" s="1">
@@ -2378,15 +2378,15 @@
       <c r="AN11" s="1" t="n">
         <v>300100001</v>
       </c>
-      <c r="AO11" s="1" t="n">
+      <c r="AO11" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR11" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="AP11" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AS11" s="0" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -2490,15 +2490,15 @@
       <c r="AN12" s="1" t="n">
         <v>300100002</v>
       </c>
-      <c r="AO12" s="1" t="n">
+      <c r="AO12" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR12" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="AP12" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS12" t="n">
+      <c r="AS12" s="0" t="n">
         <v>1002</v>
       </c>
     </row>
@@ -2594,15 +2594,15 @@
       <c r="AN13" s="1" t="n">
         <v>300100003</v>
       </c>
-      <c r="AO13" s="1" t="n">
+      <c r="AO13" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR13" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="AP13" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS13" t="n">
+      <c r="AS13" s="0" t="n">
         <v>1003</v>
       </c>
     </row>
@@ -2698,15 +2698,15 @@
       <c r="AN14" s="1" t="n">
         <v>300100004</v>
       </c>
-      <c r="AO14" s="1" t="n">
+      <c r="AO14" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR14" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="AP14" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS14" t="n">
+      <c r="AS14" s="0" t="n">
         <v>1004</v>
       </c>
     </row>
@@ -2802,15 +2802,15 @@
       <c r="AN15" s="1" t="n">
         <v>300200001</v>
       </c>
-      <c r="AO15" s="1" t="n">
+      <c r="AO15" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR15" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="AP15" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS15" t="n">
+      <c r="AS15" s="0" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2911,15 +2911,15 @@
       <c r="AN16" s="1" t="n">
         <v>300200002</v>
       </c>
-      <c r="AO16" s="1" t="n">
+      <c r="AO16" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR16" s="1" t="n">
         <v>2002</v>
       </c>
-      <c r="AP16" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS16" t="n">
+      <c r="AS16" s="0" t="n">
         <v>2002</v>
       </c>
     </row>
@@ -3020,15 +3020,15 @@
       <c r="AN17" s="1" t="n">
         <v>300200003</v>
       </c>
-      <c r="AO17" s="1" t="n">
+      <c r="AO17" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR17" s="1" t="n">
         <v>2003</v>
       </c>
-      <c r="AP17" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AS17" s="0" t="n">
         <v>2003</v>
       </c>
     </row>
@@ -3129,15 +3129,15 @@
       <c r="AN18" s="1" t="n">
         <v>300200004</v>
       </c>
-      <c r="AO18" s="1" t="n">
+      <c r="AO18" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR18" s="1" t="n">
         <v>2004</v>
       </c>
-      <c r="AP18" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS18" t="n">
+      <c r="AS18" s="0" t="n">
         <v>2004</v>
       </c>
     </row>
@@ -3219,20 +3219,20 @@
       <c r="AN19" s="1" t="n">
         <v>300300001</v>
       </c>
-      <c r="AO19" s="1" t="n">
+      <c r="AO19" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AP19" s="0" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
+      <c r="AR19" s="1" t="n">
         <v>3001</v>
       </c>
-      <c r="AP19" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AQ19" s="0" t="inlineStr">
-        <is>
-          <t>0,0.2,0</t>
-        </is>
-      </c>
-      <c r="AS19" t="n">
+      <c r="AS19" s="0" t="n">
         <v>3001</v>
       </c>
     </row>
@@ -3322,20 +3322,20 @@
       <c r="AN20" s="1" t="n">
         <v>300300002</v>
       </c>
-      <c r="AO20" s="1" t="n">
+      <c r="AO20" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AP20" s="0" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
+      <c r="AR20" s="1" t="n">
         <v>3002</v>
       </c>
-      <c r="AP20" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AQ20" s="0" t="inlineStr">
-        <is>
-          <t>0,0.2,0</t>
-        </is>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AS20" s="0" t="n">
         <v>3002</v>
       </c>
     </row>
@@ -3433,20 +3433,20 @@
       <c r="AN21" s="1" t="n">
         <v>300300003</v>
       </c>
-      <c r="AO21" s="1" t="n">
+      <c r="AO21" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AP21" s="0" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
+      <c r="AR21" s="1" t="n">
         <v>3003</v>
       </c>
-      <c r="AP21" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AQ21" s="0" t="inlineStr">
-        <is>
-          <t>0,0.2,0</t>
-        </is>
-      </c>
-      <c r="AS21" t="n">
+      <c r="AS21" s="0" t="n">
         <v>3003</v>
       </c>
     </row>
@@ -3544,20 +3544,20 @@
       <c r="AN22" s="1" t="n">
         <v>300300004</v>
       </c>
-      <c r="AO22" s="1" t="n">
+      <c r="AO22" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AP22" s="0" t="inlineStr">
+        <is>
+          <t>0,0.2,0</t>
+        </is>
+      </c>
+      <c r="AR22" s="1" t="n">
         <v>3004</v>
       </c>
-      <c r="AP22" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AQ22" s="0" t="inlineStr">
-        <is>
-          <t>0,0.2,0</t>
-        </is>
-      </c>
-      <c r="AS22" t="n">
+      <c r="AS22" s="0" t="n">
         <v>3004</v>
       </c>
     </row>
@@ -3658,15 +3658,15 @@
       <c r="AN23" s="1" t="n">
         <v>300400001</v>
       </c>
-      <c r="AO23" s="1" t="n">
+      <c r="AO23" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR23" s="1" t="n">
         <v>4001</v>
       </c>
-      <c r="AP23" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS23" t="n">
+      <c r="AS23" s="0" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -3754,15 +3754,15 @@
       <c r="AN24" s="1" t="n">
         <v>300400002</v>
       </c>
-      <c r="AO24" s="1" t="n">
+      <c r="AO24" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR24" s="1" t="n">
         <v>4002</v>
       </c>
-      <c r="AP24" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS24" t="n">
+      <c r="AS24" s="0" t="n">
         <v>4002</v>
       </c>
     </row>
@@ -3855,15 +3855,15 @@
       <c r="AN25" s="1" t="n">
         <v>300400003</v>
       </c>
-      <c r="AO25" s="1" t="n">
+      <c r="AO25" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR25" s="1" t="n">
         <v>4003</v>
       </c>
-      <c r="AP25" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS25" t="n">
+      <c r="AS25" s="0" t="n">
         <v>4003</v>
       </c>
     </row>
@@ -3956,15 +3956,15 @@
       <c r="AN26" s="1" t="n">
         <v>300400004</v>
       </c>
-      <c r="AO26" s="1" t="n">
+      <c r="AO26" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR26" s="1" t="n">
         <v>4004</v>
       </c>
-      <c r="AP26" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS26" t="n">
+      <c r="AS26" s="0" t="n">
         <v>4004</v>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
         <v>100</v>
       </c>
       <c r="AE27" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AL27" s="1" t="inlineStr">
         <is>
-          <t>ui_class_8</t>
+          <t>ui_class_16</t>
         </is>
       </c>
       <c r="AM27" s="1" t="inlineStr">
@@ -4052,15 +4052,15 @@
       <c r="AN27" s="1" t="n">
         <v>300400005</v>
       </c>
-      <c r="AO27" s="1" t="n">
+      <c r="AO27" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR27" s="1" t="n">
         <v>4005</v>
       </c>
-      <c r="AP27" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS27" t="n">
+      <c r="AS27" s="0" t="n">
         <v>4005</v>
       </c>
     </row>
@@ -4148,15 +4148,15 @@
       <c r="AN28" s="1" t="n">
         <v>300500001</v>
       </c>
-      <c r="AO28" s="1" t="n">
+      <c r="AO28" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR28" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="AP28" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS28" t="n">
+      <c r="AS28" s="0" t="n">
         <v>5001</v>
       </c>
     </row>
@@ -4255,15 +4255,15 @@
       <c r="AN29" s="1" t="n">
         <v>300500002</v>
       </c>
-      <c r="AO29" s="1" t="n">
+      <c r="AO29" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR29" s="1" t="n">
         <v>5002</v>
       </c>
-      <c r="AP29" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS29" t="n">
+      <c r="AS29" s="0" t="n">
         <v>5002</v>
       </c>
     </row>
@@ -4351,15 +4351,15 @@
       <c r="AN30" s="1" t="n">
         <v>300500003</v>
       </c>
-      <c r="AO30" s="1" t="n">
+      <c r="AO30" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR30" s="1" t="n">
         <v>5003</v>
       </c>
-      <c r="AP30" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS30" t="n">
+      <c r="AS30" s="0" t="n">
         <v>5003</v>
       </c>
     </row>
@@ -4447,15 +4447,15 @@
       <c r="AN31" s="1" t="n">
         <v>300500004</v>
       </c>
-      <c r="AO31" s="1" t="n">
+      <c r="AO31" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR31" s="1" t="n">
         <v>5004</v>
       </c>
-      <c r="AP31" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS31" t="n">
+      <c r="AS31" s="0" t="n">
         <v>5004</v>
       </c>
     </row>
@@ -4554,15 +4554,15 @@
       <c r="AN32" s="1" t="n">
         <v>300600001</v>
       </c>
-      <c r="AO32" s="1" t="n">
+      <c r="AO32" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR32" s="1" t="n">
         <v>6001</v>
       </c>
-      <c r="AP32" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS32" t="n">
+      <c r="AS32" s="0" t="n">
         <v>6001</v>
       </c>
     </row>
@@ -4663,15 +4663,15 @@
       <c r="AN33" s="1" t="n">
         <v>300600002</v>
       </c>
-      <c r="AO33" s="1" t="n">
+      <c r="AO33" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR33" s="1" t="n">
         <v>6002</v>
       </c>
-      <c r="AP33" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS33" t="n">
+      <c r="AS33" s="0" t="n">
         <v>6002</v>
       </c>
     </row>
@@ -4701,6 +4701,11 @@
       <c r="J34" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="M34" s="0" t="inlineStr">
+        <is>
+          <t>Walk2</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="n">
         <v>300002</v>
       </c>
@@ -4762,18 +4767,18 @@
       <c r="AN34" s="1" t="n">
         <v>300600003</v>
       </c>
-      <c r="AO34" s="1" t="n">
+      <c r="AO34" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AQ34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" s="1" t="n">
         <v>6003</v>
       </c>
-      <c r="AP34" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AR34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS34" t="n">
+      <c r="AS34" s="0" t="n">
         <v>6003</v>
       </c>
     </row>
@@ -4874,15 +4879,15 @@
       <c r="AN35" s="1" t="n">
         <v>300600004</v>
       </c>
-      <c r="AO35" s="1" t="n">
+      <c r="AO35" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR35" s="1" t="n">
         <v>6004</v>
       </c>
-      <c r="AP35" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS35" t="n">
+      <c r="AS35" s="0" t="n">
         <v>6004</v>
       </c>
     </row>
@@ -4983,15 +4988,15 @@
       <c r="AN36" s="1" t="n">
         <v>300600005</v>
       </c>
-      <c r="AO36" s="1" t="n">
+      <c r="AO36" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR36" s="1" t="n">
         <v>6005</v>
       </c>
-      <c r="AP36" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS36" t="n">
+      <c r="AS36" s="0" t="n">
         <v>6005</v>
       </c>
     </row>
@@ -5087,15 +5092,15 @@
       <c r="AN37" s="1" t="n">
         <v>300700001</v>
       </c>
-      <c r="AO37" s="1" t="n">
+      <c r="AO37" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR37" s="1" t="n">
         <v>7001</v>
       </c>
-      <c r="AP37" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS37" t="n">
+      <c r="AS37" s="0" t="n">
         <v>7001</v>
       </c>
     </row>
@@ -5196,15 +5201,15 @@
       <c r="AN38" s="1" t="n">
         <v>300700002</v>
       </c>
-      <c r="AO38" s="1" t="n">
+      <c r="AO38" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR38" s="1" t="n">
         <v>7002</v>
       </c>
-      <c r="AP38" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS38" t="n">
+      <c r="AS38" s="0" t="n">
         <v>7002</v>
       </c>
     </row>
@@ -5305,15 +5310,15 @@
       <c r="AN39" s="1" t="n">
         <v>300700003</v>
       </c>
-      <c r="AO39" s="1" t="n">
+      <c r="AO39" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR39" s="1" t="n">
         <v>7003</v>
       </c>
-      <c r="AP39" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS39" t="n">
+      <c r="AS39" s="0" t="n">
         <v>7003</v>
       </c>
     </row>
@@ -5414,15 +5419,15 @@
       <c r="AN40" s="1" t="n">
         <v>300700004</v>
       </c>
-      <c r="AO40" s="1" t="n">
+      <c r="AO40" s="0" t="inlineStr">
+        <is>
+          <t>0.9,1.1</t>
+        </is>
+      </c>
+      <c r="AR40" s="1" t="n">
         <v>7004</v>
       </c>
-      <c r="AP40" s="0" t="inlineStr">
-        <is>
-          <t>0.9,1.1</t>
-        </is>
-      </c>
-      <c r="AS40" t="n">
+      <c r="AS40" s="0" t="n">
         <v>7004</v>
       </c>
     </row>
@@ -5519,7 +5524,7 @@
         </is>
       </c>
       <c r="AN41" s="4" t="n"/>
-      <c r="AO41" s="4" t="n">
+      <c r="AR41" s="4" t="n">
         <v>101001</v>
       </c>
     </row>
@@ -5622,7 +5627,7 @@
         </is>
       </c>
       <c r="AN42" s="4" t="n"/>
-      <c r="AO42" s="4" t="n">
+      <c r="AR42" s="4" t="n">
         <v>101002</v>
       </c>
     </row>
@@ -5663,7 +5668,7 @@
       </c>
       <c r="O43" s="4" t="n"/>
       <c r="P43" s="4" t="n">
-        <v>200001</v>
+        <v>207001</v>
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
@@ -5727,7 +5732,7 @@
         </is>
       </c>
       <c r="AN43" s="4" t="n"/>
-      <c r="AO43" s="4" t="n">
+      <c r="AR43" s="4" t="n">
         <v>102001</v>
       </c>
     </row>
@@ -5768,7 +5773,7 @@
       </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n">
-        <v>200001</v>
+        <v>207001</v>
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
@@ -5832,7 +5837,7 @@
         </is>
       </c>
       <c r="AN44" s="4" t="n"/>
-      <c r="AO44" s="4" t="n">
+      <c r="AR44" s="4" t="n">
         <v>102002</v>
       </c>
     </row>
@@ -5873,7 +5878,7 @@
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n">
-        <v>200001</v>
+        <v>207001</v>
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
@@ -5937,7 +5942,7 @@
         </is>
       </c>
       <c r="AN45" s="4" t="n"/>
-      <c r="AO45" s="4" t="n">
+      <c r="AR45" s="4" t="n">
         <v>102003</v>
       </c>
     </row>
@@ -6042,7 +6047,7 @@
         </is>
       </c>
       <c r="AN46" s="4" t="n"/>
-      <c r="AO46" s="4" t="n">
+      <c r="AR46" s="4" t="n">
         <v>103001</v>
       </c>
     </row>
@@ -6147,7 +6152,7 @@
         </is>
       </c>
       <c r="AN47" s="4" t="n"/>
-      <c r="AO47" s="4" t="n">
+      <c r="AR47" s="4" t="n">
         <v>103002</v>
       </c>
     </row>
@@ -6252,7 +6257,7 @@
         </is>
       </c>
       <c r="AN48" s="4" t="n"/>
-      <c r="AO48" s="4" t="n">
+      <c r="AR48" s="4" t="n">
         <v>103003</v>
       </c>
     </row>
@@ -6357,7 +6362,7 @@
         </is>
       </c>
       <c r="AN49" s="4" t="n"/>
-      <c r="AO49" s="4" t="n">
+      <c r="AR49" s="4" t="n">
         <v>103004</v>
       </c>
     </row>
@@ -6462,7 +6467,7 @@
         </is>
       </c>
       <c r="AN50" s="4" t="n"/>
-      <c r="AO50" s="4" t="n">
+      <c r="AR50" s="4" t="n">
         <v>103101</v>
       </c>
     </row>
@@ -6567,7 +6572,7 @@
         </is>
       </c>
       <c r="AN51" s="4" t="n"/>
-      <c r="AO51" s="4" t="n">
+      <c r="AR51" s="4" t="n">
         <v>103102</v>
       </c>
     </row>
@@ -6672,7 +6677,7 @@
         </is>
       </c>
       <c r="AN52" s="4" t="n"/>
-      <c r="AO52" s="4" t="n">
+      <c r="AR52" s="4" t="n">
         <v>103103</v>
       </c>
     </row>
@@ -6781,7 +6786,7 @@
       <c r="AN53" s="5" t="n">
         <v>300200001</v>
       </c>
-      <c r="AO53" s="5" t="n">
+      <c r="AR53" s="5" t="n">
         <v>900001</v>
       </c>
     </row>
@@ -6894,7 +6899,7 @@
       <c r="AN54" s="5" t="n">
         <v>300200002</v>
       </c>
-      <c r="AO54" s="5" t="n">
+      <c r="AR54" s="5" t="n">
         <v>900002</v>
       </c>
     </row>
@@ -6957,7 +6962,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO55" s="0" t="n">
+      <c r="AR55" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7020,7 +7025,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO56" s="0" t="n">
+      <c r="AR56" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7083,7 +7088,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO57" s="0" t="n">
+      <c r="AR57" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7144,7 +7149,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO58" s="0" t="n">
+      <c r="AR58" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7207,7 +7212,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO59" s="0" t="n">
+      <c r="AR59" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7270,7 +7275,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO60" s="0" t="n">
+      <c r="AR60" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7333,7 +7338,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO61" s="0" t="n">
+      <c r="AR61" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7396,7 +7401,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO62" s="0" t="n">
+      <c r="AR62" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7459,7 +7464,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO63" s="0" t="n">
+      <c r="AR63" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7522,7 +7527,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO64" s="0" t="n">
+      <c r="AR64" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7585,7 +7590,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO65" s="0" t="n">
+      <c r="AR65" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7648,7 +7653,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO66" s="0" t="n">
+      <c r="AR66" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7711,7 +7716,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO67" s="0" t="n">
+      <c r="AR67" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7774,7 +7779,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO68" s="0" t="n">
+      <c r="AR68" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7837,7 +7842,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO69" s="0" t="n">
+      <c r="AR69" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7900,7 +7905,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO70" s="0" t="n">
+      <c r="AR70" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7963,7 +7968,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO71" s="0" t="n">
+      <c r="AR71" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8026,7 +8031,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO72" s="0" t="n">
+      <c r="AR72" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8089,7 +8094,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO73" s="0" t="n">
+      <c r="AR73" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8152,7 +8157,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO74" s="0" t="n">
+      <c r="AR74" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8215,7 +8220,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO75" s="0" t="n">
+      <c r="AR75" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8278,7 +8283,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO76" s="0" t="n">
+      <c r="AR76" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8341,7 +8346,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO77" s="0" t="n">
+      <c r="AR77" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8404,7 +8409,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO78" s="0" t="n">
+      <c r="AR78" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8467,7 +8472,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO79" s="0" t="n">
+      <c r="AR79" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8530,7 +8535,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO80" s="0" t="n">
+      <c r="AR80" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8593,7 +8598,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO81" s="0" t="n">
+      <c r="AR81" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8656,7 +8661,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO82" s="0" t="n">
+      <c r="AR82" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8719,7 +8724,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO83" s="0" t="n">
+      <c r="AR83" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8782,7 +8787,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO84" s="0" t="n">
+      <c r="AR84" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8845,7 +8850,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO85" s="0" t="n">
+      <c r="AR85" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8908,7 +8913,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO86" s="0" t="n">
+      <c r="AR86" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8971,7 +8976,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO87" s="0" t="n">
+      <c r="AR87" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9034,7 +9039,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO88" s="0" t="n">
+      <c r="AR88" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9097,7 +9102,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO89" s="0" t="n">
+      <c r="AR89" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9160,7 +9165,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO90" s="0" t="n">
+      <c r="AR90" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9223,7 +9228,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO91" s="0" t="n">
+      <c r="AR91" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9286,7 +9291,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO92" s="0" t="n">
+      <c r="AR92" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9349,7 +9354,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO93" s="0" t="n">
+      <c r="AR93" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9409,7 +9414,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO94" s="0" t="n">
+      <c r="AR94" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9469,7 +9474,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO95" s="0" t="n">
+      <c r="AR95" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9529,7 +9534,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO96" s="0" t="n">
+      <c r="AR96" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9589,7 +9594,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO97" s="0" t="n">
+      <c r="AR97" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9649,7 +9654,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO98" s="0" t="n">
+      <c r="AR98" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9709,7 +9714,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO99" s="0" t="n">
+      <c r="AR99" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9769,7 +9774,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO100" s="0" t="n">
+      <c r="AR100" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9829,7 +9834,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO101" s="0" t="n">
+      <c r="AR101" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9889,7 +9894,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO102" s="0" t="n">
+      <c r="AR102" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9949,7 +9954,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO103" s="0" t="n">
+      <c r="AR103" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10009,7 +10014,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO104" s="0" t="n">
+      <c r="AR104" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10069,7 +10074,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO105" s="0" t="n">
+      <c r="AR105" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10129,7 +10134,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO106" s="0" t="n">
+      <c r="AR106" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10189,7 +10194,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO107" s="0" t="n">
+      <c r="AR107" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10249,7 +10254,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO108" s="0" t="n">
+      <c r="AR108" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10309,7 +10314,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO109" s="0" t="n">
+      <c r="AR109" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10369,7 +10374,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO110" s="0" t="n">
+      <c r="AR110" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10429,7 +10434,7 @@
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AO111" s="0" t="n">
+      <c r="AR111" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10454,7 +10459,7 @@
     <row r="180" ht="12" customHeight="1" s="3"/>
     <row r="181" ht="12" customHeight="1" s="3"/>
   </sheetData>
-  <autoFilter ref="A1:AO111"/>
+  <autoFilter ref="A1:AN111"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -5773,7 +5773,7 @@
       </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n">
-        <v>207001</v>
+        <v>205001</v>
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n">
-        <v>207001</v>
+        <v>204001</v>
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS111"/>
+  <dimension ref="A1:AT111"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -1348,6 +1348,11 @@
           <t>details[language_1]</t>
         </is>
       </c>
+      <c r="AT1" s="0" t="inlineStr">
+        <is>
+          <t>show_attribute</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1575,6 +1580,11 @@
           <t>long</t>
         </is>
       </c>
+      <c r="AT2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1802,6 +1812,11 @@
           <t>详情描述文本id(取content_1，值=生物自身id，0或空=不显示)</t>
         </is>
       </c>
+      <c r="AT3" s="0" t="inlineStr">
+        <is>
+          <t>详情面板显示/献祭加点/创建随机加点属性(逗号分隔枚举值:1HP 3DR 4ATK 6ASPD;空=默认1,3,4,6)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
@@ -1871,6 +1886,11 @@
       <c r="AR4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT4" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1939,6 +1959,11 @@
       </c>
       <c r="AR5" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AT5" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2011,6 +2036,11 @@
       <c r="AR6" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="AT6" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
@@ -2080,6 +2110,11 @@
       <c r="AR7" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="AT7" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
@@ -2149,6 +2184,11 @@
       <c r="AR8" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="AT8" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
@@ -2218,6 +2258,11 @@
       <c r="AR9" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="AT9" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="n">
@@ -2287,6 +2332,11 @@
       <c r="AR10" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="AT10" s="0" t="inlineStr">
+        <is>
+          <t>4,5,2,11</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="A11" s="1" t="n">
@@ -2389,6 +2439,11 @@
       <c r="AS11" s="0" t="n">
         <v>1001</v>
       </c>
+      <c r="AT11" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="1" s="1">
       <c r="A12" s="1" t="n">
@@ -2501,6 +2556,11 @@
       <c r="AS12" s="0" t="n">
         <v>1002</v>
       </c>
+      <c r="AT12" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="1" s="1">
       <c r="A13" s="1" t="n">
@@ -2605,6 +2665,11 @@
       <c r="AS13" s="0" t="n">
         <v>1003</v>
       </c>
+      <c r="AT13" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="1" s="1">
       <c r="A14" s="1" t="n">
@@ -2709,6 +2774,11 @@
       <c r="AS14" s="0" t="n">
         <v>1004</v>
       </c>
+      <c r="AT14" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="12" customFormat="1" customHeight="1" s="1">
       <c r="A15" s="1" t="n">
@@ -2813,6 +2883,11 @@
       <c r="AS15" s="0" t="n">
         <v>2001</v>
       </c>
+      <c r="AT15" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="1" s="1">
       <c r="A16" s="1" t="n">
@@ -2922,6 +2997,11 @@
       <c r="AS16" s="0" t="n">
         <v>2002</v>
       </c>
+      <c r="AT16" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="1" s="1">
       <c r="A17" s="1" t="n">
@@ -3031,6 +3111,11 @@
       <c r="AS17" s="0" t="n">
         <v>2003</v>
       </c>
+      <c r="AT17" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="1" s="1">
       <c r="A18" s="1" t="n">
@@ -3140,6 +3225,11 @@
       <c r="AS18" s="0" t="n">
         <v>2004</v>
       </c>
+      <c r="AT18" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="1" s="1">
       <c r="A19" s="1" t="n">
@@ -3235,6 +3325,11 @@
       <c r="AS19" s="0" t="n">
         <v>3001</v>
       </c>
+      <c r="AT19" s="0" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="1" s="1">
       <c r="A20" s="1" t="n">
@@ -3338,6 +3433,11 @@
       <c r="AS20" s="0" t="n">
         <v>3002</v>
       </c>
+      <c r="AT20" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="1" s="1">
       <c r="A21" s="1" t="n">
@@ -3449,6 +3549,11 @@
       <c r="AS21" s="0" t="n">
         <v>3003</v>
       </c>
+      <c r="AT21" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="1" s="1">
       <c r="A22" s="1" t="n">
@@ -3560,6 +3665,11 @@
       <c r="AS22" s="0" t="n">
         <v>3004</v>
       </c>
+      <c r="AT22" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="1" s="1">
       <c r="A23" s="1" t="n">
@@ -3669,6 +3779,11 @@
       <c r="AS23" s="0" t="n">
         <v>4001</v>
       </c>
+      <c r="AT23" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="1" s="1">
       <c r="A24" s="1" t="n">
@@ -3765,6 +3880,11 @@
       <c r="AS24" s="0" t="n">
         <v>4002</v>
       </c>
+      <c r="AT24" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="1" s="1">
       <c r="A25" s="1" t="n">
@@ -3866,6 +3986,11 @@
       <c r="AS25" s="0" t="n">
         <v>4003</v>
       </c>
+      <c r="AT25" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="1" s="1">
       <c r="A26" s="1" t="n">
@@ -3967,6 +4092,11 @@
       <c r="AS26" s="0" t="n">
         <v>4004</v>
       </c>
+      <c r="AT26" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="1" s="1">
       <c r="A27" s="1" t="n">
@@ -4063,6 +4193,11 @@
       <c r="AS27" s="0" t="n">
         <v>4005</v>
       </c>
+      <c r="AT27" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="1" s="1">
       <c r="A28" s="1" t="n">
@@ -4159,6 +4294,11 @@
       <c r="AS28" s="0" t="n">
         <v>5001</v>
       </c>
+      <c r="AT28" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="1" s="1">
       <c r="A29" s="1" t="n">
@@ -4266,6 +4406,11 @@
       <c r="AS29" s="0" t="n">
         <v>5002</v>
       </c>
+      <c r="AT29" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="1" s="1">
       <c r="A30" s="1" t="n">
@@ -4362,6 +4507,11 @@
       <c r="AS30" s="0" t="n">
         <v>5003</v>
       </c>
+      <c r="AT30" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="1" s="1">
       <c r="A31" s="1" t="n">
@@ -4458,6 +4608,11 @@
       <c r="AS31" s="0" t="n">
         <v>5004</v>
       </c>
+      <c r="AT31" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="1" s="1">
       <c r="A32" s="1" t="n">
@@ -4565,6 +4720,11 @@
       <c r="AS32" s="0" t="n">
         <v>6001</v>
       </c>
+      <c r="AT32" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="1" s="1">
       <c r="A33" s="1" t="n">
@@ -4674,6 +4834,11 @@
       <c r="AS33" s="0" t="n">
         <v>6002</v>
       </c>
+      <c r="AT33" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="1" s="1">
       <c r="A34" s="1" t="n">
@@ -4781,6 +4946,11 @@
       <c r="AS34" s="0" t="n">
         <v>6003</v>
       </c>
+      <c r="AT34" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="1" s="1">
       <c r="A35" s="1" t="n">
@@ -4890,6 +5060,11 @@
       <c r="AS35" s="0" t="n">
         <v>6004</v>
       </c>
+      <c r="AT35" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="1" s="1">
       <c r="A36" s="1" t="n">
@@ -4999,6 +5174,11 @@
       <c r="AS36" s="0" t="n">
         <v>6005</v>
       </c>
+      <c r="AT36" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="1" s="1">
       <c r="A37" s="1" t="n">
@@ -5103,6 +5283,11 @@
       <c r="AS37" s="0" t="n">
         <v>7001</v>
       </c>
+      <c r="AT37" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="1" s="1">
       <c r="A38" s="1" t="n">
@@ -5212,6 +5397,11 @@
       <c r="AS38" s="0" t="n">
         <v>7002</v>
       </c>
+      <c r="AT38" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="1" s="1">
       <c r="A39" s="1" t="n">
@@ -5321,6 +5511,11 @@
       <c r="AS39" s="0" t="n">
         <v>7003</v>
       </c>
+      <c r="AT39" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="1" s="1">
       <c r="A40" s="1" t="n">
@@ -5429,6 +5624,11 @@
       </c>
       <c r="AS40" s="0" t="n">
         <v>7004</v>
+      </c>
+      <c r="AT40" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
       </c>
     </row>
     <row r="41" customFormat="1" s="2">
@@ -5527,6 +5727,11 @@
       <c r="AR41" s="4" t="n">
         <v>101001</v>
       </c>
+      <c r="AT41" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="1" s="2">
       <c r="A42" s="4" t="n">
@@ -5630,6 +5835,11 @@
       <c r="AR42" s="4" t="n">
         <v>101002</v>
       </c>
+      <c r="AT42" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="1" s="2">
       <c r="A43" s="4" t="n">
@@ -5735,6 +5945,11 @@
       <c r="AR43" s="4" t="n">
         <v>102001</v>
       </c>
+      <c r="AT43" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="1" s="2">
       <c r="A44" s="4" t="n">
@@ -5840,6 +6055,11 @@
       <c r="AR44" s="4" t="n">
         <v>102002</v>
       </c>
+      <c r="AT44" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="1" s="2">
       <c r="A45" s="4" t="n">
@@ -5945,6 +6165,11 @@
       <c r="AR45" s="4" t="n">
         <v>102003</v>
       </c>
+      <c r="AT45" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="46" customFormat="1" s="2">
       <c r="A46" s="4" t="n">
@@ -6050,6 +6275,11 @@
       <c r="AR46" s="4" t="n">
         <v>103001</v>
       </c>
+      <c r="AT46" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="47" customFormat="1" s="2">
       <c r="A47" s="4" t="n">
@@ -6155,6 +6385,11 @@
       <c r="AR47" s="4" t="n">
         <v>103002</v>
       </c>
+      <c r="AT47" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="48" customFormat="1" s="2">
       <c r="A48" s="4" t="n">
@@ -6260,6 +6495,11 @@
       <c r="AR48" s="4" t="n">
         <v>103003</v>
       </c>
+      <c r="AT48" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="49" customFormat="1" s="2">
       <c r="A49" s="4" t="n">
@@ -6365,6 +6605,11 @@
       <c r="AR49" s="4" t="n">
         <v>103004</v>
       </c>
+      <c r="AT49" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="50" customFormat="1" s="2">
       <c r="A50" s="4" t="n">
@@ -6470,6 +6715,11 @@
       <c r="AR50" s="4" t="n">
         <v>103101</v>
       </c>
+      <c r="AT50" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="1" s="2">
       <c r="A51" s="4" t="n">
@@ -6575,6 +6825,11 @@
       <c r="AR51" s="4" t="n">
         <v>103102</v>
       </c>
+      <c r="AT51" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="52" customFormat="1" s="2">
       <c r="A52" s="4" t="n">
@@ -6680,6 +6935,11 @@
       <c r="AR52" s="4" t="n">
         <v>103103</v>
       </c>
+      <c r="AT52" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -6789,6 +7049,11 @@
       <c r="AR53" s="5" t="n">
         <v>900001</v>
       </c>
+      <c r="AT53" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -6902,6 +7167,11 @@
       <c r="AR54" s="5" t="n">
         <v>900002</v>
       </c>
+      <c r="AT54" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
@@ -6965,6 +7235,11 @@
       <c r="AR55" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT55" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
@@ -7028,6 +7303,11 @@
       <c r="AR56" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT56" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="n">
@@ -7091,6 +7371,11 @@
       <c r="AR57" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT57" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="n">
@@ -7152,6 +7437,11 @@
       <c r="AR58" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT58" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
@@ -7215,6 +7505,11 @@
       <c r="AR59" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT59" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
@@ -7278,6 +7573,11 @@
       <c r="AR60" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT60" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
@@ -7341,6 +7641,11 @@
       <c r="AR61" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT61" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
@@ -7404,6 +7709,11 @@
       <c r="AR62" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT62" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
@@ -7467,6 +7777,11 @@
       <c r="AR63" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT63" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
@@ -7530,6 +7845,11 @@
       <c r="AR64" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT64" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
@@ -7593,6 +7913,11 @@
       <c r="AR65" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT65" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
@@ -7656,6 +7981,11 @@
       <c r="AR66" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT66" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
@@ -7719,6 +8049,11 @@
       <c r="AR67" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT67" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
@@ -7782,6 +8117,11 @@
       <c r="AR68" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT68" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
@@ -7845,6 +8185,11 @@
       <c r="AR69" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT69" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
@@ -7908,6 +8253,11 @@
       <c r="AR70" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT70" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
@@ -7971,6 +8321,11 @@
       <c r="AR71" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT71" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
@@ -8034,6 +8389,11 @@
       <c r="AR72" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT72" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
@@ -8097,6 +8457,11 @@
       <c r="AR73" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT73" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
@@ -8160,6 +8525,11 @@
       <c r="AR74" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT74" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
@@ -8223,6 +8593,11 @@
       <c r="AR75" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT75" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
@@ -8286,6 +8661,11 @@
       <c r="AR76" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT76" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
@@ -8349,6 +8729,11 @@
       <c r="AR77" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT77" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
@@ -8412,6 +8797,11 @@
       <c r="AR78" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT78" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
@@ -8475,6 +8865,11 @@
       <c r="AR79" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT79" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
@@ -8538,6 +8933,11 @@
       <c r="AR80" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT80" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
@@ -8601,6 +9001,11 @@
       <c r="AR81" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT81" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
@@ -8664,6 +9069,11 @@
       <c r="AR82" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT82" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
@@ -8727,6 +9137,11 @@
       <c r="AR83" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT83" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
@@ -8790,6 +9205,11 @@
       <c r="AR84" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT84" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
@@ -8853,6 +9273,11 @@
       <c r="AR85" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT85" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
@@ -8916,6 +9341,11 @@
       <c r="AR86" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT86" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
@@ -8979,6 +9409,11 @@
       <c r="AR87" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT87" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
@@ -9042,6 +9477,11 @@
       <c r="AR88" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT88" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
@@ -9105,6 +9545,11 @@
       <c r="AR89" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT89" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
@@ -9168,6 +9613,11 @@
       <c r="AR90" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT90" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
@@ -9231,6 +9681,11 @@
       <c r="AR91" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT91" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
@@ -9294,6 +9749,11 @@
       <c r="AR92" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT92" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
@@ -9357,6 +9817,11 @@
       <c r="AR93" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT93" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
@@ -9417,6 +9882,11 @@
       <c r="AR94" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT94" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
@@ -9477,6 +9947,11 @@
       <c r="AR95" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT95" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
@@ -9537,6 +10012,11 @@
       <c r="AR96" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT96" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
@@ -9597,6 +10077,11 @@
       <c r="AR97" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT97" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
@@ -9657,6 +10142,11 @@
       <c r="AR98" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT98" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
@@ -9717,6 +10207,11 @@
       <c r="AR99" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT99" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
@@ -9777,6 +10272,11 @@
       <c r="AR100" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT100" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
@@ -9837,6 +10337,11 @@
       <c r="AR101" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT101" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
@@ -9897,6 +10402,11 @@
       <c r="AR102" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT102" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
@@ -9957,6 +10467,11 @@
       <c r="AR103" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT103" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
@@ -10017,6 +10532,11 @@
       <c r="AR104" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT104" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
@@ -10077,6 +10597,11 @@
       <c r="AR105" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT105" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
@@ -10137,6 +10662,11 @@
       <c r="AR106" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT106" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
@@ -10197,6 +10727,11 @@
       <c r="AR107" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT107" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
@@ -10257,6 +10792,11 @@
       <c r="AR108" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT108" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
@@ -10317,6 +10857,11 @@
       <c r="AR109" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT109" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
@@ -10377,6 +10922,11 @@
       <c r="AR110" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="AT110" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
@@ -10436,6 +10986,11 @@
       </c>
       <c r="AR111" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="AT111" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_info[生物信息].xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT111"/>
+  <dimension ref="A1:AT115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="7.375" customWidth="1" style="3" min="1" max="1"/>
@@ -6942,112 +6942,82 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>900001</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅战士</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>21010001</v>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="A53" s="0" t="n">
+        <v>104001</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>人类-盗贼</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>Attack2</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n">
+      <c r="J53" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P53" s="0" t="n">
         <v>100001</v>
       </c>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
-      <c r="S53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T53" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U53" s="5" t="n">
+      <c r="S53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U53" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V53" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y53" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB53" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC53" s="5" t="n"/>
-      <c r="AD53" s="5" t="n"/>
-      <c r="AE53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF53" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH53" s="5" t="n"/>
-      <c r="AI53" s="5" t="n"/>
-      <c r="AJ53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK53" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL53" s="5" t="inlineStr">
+      <c r="W53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y53" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB53" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE53" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK53" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL53" s="0" t="inlineStr">
         <is>
           <t>ui_class_3</t>
         </is>
       </c>
-      <c r="AM53" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN53" s="5" t="n">
-        <v>300200001</v>
-      </c>
-      <c r="AR53" s="5" t="n">
-        <v>900001</v>
+      <c r="AM53" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR53" s="0" t="n">
+        <v>104001</v>
       </c>
       <c r="AT53" s="0" t="inlineStr">
         <is>
@@ -7056,116 +7026,82 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>900002</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>测试骷髅投手</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>21000001</v>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="A54" s="0" t="n">
+        <v>104002</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>人类-双持战士</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>1,2,3,10,</t>
         </is>
       </c>
-      <c r="J54" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n">
-        <v>200001</v>
-      </c>
-      <c r="Q54" s="5" t="inlineStr">
-        <is>
-          <t>0,0.7,0</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T54" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U54" s="5" t="n">
+      <c r="J54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>100001</v>
+      </c>
+      <c r="S54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V54" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y54" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z54" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA54" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB54" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AC54" s="5" t="n"/>
-      <c r="AD54" s="5" t="n"/>
-      <c r="AE54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH54" s="5" t="n"/>
-      <c r="AI54" s="5" t="n"/>
-      <c r="AJ54" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK54" s="5" t="n">
-        <v>2000001</v>
-      </c>
-      <c r="AL54" s="5" t="inlineStr">
-        <is>
-          <t>ui_class_6</t>
-        </is>
-      </c>
-      <c r="AM54" s="5" t="inlineStr">
-        <is>
-          <t>Card_Scene_1</t>
-        </is>
-      </c>
-      <c r="AN54" s="5" t="n">
-        <v>300200002</v>
-      </c>
-      <c r="AR54" s="5" t="n">
-        <v>900002</v>
+      <c r="W54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y54" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB54" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK54" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL54" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM54" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_2</t>
+        </is>
+      </c>
+      <c r="AR54" s="0" t="n">
+        <v>104002</v>
       </c>
       <c r="AT54" s="0" t="inlineStr">
         <is>
@@ -7175,24 +7111,35 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="n">
-        <v>989996</v>
+        <v>104101</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>测试数据</t>
+          <t>人类-大剑战士</t>
         </is>
       </c>
       <c r="C55" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>200001</v>
+        <v>101006</v>
       </c>
       <c r="S55" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" s="0" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="U55" s="0" t="n">
         <v>1</v>
@@ -7209,31 +7156,39 @@
       <c r="Y55" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z55" s="0" t="n"/>
       <c r="AB55" s="0" t="n">
         <v>100</v>
       </c>
+      <c r="AD55" s="0" t="n">
+        <v>100</v>
+      </c>
       <c r="AE55" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AJ55" s="0" t="n">
-        <v>989996</v>
-      </c>
-      <c r="AK55" s="0" t="n"/>
-      <c r="AL55" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AK55" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL55" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
       <c r="AM55" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_4</t>
+          <t>Card_Scene_2</t>
         </is>
       </c>
       <c r="AR55" s="0" t="n">
-        <v>1</v>
+        <v>104101</v>
       </c>
       <c r="AT55" s="0" t="inlineStr">
         <is>
@@ -7243,24 +7198,40 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="n">
-        <v>989997</v>
+        <v>104102</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>测试数据</t>
+          <t>人类-大盾战士</t>
         </is>
       </c>
       <c r="C56" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" s="0" t="inlineStr">
+        <is>
+          <t>Attack5</t>
+        </is>
       </c>
       <c r="P56" s="0" t="n">
-        <v>200001</v>
+        <v>100001</v>
       </c>
       <c r="S56" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T56" s="0" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>1</v>
@@ -7277,31 +7248,39 @@
       <c r="Y56" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z56" s="0" t="n"/>
       <c r="AB56" s="0" t="n">
         <v>100</v>
       </c>
+      <c r="AD56" s="0" t="n">
+        <v>100</v>
+      </c>
       <c r="AE56" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="0" t="n">
         <v>10</v>
       </c>
       <c r="AJ56" s="0" t="n">
-        <v>989997</v>
-      </c>
-      <c r="AK56" s="0" t="n"/>
-      <c r="AL56" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AK56" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="AL56" s="0" t="inlineStr">
+        <is>
+          <t>ui_class_7</t>
+        </is>
+      </c>
       <c r="AM56" s="0" t="inlineStr">
         <is>
-          <t>Card_Scene_4</t>
+          <t>Card_Scene_2</t>
         </is>
       </c>
       <c r="AR56" s="0" t="n">
-        <v>1</v>
+        <v>104102</v>
       </c>
       <c r="AT56" s="0" t="inlineStr">
         <is>
@@ -7310,115 +7289,200 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="n">
-        <v>989998</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" s="0" t="n">
+      <c r="A57" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅战士</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>21010001</v>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>Attack2</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y57" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB57" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC57" s="5" t="n"/>
+      <c r="AD57" s="5" t="n"/>
+      <c r="AE57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH57" s="5" t="n"/>
+      <c r="AI57" s="5" t="n"/>
+      <c r="AJ57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK57" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL57" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_3</t>
+        </is>
+      </c>
+      <c r="AM57" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN57" s="5" t="n">
+        <v>300200001</v>
+      </c>
+      <c r="AR57" s="5" t="n">
+        <v>900001</v>
+      </c>
+      <c r="AT57" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>900002</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>测试骷髅投手</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>21000001</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>1,2,3,10,</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n">
         <v>200001</v>
       </c>
-      <c r="S57" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T57" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y57" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z57" s="0" t="n"/>
-      <c r="AB57" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE57" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="AF57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ57" s="0" t="n">
-        <v>989998</v>
-      </c>
-      <c r="AK57" s="0" t="n"/>
-      <c r="AL57" s="0" t="n"/>
-      <c r="AM57" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR57" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT57" s="0" t="inlineStr">
-        <is>
-          <t>1,3,4,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="n">
-        <v>989999</v>
-      </c>
-      <c r="B58" s="0" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="S58" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="U58" s="0" t="n">
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>0,0.7,0</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U58" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X58" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y58" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z58" s="0" t="n"/>
-      <c r="AB58" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE58" s="0" t="n">
-        <v>35</v>
+      <c r="W58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y58" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z58" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA58" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB58" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AC58" s="5" t="n"/>
+      <c r="AD58" s="5" t="n"/>
+      <c r="AE58" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="AF58" s="1" t="n">
         <v>0</v>
@@ -7426,16 +7490,29 @@
       <c r="AG58" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AJ58" s="0" t="n">
-        <v>989999</v>
-      </c>
-      <c r="AM58" s="0" t="inlineStr">
-        <is>
-          <t>Card_Scene_4</t>
-        </is>
-      </c>
-      <c r="AR58" s="0" t="n">
-        <v>1</v>
+      <c r="AH58" s="5" t="n"/>
+      <c r="AI58" s="5" t="n"/>
+      <c r="AJ58" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK58" s="5" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="AL58" s="5" t="inlineStr">
+        <is>
+          <t>ui_class_6</t>
+        </is>
+      </c>
+      <c r="AM58" s="5" t="inlineStr">
+        <is>
+          <t>Card_Scene_1</t>
+        </is>
+      </c>
+      <c r="AN58" s="5" t="n">
+        <v>300200002</v>
+      </c>
+      <c r="AR58" s="5" t="n">
+        <v>900002</v>
       </c>
       <c r="AT58" s="0" t="inlineStr">
         <is>
@@ -7445,7 +7522,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="n">
-        <v>999947</v>
+        <v>989996</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
@@ -7493,7 +7570,7 @@
         <v>10</v>
       </c>
       <c r="AJ59" s="0" t="n">
-        <v>999947</v>
+        <v>989996</v>
       </c>
       <c r="AK59" s="0" t="n"/>
       <c r="AL59" s="0" t="n"/>
@@ -7513,7 +7590,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="n">
-        <v>999948</v>
+        <v>989997</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
@@ -7561,7 +7638,7 @@
         <v>10</v>
       </c>
       <c r="AJ60" s="0" t="n">
-        <v>999948</v>
+        <v>989997</v>
       </c>
       <c r="AK60" s="0" t="n"/>
       <c r="AL60" s="0" t="n"/>
@@ -7581,7 +7658,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>999949</v>
+        <v>989998</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -7629,7 +7706,7 @@
         <v>10</v>
       </c>
       <c r="AJ61" s="0" t="n">
-        <v>999949</v>
+        <v>989998</v>
       </c>
       <c r="AK61" s="0" t="n"/>
       <c r="AL61" s="0" t="n"/>
@@ -7649,7 +7726,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>999950</v>
+        <v>989999</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
@@ -7697,10 +7774,8 @@
         <v>10</v>
       </c>
       <c r="AJ62" s="0" t="n">
-        <v>999950</v>
-      </c>
-      <c r="AK62" s="0" t="n"/>
-      <c r="AL62" s="0" t="n"/>
+        <v>989999</v>
+      </c>
       <c r="AM62" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -7717,7 +7792,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>999951</v>
+        <v>999947</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -7765,7 +7840,7 @@
         <v>10</v>
       </c>
       <c r="AJ63" s="0" t="n">
-        <v>999951</v>
+        <v>999947</v>
       </c>
       <c r="AK63" s="0" t="n"/>
       <c r="AL63" s="0" t="n"/>
@@ -7785,7 +7860,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>999952</v>
+        <v>999948</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -7833,7 +7908,7 @@
         <v>10</v>
       </c>
       <c r="AJ64" s="0" t="n">
-        <v>999952</v>
+        <v>999948</v>
       </c>
       <c r="AK64" s="0" t="n"/>
       <c r="AL64" s="0" t="n"/>
@@ -7853,7 +7928,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>999953</v>
+        <v>999949</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -7901,7 +7976,7 @@
         <v>10</v>
       </c>
       <c r="AJ65" s="0" t="n">
-        <v>999953</v>
+        <v>999949</v>
       </c>
       <c r="AK65" s="0" t="n"/>
       <c r="AL65" s="0" t="n"/>
@@ -7921,7 +7996,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>999954</v>
+        <v>999950</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -7969,7 +8044,7 @@
         <v>10</v>
       </c>
       <c r="AJ66" s="0" t="n">
-        <v>999954</v>
+        <v>999950</v>
       </c>
       <c r="AK66" s="0" t="n"/>
       <c r="AL66" s="0" t="n"/>
@@ -7989,7 +8064,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>999955</v>
+        <v>999951</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -8037,7 +8112,7 @@
         <v>10</v>
       </c>
       <c r="AJ67" s="0" t="n">
-        <v>999955</v>
+        <v>999951</v>
       </c>
       <c r="AK67" s="0" t="n"/>
       <c r="AL67" s="0" t="n"/>
@@ -8057,7 +8132,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>999956</v>
+        <v>999952</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -8105,7 +8180,7 @@
         <v>10</v>
       </c>
       <c r="AJ68" s="0" t="n">
-        <v>999956</v>
+        <v>999952</v>
       </c>
       <c r="AK68" s="0" t="n"/>
       <c r="AL68" s="0" t="n"/>
@@ -8125,7 +8200,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="n">
-        <v>999957</v>
+        <v>999953</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -8173,7 +8248,7 @@
         <v>10</v>
       </c>
       <c r="AJ69" s="0" t="n">
-        <v>999957</v>
+        <v>999953</v>
       </c>
       <c r="AK69" s="0" t="n"/>
       <c r="AL69" s="0" t="n"/>
@@ -8193,7 +8268,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="n">
-        <v>999958</v>
+        <v>999954</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -8241,7 +8316,7 @@
         <v>10</v>
       </c>
       <c r="AJ70" s="0" t="n">
-        <v>999958</v>
+        <v>999954</v>
       </c>
       <c r="AK70" s="0" t="n"/>
       <c r="AL70" s="0" t="n"/>
@@ -8261,7 +8336,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="n">
-        <v>999959</v>
+        <v>999955</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -8309,7 +8384,7 @@
         <v>10</v>
       </c>
       <c r="AJ71" s="0" t="n">
-        <v>999959</v>
+        <v>999955</v>
       </c>
       <c r="AK71" s="0" t="n"/>
       <c r="AL71" s="0" t="n"/>
@@ -8329,7 +8404,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>999960</v>
+        <v>999956</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -8377,7 +8452,7 @@
         <v>10</v>
       </c>
       <c r="AJ72" s="0" t="n">
-        <v>999960</v>
+        <v>999956</v>
       </c>
       <c r="AK72" s="0" t="n"/>
       <c r="AL72" s="0" t="n"/>
@@ -8397,7 +8472,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>999961</v>
+        <v>999957</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -8445,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="AJ73" s="0" t="n">
-        <v>999961</v>
+        <v>999957</v>
       </c>
       <c r="AK73" s="0" t="n"/>
       <c r="AL73" s="0" t="n"/>
@@ -8465,7 +8540,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>999962</v>
+        <v>999958</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -8513,7 +8588,7 @@
         <v>10</v>
       </c>
       <c r="AJ74" s="0" t="n">
-        <v>999962</v>
+        <v>999958</v>
       </c>
       <c r="AK74" s="0" t="n"/>
       <c r="AL74" s="0" t="n"/>
@@ -8533,7 +8608,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>999963</v>
+        <v>999959</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -8581,7 +8656,7 @@
         <v>10</v>
       </c>
       <c r="AJ75" s="0" t="n">
-        <v>999963</v>
+        <v>999959</v>
       </c>
       <c r="AK75" s="0" t="n"/>
       <c r="AL75" s="0" t="n"/>
@@ -8601,7 +8676,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>999964</v>
+        <v>999960</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -8649,7 +8724,7 @@
         <v>10</v>
       </c>
       <c r="AJ76" s="0" t="n">
-        <v>999964</v>
+        <v>999960</v>
       </c>
       <c r="AK76" s="0" t="n"/>
       <c r="AL76" s="0" t="n"/>
@@ -8669,7 +8744,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>999965</v>
+        <v>999961</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -8717,7 +8792,7 @@
         <v>10</v>
       </c>
       <c r="AJ77" s="0" t="n">
-        <v>999965</v>
+        <v>999961</v>
       </c>
       <c r="AK77" s="0" t="n"/>
       <c r="AL77" s="0" t="n"/>
@@ -8737,7 +8812,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>999966</v>
+        <v>999962</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -8785,7 +8860,7 @@
         <v>10</v>
       </c>
       <c r="AJ78" s="0" t="n">
-        <v>999966</v>
+        <v>999962</v>
       </c>
       <c r="AK78" s="0" t="n"/>
       <c r="AL78" s="0" t="n"/>
@@ -8805,7 +8880,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>999967</v>
+        <v>999963</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -8853,7 +8928,7 @@
         <v>10</v>
       </c>
       <c r="AJ79" s="0" t="n">
-        <v>999967</v>
+        <v>999963</v>
       </c>
       <c r="AK79" s="0" t="n"/>
       <c r="AL79" s="0" t="n"/>
@@ -8873,7 +8948,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>999968</v>
+        <v>999964</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -8921,7 +8996,7 @@
         <v>10</v>
       </c>
       <c r="AJ80" s="0" t="n">
-        <v>999968</v>
+        <v>999964</v>
       </c>
       <c r="AK80" s="0" t="n"/>
       <c r="AL80" s="0" t="n"/>
@@ -8941,7 +9016,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>999969</v>
+        <v>999965</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -8989,7 +9064,7 @@
         <v>10</v>
       </c>
       <c r="AJ81" s="0" t="n">
-        <v>999969</v>
+        <v>999965</v>
       </c>
       <c r="AK81" s="0" t="n"/>
       <c r="AL81" s="0" t="n"/>
@@ -9009,7 +9084,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>999970</v>
+        <v>999966</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -9057,7 +9132,7 @@
         <v>10</v>
       </c>
       <c r="AJ82" s="0" t="n">
-        <v>999970</v>
+        <v>999966</v>
       </c>
       <c r="AK82" s="0" t="n"/>
       <c r="AL82" s="0" t="n"/>
@@ -9077,7 +9152,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>999971</v>
+        <v>999967</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -9125,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="AJ83" s="0" t="n">
-        <v>999971</v>
+        <v>999967</v>
       </c>
       <c r="AK83" s="0" t="n"/>
       <c r="AL83" s="0" t="n"/>
@@ -9145,7 +9220,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>999972</v>
+        <v>999968</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -9193,7 +9268,7 @@
         <v>10</v>
       </c>
       <c r="AJ84" s="0" t="n">
-        <v>999972</v>
+        <v>999968</v>
       </c>
       <c r="AK84" s="0" t="n"/>
       <c r="AL84" s="0" t="n"/>
@@ -9213,7 +9288,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>999973</v>
+        <v>999969</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -9261,7 +9336,7 @@
         <v>10</v>
       </c>
       <c r="AJ85" s="0" t="n">
-        <v>999973</v>
+        <v>999969</v>
       </c>
       <c r="AK85" s="0" t="n"/>
       <c r="AL85" s="0" t="n"/>
@@ -9281,7 +9356,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>999974</v>
+        <v>999970</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -9329,7 +9404,7 @@
         <v>10</v>
       </c>
       <c r="AJ86" s="0" t="n">
-        <v>999974</v>
+        <v>999970</v>
       </c>
       <c r="AK86" s="0" t="n"/>
       <c r="AL86" s="0" t="n"/>
@@ -9349,7 +9424,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>999975</v>
+        <v>999971</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -9397,7 +9472,7 @@
         <v>10</v>
       </c>
       <c r="AJ87" s="0" t="n">
-        <v>999975</v>
+        <v>999971</v>
       </c>
       <c r="AK87" s="0" t="n"/>
       <c r="AL87" s="0" t="n"/>
@@ -9417,7 +9492,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>999976</v>
+        <v>999972</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -9465,7 +9540,7 @@
         <v>10</v>
       </c>
       <c r="AJ88" s="0" t="n">
-        <v>999976</v>
+        <v>999972</v>
       </c>
       <c r="AK88" s="0" t="n"/>
       <c r="AL88" s="0" t="n"/>
@@ -9485,7 +9560,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>999977</v>
+        <v>999973</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -9533,7 +9608,7 @@
         <v>10</v>
       </c>
       <c r="AJ89" s="0" t="n">
-        <v>999977</v>
+        <v>999973</v>
       </c>
       <c r="AK89" s="0" t="n"/>
       <c r="AL89" s="0" t="n"/>
@@ -9553,7 +9628,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>999978</v>
+        <v>999974</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -9601,7 +9676,7 @@
         <v>10</v>
       </c>
       <c r="AJ90" s="0" t="n">
-        <v>999978</v>
+        <v>999974</v>
       </c>
       <c r="AK90" s="0" t="n"/>
       <c r="AL90" s="0" t="n"/>
@@ -9621,7 +9696,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>999979</v>
+        <v>999975</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -9669,7 +9744,7 @@
         <v>10</v>
       </c>
       <c r="AJ91" s="0" t="n">
-        <v>999979</v>
+        <v>999975</v>
       </c>
       <c r="AK91" s="0" t="n"/>
       <c r="AL91" s="0" t="n"/>
@@ -9689,7 +9764,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>999980</v>
+        <v>999976</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -9737,7 +9812,7 @@
         <v>10</v>
       </c>
       <c r="AJ92" s="0" t="n">
-        <v>999980</v>
+        <v>999976</v>
       </c>
       <c r="AK92" s="0" t="n"/>
       <c r="AL92" s="0" t="n"/>
@@ -9757,7 +9832,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>999981</v>
+        <v>999977</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -9805,7 +9880,7 @@
         <v>10</v>
       </c>
       <c r="AJ93" s="0" t="n">
-        <v>999981</v>
+        <v>999977</v>
       </c>
       <c r="AK93" s="0" t="n"/>
       <c r="AL93" s="0" t="n"/>
@@ -9825,7 +9900,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>999982</v>
+        <v>999978</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -9859,6 +9934,7 @@
       <c r="Y94" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z94" s="0" t="n"/>
       <c r="AB94" s="0" t="n">
         <v>100</v>
       </c>
@@ -9872,8 +9948,10 @@
         <v>10</v>
       </c>
       <c r="AJ94" s="0" t="n">
-        <v>999982</v>
-      </c>
+        <v>999978</v>
+      </c>
+      <c r="AK94" s="0" t="n"/>
+      <c r="AL94" s="0" t="n"/>
       <c r="AM94" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -9890,7 +9968,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>999983</v>
+        <v>999979</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -9924,6 +10002,7 @@
       <c r="Y95" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z95" s="0" t="n"/>
       <c r="AB95" s="0" t="n">
         <v>100</v>
       </c>
@@ -9937,8 +10016,10 @@
         <v>10</v>
       </c>
       <c r="AJ95" s="0" t="n">
-        <v>999983</v>
-      </c>
+        <v>999979</v>
+      </c>
+      <c r="AK95" s="0" t="n"/>
+      <c r="AL95" s="0" t="n"/>
       <c r="AM95" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -9955,7 +10036,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>999984</v>
+        <v>999980</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -9989,6 +10070,7 @@
       <c r="Y96" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z96" s="0" t="n"/>
       <c r="AB96" s="0" t="n">
         <v>100</v>
       </c>
@@ -10002,8 +10084,10 @@
         <v>10</v>
       </c>
       <c r="AJ96" s="0" t="n">
-        <v>999984</v>
-      </c>
+        <v>999980</v>
+      </c>
+      <c r="AK96" s="0" t="n"/>
+      <c r="AL96" s="0" t="n"/>
       <c r="AM96" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10020,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>999985</v>
+        <v>999981</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -10054,6 +10138,7 @@
       <c r="Y97" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="Z97" s="0" t="n"/>
       <c r="AB97" s="0" t="n">
         <v>100</v>
       </c>
@@ -10067,8 +10152,10 @@
         <v>10</v>
       </c>
       <c r="AJ97" s="0" t="n">
-        <v>999985</v>
-      </c>
+        <v>999981</v>
+      </c>
+      <c r="AK97" s="0" t="n"/>
+      <c r="AL97" s="0" t="n"/>
       <c r="AM97" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
@@ -10085,7 +10172,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>999986</v>
+        <v>999982</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -10132,7 +10219,7 @@
         <v>10</v>
       </c>
       <c r="AJ98" s="0" t="n">
-        <v>999986</v>
+        <v>999982</v>
       </c>
       <c r="AM98" s="0" t="inlineStr">
         <is>
@@ -10150,7 +10237,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>999987</v>
+        <v>999983</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -10197,7 +10284,7 @@
         <v>10</v>
       </c>
       <c r="AJ99" s="0" t="n">
-        <v>999987</v>
+        <v>999983</v>
       </c>
       <c r="AM99" s="0" t="inlineStr">
         <is>
@@ -10215,7 +10302,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>999988</v>
+        <v>999984</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -10262,7 +10349,7 @@
         <v>10</v>
       </c>
       <c r="AJ100" s="0" t="n">
-        <v>999988</v>
+        <v>999984</v>
       </c>
       <c r="AM100" s="0" t="inlineStr">
         <is>
@@ -10280,7 +10367,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>999989</v>
+        <v>999985</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -10327,7 +10414,7 @@
         <v>10</v>
       </c>
       <c r="AJ101" s="0" t="n">
-        <v>999989</v>
+        <v>999985</v>
       </c>
       <c r="AM101" s="0" t="inlineStr">
         <is>
@@ -10345,7 +10432,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>999990</v>
+        <v>999986</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -10392,7 +10479,7 @@
         <v>10</v>
       </c>
       <c r="AJ102" s="0" t="n">
-        <v>999990</v>
+        <v>999986</v>
       </c>
       <c r="AM102" s="0" t="inlineStr">
         <is>
@@ -10410,7 +10497,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>999991</v>
+        <v>999987</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -10457,7 +10544,7 @@
         <v>10</v>
       </c>
       <c r="AJ103" s="0" t="n">
-        <v>999991</v>
+        <v>999987</v>
       </c>
       <c r="AM103" s="0" t="inlineStr">
         <is>
@@ -10475,7 +10562,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>999992</v>
+        <v>999988</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -10522,7 +10609,7 @@
         <v>10</v>
       </c>
       <c r="AJ104" s="0" t="n">
-        <v>999992</v>
+        <v>999988</v>
       </c>
       <c r="AM104" s="0" t="inlineStr">
         <is>
@@ -10540,7 +10627,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>999993</v>
+        <v>999989</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -10587,7 +10674,7 @@
         <v>10</v>
       </c>
       <c r="AJ105" s="0" t="n">
-        <v>999993</v>
+        <v>999989</v>
       </c>
       <c r="AM105" s="0" t="inlineStr">
         <is>
@@ -10605,7 +10692,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>999994</v>
+        <v>999990</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -10652,7 +10739,7 @@
         <v>10</v>
       </c>
       <c r="AJ106" s="0" t="n">
-        <v>999994</v>
+        <v>999990</v>
       </c>
       <c r="AM106" s="0" t="inlineStr">
         <is>
@@ -10670,7 +10757,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>999995</v>
+        <v>999991</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -10717,7 +10804,7 @@
         <v>10</v>
       </c>
       <c r="AJ107" s="0" t="n">
-        <v>999995</v>
+        <v>999991</v>
       </c>
       <c r="AM107" s="0" t="inlineStr">
         <is>
@@ -10735,7 +10822,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>999996</v>
+        <v>999992</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -10782,7 +10869,7 @@
         <v>10</v>
       </c>
       <c r="AJ108" s="0" t="n">
-        <v>999996</v>
+        <v>999992</v>
       </c>
       <c r="AM108" s="0" t="inlineStr">
         <is>
@@ -10800,7 +10887,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>999997</v>
+        <v>999993</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -10847,7 +10934,7 @@
         <v>10</v>
       </c>
       <c r="AJ109" s="0" t="n">
-        <v>999997</v>
+        <v>999993</v>
       </c>
       <c r="AM109" s="0" t="inlineStr">
         <is>
@@ -10865,7 +10952,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>999998</v>
+        <v>999994</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -10912,7 +10999,7 @@
         <v>10</v>
       </c>
       <c r="AJ110" s="0" t="n">
-        <v>999998</v>
+        <v>999994</v>
       </c>
       <c r="AM110" s="0" t="inlineStr">
         <is>
@@ -10930,7 +11017,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>999999</v>
+        <v>999995</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -10977,17 +11064,277 @@
         <v>10</v>
       </c>
       <c r="AJ111" s="0" t="n">
+        <v>999995</v>
+      </c>
+      <c r="AM111" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR111" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT111" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="n">
+        <v>999996</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S112" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T112" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X112" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y112" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB112" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE112" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ112" s="0" t="n">
+        <v>999996</v>
+      </c>
+      <c r="AM112" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT112" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="n">
+        <v>999997</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S113" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T113" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X113" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y113" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB113" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE113" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG113" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ113" s="0" t="n">
+        <v>999997</v>
+      </c>
+      <c r="AM113" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT113" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S114" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T114" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X114" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y114" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB114" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE114" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG114" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ114" s="0" t="n">
+        <v>999998</v>
+      </c>
+      <c r="AM114" s="0" t="inlineStr">
+        <is>
+          <t>Card_Scene_4</t>
+        </is>
+      </c>
+      <c r="AR114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT114" s="0" t="inlineStr">
+        <is>
+          <t>1,3,4,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="n">
         <v>999999</v>
       </c>
-      <c r="AM111" s="0" t="inlineStr">
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" s="0" t="n">
+        <v>200001</v>
+      </c>
+      <c r="S115" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="U115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X115" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y115" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB115" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE115" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG115" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ115" s="0" t="n">
+        <v>999999</v>
+      </c>
+      <c r="AM115" s="0" t="inlineStr">
         <is>
           <t>Card_Scene_4</t>
         </is>
       </c>
-      <c r="AR111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT111" s="0" t="inlineStr">
+      <c r="AR115" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT115" s="0" t="inlineStr">
         <is>
           <t>1,3,4,6</t>
         </is>
